--- a/results/job_matches_2026-03-06.xlsx
+++ b/results/job_matches_2026-03-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G222"/>
+  <dimension ref="A1:G227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (React + Node.js)-5</t>
+          <t>Software Engineer - Sr. Consultant level - DevOps</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,42 +521,42 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01d5f2b9fa96100b</t>
+          <t>https://www.indeed.com/viewjob?jk=28ca6064f69a534e</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Full Stack Engineer (React + Node.js)-5</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, MongoDB, NoSQL</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60711b668acbd0b3</t>
+          <t>https://www.indeed.com/viewjob?jk=01d5f2b9fa96100b</t>
         </is>
       </c>
     </row>
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db8a35e2b334dacc</t>
+          <t>https://www.indeed.com/viewjob?jk=60711b668acbd0b3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer – DE20260503002</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>eGrove Systems Corporation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, Spark, Scala, Oracle</t>
+          <t>AWS, Redshift, S3, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6093ead5fe385f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=db8a35e2b334dacc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Engineer – DE20260503002</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Spire Energy</t>
+          <t>eGrove Systems Corporation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, Spark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df7314eb6a45de22</t>
+          <t>https://www.indeed.com/viewjob?jk=6093ead5fe385f5d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Spire Energy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd9f71c3bc119fac</t>
+          <t>https://www.indeed.com/viewjob?jk=df7314eb6a45de22</t>
         </is>
       </c>
     </row>
@@ -741,59 +741,59 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bc520629d7c84b2</t>
+          <t>https://www.indeed.com/viewjob?jk=fd9f71c3bc119fac</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Valvoline Global Operations</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab16510fd1c2841d</t>
+          <t>https://www.indeed.com/viewjob?jk=7bc520629d7c84b2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - INDIA</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Valvoline Global Operations</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Prosper, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8eebff65cda31d0</t>
+          <t>https://www.indeed.com/viewjob?jk=ab16510fd1c2841d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Data Engineer - INDIA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Prosper, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,94 +846,94 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc1fd3766a845e85</t>
+          <t>https://www.indeed.com/viewjob?jk=f8eebff65cda31d0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Analyst, Risk Data Engineering</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Lincoln Financial Group</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32d044bc27a4af8a</t>
+          <t>https://www.indeed.com/viewjob?jk=4c054d24fbe757c5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aed60e56cae31294</t>
+          <t>https://www.indeed.com/viewjob?jk=fc1fd3766a845e85</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -946,29 +946,29 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44f958ba0cbc0f43</t>
+          <t>https://www.indeed.com/viewjob?jk=3c46cd564ba01b6c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (Python, Spark, AWS)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JBS Dev</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49f6c2df00dd6e11</t>
+          <t>https://www.indeed.com/viewjob?jk=6d52dce08f82e688</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Costa Rica)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JBS Dev</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05c819aa2a88511d</t>
+          <t>https://www.indeed.com/viewjob?jk=175b82022b025c3d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Typescript and AWS services</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=021dcffcbccd49c9</t>
+          <t>https://www.indeed.com/viewjob?jk=32d044bc27a4af8a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>System Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Systems Engineering Solutions Corporation</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,77 +1081,77 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=634fcd15ef04d7bf</t>
+          <t>https://www.indeed.com/viewjob?jk=aed60e56cae31294</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7869ee373ec84ed</t>
+          <t>https://www.indeed.com/viewjob?jk=44f958ba0cbc0f43</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CLOUD ENGINEER (AWS) (REMOTE/USA) - GDM (GRAY MEDIA GROUP)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GRAY MEDIA</t>
+          <t>JBS Dev</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, DynamoDB</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0beb94e2f1648144</t>
+          <t>https://www.indeed.com/viewjob?jk=49f6c2df00dd6e11</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Engineer (Costa Rica)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>JBS Dev</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e83bd0fd320bb829</t>
+          <t>https://www.indeed.com/viewjob?jk=05c819aa2a88511d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>System Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Systems Engineering Solutions Corporation</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=105f562c4b87c831</t>
+          <t>https://www.indeed.com/viewjob?jk=634fcd15ef04d7bf</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Scala, Snowflake</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56a2fccd9b09c654</t>
+          <t>https://www.indeed.com/viewjob?jk=c7869ee373ec84ed</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>CLOUD ENGINEER (AWS) (REMOTE/USA) - GDM (GRAY MEDIA GROUP)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>GRAY MEDIA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afa51ac883fa48a6</t>
+          <t>https://www.indeed.com/viewjob?jk=0beb94e2f1648144</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Senior Software Engineer - Clinical Systems (Lab Ops)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Caris Life Sciences</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, GCP, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=459162c660bc8082</t>
+          <t>https://www.indeed.com/viewjob?jk=fb8de235a110895a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Upstart</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,94 +1371,94 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dab96c17b78fc32</t>
+          <t>https://www.indeed.com/viewjob?jk=e83bd0fd320bb829</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Remote)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Inspira Financial</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1733261c550fa238</t>
+          <t>https://www.indeed.com/viewjob?jk=105f562c4b87c831</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Remote)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Inspira Financial</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0e899d198425eb</t>
+          <t>https://www.indeed.com/viewjob?jk=56a2fccd9b09c654</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Azure CI/CD Developer (FTE / Hybrid)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Oaks, PA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,19 +1476,19 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffe5d7e4f5833213</t>
+          <t>https://www.indeed.com/viewjob?jk=afa51ac883fa48a6</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, Splunk</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=022d9e279d3ddb80</t>
+          <t>https://www.indeed.com/viewjob?jk=459162c660bc8082</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python/PySpark</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Upstart</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b1dd2ce5d3671a</t>
+          <t>https://www.indeed.com/viewjob?jk=3dab96c17b78fc32</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer</t>
+          <t>REFRAME Platform Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>North Carolina State University</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6efe960a7ab141ac</t>
+          <t>https://www.indeed.com/viewjob?jk=22e67d3b77565a62</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SENIOR DATA ENGINEER</t>
+          <t>Cloud Data Platform Administartor</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Evolvers Group</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,102 +1616,102 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bee5a340a7f65e61</t>
+          <t>https://www.indeed.com/viewjob?jk=3909667b0ea7e00b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer - Authentication</t>
+          <t>Sr. Software Engineer (Remote)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Pindrop</t>
+          <t>Inspira Financial</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, MySQL, DynamoDB, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6513fcf97bbfd044</t>
+          <t>https://www.indeed.com/viewjob?jk=1733261c550fa238</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AI Support Engineer</t>
+          <t>Sr. Software Engineer (Remote)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Inspira Financial</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=625bf5ef0b332ad3</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0e899d198425eb</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AI Support Engineer</t>
+          <t>Azure CI/CD Developer (FTE / Hybrid)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Oaks, PA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd39a203b7587e31</t>
+          <t>https://www.indeed.com/viewjob?jk=ffe5d7e4f5833213</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Yusen Logistics</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kimball, ELT, dbt</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,19 +1756,19 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f92de33105c0bad</t>
+          <t>https://www.indeed.com/viewjob?jk=022d9e279d3ddb80</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Yusen Logistics</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kimball, ELT, dbt</t>
+          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=772460af87c5b60c</t>
+          <t>https://www.indeed.com/viewjob?jk=f059a12d002721db</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III- Python/PySpark</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Royal Oak, MI, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bb3681c5da818f2</t>
+          <t>https://www.indeed.com/viewjob?jk=82b1dd2ce5d3671a</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Software Development Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=343b07159d1b6928</t>
+          <t>https://www.indeed.com/viewjob?jk=6efe960a7ab141ac</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer - Virtual</t>
+          <t>SENIOR DATA ENGINEER</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Alight Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a286c7ca862c4e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=bee5a340a7f65e61</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Software Engineer - Authentication</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>TWG Global AI</t>
+          <t>Pindrop</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Kinesis, S3, RDS, Scala, MySQL, DynamoDB, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edb6a72ac37333e2</t>
+          <t>https://www.indeed.com/viewjob?jk=6513fcf97bbfd044</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>AllCloud</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,67 +1966,67 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49fcd1d4ac195cdf</t>
+          <t>https://www.indeed.com/viewjob?jk=ba5a22f3941b5b26</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Commercial Software</t>
+          <t>AI Support Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f3de39cf73c3663</t>
+          <t>https://www.indeed.com/viewjob?jk=625bf5ef0b332ad3</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>IT BI Solutions Engineer, ES</t>
+          <t>AI Support Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Terex Corporation</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chattanooga, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8376f8e501b07a8</t>
+          <t>https://www.indeed.com/viewjob?jk=dd39a203b7587e31</t>
         </is>
       </c>
     </row>
@@ -2048,20 +2048,20 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Yusen Logistics</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Medallion Architecture, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions, AWS CodePipeline</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83c604950fd47a32</t>
+          <t>https://www.indeed.com/viewjob?jk=7f92de33105c0bad</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-3</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Yusen Logistics</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f753e538739bd670</t>
+          <t>https://www.indeed.com/viewjob?jk=772460af87c5b60c</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Advance Auto Parts</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Royal Oak, MI, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,67 +2141,67 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e2d8bc5a4c9174d</t>
+          <t>https://www.indeed.com/viewjob?jk=6bb3681c5da818f2</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>IT Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Novolex</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Lake Forest, IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=024a63ca708c8a8f</t>
+          <t>https://www.indeed.com/viewjob?jk=343b07159d1b6928</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Cloud Platform Engineer - Virtual</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, Power BI</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76cb3bc7e109c2ac</t>
+          <t>https://www.indeed.com/viewjob?jk=a286c7ca862c4e1a</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>TWG Global AI</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8547c2271ca5aef</t>
+          <t>https://www.indeed.com/viewjob?jk=edb6a72ac37333e2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>AllCloud</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90d33ae33b62c3a0</t>
+          <t>https://www.indeed.com/viewjob?jk=49fcd1d4ac195cdf</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>IT BI Solutions Engineer, ES</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Terex Corporation</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chattanooga, TN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec56a8fbf5328856</t>
+          <t>https://www.indeed.com/viewjob?jk=e8376f8e501b07a8</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Step Functions, Medallion Architecture, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d4834b7dd63e5a3</t>
+          <t>https://www.indeed.com/viewjob?jk=83c604950fd47a32</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Data Platform Engineer-3</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec0d14ba7f6cc782</t>
+          <t>https://www.indeed.com/viewjob?jk=f753e538739bd670</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Advance Auto Parts</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd9783225b203a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=3e2d8bc5a4c9174d</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>IT Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Novolex</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Lake Forest, IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=154ab74a68ca6406</t>
+          <t>https://www.indeed.com/viewjob?jk=024a63ca708c8a8f</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, Power BI</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31f45e1ed037bd50</t>
+          <t>https://www.indeed.com/viewjob?jk=76cb3bc7e109c2ac</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, Power BI</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5d14ef4e88a3e5a</t>
+          <t>https://www.indeed.com/viewjob?jk=c8547c2271ca5aef</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f6ccf05e64c984b</t>
+          <t>https://www.indeed.com/viewjob?jk=90d33ae33b62c3a0</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b4b4f98c48563cd</t>
+          <t>https://www.indeed.com/viewjob?jk=ec56a8fbf5328856</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fbafb89e71fb39e</t>
+          <t>https://www.indeed.com/viewjob?jk=3d4834b7dd63e5a3</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c433c70839583dc</t>
+          <t>https://www.indeed.com/viewjob?jk=ec0d14ba7f6cc782</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35e828bfc556b676</t>
+          <t>https://www.indeed.com/viewjob?jk=cd9783225b203a0f</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3058b24332d31ded</t>
+          <t>https://www.indeed.com/viewjob?jk=154ab74a68ca6406</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17b7c64ee8dc67e0</t>
+          <t>https://www.indeed.com/viewjob?jk=31f45e1ed037bd50</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a75982d2aedba052</t>
+          <t>https://www.indeed.com/viewjob?jk=f5d14ef4e88a3e5a</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b3d8d96e19fcbe6</t>
+          <t>https://www.indeed.com/viewjob?jk=5f6ccf05e64c984b</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a58d376929282400</t>
+          <t>https://www.indeed.com/viewjob?jk=7b4b4f98c48563cd</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=559d1352317c1f33</t>
+          <t>https://www.indeed.com/viewjob?jk=9fbafb89e71fb39e</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Junior AI/MLOps Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, NoSQL, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe34817d3b1a40dc</t>
+          <t>https://www.indeed.com/viewjob?jk=0c433c70839583dc</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Java Software Engineer II (US)</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>TD Bank</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,24 +2971,24 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, NoSQL, Splunk, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ee89e940b02cc06</t>
+          <t>https://www.indeed.com/viewjob?jk=35e828bfc556b676</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,14 +3016,14 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=314cd9d2f824e302</t>
+          <t>https://www.indeed.com/viewjob?jk=3058b24332d31ded</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,14 +3051,14 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fcdb3a443f803a9</t>
+          <t>https://www.indeed.com/viewjob?jk=17b7c64ee8dc67e0</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,14 +3086,14 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6c2c604bb89e64b</t>
+          <t>https://www.indeed.com/viewjob?jk=a75982d2aedba052</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,14 +3121,14 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e02fe4d607063c1</t>
+          <t>https://www.indeed.com/viewjob?jk=4b3d8d96e19fcbe6</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,14 +3156,14 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8ac438ef838975b</t>
+          <t>https://www.indeed.com/viewjob?jk=a58d376929282400</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74bd0f0f93d9a1a5</t>
+          <t>https://www.indeed.com/viewjob?jk=559d1352317c1f33</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Junior AI/MLOps Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, NoSQL, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c53e85e359970d4</t>
+          <t>https://www.indeed.com/viewjob?jk=fe34817d3b1a40dc</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Java Software Engineer II (US)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>TD Bank</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,17 +3251,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>RDS, Azure, Scala, NoSQL, Splunk, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10e23f958e9e8b09</t>
+          <t>https://www.indeed.com/viewjob?jk=8ee89e940b02cc06</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=357547d890623cb5</t>
+          <t>https://www.indeed.com/viewjob?jk=314cd9d2f824e302</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3884844e18945dee</t>
+          <t>https://www.indeed.com/viewjob?jk=5fcdb3a443f803a9</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a60a56d62d329dea</t>
+          <t>https://www.indeed.com/viewjob?jk=c6c2c604bb89e64b</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93902824d8ac4d0c</t>
+          <t>https://www.indeed.com/viewjob?jk=6e02fe4d607063c1</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=088398b8f22d3683</t>
+          <t>https://www.indeed.com/viewjob?jk=e8ac438ef838975b</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f8a4d4b303056b</t>
+          <t>https://www.indeed.com/viewjob?jk=74bd0f0f93d9a1a5</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=459cc0fec55fdc6f</t>
+          <t>https://www.indeed.com/viewjob?jk=4c53e85e359970d4</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=521ae718282fb788</t>
+          <t>https://www.indeed.com/viewjob?jk=10e23f958e9e8b09</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=361e87b55f4161f4</t>
+          <t>https://www.indeed.com/viewjob?jk=357547d890623cb5</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32e0b2833cebefe3</t>
+          <t>https://www.indeed.com/viewjob?jk=3884844e18945dee</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f5df27af3031e62</t>
+          <t>https://www.indeed.com/viewjob?jk=a60a56d62d329dea</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Kubernetes, Airflow</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d20f4b9e6a3cbb70</t>
+          <t>https://www.indeed.com/viewjob?jk=93902824d8ac4d0c</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Kubernetes, Airflow</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,14 +3716,14 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c89d6a7d2041de38</t>
+          <t>https://www.indeed.com/viewjob?jk=088398b8f22d3683</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend + Data pipelines)</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3733,15 +3733,15 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,14 +3751,14 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4fca4ad337ae6c</t>
+          <t>https://www.indeed.com/viewjob?jk=60f8a4d4b303056b</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend + Data pipelines)</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3768,15 +3768,15 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,14 +3786,14 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ae76b185563f91b</t>
+          <t>https://www.indeed.com/viewjob?jk=459cc0fec55fdc6f</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend + Data pipelines)</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3803,15 +3803,15 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,14 +3821,14 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef2a73b324528506</t>
+          <t>https://www.indeed.com/viewjob?jk=521ae718282fb788</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend + Data pipelines)</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3838,15 +3838,15 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,14 +3856,14 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92aaafaf1efb9ec4</t>
+          <t>https://www.indeed.com/viewjob?jk=361e87b55f4161f4</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend + Data pipelines)</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3873,15 +3873,15 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,14 +3891,14 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9981aefe519f0cd</t>
+          <t>https://www.indeed.com/viewjob?jk=32e0b2833cebefe3</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend + Data pipelines)</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3912,11 +3912,11 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fce2095df8206466</t>
+          <t>https://www.indeed.com/viewjob?jk=9f5df27af3031e62</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend + Data pipelines)</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Genentech</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, Step Functions, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee34633b7838a9b3</t>
+          <t>https://www.indeed.com/viewjob?jk=d20f4b9e6a3cbb70</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend + Data pipelines)</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Genentech</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, Step Functions, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc57f588c654f1cd</t>
+          <t>https://www.indeed.com/viewjob?jk=c89d6a7d2041de38</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend + Data pipelines)</t>
+          <t>Senior Site Reliability Developer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5aaeb4c54cdfa77e</t>
+          <t>https://www.indeed.com/viewjob?jk=3fedd79bbbee99bb</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb06d74f6367bb04</t>
+          <t>https://www.indeed.com/viewjob?jk=7d4fca4ad337ae6c</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49799e02e3e0a925</t>
+          <t>https://www.indeed.com/viewjob?jk=1ae76b185563f91b</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52ff9083bc8990ce</t>
+          <t>https://www.indeed.com/viewjob?jk=ef2a73b324528506</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f89817131cfa0d</t>
+          <t>https://www.indeed.com/viewjob?jk=92aaafaf1efb9ec4</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdb757efdefad0ca</t>
+          <t>https://www.indeed.com/viewjob?jk=c9981aefe519f0cd</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57fc4e97a319b123</t>
+          <t>https://www.indeed.com/viewjob?jk=fce2095df8206466</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fcc67143e3ff8a</t>
+          <t>https://www.indeed.com/viewjob?jk=ee34633b7838a9b3</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dad4bf1e950e1c9</t>
+          <t>https://www.indeed.com/viewjob?jk=cc57f588c654f1cd</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f9ed5d278a8086d</t>
+          <t>https://www.indeed.com/viewjob?jk=5aaeb4c54cdfa77e</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8809421834292084</t>
+          <t>https://www.indeed.com/viewjob?jk=eb06d74f6367bb04</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Engineer II (Backend + Data pipelines)</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1df7caac86af2291</t>
+          <t>https://www.indeed.com/viewjob?jk=49799e02e3e0a925</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ATC - AI &amp; Data Analyst - NAELFY26</t>
+          <t>Software Engineer II (Backend + Data pipelines)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ce7a50a4bbe9ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=52ff9083bc8990ce</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Software Engineer II (Backend + Data pipelines)</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22b3d9d74319cb4d</t>
+          <t>https://www.indeed.com/viewjob?jk=66f89817131cfa0d</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Software Engineer II (Backend + Data pipelines)</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c6fa42304d7e851</t>
+          <t>https://www.indeed.com/viewjob?jk=cdb757efdefad0ca</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Software Engineer II (Backend + Data pipelines)</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf51adf8a1f9c98</t>
+          <t>https://www.indeed.com/viewjob?jk=57fc4e97a319b123</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Software Engineer II (Backend + Data pipelines)</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,14 +4591,14 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfd0ac225b61c5b4</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fcc67143e3ff8a</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Search)</t>
+          <t>Software Engineer II (Backend + Data pipelines)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,14 +4626,14 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cff2f5a9dcacb28f</t>
+          <t>https://www.indeed.com/viewjob?jk=5dad4bf1e950e1c9</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Search)</t>
+          <t>Software Engineer II (Backend + Data pipelines)</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,14 +4661,14 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3216b4c3b2c151f8</t>
+          <t>https://www.indeed.com/viewjob?jk=0f9ed5d278a8086d</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Search)</t>
+          <t>Software Engineer II (Backend + Data pipelines)</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0fc0424a2f74ea8</t>
+          <t>https://www.indeed.com/viewjob?jk=8809421834292084</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Search)</t>
+          <t>Sr. Business Development Consultant</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0ff98f788ff107b</t>
+          <t>https://www.indeed.com/viewjob?jk=1da3fc8da87b47c9</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Search)</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0442372baf83ee82</t>
+          <t>https://www.indeed.com/viewjob?jk=22b3d9d74319cb4d</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Search)</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe6ea91421159ece</t>
+          <t>https://www.indeed.com/viewjob?jk=5c6fa42304d7e851</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Search)</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aecbf4d450f1441b</t>
+          <t>https://www.indeed.com/viewjob?jk=cdf51adf8a1f9c98</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Search)</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31056dc236b5ce67</t>
+          <t>https://www.indeed.com/viewjob?jk=dfd0ac225b61c5b4</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eca84bb19e700f2b</t>
+          <t>https://www.indeed.com/viewjob?jk=cff2f5a9dcacb28f</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7401294591da0c90</t>
+          <t>https://www.indeed.com/viewjob?jk=3216b4c3b2c151f8</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eed535b1fcfea26</t>
+          <t>https://www.indeed.com/viewjob?jk=a0fc0424a2f74ea8</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29243583190aa6a</t>
+          <t>https://www.indeed.com/viewjob?jk=c0ff98f788ff107b</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c0d7ebd3a2ee36f</t>
+          <t>https://www.indeed.com/viewjob?jk=0442372baf83ee82</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e3397c0e70024e</t>
+          <t>https://www.indeed.com/viewjob?jk=fe6ea91421159ece</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35f50cc085f1bbd9</t>
+          <t>https://www.indeed.com/viewjob?jk=aecbf4d450f1441b</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72be3b8aba169a59</t>
+          <t>https://www.indeed.com/viewjob?jk=31056dc236b5ce67</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b61af8e418fcf231</t>
+          <t>https://www.indeed.com/viewjob?jk=eca84bb19e700f2b</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=552a8172dcf24a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=7401294591da0c90</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fa51ea3c52768d7</t>
+          <t>https://www.indeed.com/viewjob?jk=5eed535b1fcfea26</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Senior LLM Engineer</t>
+          <t>Senior Machine Learning Engineer (Search)</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, MLOps</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109c9c4a6595ba95</t>
+          <t>https://www.indeed.com/viewjob?jk=b29243583190aa6a</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Senior LLM Engineer</t>
+          <t>Senior Machine Learning Engineer (Search)</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, MLOps</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8723fa94634ae387</t>
+          <t>https://www.indeed.com/viewjob?jk=1c0d7ebd3a2ee36f</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Application Platform Architect - 6163848</t>
+          <t>Senior Machine Learning Engineer (Search)</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Hadoop, Scala, PostgreSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ea7fc0fae83610a</t>
+          <t>https://www.indeed.com/viewjob?jk=28e3397c0e70024e</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Machine Learning Engineer (Search)</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>LERETA, LLC</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Pomona, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad5d067156fc62f1</t>
+          <t>https://www.indeed.com/viewjob?jk=35f50cc085f1bbd9</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>MLOps Engineer</t>
+          <t>Senior Machine Learning Engineer (Search)</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,34 +5421,34 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, MLOps, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d9f82346c5ff2d3</t>
+          <t>https://www.indeed.com/viewjob?jk=72be3b8aba169a59</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Software Systems Engineer, Release Reliability &amp; Automation (Autonomous Vehicles)</t>
+          <t>Senior Machine Learning Engineer (Search)</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,34 +5456,34 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=864266ab5f8e3aac</t>
+          <t>https://www.indeed.com/viewjob?jk=b61af8e418fcf231</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer (Search)</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Stanley Martin Homes</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, SQL Server, Dimensional Modeling, ETL, MLOps</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f934b2c21443f198</t>
+          <t>https://www.indeed.com/viewjob?jk=552a8172dcf24a7a</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Senior Machine Learning Engineer (Search)</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Hard Rock International</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Hollywood, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, Snowflake, PostgreSQL, Cassandra, CI/CD, Terraform</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,32 +5536,32 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=169d4a00d377fdae</t>
+          <t>https://www.indeed.com/viewjob?jk=4fa51ea3c52768d7</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Application Platform Architect - 6163848</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Power BI, Tableau, MLOps, MLflow</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Hadoop, Scala, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,14 +5571,14 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaf9596bf4159924</t>
+          <t>https://www.indeed.com/viewjob?jk=7ea7fc0fae83610a</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior LLM Engineer</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -5592,11 +5592,11 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Power BI, Tableau, MLOps, MLflow</t>
+          <t>AWS, Azure, Vertex AI, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,102 +5606,102 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab90611f6b141379</t>
+          <t>https://www.indeed.com/viewjob?jk=109c9c4a6595ba95</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Python)</t>
+          <t>Senior LLM Engineer</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, Azure, Vertex AI, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f65ac6c3f1cf1646</t>
+          <t>https://www.indeed.com/viewjob?jk=8723fa94634ae387</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>LERETA, LLC</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Pomona, CA, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
+          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd1518c4c02c12ef</t>
+          <t>https://www.indeed.com/viewjob?jk=ad5d067156fc62f1</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Sr. ETL/SQL Engineer</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Capgemini Government Solutions</t>
+          <t>Hard Rock International</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Hollywood, FL, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, Snowflake, PostgreSQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5711,24 +5711,24 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724ffe7f1d3da135</t>
+          <t>https://www.indeed.com/viewjob?jk=169d4a00d377fdae</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Software Engineering Intern – Data Engineering (Cloud &amp; Streaming)</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Space Telescope Science Institute</t>
+          <t>NextPower</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Hive, Scala, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5746,24 +5746,24 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6055970eb603df79</t>
+          <t>https://www.indeed.com/viewjob?jk=28e588be3c533008</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>AI Engineer III</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>CareSource</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Power BI, Tableau, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -5781,24 +5781,24 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=640c68fe3716b1e6</t>
+          <t>https://www.indeed.com/viewjob?jk=aaf9596bf4159924</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Power BI, Tableau, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5816,24 +5816,24 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f85f1e8c0778adba</t>
+          <t>https://www.indeed.com/viewjob?jk=ab90611f6b141379</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Senior Software Engineer, Back End (Python)</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,34 +5841,34 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e2da1f14c27a331</t>
+          <t>https://www.indeed.com/viewjob?jk=f65ac6c3f1cf1646</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,34 +5876,34 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=140d02e1f58501f6</t>
+          <t>https://www.indeed.com/viewjob?jk=dd1518c4c02c12ef</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Senior Cloud Systems Engineer (Databricks Administrator)</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Providge Consulting</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5921,24 +5921,24 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eff547fec829449a</t>
+          <t>https://www.indeed.com/viewjob?jk=e094ab218ebab2ed</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Sr. ETL/SQL Engineer</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Capgemini Government Solutions</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,34 +5946,34 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29d22d712d7958f0</t>
+          <t>https://www.indeed.com/viewjob?jk=724ffe7f1d3da135</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>Space Telescope Science Institute</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5981,34 +5981,34 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, Hive, Scala, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3886cb86a753634c</t>
+          <t>https://www.indeed.com/viewjob?jk=6055970eb603df79</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python + Distributed systems)</t>
+          <t>AI Engineer III</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>CareSource</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>API Gateway, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6026,24 +6026,24 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4af4ef5dfeb0026</t>
+          <t>https://www.indeed.com/viewjob?jk=640c68fe3716b1e6</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python + Distributed systems)</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6061,24 +6061,24 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c116b8acf805f138</t>
+          <t>https://www.indeed.com/viewjob?jk=f85f1e8c0778adba</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python + Distributed systems)</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -6096,24 +6096,24 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f996f9a35281bba7</t>
+          <t>https://www.indeed.com/viewjob?jk=3e2da1f14c27a331</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python + Distributed systems)</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -6131,24 +6131,24 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca3982c4f2be4e49</t>
+          <t>https://www.indeed.com/viewjob?jk=140d02e1f58501f6</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python + Distributed systems)</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -6166,19 +6166,19 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f2a3e577d5623a4</t>
+          <t>https://www.indeed.com/viewjob?jk=eff547fec829449a</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python + Distributed systems)</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -6191,34 +6191,34 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=629b89e40e1e1bb5</t>
+          <t>https://www.indeed.com/viewjob?jk=29d22d712d7958f0</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python + Distributed systems)</t>
+          <t>AWS Data Engineer</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Appex Innovation</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6226,17 +6226,17 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db6cf98112c1bc9f</t>
+          <t>https://www.indeed.com/viewjob?jk=3886cb86a753634c</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80b26c4d48449b15</t>
+          <t>https://www.indeed.com/viewjob?jk=c4af4ef5dfeb0026</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83ba9763cad5f2f8</t>
+          <t>https://www.indeed.com/viewjob?jk=c116b8acf805f138</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05460d1c364a2974</t>
+          <t>https://www.indeed.com/viewjob?jk=f996f9a35281bba7</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b01dc956f073aaf8</t>
+          <t>https://www.indeed.com/viewjob?jk=ca3982c4f2be4e49</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=807aad5f4045241d</t>
+          <t>https://www.indeed.com/viewjob?jk=9f2a3e577d5623a4</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=655ea21e25dbce1e</t>
+          <t>https://www.indeed.com/viewjob?jk=629b89e40e1e1bb5</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c46ceb995e304d69</t>
+          <t>https://www.indeed.com/viewjob?jk=db6cf98112c1bc9f</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f29df76fe446a26</t>
+          <t>https://www.indeed.com/viewjob?jk=80b26c4d48449b15</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6574f30d9366e40</t>
+          <t>https://www.indeed.com/viewjob?jk=83ba9763cad5f2f8</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8536b186707d6516</t>
+          <t>https://www.indeed.com/viewjob?jk=05460d1c364a2974</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a4c9600c5ead18d</t>
+          <t>https://www.indeed.com/viewjob?jk=b01dc956f073aaf8</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6656,24 +6656,24 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78388f22c8e1c7cc</t>
+          <t>https://www.indeed.com/viewjob?jk=807aad5f4045241d</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Software Engineer (Python + Distributed systems)</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>H2O.ai</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -6691,24 +6691,24 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe52f92aedddcda4</t>
+          <t>https://www.indeed.com/viewjob?jk=655ea21e25dbce1e</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Software Engineer (Python + Distributed systems)</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>H2O.ai</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -6726,24 +6726,24 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d2b8979a3b5f81b</t>
+          <t>https://www.indeed.com/viewjob?jk=c46ceb995e304d69</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Specialist - Software Engineering</t>
+          <t>Senior Software Engineer (Python + Distributed systems)</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, Splunk, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -6761,24 +6761,24 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3c595f778e26600</t>
+          <t>https://www.indeed.com/viewjob?jk=7f29df76fe446a26</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Specialist - Software Engineering</t>
+          <t>Senior Software Engineer (Python + Distributed systems)</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, Splunk, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -6796,24 +6796,24 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=678f6a09a0ac0c26</t>
+          <t>https://www.indeed.com/viewjob?jk=d6574f30d9366e40</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Specialist - Software Engineering</t>
+          <t>Senior Software Engineer (Python + Distributed systems)</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Kafka, NoSQL, Splunk, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -6831,24 +6831,24 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6e8b8be5cf1c082</t>
+          <t>https://www.indeed.com/viewjob?jk=8536b186707d6516</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Software Engineer (Python + Distributed systems)</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -6866,24 +6866,24 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d44e3274520e56d6</t>
+          <t>https://www.indeed.com/viewjob?jk=6a4c9600c5ead18d</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Software Engineer (Python + Distributed systems)</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Centene</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6891,34 +6891,34 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11d92da9c37770a7</t>
+          <t>https://www.indeed.com/viewjob?jk=78388f22c8e1c7cc</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data &amp; Analytics</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>WesBanco Bank, Inc.</t>
+          <t>H2O.ai</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Bowie, MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -6936,24 +6936,24 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a02cdb2b181be3</t>
+          <t>https://www.indeed.com/viewjob?jk=fe52f92aedddcda4</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data &amp; Analytics</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>WesBanco Bank, Inc.</t>
+          <t>H2O.ai</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Wheeling, WV, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -6971,24 +6971,24 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb6ee55d393e301c</t>
+          <t>https://www.indeed.com/viewjob?jk=0d2b8979a3b5f81b</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Software Developer - Database Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>RAMSOFT</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, HBase, Scala, Snowflake, MySQL, NoSQL, Data Modeling, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -7006,24 +7006,24 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ce0ac7d0a937f32</t>
+          <t>https://www.indeed.com/viewjob?jk=d44e3274520e56d6</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>RapidFire Safety &amp; Security</t>
+          <t>Centene</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, Star Schema, Fact Tables, Dimension Tables, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -7041,24 +7041,24 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8afc73df8ef8f40e</t>
+          <t>https://www.indeed.com/viewjob?jk=11d92da9c37770a7</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>Senior Data Engineer - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>WesBanco Bank, Inc.</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Bowie, MD, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -7076,24 +7076,24 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2b622ee37d8f63f</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a02cdb2b181be3</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>Senior Data Engineer - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>WesBanco Bank, Inc.</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Wheeling, WV, US USA</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -7111,24 +7111,24 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ba10ede755adc88</t>
+          <t>https://www.indeed.com/viewjob?jk=fb6ee55d393e301c</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>Software Developer - Database Engineer</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>RAMSOFT</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, HBase, Scala, Snowflake, MySQL, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -7146,7 +7146,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=035e833a0affea06</t>
+          <t>https://www.indeed.com/viewjob?jk=4ce0ac7d0a937f32</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ea65634bf231fc</t>
+          <t>https://www.indeed.com/viewjob?jk=e2b622ee37d8f63f</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db2fffa7ab4fc3c6</t>
+          <t>https://www.indeed.com/viewjob?jk=7ba10ede755adc88</t>
         </is>
       </c>
     </row>
@@ -7233,7 +7233,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=726fca60377106fb</t>
+          <t>https://www.indeed.com/viewjob?jk=035e833a0affea06</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae1bbd4c5bfc6dc1</t>
+          <t>https://www.indeed.com/viewjob?jk=34ea65634bf231fc</t>
         </is>
       </c>
     </row>
@@ -7303,7 +7303,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d44fb63e0c3570e</t>
+          <t>https://www.indeed.com/viewjob?jk=db2fffa7ab4fc3c6</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac1d3f6a217585b1</t>
+          <t>https://www.indeed.com/viewjob?jk=726fca60377106fb</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=594c2209c74b60f3</t>
+          <t>https://www.indeed.com/viewjob?jk=ae1bbd4c5bfc6dc1</t>
         </is>
       </c>
     </row>
@@ -7408,7 +7408,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=300951fa8a03d9ab</t>
+          <t>https://www.indeed.com/viewjob?jk=7d44fb63e0c3570e</t>
         </is>
       </c>
     </row>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224f85378fe66226</t>
+          <t>https://www.indeed.com/viewjob?jk=ac1d3f6a217585b1</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=609ed15647075bf2</t>
+          <t>https://www.indeed.com/viewjob?jk=594c2209c74b60f3</t>
         </is>
       </c>
     </row>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7da2bae9861dfa9</t>
+          <t>https://www.indeed.com/viewjob?jk=300951fa8a03d9ab</t>
         </is>
       </c>
     </row>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f44f95326fb5d8b</t>
+          <t>https://www.indeed.com/viewjob?jk=224f85378fe66226</t>
         </is>
       </c>
     </row>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7f6777f3346c150</t>
+          <t>https://www.indeed.com/viewjob?jk=609ed15647075bf2</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99001099f8e56675</t>
+          <t>https://www.indeed.com/viewjob?jk=f7da2bae9861dfa9</t>
         </is>
       </c>
     </row>
@@ -7653,7 +7653,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D207" t="n">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d562fde2d3ab4ec</t>
+          <t>https://www.indeed.com/viewjob?jk=9f44f95326fb5d8b</t>
         </is>
       </c>
     </row>
@@ -7688,7 +7688,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D208" t="n">
@@ -7706,32 +7706,32 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49363af061447f75</t>
+          <t>https://www.indeed.com/viewjob?jk=f7f6777f3346c150</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -7741,32 +7741,32 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e60ff8bc1e60898</t>
+          <t>https://www.indeed.com/viewjob?jk=99001099f8e56675</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>LLM Application Engineer</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -7776,32 +7776,32 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5633278896c16c3b</t>
+          <t>https://www.indeed.com/viewjob?jk=1d562fde2d3ab4ec</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>LLM Application Engineer</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -7811,24 +7811,24 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e56614bfb72e3b3</t>
+          <t>https://www.indeed.com/viewjob?jk=49363af061447f75</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Product Architect Big Data Google Cloud Platform</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Reston Hospital Center - Reston</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D212" t="n">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -7846,24 +7846,24 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc86aeda9d2a8bcb</t>
+          <t>https://www.indeed.com/viewjob?jk=ed1b9b0328def6aa</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Product Architect Big Data Google Cloud Platform</t>
+          <t>SAP NS2 Senior HANA Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>St. David's HealthCare</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D213" t="n">
@@ -7871,7 +7871,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Docker</t>
+          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -7881,24 +7881,24 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613cb57ccf3485d6</t>
+          <t>https://www.indeed.com/viewjob?jk=8999a6d9da6831ef</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Product Architect Big Data Google Cloud Platform</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>HCA Florida West Tampa Hospital</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D214" t="n">
@@ -7906,7 +7906,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Docker</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -7916,24 +7916,24 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ee6462dda08d180</t>
+          <t>https://www.indeed.com/viewjob?jk=2e60ff8bc1e60898</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Product Architect Big Data Google Cloud Platform</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Medical City Healthcare</t>
+          <t>Callaway Golf</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D215" t="n">
@@ -7941,34 +7941,34 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Docker</t>
+          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae11beaa0be9d78e</t>
+          <t>https://www.indeed.com/viewjob?jk=9ae59fccd3421dc5</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Snowflake Administrator</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D216" t="n">
@@ -7976,7 +7976,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -7986,24 +7986,24 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c70cf8723aeaf7eb</t>
+          <t>https://www.indeed.com/viewjob?jk=085de5867e567658</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>LLM Application Engineer</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D217" t="n">
@@ -8011,7 +8011,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -8021,24 +8021,24 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f106012aaf32c49</t>
+          <t>https://www.indeed.com/viewjob?jk=5633278896c16c3b</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
+          <t>LLM Application Engineer</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D218" t="n">
@@ -8046,7 +8046,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -8056,24 +8056,24 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1593d7242ad3914</t>
+          <t>https://www.indeed.com/viewjob?jk=4e56614bfb72e3b3</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Product Architect Big Data Google Cloud Platform</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Reston Hospital Center - Reston</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D219" t="n">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>Lambda, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Docker</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -8091,24 +8091,24 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1315e6e62a7714e8</t>
+          <t>https://www.indeed.com/viewjob?jk=cc86aeda9d2a8bcb</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Product Architect Big Data Google Cloud Platform</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Guidewire Software, Inc.</t>
+          <t>St. David's HealthCare</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D220" t="n">
@@ -8116,34 +8116,34 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>Lambda, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Docker</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b5e082bd1857b0f</t>
+          <t>https://www.indeed.com/viewjob?jk=613cb57ccf3485d6</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Sr. Informatica IDMC MDM Software Engineer</t>
+          <t>Product Architect Big Data Google Cloud Platform</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>RBC</t>
+          <t>HCA Florida West Tampa Hospital</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D221" t="n">
@@ -8151,34 +8151,34 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Snowflake, SQL Server, ETL, CI/CD</t>
+          <t>Lambda, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Docker</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5346f4c5e2b5352a</t>
+          <t>https://www.indeed.com/viewjob?jk=1ee6462dda08d180</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Product Architect Big Data Google Cloud Platform</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Daniels Health</t>
+          <t>Medical City Healthcare</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D222" t="n">
@@ -8186,7 +8186,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, ETL, ELT, Git</t>
+          <t>Lambda, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Docker</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -8196,7 +8196,182 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aedcadc853d15f82</t>
+          <t>https://www.indeed.com/viewjob?jk=ae11beaa0be9d78e</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Sr. Full Stack Software Engineer (Onsite - San Diego)</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Carlsmed</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Carlsbad, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, Scala, PostgreSQL, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=47ffb86f604e14df</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Engineer II- Java</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c70cf8723aeaf7eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Engineer II- Java</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f106012aaf32c49</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>CrowdStrike</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a1593d7242ad3914</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Walkme</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D227" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=36669407e627b585</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-06.xlsx
+++ b/results/job_matches_2026-03-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G227"/>
+  <dimension ref="A1:G231"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,17 +783,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - INDIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Valvoline Global Operations</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Prosper, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, GCP, Cloud Storage, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab16510fd1c2841d</t>
+          <t>https://www.indeed.com/viewjob?jk=f8eebff65cda31d0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - INDIA</t>
+          <t>Senior Analyst, Risk Data Engineering</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Lincoln Financial Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Prosper, TX, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8eebff65cda31d0</t>
+          <t>https://www.indeed.com/viewjob?jk=4c054d24fbe757c5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Analyst, Risk Data Engineering</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lincoln Financial Group</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,42 +871,42 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c054d24fbe757c5</t>
+          <t>https://www.indeed.com/viewjob?jk=fc1fd3766a845e85</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc1fd3766a845e85</t>
+          <t>https://www.indeed.com/viewjob?jk=3c46cd564ba01b6c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
+          <t>Senior Data Engineer (Python, Spark, AWS)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -951,14 +951,14 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c46cd564ba01b6c</t>
+          <t>https://www.indeed.com/viewjob?jk=6d52dce08f82e688</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python, Spark, AWS)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d52dce08f82e688</t>
+          <t>https://www.indeed.com/viewjob?jk=175b82022b025c3d</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=175b82022b025c3d</t>
+          <t>https://www.indeed.com/viewjob?jk=32d044bc27a4af8a</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1051,12 +1051,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32d044bc27a4af8a</t>
+          <t>https://www.indeed.com/viewjob?jk=aed60e56cae31294</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aed60e56cae31294</t>
+          <t>https://www.indeed.com/viewjob?jk=44f958ba0cbc0f43</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>JBS Dev</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,24 +1116,24 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44f958ba0cbc0f43</t>
+          <t>https://www.indeed.com/viewjob?jk=49f6c2df00dd6e11</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (Costa Rica)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49f6c2df00dd6e11</t>
+          <t>https://www.indeed.com/viewjob?jk=05c819aa2a88511d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Costa Rica)</t>
+          <t>System Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>JBS Dev</t>
+          <t>Systems Engineering Solutions Corporation</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05c819aa2a88511d</t>
+          <t>https://www.indeed.com/viewjob?jk=634fcd15ef04d7bf</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>System Architect</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Systems Engineering Solutions Corporation</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=634fcd15ef04d7bf</t>
+          <t>https://www.indeed.com/viewjob?jk=c7869ee373ec84ed</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>CLOUD ENGINEER (AWS) (REMOTE/USA) - GDM (GRAY MEDIA GROUP)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>GRAY MEDIA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7869ee373ec84ed</t>
+          <t>https://www.indeed.com/viewjob?jk=0beb94e2f1648144</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CLOUD ENGINEER (AWS) (REMOTE/USA) - GDM (GRAY MEDIA GROUP)</t>
+          <t>Senior Software Engineer - Clinical Systems (Lab Ops)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GRAY MEDIA</t>
+          <t>Caris Life Sciences</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, DynamoDB</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, GCP, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0beb94e2f1648144</t>
+          <t>https://www.indeed.com/viewjob?jk=fb8de235a110895a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Clinical Systems (Lab Ops)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Caris Life Sciences</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, GCP, Scala, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb8de235a110895a</t>
+          <t>https://www.indeed.com/viewjob?jk=e83bd0fd320bb829</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e83bd0fd320bb829</t>
+          <t>https://www.indeed.com/viewjob?jk=105f562c4b87c831</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=105f562c4b87c831</t>
+          <t>https://www.indeed.com/viewjob?jk=56a2fccd9b09c654</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Scala, Snowflake</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56a2fccd9b09c654</t>
+          <t>https://www.indeed.com/viewjob?jk=afa51ac883fa48a6</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afa51ac883fa48a6</t>
+          <t>https://www.indeed.com/viewjob?jk=459162c660bc8082</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Upstart</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=459162c660bc8082</t>
+          <t>https://www.indeed.com/viewjob?jk=3dab96c17b78fc32</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>REFRAME Platform Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Upstart</t>
+          <t>North Carolina State University</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dab96c17b78fc32</t>
+          <t>https://www.indeed.com/viewjob?jk=22e67d3b77565a62</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>REFRAME Platform Architect</t>
+          <t>Cloud Data Platform Administartor</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>North Carolina State University</t>
+          <t>The Evolvers Group</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLOps, MLflow</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22e67d3b77565a62</t>
+          <t>https://www.indeed.com/viewjob?jk=3909667b0ea7e00b</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cloud Data Platform Administartor</t>
+          <t>Sr. Software Engineer (Remote)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>The Evolvers Group</t>
+          <t>Inspira Financial</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,17 +1606,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3909667b0ea7e00b</t>
+          <t>https://www.indeed.com/viewjob?jk=1733261c550fa238</t>
         </is>
       </c>
     </row>
@@ -1646,29 +1646,29 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1733261c550fa238</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0e899d198425eb</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Remote)</t>
+          <t>Azure CI/CD Developer (FTE / Hybrid)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Inspira Financial</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Oaks, PA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0e899d198425eb</t>
+          <t>https://www.indeed.com/viewjob?jk=ffe5d7e4f5833213</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Azure CI/CD Developer (FTE / Hybrid)</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Oaks, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffe5d7e4f5833213</t>
+          <t>https://www.indeed.com/viewjob?jk=022d9e279d3ddb80</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, Splunk</t>
+          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=022d9e279d3ddb80</t>
+          <t>https://www.indeed.com/viewjob?jk=f059a12d002721db</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III- Python/PySpark</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f059a12d002721db</t>
+          <t>https://www.indeed.com/viewjob?jk=82b1dd2ce5d3671a</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python/PySpark</t>
+          <t>Sr Software Development Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
+          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b1dd2ce5d3671a</t>
+          <t>https://www.indeed.com/viewjob?jk=6efe960a7ab141ac</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer</t>
+          <t>SENIOR DATA ENGINEER</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6efe960a7ab141ac</t>
+          <t>https://www.indeed.com/viewjob?jk=bee5a340a7f65e61</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SENIOR DATA ENGINEER</t>
+          <t>Software Engineer - Authentication</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Pindrop</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Kinesis, S3, RDS, Scala, MySQL, DynamoDB, MLOps, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bee5a340a7f65e61</t>
+          <t>https://www.indeed.com/viewjob?jk=6513fcf97bbfd044</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer - Authentication</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Pindrop</t>
+          <t>BOULDER SCIENTIFIC CO</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Longmont, CO, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, MySQL, DynamoDB, MLOps, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6513fcf97bbfd044</t>
+          <t>https://www.indeed.com/viewjob?jk=9486135c47b58364</t>
         </is>
       </c>
     </row>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3233,17 +3233,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Java Software Engineer II (US)</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>TD Bank</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,17 +3251,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, NoSQL, Splunk, Jenkins, Maven, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ee89e940b02cc06</t>
+          <t>https://www.indeed.com/viewjob?jk=314cd9d2f824e302</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=314cd9d2f824e302</t>
+          <t>https://www.indeed.com/viewjob?jk=5fcdb3a443f803a9</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fcdb3a443f803a9</t>
+          <t>https://www.indeed.com/viewjob?jk=c6c2c604bb89e64b</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6c2c604bb89e64b</t>
+          <t>https://www.indeed.com/viewjob?jk=6e02fe4d607063c1</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e02fe4d607063c1</t>
+          <t>https://www.indeed.com/viewjob?jk=e8ac438ef838975b</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8ac438ef838975b</t>
+          <t>https://www.indeed.com/viewjob?jk=74bd0f0f93d9a1a5</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74bd0f0f93d9a1a5</t>
+          <t>https://www.indeed.com/viewjob?jk=4c53e85e359970d4</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c53e85e359970d4</t>
+          <t>https://www.indeed.com/viewjob?jk=10e23f958e9e8b09</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10e23f958e9e8b09</t>
+          <t>https://www.indeed.com/viewjob?jk=357547d890623cb5</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=357547d890623cb5</t>
+          <t>https://www.indeed.com/viewjob?jk=3884844e18945dee</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3884844e18945dee</t>
+          <t>https://www.indeed.com/viewjob?jk=a60a56d62d329dea</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a60a56d62d329dea</t>
+          <t>https://www.indeed.com/viewjob?jk=93902824d8ac4d0c</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93902824d8ac4d0c</t>
+          <t>https://www.indeed.com/viewjob?jk=088398b8f22d3683</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=088398b8f22d3683</t>
+          <t>https://www.indeed.com/viewjob?jk=60f8a4d4b303056b</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f8a4d4b303056b</t>
+          <t>https://www.indeed.com/viewjob?jk=459cc0fec55fdc6f</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=459cc0fec55fdc6f</t>
+          <t>https://www.indeed.com/viewjob?jk=521ae718282fb788</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=521ae718282fb788</t>
+          <t>https://www.indeed.com/viewjob?jk=361e87b55f4161f4</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=361e87b55f4161f4</t>
+          <t>https://www.indeed.com/viewjob?jk=32e0b2833cebefe3</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32e0b2833cebefe3</t>
+          <t>https://www.indeed.com/viewjob?jk=9f5df27af3031e62</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Genentech</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Step Functions, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f5df27af3031e62</t>
+          <t>https://www.indeed.com/viewjob?jk=d20f4b9e6a3cbb70</t>
         </is>
       </c>
     </row>
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d20f4b9e6a3cbb70</t>
+          <t>https://www.indeed.com/viewjob?jk=c89d6a7d2041de38</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Site Reliability Developer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Kubernetes, Airflow</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c89d6a7d2041de38</t>
+          <t>https://www.indeed.com/viewjob?jk=3fedd79bbbee99bb</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Developer</t>
+          <t>Software Engineer II (Backend + Data pipelines)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fedd79bbbee99bb</t>
+          <t>https://www.indeed.com/viewjob?jk=7d4fca4ad337ae6c</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4fca4ad337ae6c</t>
+          <t>https://www.indeed.com/viewjob?jk=1ae76b185563f91b</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ae76b185563f91b</t>
+          <t>https://www.indeed.com/viewjob?jk=ef2a73b324528506</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef2a73b324528506</t>
+          <t>https://www.indeed.com/viewjob?jk=92aaafaf1efb9ec4</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92aaafaf1efb9ec4</t>
+          <t>https://www.indeed.com/viewjob?jk=c9981aefe519f0cd</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9981aefe519f0cd</t>
+          <t>https://www.indeed.com/viewjob?jk=fce2095df8206466</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fce2095df8206466</t>
+          <t>https://www.indeed.com/viewjob?jk=ee34633b7838a9b3</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee34633b7838a9b3</t>
+          <t>https://www.indeed.com/viewjob?jk=cc57f588c654f1cd</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc57f588c654f1cd</t>
+          <t>https://www.indeed.com/viewjob?jk=5aaeb4c54cdfa77e</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5aaeb4c54cdfa77e</t>
+          <t>https://www.indeed.com/viewjob?jk=eb06d74f6367bb04</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb06d74f6367bb04</t>
+          <t>https://www.indeed.com/viewjob?jk=49799e02e3e0a925</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49799e02e3e0a925</t>
+          <t>https://www.indeed.com/viewjob?jk=52ff9083bc8990ce</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52ff9083bc8990ce</t>
+          <t>https://www.indeed.com/viewjob?jk=66f89817131cfa0d</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f89817131cfa0d</t>
+          <t>https://www.indeed.com/viewjob?jk=cdb757efdefad0ca</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdb757efdefad0ca</t>
+          <t>https://www.indeed.com/viewjob?jk=57fc4e97a319b123</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57fc4e97a319b123</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fcc67143e3ff8a</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fcc67143e3ff8a</t>
+          <t>https://www.indeed.com/viewjob?jk=5dad4bf1e950e1c9</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dad4bf1e950e1c9</t>
+          <t>https://www.indeed.com/viewjob?jk=0f9ed5d278a8086d</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f9ed5d278a8086d</t>
+          <t>https://www.indeed.com/viewjob?jk=8809421834292084</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend + Data pipelines)</t>
+          <t>Sr. Business Development Consultant</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8809421834292084</t>
+          <t>https://www.indeed.com/viewjob?jk=1da3fc8da87b47c9</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Sr. Business Development Consultant</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1da3fc8da87b47c9</t>
+          <t>https://www.indeed.com/viewjob?jk=22b3d9d74319cb4d</t>
         </is>
       </c>
     </row>
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22b3d9d74319cb4d</t>
+          <t>https://www.indeed.com/viewjob?jk=5c6fa42304d7e851</t>
         </is>
       </c>
     </row>
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c6fa42304d7e851</t>
+          <t>https://www.indeed.com/viewjob?jk=cdf51adf8a1f9c98</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf51adf8a1f9c98</t>
+          <t>https://www.indeed.com/viewjob?jk=dfd0ac225b61c5b4</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Senior Machine Learning Engineer (Search)</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfd0ac225b61c5b4</t>
+          <t>https://www.indeed.com/viewjob?jk=cff2f5a9dcacb28f</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cff2f5a9dcacb28f</t>
+          <t>https://www.indeed.com/viewjob?jk=3216b4c3b2c151f8</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3216b4c3b2c151f8</t>
+          <t>https://www.indeed.com/viewjob?jk=a0fc0424a2f74ea8</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0fc0424a2f74ea8</t>
+          <t>https://www.indeed.com/viewjob?jk=c0ff98f788ff107b</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0ff98f788ff107b</t>
+          <t>https://www.indeed.com/viewjob?jk=0442372baf83ee82</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0442372baf83ee82</t>
+          <t>https://www.indeed.com/viewjob?jk=fe6ea91421159ece</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe6ea91421159ece</t>
+          <t>https://www.indeed.com/viewjob?jk=aecbf4d450f1441b</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aecbf4d450f1441b</t>
+          <t>https://www.indeed.com/viewjob?jk=31056dc236b5ce67</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31056dc236b5ce67</t>
+          <t>https://www.indeed.com/viewjob?jk=eca84bb19e700f2b</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eca84bb19e700f2b</t>
+          <t>https://www.indeed.com/viewjob?jk=7401294591da0c90</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7401294591da0c90</t>
+          <t>https://www.indeed.com/viewjob?jk=5eed535b1fcfea26</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eed535b1fcfea26</t>
+          <t>https://www.indeed.com/viewjob?jk=b29243583190aa6a</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29243583190aa6a</t>
+          <t>https://www.indeed.com/viewjob?jk=1c0d7ebd3a2ee36f</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c0d7ebd3a2ee36f</t>
+          <t>https://www.indeed.com/viewjob?jk=28e3397c0e70024e</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e3397c0e70024e</t>
+          <t>https://www.indeed.com/viewjob?jk=35f50cc085f1bbd9</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35f50cc085f1bbd9</t>
+          <t>https://www.indeed.com/viewjob?jk=72be3b8aba169a59</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72be3b8aba169a59</t>
+          <t>https://www.indeed.com/viewjob?jk=b61af8e418fcf231</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b61af8e418fcf231</t>
+          <t>https://www.indeed.com/viewjob?jk=552a8172dcf24a7a</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=552a8172dcf24a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=4fa51ea3c52768d7</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Search)</t>
+          <t>Senior Application Platform Architect - 6163848</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Hadoop, Scala, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fa51ea3c52768d7</t>
+          <t>https://www.indeed.com/viewjob?jk=7ea7fc0fae83610a</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Senior Application Platform Architect - 6163848</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>LERETA, LLC</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Pomona, CA, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Hadoop, Scala, PostgreSQL, CI/CD, Docker</t>
+          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,24 +5571,24 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ea7fc0fae83610a</t>
+          <t>https://www.indeed.com/viewjob?jk=ad5d067156fc62f1</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Senior LLM Engineer</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Hard Rock International</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Hollywood, FL, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, Snowflake, PostgreSQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109c9c4a6595ba95</t>
+          <t>https://www.indeed.com/viewjob?jk=169d4a00d377fdae</t>
         </is>
       </c>
     </row>
@@ -5641,24 +5641,24 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8723fa94634ae387</t>
+          <t>https://www.indeed.com/viewjob?jk=109c9c4a6595ba95</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior LLM Engineer</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>LERETA, LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Pomona, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
+          <t>AWS, Azure, Vertex AI, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,32 +5676,32 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad5d067156fc62f1</t>
+          <t>https://www.indeed.com/viewjob?jk=8723fa94634ae387</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Software Engineering Intern – Data Engineering (Cloud &amp; Streaming)</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Hard Rock International</t>
+          <t>NextPower</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Hollywood, FL, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, Snowflake, PostgreSQL, Cassandra, CI/CD, Terraform</t>
+          <t>AWS, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5711,24 +5711,24 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=169d4a00d377fdae</t>
+          <t>https://www.indeed.com/viewjob?jk=28e588be3c533008</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Software Engineering Intern – Data Engineering (Cloud &amp; Streaming)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>NextPower</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Power BI, Tableau, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e588be3c533008</t>
+          <t>https://www.indeed.com/viewjob?jk=aaf9596bf4159924</t>
         </is>
       </c>
     </row>
@@ -5781,24 +5781,24 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaf9596bf4159924</t>
+          <t>https://www.indeed.com/viewjob?jk=ab90611f6b141379</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Software Engineer, Back End (Python)</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,34 +5806,34 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Power BI, Tableau, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab90611f6b141379</t>
+          <t>https://www.indeed.com/viewjob?jk=f65ac6c3f1cf1646</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Python)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -5851,24 +5851,24 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f65ac6c3f1cf1646</t>
+          <t>https://www.indeed.com/viewjob?jk=dd1518c4c02c12ef</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Cloud Systems Engineer (Databricks Administrator)</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Providge Consulting</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,34 +5876,34 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd1518c4c02c12ef</t>
+          <t>https://www.indeed.com/viewjob?jk=e094ab218ebab2ed</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Senior Cloud Systems Engineer (Databricks Administrator)</t>
+          <t>Sr. ETL/SQL Engineer</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Providge Consulting</t>
+          <t>Capgemini Government Solutions</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Scala, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5921,24 +5921,24 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e094ab218ebab2ed</t>
+          <t>https://www.indeed.com/viewjob?jk=724ffe7f1d3da135</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Sr. ETL/SQL Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Capgemini Government Solutions</t>
+          <t>Space Telescope Science Institute</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, ECS, IAM, Hive, Scala, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5956,24 +5956,24 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724ffe7f1d3da135</t>
+          <t>https://www.indeed.com/viewjob?jk=6055970eb603df79</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>AI Engineer III</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Space Telescope Science Institute</t>
+          <t>CareSource</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Hive, Scala, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>API Gateway, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5991,24 +5991,24 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6055970eb603df79</t>
+          <t>https://www.indeed.com/viewjob?jk=640c68fe3716b1e6</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>AI Engineer III</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>CareSource</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=640c68fe3716b1e6</t>
+          <t>https://www.indeed.com/viewjob?jk=f85f1e8c0778adba</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f85f1e8c0778adba</t>
+          <t>https://www.indeed.com/viewjob?jk=3e2da1f14c27a331</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e2da1f14c27a331</t>
+          <t>https://www.indeed.com/viewjob?jk=140d02e1f58501f6</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=140d02e1f58501f6</t>
+          <t>https://www.indeed.com/viewjob?jk=eff547fec829449a</t>
         </is>
       </c>
     </row>
@@ -6161,29 +6161,29 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eff547fec829449a</t>
+          <t>https://www.indeed.com/viewjob?jk=29d22d712d7958f0</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Senior Software Engineer (Python + Distributed systems)</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6191,34 +6191,34 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29d22d712d7958f0</t>
+          <t>https://www.indeed.com/viewjob?jk=c4af4ef5dfeb0026</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Senior Software Engineer (Python + Distributed systems)</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Appex Innovation</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6226,17 +6226,17 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3886cb86a753634c</t>
+          <t>https://www.indeed.com/viewjob?jk=c116b8acf805f138</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4af4ef5dfeb0026</t>
+          <t>https://www.indeed.com/viewjob?jk=f996f9a35281bba7</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c116b8acf805f138</t>
+          <t>https://www.indeed.com/viewjob?jk=ca3982c4f2be4e49</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f996f9a35281bba7</t>
+          <t>https://www.indeed.com/viewjob?jk=9f2a3e577d5623a4</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca3982c4f2be4e49</t>
+          <t>https://www.indeed.com/viewjob?jk=629b89e40e1e1bb5</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f2a3e577d5623a4</t>
+          <t>https://www.indeed.com/viewjob?jk=db6cf98112c1bc9f</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=629b89e40e1e1bb5</t>
+          <t>https://www.indeed.com/viewjob?jk=80b26c4d48449b15</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db6cf98112c1bc9f</t>
+          <t>https://www.indeed.com/viewjob?jk=83ba9763cad5f2f8</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80b26c4d48449b15</t>
+          <t>https://www.indeed.com/viewjob?jk=05460d1c364a2974</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83ba9763cad5f2f8</t>
+          <t>https://www.indeed.com/viewjob?jk=b01dc956f073aaf8</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05460d1c364a2974</t>
+          <t>https://www.indeed.com/viewjob?jk=807aad5f4045241d</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b01dc956f073aaf8</t>
+          <t>https://www.indeed.com/viewjob?jk=655ea21e25dbce1e</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=807aad5f4045241d</t>
+          <t>https://www.indeed.com/viewjob?jk=c46ceb995e304d69</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=655ea21e25dbce1e</t>
+          <t>https://www.indeed.com/viewjob?jk=7f29df76fe446a26</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c46ceb995e304d69</t>
+          <t>https://www.indeed.com/viewjob?jk=d6574f30d9366e40</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f29df76fe446a26</t>
+          <t>https://www.indeed.com/viewjob?jk=8536b186707d6516</t>
         </is>
       </c>
     </row>
@@ -6778,7 +6778,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6574f30d9366e40</t>
+          <t>https://www.indeed.com/viewjob?jk=6a4c9600c5ead18d</t>
         </is>
       </c>
     </row>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6831,24 +6831,24 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8536b186707d6516</t>
+          <t>https://www.indeed.com/viewjob?jk=78388f22c8e1c7cc</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python + Distributed systems)</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>H2O.ai</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -6866,24 +6866,24 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a4c9600c5ead18d</t>
+          <t>https://www.indeed.com/viewjob?jk=fe52f92aedddcda4</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python + Distributed systems)</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>H2O.ai</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -6901,24 +6901,24 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78388f22c8e1c7cc</t>
+          <t>https://www.indeed.com/viewjob?jk=0d2b8979a3b5f81b</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>H2O.ai</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -6936,24 +6936,24 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe52f92aedddcda4</t>
+          <t>https://www.indeed.com/viewjob?jk=d44e3274520e56d6</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Data Engineer - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>H2O.ai</t>
+          <t>WesBanco Bank, Inc.</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bowie, MD, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -6971,24 +6971,24 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d2b8979a3b5f81b</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a02cdb2b181be3</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Data Engineer - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>WesBanco Bank, Inc.</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Wheeling, WV, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -7006,24 +7006,24 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d44e3274520e56d6</t>
+          <t>https://www.indeed.com/viewjob?jk=fb6ee55d393e301c</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Software Developer - Database Engineer</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Centene</t>
+          <t>RAMSOFT</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -7031,34 +7031,34 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, HBase, Scala, Snowflake, MySQL, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11d92da9c37770a7</t>
+          <t>https://www.indeed.com/viewjob?jk=4ce0ac7d0a937f32</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data &amp; Analytics</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>WesBanco Bank, Inc.</t>
+          <t>Centene</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Bowie, MD, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -7066,34 +7066,34 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a02cdb2b181be3</t>
+          <t>https://www.indeed.com/viewjob?jk=11d92da9c37770a7</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data &amp; Analytics</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>WesBanco Bank, Inc.</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Wheeling, WV, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -7111,24 +7111,24 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb6ee55d393e301c</t>
+          <t>https://www.indeed.com/viewjob?jk=e2b622ee37d8f63f</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Software Developer - Database Engineer</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>RAMSOFT</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, HBase, Scala, Snowflake, MySQL, NoSQL, Data Modeling, Power BI</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -7146,7 +7146,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ce0ac7d0a937f32</t>
+          <t>https://www.indeed.com/viewjob?jk=7ba10ede755adc88</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2b622ee37d8f63f</t>
+          <t>https://www.indeed.com/viewjob?jk=035e833a0affea06</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ba10ede755adc88</t>
+          <t>https://www.indeed.com/viewjob?jk=34ea65634bf231fc</t>
         </is>
       </c>
     </row>
@@ -7233,7 +7233,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=035e833a0affea06</t>
+          <t>https://www.indeed.com/viewjob?jk=db2fffa7ab4fc3c6</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ea65634bf231fc</t>
+          <t>https://www.indeed.com/viewjob?jk=726fca60377106fb</t>
         </is>
       </c>
     </row>
@@ -7303,7 +7303,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db2fffa7ab4fc3c6</t>
+          <t>https://www.indeed.com/viewjob?jk=ae1bbd4c5bfc6dc1</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=726fca60377106fb</t>
+          <t>https://www.indeed.com/viewjob?jk=7d44fb63e0c3570e</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae1bbd4c5bfc6dc1</t>
+          <t>https://www.indeed.com/viewjob?jk=ac1d3f6a217585b1</t>
         </is>
       </c>
     </row>
@@ -7408,7 +7408,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d44fb63e0c3570e</t>
+          <t>https://www.indeed.com/viewjob?jk=594c2209c74b60f3</t>
         </is>
       </c>
     </row>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac1d3f6a217585b1</t>
+          <t>https://www.indeed.com/viewjob?jk=300951fa8a03d9ab</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=594c2209c74b60f3</t>
+          <t>https://www.indeed.com/viewjob?jk=224f85378fe66226</t>
         </is>
       </c>
     </row>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=300951fa8a03d9ab</t>
+          <t>https://www.indeed.com/viewjob?jk=609ed15647075bf2</t>
         </is>
       </c>
     </row>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224f85378fe66226</t>
+          <t>https://www.indeed.com/viewjob?jk=f7da2bae9861dfa9</t>
         </is>
       </c>
     </row>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=609ed15647075bf2</t>
+          <t>https://www.indeed.com/viewjob?jk=9f44f95326fb5d8b</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7da2bae9861dfa9</t>
+          <t>https://www.indeed.com/viewjob?jk=f7f6777f3346c150</t>
         </is>
       </c>
     </row>
@@ -7653,7 +7653,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D207" t="n">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f44f95326fb5d8b</t>
+          <t>https://www.indeed.com/viewjob?jk=99001099f8e56675</t>
         </is>
       </c>
     </row>
@@ -7688,7 +7688,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D208" t="n">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7f6777f3346c150</t>
+          <t>https://www.indeed.com/viewjob?jk=1d562fde2d3ab4ec</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D209" t="n">
@@ -7741,32 +7741,32 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99001099f8e56675</t>
+          <t>https://www.indeed.com/viewjob?jk=49363af061447f75</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -7776,32 +7776,32 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d562fde2d3ab4ec</t>
+          <t>https://www.indeed.com/viewjob?jk=ed1b9b0328def6aa</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>SAP NS2 Senior HANA Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -7811,24 +7811,24 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49363af061447f75</t>
+          <t>https://www.indeed.com/viewjob?jk=8999a6d9da6831ef</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D212" t="n">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -7846,24 +7846,24 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed1b9b0328def6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=2e60ff8bc1e60898</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>SAP NS2 Senior HANA Cloud DevOps Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Callaway Golf</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D213" t="n">
@@ -7871,34 +7871,34 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8999a6d9da6831ef</t>
+          <t>https://www.indeed.com/viewjob?jk=9ae59fccd3421dc5</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Snowflake Administrator</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D214" t="n">
@@ -7906,7 +7906,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -7916,24 +7916,24 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e60ff8bc1e60898</t>
+          <t>https://www.indeed.com/viewjob?jk=085de5867e567658</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>LLM Application Engineer</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Callaway Golf</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D215" t="n">
@@ -7941,34 +7941,34 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
+          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ae59fccd3421dc5</t>
+          <t>https://www.indeed.com/viewjob?jk=5633278896c16c3b</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Snowflake Administrator</t>
+          <t>LLM Application Engineer</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D216" t="n">
@@ -7976,7 +7976,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
+          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -7986,24 +7986,24 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=085de5867e567658</t>
+          <t>https://www.indeed.com/viewjob?jk=4e56614bfb72e3b3</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>LLM Application Engineer</t>
+          <t>Product Architect Big Data Google Cloud Platform</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Reston Hospital Center - Reston</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D217" t="n">
@@ -8011,7 +8011,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
+          <t>Lambda, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Docker</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -8021,24 +8021,24 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5633278896c16c3b</t>
+          <t>https://www.indeed.com/viewjob?jk=cc86aeda9d2a8bcb</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>LLM Application Engineer</t>
+          <t>Product Architect Big Data Google Cloud Platform</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>St. David's HealthCare</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D218" t="n">
@@ -8046,7 +8046,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
+          <t>Lambda, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Docker</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e56614bfb72e3b3</t>
+          <t>https://www.indeed.com/viewjob?jk=613cb57ccf3485d6</t>
         </is>
       </c>
     </row>
@@ -8068,12 +8068,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Reston Hospital Center - Reston</t>
+          <t>HCA Florida West Tampa Hospital</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D219" t="n">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc86aeda9d2a8bcb</t>
+          <t>https://www.indeed.com/viewjob?jk=1ee6462dda08d180</t>
         </is>
       </c>
     </row>
@@ -8103,12 +8103,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>St. David's HealthCare</t>
+          <t>Medical City Healthcare</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D220" t="n">
@@ -8126,24 +8126,24 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613cb57ccf3485d6</t>
+          <t>https://www.indeed.com/viewjob?jk=ae11beaa0be9d78e</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Product Architect Big Data Google Cloud Platform</t>
+          <t>Sr. Full Stack Software Engineer (Onsite - San Diego)</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>HCA Florida West Tampa Hospital</t>
+          <t>Carlsmed</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D221" t="n">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, Scala, PostgreSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -8161,24 +8161,24 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ee6462dda08d180</t>
+          <t>https://www.indeed.com/viewjob?jk=47ffb86f604e14df</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Product Architect Big Data Google Cloud Platform</t>
+          <t>Senior BI Developer - Investment Services</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Medical City Healthcare</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D222" t="n">
@@ -8186,7 +8186,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -8196,24 +8196,24 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae11beaa0be9d78e</t>
+          <t>https://www.indeed.com/viewjob?jk=6861136ad5c92fec</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Software Engineer (Onsite - San Diego)</t>
+          <t>Senior BI Developer - Investment Services</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Carlsmed</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D223" t="n">
@@ -8221,7 +8221,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, Scala, PostgreSQL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -8231,24 +8231,24 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47ffb86f604e14df</t>
+          <t>https://www.indeed.com/viewjob?jk=d0459e004fd012bc</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Senior BI Developer - Investment Services</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D224" t="n">
@@ -8256,7 +8256,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -8266,24 +8266,24 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c70cf8723aeaf7eb</t>
+          <t>https://www.indeed.com/viewjob?jk=00bd0c85ee5af1cc</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Senior BI Developer - Investment Services</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D225" t="n">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -8301,24 +8301,24 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f106012aaf32c49</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a227aff44c18bd</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
+          <t>Senior BI Developer - Investment Services</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D226" t="n">
@@ -8326,7 +8326,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -8336,24 +8336,24 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1593d7242ad3914</t>
+          <t>https://www.indeed.com/viewjob?jk=f36e77b3ab4b1808</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior BI Developer - Investment Services</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Walkme</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D227" t="n">
@@ -8361,15 +8361,155 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b03b046a7e4b4373</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Engineer II- Java</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D228" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c70cf8723aeaf7eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Engineer II- Java</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D229" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f106012aaf32c49</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>CrowdStrike</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D230" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a1593d7242ad3914</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Walkme</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D231" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
           <t>AWS, RDS, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
-      <c r="F227" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G227" t="inlineStr">
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=36669407e627b585</t>
         </is>

--- a/results/job_matches_2026-03-06.xlsx
+++ b/results/job_matches_2026-03-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G231"/>
+  <dimension ref="A1:G234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1448,17 +1448,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Senior BI Analyst</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=459162c660bc8082</t>
+          <t>https://www.indeed.com/viewjob?jk=ad414f3a9ab0a2bc</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Upstart</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dab96c17b78fc32</t>
+          <t>https://www.indeed.com/viewjob?jk=459162c660bc8082</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>REFRAME Platform Architect</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>North Carolina State University</t>
+          <t>Upstart</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLOps, MLflow</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22e67d3b77565a62</t>
+          <t>https://www.indeed.com/viewjob?jk=3dab96c17b78fc32</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Cloud Data Platform Administartor</t>
+          <t>REFRAME Platform Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>The Evolvers Group</t>
+          <t>North Carolina State University</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3909667b0ea7e00b</t>
+          <t>https://www.indeed.com/viewjob?jk=22e67d3b77565a62</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Remote)</t>
+          <t>Cloud Data Platform Administartor</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Inspira Financial</t>
+          <t>The Evolvers Group</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,17 +1606,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1733261c550fa238</t>
+          <t>https://www.indeed.com/viewjob?jk=3909667b0ea7e00b</t>
         </is>
       </c>
     </row>
@@ -1646,29 +1646,29 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0e899d198425eb</t>
+          <t>https://www.indeed.com/viewjob?jk=1733261c550fa238</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Azure CI/CD Developer (FTE / Hybrid)</t>
+          <t>Sr. Software Engineer (Remote)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Inspira Financial</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Oaks, PA, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffe5d7e4f5833213</t>
+          <t>https://www.indeed.com/viewjob?jk=5d0e899d198425eb</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Azure CI/CD Developer (FTE / Hybrid)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Oaks, PA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, Splunk</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=022d9e279d3ddb80</t>
+          <t>https://www.indeed.com/viewjob?jk=ffe5d7e4f5833213</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f059a12d002721db</t>
+          <t>https://www.indeed.com/viewjob?jk=022d9e279d3ddb80</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python/PySpark</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
+          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b1dd2ce5d3671a</t>
+          <t>https://www.indeed.com/viewjob?jk=f059a12d002721db</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer</t>
+          <t>Software Engineer III- Python/PySpark</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6efe960a7ab141ac</t>
+          <t>https://www.indeed.com/viewjob?jk=82b1dd2ce5d3671a</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SENIOR DATA ENGINEER</t>
+          <t>Sr Software Development Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bee5a340a7f65e61</t>
+          <t>https://www.indeed.com/viewjob?jk=6efe960a7ab141ac</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer - Authentication</t>
+          <t>SENIOR DATA ENGINEER</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Pindrop</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, MySQL, DynamoDB, MLOps, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6513fcf97bbfd044</t>
+          <t>https://www.indeed.com/viewjob?jk=bee5a340a7f65e61</t>
         </is>
       </c>
     </row>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5543,17 +5543,17 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior LLM Engineer</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>LERETA, LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Pomona, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
+          <t>AWS, Azure, Vertex AI, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,24 +5571,24 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad5d067156fc62f1</t>
+          <t>https://www.indeed.com/viewjob?jk=109c9c4a6595ba95</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Senior LLM Engineer</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Hard Rock International</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Hollywood, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, Snowflake, PostgreSQL, Cassandra, CI/CD, Terraform</t>
+          <t>AWS, Azure, Vertex AI, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,24 +5606,24 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=169d4a00d377fdae</t>
+          <t>https://www.indeed.com/viewjob?jk=8723fa94634ae387</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Senior LLM Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>LERETA, LLC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Pomona, CA, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, MLOps</t>
+          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,24 +5641,24 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109c9c4a6595ba95</t>
+          <t>https://www.indeed.com/viewjob?jk=ad5d067156fc62f1</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Senior LLM Engineer</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Hard Rock International</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Hollywood, FL, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, Snowflake, PostgreSQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8723fa94634ae387</t>
+          <t>https://www.indeed.com/viewjob?jk=169d4a00d377fdae</t>
         </is>
       </c>
     </row>
@@ -5823,17 +5823,17 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Cloud Systems Engineer (Databricks Administrator)</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Providge Consulting</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,34 +5841,34 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, PySpark, Scala, MySQL, MongoDB, Docker, Kubernetes, Airflow</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd1518c4c02c12ef</t>
+          <t>https://www.indeed.com/viewjob?jk=e094ab218ebab2ed</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Senior Cloud Systems Engineer (Databricks Administrator)</t>
+          <t>Sr. ETL/SQL Engineer</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Providge Consulting</t>
+          <t>Capgemini Government Solutions</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Scala, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5886,24 +5886,24 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e094ab218ebab2ed</t>
+          <t>https://www.indeed.com/viewjob?jk=724ffe7f1d3da135</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Sr. ETL/SQL Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Capgemini Government Solutions</t>
+          <t>Space Telescope Science Institute</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, ECS, IAM, Hive, Scala, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5921,24 +5921,24 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724ffe7f1d3da135</t>
+          <t>https://www.indeed.com/viewjob?jk=6055970eb603df79</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>AI Engineer III</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Space Telescope Science Institute</t>
+          <t>CareSource</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Hive, Scala, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>API Gateway, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5956,24 +5956,24 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6055970eb603df79</t>
+          <t>https://www.indeed.com/viewjob?jk=640c68fe3716b1e6</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>AI Engineer III</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>CareSource</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=640c68fe3716b1e6</t>
+          <t>https://www.indeed.com/viewjob?jk=f85f1e8c0778adba</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f85f1e8c0778adba</t>
+          <t>https://www.indeed.com/viewjob?jk=3e2da1f14c27a331</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e2da1f14c27a331</t>
+          <t>https://www.indeed.com/viewjob?jk=140d02e1f58501f6</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=140d02e1f58501f6</t>
+          <t>https://www.indeed.com/viewjob?jk=eff547fec829449a</t>
         </is>
       </c>
     </row>
@@ -6126,29 +6126,29 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eff547fec829449a</t>
+          <t>https://www.indeed.com/viewjob?jk=29d22d712d7958f0</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Senior Software Engineer (Python + Distributed systems)</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6156,17 +6156,17 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29d22d712d7958f0</t>
+          <t>https://www.indeed.com/viewjob?jk=c4af4ef5dfeb0026</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4af4ef5dfeb0026</t>
+          <t>https://www.indeed.com/viewjob?jk=c116b8acf805f138</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c116b8acf805f138</t>
+          <t>https://www.indeed.com/viewjob?jk=f996f9a35281bba7</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f996f9a35281bba7</t>
+          <t>https://www.indeed.com/viewjob?jk=ca3982c4f2be4e49</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca3982c4f2be4e49</t>
+          <t>https://www.indeed.com/viewjob?jk=9f2a3e577d5623a4</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f2a3e577d5623a4</t>
+          <t>https://www.indeed.com/viewjob?jk=629b89e40e1e1bb5</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=629b89e40e1e1bb5</t>
+          <t>https://www.indeed.com/viewjob?jk=db6cf98112c1bc9f</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db6cf98112c1bc9f</t>
+          <t>https://www.indeed.com/viewjob?jk=80b26c4d48449b15</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80b26c4d48449b15</t>
+          <t>https://www.indeed.com/viewjob?jk=83ba9763cad5f2f8</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83ba9763cad5f2f8</t>
+          <t>https://www.indeed.com/viewjob?jk=05460d1c364a2974</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05460d1c364a2974</t>
+          <t>https://www.indeed.com/viewjob?jk=b01dc956f073aaf8</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b01dc956f073aaf8</t>
+          <t>https://www.indeed.com/viewjob?jk=807aad5f4045241d</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=807aad5f4045241d</t>
+          <t>https://www.indeed.com/viewjob?jk=655ea21e25dbce1e</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=655ea21e25dbce1e</t>
+          <t>https://www.indeed.com/viewjob?jk=c46ceb995e304d69</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c46ceb995e304d69</t>
+          <t>https://www.indeed.com/viewjob?jk=7f29df76fe446a26</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f29df76fe446a26</t>
+          <t>https://www.indeed.com/viewjob?jk=d6574f30d9366e40</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6574f30d9366e40</t>
+          <t>https://www.indeed.com/viewjob?jk=8536b186707d6516</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8536b186707d6516</t>
+          <t>https://www.indeed.com/viewjob?jk=6a4c9600c5ead18d</t>
         </is>
       </c>
     </row>
@@ -6778,7 +6778,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6796,24 +6796,24 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a4c9600c5ead18d</t>
+          <t>https://www.indeed.com/viewjob?jk=78388f22c8e1c7cc</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python + Distributed systems)</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>H2O.ai</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78388f22c8e1c7cc</t>
+          <t>https://www.indeed.com/viewjob?jk=fe52f92aedddcda4</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6866,24 +6866,24 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe52f92aedddcda4</t>
+          <t>https://www.indeed.com/viewjob?jk=0d2b8979a3b5f81b</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>H2O.ai</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -6901,24 +6901,24 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d2b8979a3b5f81b</t>
+          <t>https://www.indeed.com/viewjob?jk=d44e3274520e56d6</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Centene</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6926,17 +6926,17 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d44e3274520e56d6</t>
+          <t>https://www.indeed.com/viewjob?jk=11d92da9c37770a7</t>
         </is>
       </c>
     </row>
@@ -7048,17 +7048,17 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Centene</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -7066,17 +7066,17 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11d92da9c37770a7</t>
+          <t>https://www.indeed.com/viewjob?jk=e2b622ee37d8f63f</t>
         </is>
       </c>
     </row>
@@ -7093,7 +7093,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2b622ee37d8f63f</t>
+          <t>https://www.indeed.com/viewjob?jk=7ba10ede755adc88</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -7146,7 +7146,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ba10ede755adc88</t>
+          <t>https://www.indeed.com/viewjob?jk=035e833a0affea06</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=035e833a0affea06</t>
+          <t>https://www.indeed.com/viewjob?jk=34ea65634bf231fc</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ea65634bf231fc</t>
+          <t>https://www.indeed.com/viewjob?jk=db2fffa7ab4fc3c6</t>
         </is>
       </c>
     </row>
@@ -7233,7 +7233,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db2fffa7ab4fc3c6</t>
+          <t>https://www.indeed.com/viewjob?jk=726fca60377106fb</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=726fca60377106fb</t>
+          <t>https://www.indeed.com/viewjob?jk=ae1bbd4c5bfc6dc1</t>
         </is>
       </c>
     </row>
@@ -7303,7 +7303,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae1bbd4c5bfc6dc1</t>
+          <t>https://www.indeed.com/viewjob?jk=7d44fb63e0c3570e</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d44fb63e0c3570e</t>
+          <t>https://www.indeed.com/viewjob?jk=ac1d3f6a217585b1</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac1d3f6a217585b1</t>
+          <t>https://www.indeed.com/viewjob?jk=594c2209c74b60f3</t>
         </is>
       </c>
     </row>
@@ -7408,7 +7408,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=594c2209c74b60f3</t>
+          <t>https://www.indeed.com/viewjob?jk=300951fa8a03d9ab</t>
         </is>
       </c>
     </row>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=300951fa8a03d9ab</t>
+          <t>https://www.indeed.com/viewjob?jk=224f85378fe66226</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224f85378fe66226</t>
+          <t>https://www.indeed.com/viewjob?jk=609ed15647075bf2</t>
         </is>
       </c>
     </row>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=609ed15647075bf2</t>
+          <t>https://www.indeed.com/viewjob?jk=f7da2bae9861dfa9</t>
         </is>
       </c>
     </row>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7da2bae9861dfa9</t>
+          <t>https://www.indeed.com/viewjob?jk=9f44f95326fb5d8b</t>
         </is>
       </c>
     </row>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f44f95326fb5d8b</t>
+          <t>https://www.indeed.com/viewjob?jk=f7f6777f3346c150</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7f6777f3346c150</t>
+          <t>https://www.indeed.com/viewjob?jk=99001099f8e56675</t>
         </is>
       </c>
     </row>
@@ -7653,7 +7653,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D207" t="n">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99001099f8e56675</t>
+          <t>https://www.indeed.com/viewjob?jk=1d562fde2d3ab4ec</t>
         </is>
       </c>
     </row>
@@ -7688,7 +7688,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D208" t="n">
@@ -7706,32 +7706,32 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d562fde2d3ab4ec</t>
+          <t>https://www.indeed.com/viewjob?jk=49363af061447f75</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -7741,24 +7741,24 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49363af061447f75</t>
+          <t>https://www.indeed.com/viewjob?jk=ed1b9b0328def6aa</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>SAP NS2 Senior HANA Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D210" t="n">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -7776,24 +7776,24 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed1b9b0328def6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=8999a6d9da6831ef</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>SAP NS2 Senior HANA Cloud DevOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D211" t="n">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -7811,24 +7811,24 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8999a6d9da6831ef</t>
+          <t>https://www.indeed.com/viewjob?jk=2e60ff8bc1e60898</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>Callaway Golf</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D212" t="n">
@@ -7836,34 +7836,34 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e60ff8bc1e60898</t>
+          <t>https://www.indeed.com/viewjob?jk=9ae59fccd3421dc5</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Callaway Golf</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D213" t="n">
@@ -7871,34 +7871,34 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ae59fccd3421dc5</t>
+          <t>https://www.indeed.com/viewjob?jk=50c61f5469ce333f</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Snowflake Administrator</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D214" t="n">
@@ -7906,34 +7906,34 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=085de5867e567658</t>
+          <t>https://www.indeed.com/viewjob?jk=4303ceb5e8c627c4</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>LLM Application Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D215" t="n">
@@ -7941,34 +7941,34 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5633278896c16c3b</t>
+          <t>https://www.indeed.com/viewjob?jk=0c4db6d385ae6ea3</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>LLM Application Engineer</t>
+          <t>Snowflake Administrator</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D216" t="n">
@@ -7976,7 +7976,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -7986,24 +7986,24 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e56614bfb72e3b3</t>
+          <t>https://www.indeed.com/viewjob?jk=085de5867e567658</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Product Architect Big Data Google Cloud Platform</t>
+          <t>LLM Application Engineer</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Reston Hospital Center - Reston</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D217" t="n">
@@ -8011,7 +8011,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Docker</t>
+          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -8021,24 +8021,24 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc86aeda9d2a8bcb</t>
+          <t>https://www.indeed.com/viewjob?jk=5633278896c16c3b</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Product Architect Big Data Google Cloud Platform</t>
+          <t>LLM Application Engineer</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>St. David's HealthCare</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D218" t="n">
@@ -8046,7 +8046,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Docker</t>
+          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613cb57ccf3485d6</t>
+          <t>https://www.indeed.com/viewjob?jk=4e56614bfb72e3b3</t>
         </is>
       </c>
     </row>
@@ -8068,12 +8068,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>HCA Florida West Tampa Hospital</t>
+          <t>Reston Hospital Center - Reston</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D219" t="n">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ee6462dda08d180</t>
+          <t>https://www.indeed.com/viewjob?jk=cc86aeda9d2a8bcb</t>
         </is>
       </c>
     </row>
@@ -8103,12 +8103,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Medical City Healthcare</t>
+          <t>St. David's HealthCare</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D220" t="n">
@@ -8126,24 +8126,24 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae11beaa0be9d78e</t>
+          <t>https://www.indeed.com/viewjob?jk=613cb57ccf3485d6</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Software Engineer (Onsite - San Diego)</t>
+          <t>Product Architect Big Data Google Cloud Platform</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Carlsmed</t>
+          <t>HCA Florida West Tampa Hospital</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D221" t="n">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, Scala, PostgreSQL, CI/CD, Git</t>
+          <t>Lambda, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Docker</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -8161,24 +8161,24 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47ffb86f604e14df</t>
+          <t>https://www.indeed.com/viewjob?jk=1ee6462dda08d180</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Senior BI Developer - Investment Services</t>
+          <t>Product Architect Big Data Google Cloud Platform</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Medical City Healthcare</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D222" t="n">
@@ -8186,7 +8186,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
+          <t>Lambda, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Docker</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -8196,24 +8196,24 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6861136ad5c92fec</t>
+          <t>https://www.indeed.com/viewjob?jk=ae11beaa0be9d78e</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Senior BI Developer - Investment Services</t>
+          <t>Sr. Full Stack Software Engineer (Onsite - San Diego)</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Carlsmed</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D223" t="n">
@@ -8221,7 +8221,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, Scala, PostgreSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0459e004fd012bc</t>
+          <t>https://www.indeed.com/viewjob?jk=47ffb86f604e14df</t>
         </is>
       </c>
     </row>
@@ -8248,7 +8248,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D224" t="n">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00bd0c85ee5af1cc</t>
+          <t>https://www.indeed.com/viewjob?jk=6861136ad5c92fec</t>
         </is>
       </c>
     </row>
@@ -8283,7 +8283,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D225" t="n">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a227aff44c18bd</t>
+          <t>https://www.indeed.com/viewjob?jk=d0459e004fd012bc</t>
         </is>
       </c>
     </row>
@@ -8318,7 +8318,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D226" t="n">
@@ -8336,7 +8336,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f36e77b3ab4b1808</t>
+          <t>https://www.indeed.com/viewjob?jk=00bd0c85ee5af1cc</t>
         </is>
       </c>
     </row>
@@ -8353,7 +8353,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D227" t="n">
@@ -8371,24 +8371,24 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b03b046a7e4b4373</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a227aff44c18bd</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Senior BI Developer - Investment Services</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D228" t="n">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -8406,24 +8406,24 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c70cf8723aeaf7eb</t>
+          <t>https://www.indeed.com/viewjob?jk=f36e77b3ab4b1808</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Senior BI Developer - Investment Services</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D229" t="n">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -8441,24 +8441,24 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f106012aaf32c49</t>
+          <t>https://www.indeed.com/viewjob?jk=b03b046a7e4b4373</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D230" t="n">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -8476,24 +8476,24 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1593d7242ad3914</t>
+          <t>https://www.indeed.com/viewjob?jk=c70cf8723aeaf7eb</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Walkme</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D231" t="n">
@@ -8501,15 +8501,120 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f106012aaf32c49</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>CrowdStrike</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D232" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a1593d7242ad3914</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Teradata Developer</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D233" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7fddb4ec439f1237</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Walkme</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D234" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
           <t>AWS, RDS, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
-      <c r="F231" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G231" t="inlineStr">
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=36669407e627b585</t>
         </is>

--- a/results/job_matches_2026-03-06.xlsx
+++ b/results/job_matches_2026-03-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G234"/>
+  <dimension ref="A1:G235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1623,17 +1623,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Remote)</t>
+          <t>Azure CI/CD Developer (FTE / Hybrid)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Inspira Financial</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Oaks, PA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1733261c550fa238</t>
+          <t>https://www.indeed.com/viewjob?jk=ffe5d7e4f5833213</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Remote)</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Inspira Financial</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,42 +1676,42 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MongoDB, Azure Cosmos DB, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d0e899d198425eb</t>
+          <t>https://www.indeed.com/viewjob?jk=022d9e279d3ddb80</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Azure CI/CD Developer (FTE / Hybrid)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Oaks, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffe5d7e4f5833213</t>
+          <t>https://www.indeed.com/viewjob?jk=f059a12d002721db</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Software Engineer III- Python/PySpark</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, Splunk</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=022d9e279d3ddb80</t>
+          <t>https://www.indeed.com/viewjob?jk=82b1dd2ce5d3671a</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Software Development Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
+          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f059a12d002721db</t>
+          <t>https://www.indeed.com/viewjob?jk=6efe960a7ab141ac</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python/PySpark</t>
+          <t>SENIOR DATA ENGINEER</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b1dd2ce5d3671a</t>
+          <t>https://www.indeed.com/viewjob?jk=bee5a340a7f65e61</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>BOULDER SCIENTIFIC CO</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Longmont, CO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6efe960a7ab141ac</t>
+          <t>https://www.indeed.com/viewjob?jk=9486135c47b58364</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SENIOR DATA ENGINEER</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bee5a340a7f65e61</t>
+          <t>https://www.indeed.com/viewjob?jk=ba5a22f3941b5b26</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Support Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BOULDER SCIENTIFIC CO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Longmont, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9486135c47b58364</t>
+          <t>https://www.indeed.com/viewjob?jk=625bf5ef0b332ad3</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Support Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba5a22f3941b5b26</t>
+          <t>https://www.indeed.com/viewjob?jk=dd39a203b7587e31</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AI Support Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Yusen Logistics</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=625bf5ef0b332ad3</t>
+          <t>https://www.indeed.com/viewjob?jk=7f92de33105c0bad</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AI Support Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Yusen Logistics</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd39a203b7587e31</t>
+          <t>https://www.indeed.com/viewjob?jk=772460af87c5b60c</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Yusen Logistics</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Royal Oak, MI, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kimball, ELT, dbt</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f92de33105c0bad</t>
+          <t>https://www.indeed.com/viewjob?jk=6bb3681c5da818f2</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Yusen Logistics</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kimball, ELT, dbt</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=772460af87c5b60c</t>
+          <t>https://www.indeed.com/viewjob?jk=343b07159d1b6928</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Platform Engineer - Virtual</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Royal Oak, MI, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bb3681c5da818f2</t>
+          <t>https://www.indeed.com/viewjob?jk=a286c7ca862c4e1a</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>TWG Global AI</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=343b07159d1b6928</t>
+          <t>https://www.indeed.com/viewjob?jk=edb6a72ac37333e2</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer - Virtual</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Alight Solutions</t>
+          <t>AllCloud</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a286c7ca862c4e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=49fcd1d4ac195cdf</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>IT BI Solutions Engineer, ES</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>TWG Global AI</t>
+          <t>Terex Corporation</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Chattanooga, TN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, RDS, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edb6a72ac37333e2</t>
+          <t>https://www.indeed.com/viewjob?jk=e8376f8e501b07a8</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>AllCloud</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
+          <t>AWS, Step Functions, Medallion Architecture, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49fcd1d4ac195cdf</t>
+          <t>https://www.indeed.com/viewjob?jk=83c604950fd47a32</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>IT BI Solutions Engineer, ES</t>
+          <t>Data Platform Engineer-3</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Terex Corporation</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chattanooga, TN, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8376f8e501b07a8</t>
+          <t>https://www.indeed.com/viewjob?jk=f753e538739bd670</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Advance Auto Parts</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Medallion Architecture, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions, AWS CodePipeline</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83c604950fd47a32</t>
+          <t>https://www.indeed.com/viewjob?jk=3e2d8bc5a4c9174d</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-3</t>
+          <t>IT Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Novolex</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Lake Forest, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f753e538739bd670</t>
+          <t>https://www.indeed.com/viewjob?jk=024a63ca708c8a8f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Advance Auto Parts</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, Power BI</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e2d8bc5a4c9174d</t>
+          <t>https://www.indeed.com/viewjob?jk=76cb3bc7e109c2ac</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>IT Data Engineer</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Novolex</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Lake Forest, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, Power BI</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=024a63ca708c8a8f</t>
+          <t>https://www.indeed.com/viewjob?jk=c8547c2271ca5aef</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, Power BI</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76cb3bc7e109c2ac</t>
+          <t>https://www.indeed.com/viewjob?jk=90d33ae33b62c3a0</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, Power BI</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8547c2271ca5aef</t>
+          <t>https://www.indeed.com/viewjob?jk=ec56a8fbf5328856</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90d33ae33b62c3a0</t>
+          <t>https://www.indeed.com/viewjob?jk=3d4834b7dd63e5a3</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec56a8fbf5328856</t>
+          <t>https://www.indeed.com/viewjob?jk=ec0d14ba7f6cc782</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d4834b7dd63e5a3</t>
+          <t>https://www.indeed.com/viewjob?jk=cd9783225b203a0f</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec0d14ba7f6cc782</t>
+          <t>https://www.indeed.com/viewjob?jk=154ab74a68ca6406</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd9783225b203a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=31f45e1ed037bd50</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=154ab74a68ca6406</t>
+          <t>https://www.indeed.com/viewjob?jk=f5d14ef4e88a3e5a</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31f45e1ed037bd50</t>
+          <t>https://www.indeed.com/viewjob?jk=5f6ccf05e64c984b</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5d14ef4e88a3e5a</t>
+          <t>https://www.indeed.com/viewjob?jk=7b4b4f98c48563cd</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f6ccf05e64c984b</t>
+          <t>https://www.indeed.com/viewjob?jk=9fbafb89e71fb39e</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b4b4f98c48563cd</t>
+          <t>https://www.indeed.com/viewjob?jk=0c433c70839583dc</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Junior AI/MLOps Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, NoSQL, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,14 +2911,14 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fbafb89e71fb39e</t>
+          <t>https://www.indeed.com/viewjob?jk=fe34817d3b1a40dc</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,14 +2946,14 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c433c70839583dc</t>
+          <t>https://www.indeed.com/viewjob?jk=314cd9d2f824e302</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,14 +2981,14 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35e828bfc556b676</t>
+          <t>https://www.indeed.com/viewjob?jk=5fcdb3a443f803a9</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,14 +3016,14 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3058b24332d31ded</t>
+          <t>https://www.indeed.com/viewjob?jk=c6c2c604bb89e64b</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,14 +3051,14 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17b7c64ee8dc67e0</t>
+          <t>https://www.indeed.com/viewjob?jk=6e02fe4d607063c1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3086,14 +3086,14 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a75982d2aedba052</t>
+          <t>https://www.indeed.com/viewjob?jk=e8ac438ef838975b</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,14 +3121,14 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b3d8d96e19fcbe6</t>
+          <t>https://www.indeed.com/viewjob?jk=74bd0f0f93d9a1a5</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a58d376929282400</t>
+          <t>https://www.indeed.com/viewjob?jk=4c53e85e359970d4</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=559d1352317c1f33</t>
+          <t>https://www.indeed.com/viewjob?jk=35e828bfc556b676</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Junior AI/MLOps Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, NoSQL, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe34817d3b1a40dc</t>
+          <t>https://www.indeed.com/viewjob?jk=3058b24332d31ded</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=314cd9d2f824e302</t>
+          <t>https://www.indeed.com/viewjob?jk=10e23f958e9e8b09</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fcdb3a443f803a9</t>
+          <t>https://www.indeed.com/viewjob?jk=357547d890623cb5</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,14 +3331,14 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6c2c604bb89e64b</t>
+          <t>https://www.indeed.com/viewjob?jk=3884844e18945dee</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,14 +3366,14 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e02fe4d607063c1</t>
+          <t>https://www.indeed.com/viewjob?jk=17b7c64ee8dc67e0</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3401,14 +3401,14 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8ac438ef838975b</t>
+          <t>https://www.indeed.com/viewjob?jk=a75982d2aedba052</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74bd0f0f93d9a1a5</t>
+          <t>https://www.indeed.com/viewjob?jk=4b3d8d96e19fcbe6</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c53e85e359970d4</t>
+          <t>https://www.indeed.com/viewjob?jk=a60a56d62d329dea</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10e23f958e9e8b09</t>
+          <t>https://www.indeed.com/viewjob?jk=93902824d8ac4d0c</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=357547d890623cb5</t>
+          <t>https://www.indeed.com/viewjob?jk=088398b8f22d3683</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3884844e18945dee</t>
+          <t>https://www.indeed.com/viewjob?jk=60f8a4d4b303056b</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,14 +3611,14 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a60a56d62d329dea</t>
+          <t>https://www.indeed.com/viewjob?jk=459cc0fec55fdc6f</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93902824d8ac4d0c</t>
+          <t>https://www.indeed.com/viewjob?jk=a58d376929282400</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,14 +3681,14 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=088398b8f22d3683</t>
+          <t>https://www.indeed.com/viewjob?jk=521ae718282fb788</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f8a4d4b303056b</t>
+          <t>https://www.indeed.com/viewjob?jk=559d1352317c1f33</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=459cc0fec55fdc6f</t>
+          <t>https://www.indeed.com/viewjob?jk=361e87b55f4161f4</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=521ae718282fb788</t>
+          <t>https://www.indeed.com/viewjob?jk=32e0b2833cebefe3</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=361e87b55f4161f4</t>
+          <t>https://www.indeed.com/viewjob?jk=9f5df27af3031e62</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Genentech</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Step Functions, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32e0b2833cebefe3</t>
+          <t>https://www.indeed.com/viewjob?jk=d20f4b9e6a3cbb70</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Genentech</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Step Functions, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,19 +3891,19 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f5df27af3031e62</t>
+          <t>https://www.indeed.com/viewjob?jk=c89d6a7d2041de38</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d20f4b9e6a3cbb70</t>
+          <t>https://www.indeed.com/viewjob?jk=38b673fd36dffa19</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Site Reliability Developer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Kubernetes, Airflow</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c89d6a7d2041de38</t>
+          <t>https://www.indeed.com/viewjob?jk=3fedd79bbbee99bb</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Developer</t>
+          <t>Software Engineer II (Backend + Data pipelines)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fedd79bbbee99bb</t>
+          <t>https://www.indeed.com/viewjob?jk=7d4fca4ad337ae6c</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4fca4ad337ae6c</t>
+          <t>https://www.indeed.com/viewjob?jk=1ae76b185563f91b</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ae76b185563f91b</t>
+          <t>https://www.indeed.com/viewjob?jk=ef2a73b324528506</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef2a73b324528506</t>
+          <t>https://www.indeed.com/viewjob?jk=92aaafaf1efb9ec4</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92aaafaf1efb9ec4</t>
+          <t>https://www.indeed.com/viewjob?jk=c9981aefe519f0cd</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9981aefe519f0cd</t>
+          <t>https://www.indeed.com/viewjob?jk=fce2095df8206466</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fce2095df8206466</t>
+          <t>https://www.indeed.com/viewjob?jk=ee34633b7838a9b3</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee34633b7838a9b3</t>
+          <t>https://www.indeed.com/viewjob?jk=cc57f588c654f1cd</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc57f588c654f1cd</t>
+          <t>https://www.indeed.com/viewjob?jk=5aaeb4c54cdfa77e</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5aaeb4c54cdfa77e</t>
+          <t>https://www.indeed.com/viewjob?jk=eb06d74f6367bb04</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb06d74f6367bb04</t>
+          <t>https://www.indeed.com/viewjob?jk=49799e02e3e0a925</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49799e02e3e0a925</t>
+          <t>https://www.indeed.com/viewjob?jk=52ff9083bc8990ce</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52ff9083bc8990ce</t>
+          <t>https://www.indeed.com/viewjob?jk=66f89817131cfa0d</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f89817131cfa0d</t>
+          <t>https://www.indeed.com/viewjob?jk=cdb757efdefad0ca</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdb757efdefad0ca</t>
+          <t>https://www.indeed.com/viewjob?jk=57fc4e97a319b123</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57fc4e97a319b123</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fcc67143e3ff8a</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fcc67143e3ff8a</t>
+          <t>https://www.indeed.com/viewjob?jk=5dad4bf1e950e1c9</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dad4bf1e950e1c9</t>
+          <t>https://www.indeed.com/viewjob?jk=0f9ed5d278a8086d</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f9ed5d278a8086d</t>
+          <t>https://www.indeed.com/viewjob?jk=8809421834292084</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend + Data pipelines)</t>
+          <t>Sr. Business Development Consultant</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8809421834292084</t>
+          <t>https://www.indeed.com/viewjob?jk=1da3fc8da87b47c9</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Sr. Business Development Consultant</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1da3fc8da87b47c9</t>
+          <t>https://www.indeed.com/viewjob?jk=22b3d9d74319cb4d</t>
         </is>
       </c>
     </row>
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22b3d9d74319cb4d</t>
+          <t>https://www.indeed.com/viewjob?jk=5c6fa42304d7e851</t>
         </is>
       </c>
     </row>
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c6fa42304d7e851</t>
+          <t>https://www.indeed.com/viewjob?jk=cdf51adf8a1f9c98</t>
         </is>
       </c>
     </row>
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf51adf8a1f9c98</t>
+          <t>https://www.indeed.com/viewjob?jk=dfd0ac225b61c5b4</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Senior Machine Learning Engineer (Search)</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfd0ac225b61c5b4</t>
+          <t>https://www.indeed.com/viewjob?jk=cff2f5a9dcacb28f</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cff2f5a9dcacb28f</t>
+          <t>https://www.indeed.com/viewjob?jk=3216b4c3b2c151f8</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3216b4c3b2c151f8</t>
+          <t>https://www.indeed.com/viewjob?jk=a0fc0424a2f74ea8</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0fc0424a2f74ea8</t>
+          <t>https://www.indeed.com/viewjob?jk=c0ff98f788ff107b</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0ff98f788ff107b</t>
+          <t>https://www.indeed.com/viewjob?jk=0442372baf83ee82</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0442372baf83ee82</t>
+          <t>https://www.indeed.com/viewjob?jk=fe6ea91421159ece</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe6ea91421159ece</t>
+          <t>https://www.indeed.com/viewjob?jk=aecbf4d450f1441b</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aecbf4d450f1441b</t>
+          <t>https://www.indeed.com/viewjob?jk=31056dc236b5ce67</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31056dc236b5ce67</t>
+          <t>https://www.indeed.com/viewjob?jk=eca84bb19e700f2b</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eca84bb19e700f2b</t>
+          <t>https://www.indeed.com/viewjob?jk=7401294591da0c90</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7401294591da0c90</t>
+          <t>https://www.indeed.com/viewjob?jk=5eed535b1fcfea26</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eed535b1fcfea26</t>
+          <t>https://www.indeed.com/viewjob?jk=b29243583190aa6a</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29243583190aa6a</t>
+          <t>https://www.indeed.com/viewjob?jk=1c0d7ebd3a2ee36f</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c0d7ebd3a2ee36f</t>
+          <t>https://www.indeed.com/viewjob?jk=28e3397c0e70024e</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e3397c0e70024e</t>
+          <t>https://www.indeed.com/viewjob?jk=35f50cc085f1bbd9</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35f50cc085f1bbd9</t>
+          <t>https://www.indeed.com/viewjob?jk=72be3b8aba169a59</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72be3b8aba169a59</t>
+          <t>https://www.indeed.com/viewjob?jk=b61af8e418fcf231</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b61af8e418fcf231</t>
+          <t>https://www.indeed.com/viewjob?jk=552a8172dcf24a7a</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=552a8172dcf24a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=4fa51ea3c52768d7</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Search)</t>
+          <t>Senior Application Platform Architect - 6163848</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Hadoop, Scala, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fa51ea3c52768d7</t>
+          <t>https://www.indeed.com/viewjob?jk=7ea7fc0fae83610a</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Senior Application Platform Architect - 6163848</t>
+          <t>Senior LLM Engineer</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Hadoop, Scala, PostgreSQL, CI/CD, Docker</t>
+          <t>AWS, Azure, Vertex AI, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ea7fc0fae83610a</t>
+          <t>https://www.indeed.com/viewjob?jk=109c9c4a6595ba95</t>
         </is>
       </c>
     </row>
@@ -5571,24 +5571,24 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109c9c4a6595ba95</t>
+          <t>https://www.indeed.com/viewjob?jk=8723fa94634ae387</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Senior LLM Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>LERETA, LLC</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Pomona, CA, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, MLOps</t>
+          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,24 +5606,24 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8723fa94634ae387</t>
+          <t>https://www.indeed.com/viewjob?jk=ad5d067156fc62f1</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>LERETA, LLC</t>
+          <t>Hard Rock International</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Pomona, CA, US USA</t>
+          <t>Hollywood, FL, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, Snowflake, PostgreSQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,32 +5641,32 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad5d067156fc62f1</t>
+          <t>https://www.indeed.com/viewjob?jk=169d4a00d377fdae</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Software Engineering Intern – Data Engineering (Cloud &amp; Streaming)</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Hard Rock International</t>
+          <t>NextPower</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Hollywood, FL, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, Snowflake, PostgreSQL, Cassandra, CI/CD, Terraform</t>
+          <t>AWS, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,24 +5676,24 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=169d4a00d377fdae</t>
+          <t>https://www.indeed.com/viewjob?jk=28e588be3c533008</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Software Engineering Intern – Data Engineering (Cloud &amp; Streaming)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>NextPower</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Power BI, Tableau, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e588be3c533008</t>
+          <t>https://www.indeed.com/viewjob?jk=aaf9596bf4159924</t>
         </is>
       </c>
     </row>
@@ -5746,24 +5746,24 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaf9596bf4159924</t>
+          <t>https://www.indeed.com/viewjob?jk=ab90611f6b141379</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Software Engineer, Back End (Python)</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,34 +5771,34 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Power BI, Tableau, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab90611f6b141379</t>
+          <t>https://www.indeed.com/viewjob?jk=f65ac6c3f1cf1646</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Python)</t>
+          <t>Senior Cloud Systems Engineer (Databricks Administrator)</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Providge Consulting</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,34 +5806,34 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f65ac6c3f1cf1646</t>
+          <t>https://www.indeed.com/viewjob?jk=e094ab218ebab2ed</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Senior Cloud Systems Engineer (Databricks Administrator)</t>
+          <t>Sr. ETL/SQL Engineer</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Providge Consulting</t>
+          <t>Capgemini Government Solutions</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Scala, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -5851,24 +5851,24 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e094ab218ebab2ed</t>
+          <t>https://www.indeed.com/viewjob?jk=724ffe7f1d3da135</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Sr. ETL/SQL Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Capgemini Government Solutions</t>
+          <t>Space Telescope Science Institute</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, ECS, IAM, Hive, Scala, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5886,24 +5886,24 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724ffe7f1d3da135</t>
+          <t>https://www.indeed.com/viewjob?jk=6055970eb603df79</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>AI Engineer III</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Space Telescope Science Institute</t>
+          <t>CareSource</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Hive, Scala, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>API Gateway, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5921,24 +5921,24 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6055970eb603df79</t>
+          <t>https://www.indeed.com/viewjob?jk=640c68fe3716b1e6</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>AI Engineer III</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>CareSource</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=640c68fe3716b1e6</t>
+          <t>https://www.indeed.com/viewjob?jk=f85f1e8c0778adba</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f85f1e8c0778adba</t>
+          <t>https://www.indeed.com/viewjob?jk=3e2da1f14c27a331</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e2da1f14c27a331</t>
+          <t>https://www.indeed.com/viewjob?jk=140d02e1f58501f6</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=140d02e1f58501f6</t>
+          <t>https://www.indeed.com/viewjob?jk=eff547fec829449a</t>
         </is>
       </c>
     </row>
@@ -6091,29 +6091,29 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eff547fec829449a</t>
+          <t>https://www.indeed.com/viewjob?jk=29d22d712d7958f0</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Senior Software Engineer (Python + Distributed systems)</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6121,17 +6121,17 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29d22d712d7958f0</t>
+          <t>https://www.indeed.com/viewjob?jk=c4af4ef5dfeb0026</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4af4ef5dfeb0026</t>
+          <t>https://www.indeed.com/viewjob?jk=c116b8acf805f138</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c116b8acf805f138</t>
+          <t>https://www.indeed.com/viewjob?jk=f996f9a35281bba7</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f996f9a35281bba7</t>
+          <t>https://www.indeed.com/viewjob?jk=ca3982c4f2be4e49</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca3982c4f2be4e49</t>
+          <t>https://www.indeed.com/viewjob?jk=9f2a3e577d5623a4</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f2a3e577d5623a4</t>
+          <t>https://www.indeed.com/viewjob?jk=629b89e40e1e1bb5</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=629b89e40e1e1bb5</t>
+          <t>https://www.indeed.com/viewjob?jk=db6cf98112c1bc9f</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db6cf98112c1bc9f</t>
+          <t>https://www.indeed.com/viewjob?jk=80b26c4d48449b15</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80b26c4d48449b15</t>
+          <t>https://www.indeed.com/viewjob?jk=83ba9763cad5f2f8</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83ba9763cad5f2f8</t>
+          <t>https://www.indeed.com/viewjob?jk=05460d1c364a2974</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05460d1c364a2974</t>
+          <t>https://www.indeed.com/viewjob?jk=b01dc956f073aaf8</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b01dc956f073aaf8</t>
+          <t>https://www.indeed.com/viewjob?jk=807aad5f4045241d</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=807aad5f4045241d</t>
+          <t>https://www.indeed.com/viewjob?jk=655ea21e25dbce1e</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=655ea21e25dbce1e</t>
+          <t>https://www.indeed.com/viewjob?jk=c46ceb995e304d69</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c46ceb995e304d69</t>
+          <t>https://www.indeed.com/viewjob?jk=7f29df76fe446a26</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f29df76fe446a26</t>
+          <t>https://www.indeed.com/viewjob?jk=d6574f30d9366e40</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6574f30d9366e40</t>
+          <t>https://www.indeed.com/viewjob?jk=8536b186707d6516</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8536b186707d6516</t>
+          <t>https://www.indeed.com/viewjob?jk=6a4c9600c5ead18d</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6761,24 +6761,24 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a4c9600c5ead18d</t>
+          <t>https://www.indeed.com/viewjob?jk=78388f22c8e1c7cc</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python + Distributed systems)</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>H2O.ai</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78388f22c8e1c7cc</t>
+          <t>https://www.indeed.com/viewjob?jk=fe52f92aedddcda4</t>
         </is>
       </c>
     </row>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6831,24 +6831,24 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe52f92aedddcda4</t>
+          <t>https://www.indeed.com/viewjob?jk=0d2b8979a3b5f81b</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>H2O.ai</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -6866,24 +6866,24 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d2b8979a3b5f81b</t>
+          <t>https://www.indeed.com/viewjob?jk=d44e3274520e56d6</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Centene</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6891,34 +6891,34 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d44e3274520e56d6</t>
+          <t>https://www.indeed.com/viewjob?jk=11d92da9c37770a7</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Data Engineer - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Centene</t>
+          <t>WesBanco Bank, Inc.</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Bowie, MD, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6926,17 +6926,17 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11d92da9c37770a7</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a02cdb2b181be3</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Bowie, MD, US USA</t>
+          <t>Wheeling, WV, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6971,24 +6971,24 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a02cdb2b181be3</t>
+          <t>https://www.indeed.com/viewjob?jk=fb6ee55d393e301c</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data &amp; Analytics</t>
+          <t>Software Developer - Database Engineer</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>WesBanco Bank, Inc.</t>
+          <t>RAMSOFT</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Wheeling, WV, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, HBase, Scala, Snowflake, MySQL, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -7006,24 +7006,24 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb6ee55d393e301c</t>
+          <t>https://www.indeed.com/viewjob?jk=4ce0ac7d0a937f32</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Software Developer - Database Engineer</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>RAMSOFT</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, HBase, Scala, Snowflake, MySQL, NoSQL, Data Modeling, Power BI</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ce0ac7d0a937f32</t>
+          <t>https://www.indeed.com/viewjob?jk=e2b622ee37d8f63f</t>
         </is>
       </c>
     </row>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2b622ee37d8f63f</t>
+          <t>https://www.indeed.com/viewjob?jk=7ba10ede755adc88</t>
         </is>
       </c>
     </row>
@@ -7093,7 +7093,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ba10ede755adc88</t>
+          <t>https://www.indeed.com/viewjob?jk=035e833a0affea06</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -7146,7 +7146,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=035e833a0affea06</t>
+          <t>https://www.indeed.com/viewjob?jk=34ea65634bf231fc</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ea65634bf231fc</t>
+          <t>https://www.indeed.com/viewjob?jk=db2fffa7ab4fc3c6</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db2fffa7ab4fc3c6</t>
+          <t>https://www.indeed.com/viewjob?jk=726fca60377106fb</t>
         </is>
       </c>
     </row>
@@ -7233,7 +7233,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=726fca60377106fb</t>
+          <t>https://www.indeed.com/viewjob?jk=ae1bbd4c5bfc6dc1</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae1bbd4c5bfc6dc1</t>
+          <t>https://www.indeed.com/viewjob?jk=7d44fb63e0c3570e</t>
         </is>
       </c>
     </row>
@@ -7303,7 +7303,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d44fb63e0c3570e</t>
+          <t>https://www.indeed.com/viewjob?jk=ac1d3f6a217585b1</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac1d3f6a217585b1</t>
+          <t>https://www.indeed.com/viewjob?jk=594c2209c74b60f3</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=594c2209c74b60f3</t>
+          <t>https://www.indeed.com/viewjob?jk=300951fa8a03d9ab</t>
         </is>
       </c>
     </row>
@@ -7408,7 +7408,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=300951fa8a03d9ab</t>
+          <t>https://www.indeed.com/viewjob?jk=224f85378fe66226</t>
         </is>
       </c>
     </row>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224f85378fe66226</t>
+          <t>https://www.indeed.com/viewjob?jk=609ed15647075bf2</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=609ed15647075bf2</t>
+          <t>https://www.indeed.com/viewjob?jk=f7da2bae9861dfa9</t>
         </is>
       </c>
     </row>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7da2bae9861dfa9</t>
+          <t>https://www.indeed.com/viewjob?jk=9f44f95326fb5d8b</t>
         </is>
       </c>
     </row>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f44f95326fb5d8b</t>
+          <t>https://www.indeed.com/viewjob?jk=f7f6777f3346c150</t>
         </is>
       </c>
     </row>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7f6777f3346c150</t>
+          <t>https://www.indeed.com/viewjob?jk=99001099f8e56675</t>
         </is>
       </c>
     </row>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99001099f8e56675</t>
+          <t>https://www.indeed.com/viewjob?jk=1d562fde2d3ab4ec</t>
         </is>
       </c>
     </row>
@@ -7653,7 +7653,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D207" t="n">
@@ -7671,32 +7671,32 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d562fde2d3ab4ec</t>
+          <t>https://www.indeed.com/viewjob?jk=49363af061447f75</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -7706,24 +7706,24 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49363af061447f75</t>
+          <t>https://www.indeed.com/viewjob?jk=ed1b9b0328def6aa</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>SAP NS2 Senior HANA Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D209" t="n">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -7741,24 +7741,24 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed1b9b0328def6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=8999a6d9da6831ef</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>SAP NS2 Senior HANA Cloud DevOps Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D210" t="n">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -7776,24 +7776,24 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8999a6d9da6831ef</t>
+          <t>https://www.indeed.com/viewjob?jk=2e60ff8bc1e60898</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>Callaway Golf</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D211" t="n">
@@ -7801,34 +7801,34 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e60ff8bc1e60898</t>
+          <t>https://www.indeed.com/viewjob?jk=9ae59fccd3421dc5</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Callaway Golf</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D212" t="n">
@@ -7836,17 +7836,17 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ae59fccd3421dc5</t>
+          <t>https://www.indeed.com/viewjob?jk=50c61f5469ce333f</t>
         </is>
       </c>
     </row>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D213" t="n">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c61f5469ce333f</t>
+          <t>https://www.indeed.com/viewjob?jk=4303ceb5e8c627c4</t>
         </is>
       </c>
     </row>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D214" t="n">
@@ -7916,24 +7916,24 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4303ceb5e8c627c4</t>
+          <t>https://www.indeed.com/viewjob?jk=0c4db6d385ae6ea3</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Snowflake Administrator</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D215" t="n">
@@ -7941,34 +7941,34 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c4db6d385ae6ea3</t>
+          <t>https://www.indeed.com/viewjob?jk=085de5867e567658</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Snowflake Administrator</t>
+          <t>LLM Application Engineer</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D216" t="n">
@@ -7976,7 +7976,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
+          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=085de5867e567658</t>
+          <t>https://www.indeed.com/viewjob?jk=5633278896c16c3b</t>
         </is>
       </c>
     </row>
@@ -8021,24 +8021,24 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5633278896c16c3b</t>
+          <t>https://www.indeed.com/viewjob?jk=4e56614bfb72e3b3</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>LLM Application Engineer</t>
+          <t>Product Architect Big Data Google Cloud Platform</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Reston Hospital Center - Reston</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D218" t="n">
@@ -8046,7 +8046,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
+          <t>Lambda, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Docker</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e56614bfb72e3b3</t>
+          <t>https://www.indeed.com/viewjob?jk=cc86aeda9d2a8bcb</t>
         </is>
       </c>
     </row>
@@ -8068,12 +8068,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Reston Hospital Center - Reston</t>
+          <t>St. David's HealthCare</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D219" t="n">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc86aeda9d2a8bcb</t>
+          <t>https://www.indeed.com/viewjob?jk=613cb57ccf3485d6</t>
         </is>
       </c>
     </row>
@@ -8103,12 +8103,12 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>St. David's HealthCare</t>
+          <t>HCA Florida West Tampa Hospital</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D220" t="n">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613cb57ccf3485d6</t>
+          <t>https://www.indeed.com/viewjob?jk=1ee6462dda08d180</t>
         </is>
       </c>
     </row>
@@ -8138,12 +8138,12 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>HCA Florida West Tampa Hospital</t>
+          <t>Medical City Healthcare</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D221" t="n">
@@ -8161,24 +8161,24 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ee6462dda08d180</t>
+          <t>https://www.indeed.com/viewjob?jk=ae11beaa0be9d78e</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Product Architect Big Data Google Cloud Platform</t>
+          <t>SENIOR DATA ENGINEER (REMOTE)</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Medical City Healthcare</t>
+          <t>Morrison Healthcare</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D222" t="n">
@@ -8186,34 +8186,34 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Snowflake, ETL, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae11beaa0be9d78e</t>
+          <t>https://www.indeed.com/viewjob?jk=d530073f998c3698</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Software Engineer (Onsite - San Diego)</t>
+          <t>Senior BI Developer - Investment Services</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Carlsmed</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D223" t="n">
@@ -8221,7 +8221,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, Scala, PostgreSQL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47ffb86f604e14df</t>
+          <t>https://www.indeed.com/viewjob?jk=6861136ad5c92fec</t>
         </is>
       </c>
     </row>
@@ -8248,7 +8248,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D224" t="n">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6861136ad5c92fec</t>
+          <t>https://www.indeed.com/viewjob?jk=d0459e004fd012bc</t>
         </is>
       </c>
     </row>
@@ -8283,7 +8283,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D225" t="n">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0459e004fd012bc</t>
+          <t>https://www.indeed.com/viewjob?jk=00bd0c85ee5af1cc</t>
         </is>
       </c>
     </row>
@@ -8318,7 +8318,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D226" t="n">
@@ -8336,7 +8336,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00bd0c85ee5af1cc</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a227aff44c18bd</t>
         </is>
       </c>
     </row>
@@ -8353,7 +8353,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D227" t="n">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a227aff44c18bd</t>
+          <t>https://www.indeed.com/viewjob?jk=f36e77b3ab4b1808</t>
         </is>
       </c>
     </row>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D228" t="n">
@@ -8406,24 +8406,24 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f36e77b3ab4b1808</t>
+          <t>https://www.indeed.com/viewjob?jk=b03b046a7e4b4373</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Senior BI Developer - Investment Services</t>
+          <t>Sr. Full Stack Software Engineer (Onsite - San Diego)</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Carlsmed</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D229" t="n">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, Scala, PostgreSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b03b046a7e4b4373</t>
+          <t>https://www.indeed.com/viewjob?jk=47ffb86f604e14df</t>
         </is>
       </c>
     </row>
@@ -8518,17 +8518,17 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
+          <t>Teradata Developer</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D232" t="n">
@@ -8536,34 +8536,34 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1593d7242ad3914</t>
+          <t>https://www.indeed.com/viewjob?jk=7fddb4ec439f1237</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Teradata Developer</t>
+          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D233" t="n">
@@ -8571,17 +8571,17 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fddb4ec439f1237</t>
+          <t>https://www.indeed.com/viewjob?jk=a1593d7242ad3914</t>
         </is>
       </c>
     </row>
@@ -8615,6 +8615,41 @@
         </is>
       </c>
       <c r="G234" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=00aac4a1caed5c4b</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Walkme</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D235" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=36669407e627b585</t>
         </is>

--- a/results/job_matches_2026-03-06.xlsx
+++ b/results/job_matches_2026-03-06.xlsx
@@ -1168,17 +1168,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>System Architect</t>
+          <t>Senior Systems Administrator, Cloud (GTA)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Systems Engineering Solutions Corporation</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=634fcd15ef04d7bf</t>
+          <t>https://www.indeed.com/viewjob?jk=094fcc384185954f</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>System Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Systems Engineering Solutions Corporation</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7869ee373ec84ed</t>
+          <t>https://www.indeed.com/viewjob?jk=634fcd15ef04d7bf</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CLOUD ENGINEER (AWS) (REMOTE/USA) - GDM (GRAY MEDIA GROUP)</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GRAY MEDIA</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, DynamoDB</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0beb94e2f1648144</t>
+          <t>https://www.indeed.com/viewjob?jk=c7869ee373ec84ed</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Clinical Systems (Lab Ops)</t>
+          <t>CLOUD ENGINEER (AWS) (REMOTE/USA) - GDM (GRAY MEDIA GROUP)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Caris Life Sciences</t>
+          <t>GRAY MEDIA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, GCP, Scala, PostgreSQL</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb8de235a110895a</t>
+          <t>https://www.indeed.com/viewjob?jk=0beb94e2f1648144</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Engineer - Clinical Systems (Lab Ops)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Caris Life Sciences</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, GCP, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e83bd0fd320bb829</t>
+          <t>https://www.indeed.com/viewjob?jk=fb8de235a110895a</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=105f562c4b87c831</t>
+          <t>https://www.indeed.com/viewjob?jk=e83bd0fd320bb829</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56a2fccd9b09c654</t>
+          <t>https://www.indeed.com/viewjob?jk=105f562c4b87c831</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afa51ac883fa48a6</t>
+          <t>https://www.indeed.com/viewjob?jk=56a2fccd9b09c654</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior BI Analyst</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad414f3a9ab0a2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=afa51ac883fa48a6</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Senior BI Analyst</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=459162c660bc8082</t>
+          <t>https://www.indeed.com/viewjob?jk=ad414f3a9ab0a2bc</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Upstart</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dab96c17b78fc32</t>
+          <t>https://www.indeed.com/viewjob?jk=459162c660bc8082</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>REFRAME Platform Architect</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>North Carolina State University</t>
+          <t>Upstart</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLOps, MLflow</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22e67d3b77565a62</t>
+          <t>https://www.indeed.com/viewjob?jk=3dab96c17b78fc32</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cloud Data Platform Administartor</t>
+          <t>REFRAME Platform Architect</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>The Evolvers Group</t>
+          <t>North Carolina State University</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3909667b0ea7e00b</t>
+          <t>https://www.indeed.com/viewjob?jk=22e67d3b77565a62</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Azure CI/CD Developer (FTE / Hybrid)</t>
+          <t>Cloud Data Platform Administartor</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>The Evolvers Group</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Oaks, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffe5d7e4f5833213</t>
+          <t>https://www.indeed.com/viewjob?jk=3909667b0ea7e00b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Azure CI/CD Developer (FTE / Hybrid)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Oaks, PA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, Splunk</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=022d9e279d3ddb80</t>
+          <t>https://www.indeed.com/viewjob?jk=ffe5d7e4f5833213</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f059a12d002721db</t>
+          <t>https://www.indeed.com/viewjob?jk=022d9e279d3ddb80</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python/PySpark</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
+          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b1dd2ce5d3671a</t>
+          <t>https://www.indeed.com/viewjob?jk=f059a12d002721db</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer</t>
+          <t>Software Engineer III- Python/PySpark</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6efe960a7ab141ac</t>
+          <t>https://www.indeed.com/viewjob?jk=82b1dd2ce5d3671a</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SENIOR DATA ENGINEER</t>
+          <t>Sr Software Development Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bee5a340a7f65e61</t>
+          <t>https://www.indeed.com/viewjob?jk=6efe960a7ab141ac</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>SENIOR DATA ENGINEER</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BOULDER SCIENTIFIC CO</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Longmont, CO, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9486135c47b58364</t>
+          <t>https://www.indeed.com/viewjob?jk=bee5a340a7f65e61</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>BOULDER SCIENTIFIC CO</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Longmont, CO, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba5a22f3941b5b26</t>
+          <t>https://www.indeed.com/viewjob?jk=9486135c47b58364</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AI Support Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=625bf5ef0b332ad3</t>
+          <t>https://www.indeed.com/viewjob?jk=ba5a22f3941b5b26</t>
         </is>
       </c>
     </row>
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd39a203b7587e31</t>
+          <t>https://www.indeed.com/viewjob?jk=625bf5ef0b332ad3</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Support Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Yusen Logistics</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kimball, ELT, dbt</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f92de33105c0bad</t>
+          <t>https://www.indeed.com/viewjob?jk=dd39a203b7587e31</t>
         </is>
       </c>
     </row>
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=772460af87c5b60c</t>
+          <t>https://www.indeed.com/viewjob?jk=7f92de33105c0bad</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Yusen Logistics</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Royal Oak, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bb3681c5da818f2</t>
+          <t>https://www.indeed.com/viewjob?jk=772460af87c5b60c</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Royal Oak, MI, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=343b07159d1b6928</t>
+          <t>https://www.indeed.com/viewjob?jk=6bb3681c5da818f2</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer - Virtual</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Alight Solutions</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a286c7ca862c4e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=343b07159d1b6928</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Cloud Platform Engineer - Virtual</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>TWG Global AI</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,67 +2176,67 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edb6a72ac37333e2</t>
+          <t>https://www.indeed.com/viewjob?jk=a286c7ca862c4e1a</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Advisor Application Designer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>AllCloud</t>
+          <t>HJ Staffing</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49fcd1d4ac195cdf</t>
+          <t>https://www.indeed.com/viewjob?jk=a988f0c0aeaa0fa5</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>IT BI Solutions Engineer, ES</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Terex Corporation</t>
+          <t>TWG Global AI</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chattanooga, TN, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8376f8e501b07a8</t>
+          <t>https://www.indeed.com/viewjob?jk=edb6a72ac37333e2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>AllCloud</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Medallion Architecture, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions, AWS CodePipeline</t>
+          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83c604950fd47a32</t>
+          <t>https://www.indeed.com/viewjob?jk=49fcd1d4ac195cdf</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-3</t>
+          <t>IT BI Solutions Engineer, ES</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Terex Corporation</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Chattanooga, TN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f753e538739bd670</t>
+          <t>https://www.indeed.com/viewjob?jk=e8376f8e501b07a8</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Advance Auto Parts</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Step Functions, Medallion Architecture, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e2d8bc5a4c9174d</t>
+          <t>https://www.indeed.com/viewjob?jk=83c604950fd47a32</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>IT Data Engineer</t>
+          <t>Data Platform Engineer-3</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Novolex</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Lake Forest, IL, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Dataflow, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=024a63ca708c8a8f</t>
+          <t>https://www.indeed.com/viewjob?jk=f753e538739bd670</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Advance Auto Parts</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, Power BI</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76cb3bc7e109c2ac</t>
+          <t>https://www.indeed.com/viewjob?jk=3e2d8bc5a4c9174d</t>
         </is>
       </c>
     </row>
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8547c2271ca5aef</t>
+          <t>https://www.indeed.com/viewjob?jk=76cb3bc7e109c2ac</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, Power BI</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90d33ae33b62c3a0</t>
+          <t>https://www.indeed.com/viewjob?jk=c8547c2271ca5aef</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec56a8fbf5328856</t>
+          <t>https://www.indeed.com/viewjob?jk=90d33ae33b62c3a0</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d4834b7dd63e5a3</t>
+          <t>https://www.indeed.com/viewjob?jk=ec56a8fbf5328856</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,14 +2596,14 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec0d14ba7f6cc782</t>
+          <t>https://www.indeed.com/viewjob?jk=3d4834b7dd63e5a3</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd9783225b203a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=314cd9d2f824e302</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=154ab74a68ca6406</t>
+          <t>https://www.indeed.com/viewjob?jk=ec0d14ba7f6cc782</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,14 +2701,14 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31f45e1ed037bd50</t>
+          <t>https://www.indeed.com/viewjob?jk=cd9783225b203a0f</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5d14ef4e88a3e5a</t>
+          <t>https://www.indeed.com/viewjob?jk=5fcdb3a443f803a9</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f6ccf05e64c984b</t>
+          <t>https://www.indeed.com/viewjob?jk=154ab74a68ca6406</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b4b4f98c48563cd</t>
+          <t>https://www.indeed.com/viewjob?jk=31f45e1ed037bd50</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fbafb89e71fb39e</t>
+          <t>https://www.indeed.com/viewjob?jk=f5d14ef4e88a3e5a</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c433c70839583dc</t>
+          <t>https://www.indeed.com/viewjob?jk=5f6ccf05e64c984b</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Junior AI/MLOps Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, NoSQL, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe34817d3b1a40dc</t>
+          <t>https://www.indeed.com/viewjob?jk=7b4b4f98c48563cd</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=314cd9d2f824e302</t>
+          <t>https://www.indeed.com/viewjob?jk=c6c2c604bb89e64b</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,14 +2981,14 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fcdb3a443f803a9</t>
+          <t>https://www.indeed.com/viewjob?jk=6e02fe4d607063c1</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6c2c604bb89e64b</t>
+          <t>https://www.indeed.com/viewjob?jk=9fbafb89e71fb39e</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e02fe4d607063c1</t>
+          <t>https://www.indeed.com/viewjob?jk=e8ac438ef838975b</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8ac438ef838975b</t>
+          <t>https://www.indeed.com/viewjob?jk=74bd0f0f93d9a1a5</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,14 +3121,14 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74bd0f0f93d9a1a5</t>
+          <t>https://www.indeed.com/viewjob?jk=4c53e85e359970d4</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c53e85e359970d4</t>
+          <t>https://www.indeed.com/viewjob?jk=0c433c70839583dc</t>
         </is>
       </c>
     </row>
@@ -3828,25 +3828,25 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Junior AI/MLOps Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, NoSQL, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d20f4b9e6a3cbb70</t>
+          <t>https://www.indeed.com/viewjob?jk=fe34817d3b1a40dc</t>
         </is>
       </c>
     </row>
@@ -3891,19 +3891,19 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c89d6a7d2041de38</t>
+          <t>https://www.indeed.com/viewjob?jk=d20f4b9e6a3cbb70</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Genentech</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Step Functions, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38b673fd36dffa19</t>
+          <t>https://www.indeed.com/viewjob?jk=c89d6a7d2041de38</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fedd79bbbee99bb</t>
+          <t>https://www.indeed.com/viewjob?jk=38b673fd36dffa19</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend + Data pipelines)</t>
+          <t>Senior Site Reliability Developer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4fca4ad337ae6c</t>
+          <t>https://www.indeed.com/viewjob?jk=3fedd79bbbee99bb</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ae76b185563f91b</t>
+          <t>https://www.indeed.com/viewjob?jk=7d4fca4ad337ae6c</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef2a73b324528506</t>
+          <t>https://www.indeed.com/viewjob?jk=1ae76b185563f91b</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92aaafaf1efb9ec4</t>
+          <t>https://www.indeed.com/viewjob?jk=ef2a73b324528506</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9981aefe519f0cd</t>
+          <t>https://www.indeed.com/viewjob?jk=92aaafaf1efb9ec4</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fce2095df8206466</t>
+          <t>https://www.indeed.com/viewjob?jk=c9981aefe519f0cd</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee34633b7838a9b3</t>
+          <t>https://www.indeed.com/viewjob?jk=fce2095df8206466</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc57f588c654f1cd</t>
+          <t>https://www.indeed.com/viewjob?jk=ee34633b7838a9b3</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5aaeb4c54cdfa77e</t>
+          <t>https://www.indeed.com/viewjob?jk=cc57f588c654f1cd</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb06d74f6367bb04</t>
+          <t>https://www.indeed.com/viewjob?jk=5aaeb4c54cdfa77e</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49799e02e3e0a925</t>
+          <t>https://www.indeed.com/viewjob?jk=eb06d74f6367bb04</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52ff9083bc8990ce</t>
+          <t>https://www.indeed.com/viewjob?jk=49799e02e3e0a925</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f89817131cfa0d</t>
+          <t>https://www.indeed.com/viewjob?jk=52ff9083bc8990ce</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdb757efdefad0ca</t>
+          <t>https://www.indeed.com/viewjob?jk=66f89817131cfa0d</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57fc4e97a319b123</t>
+          <t>https://www.indeed.com/viewjob?jk=cdb757efdefad0ca</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fcc67143e3ff8a</t>
+          <t>https://www.indeed.com/viewjob?jk=57fc4e97a319b123</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dad4bf1e950e1c9</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fcc67143e3ff8a</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f9ed5d278a8086d</t>
+          <t>https://www.indeed.com/viewjob?jk=5dad4bf1e950e1c9</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8809421834292084</t>
+          <t>https://www.indeed.com/viewjob?jk=0f9ed5d278a8086d</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Sr. Business Development Consultant</t>
+          <t>Software Engineer II (Backend + Data pipelines)</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1da3fc8da87b47c9</t>
+          <t>https://www.indeed.com/viewjob?jk=8809421834292084</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Sr. Business Development Consultant</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22b3d9d74319cb4d</t>
+          <t>https://www.indeed.com/viewjob?jk=1da3fc8da87b47c9</t>
         </is>
       </c>
     </row>
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c6fa42304d7e851</t>
+          <t>https://www.indeed.com/viewjob?jk=22b3d9d74319cb4d</t>
         </is>
       </c>
     </row>
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf51adf8a1f9c98</t>
+          <t>https://www.indeed.com/viewjob?jk=5c6fa42304d7e851</t>
         </is>
       </c>
     </row>
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfd0ac225b61c5b4</t>
+          <t>https://www.indeed.com/viewjob?jk=cdf51adf8a1f9c98</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Search)</t>
+          <t>ML Infrastructure Architect</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cff2f5a9dcacb28f</t>
+          <t>https://www.indeed.com/viewjob?jk=dfd0ac225b61c5b4</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Search)</t>
+          <t>Selenium Automation tester</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>Azure, Scala, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3216b4c3b2c151f8</t>
+          <t>https://www.indeed.com/viewjob?jk=bc0fe4c47cda2838</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Search)</t>
+          <t>Applied Machine Learning Engineer (All Levels)</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Azure, GCP, Spark, ELT, MLflow, CI/CD, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0fc0424a2f74ea8</t>
+          <t>https://www.indeed.com/viewjob?jk=c1910fa4b9572adb</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0ff98f788ff107b</t>
+          <t>https://www.indeed.com/viewjob?jk=cff2f5a9dcacb28f</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0442372baf83ee82</t>
+          <t>https://www.indeed.com/viewjob?jk=3216b4c3b2c151f8</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe6ea91421159ece</t>
+          <t>https://www.indeed.com/viewjob?jk=a0fc0424a2f74ea8</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aecbf4d450f1441b</t>
+          <t>https://www.indeed.com/viewjob?jk=c0ff98f788ff107b</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31056dc236b5ce67</t>
+          <t>https://www.indeed.com/viewjob?jk=0442372baf83ee82</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eca84bb19e700f2b</t>
+          <t>https://www.indeed.com/viewjob?jk=fe6ea91421159ece</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7401294591da0c90</t>
+          <t>https://www.indeed.com/viewjob?jk=aecbf4d450f1441b</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eed535b1fcfea26</t>
+          <t>https://www.indeed.com/viewjob?jk=31056dc236b5ce67</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29243583190aa6a</t>
+          <t>https://www.indeed.com/viewjob?jk=eca84bb19e700f2b</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c0d7ebd3a2ee36f</t>
+          <t>https://www.indeed.com/viewjob?jk=7401294591da0c90</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e3397c0e70024e</t>
+          <t>https://www.indeed.com/viewjob?jk=5eed535b1fcfea26</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35f50cc085f1bbd9</t>
+          <t>https://www.indeed.com/viewjob?jk=b29243583190aa6a</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72be3b8aba169a59</t>
+          <t>https://www.indeed.com/viewjob?jk=1c0d7ebd3a2ee36f</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b61af8e418fcf231</t>
+          <t>https://www.indeed.com/viewjob?jk=28e3397c0e70024e</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=552a8172dcf24a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=35f50cc085f1bbd9</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fa51ea3c52768d7</t>
+          <t>https://www.indeed.com/viewjob?jk=72be3b8aba169a59</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Senior Application Platform Architect - 6163848</t>
+          <t>Senior Machine Learning Engineer (Search)</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Hadoop, Scala, PostgreSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ea7fc0fae83610a</t>
+          <t>https://www.indeed.com/viewjob?jk=b61af8e418fcf231</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Senior LLM Engineer</t>
+          <t>Senior Machine Learning Engineer (Search)</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, MLOps</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109c9c4a6595ba95</t>
+          <t>https://www.indeed.com/viewjob?jk=552a8172dcf24a7a</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Senior LLM Engineer</t>
+          <t>Senior Machine Learning Engineer (Search)</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, MLOps</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,24 +5571,24 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8723fa94634ae387</t>
+          <t>https://www.indeed.com/viewjob?jk=4fa51ea3c52768d7</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Application Platform Architect - 6163848</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>LERETA, LLC</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Pomona, CA, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Hadoop, Scala, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,24 +5606,24 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad5d067156fc62f1</t>
+          <t>https://www.indeed.com/viewjob?jk=7ea7fc0fae83610a</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Hard Rock International</t>
+          <t>LERETA, LLC</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Hollywood, FL, US USA</t>
+          <t>Pomona, CA, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, Snowflake, PostgreSQL, Cassandra, CI/CD, Terraform</t>
+          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,32 +5641,32 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=169d4a00d377fdae</t>
+          <t>https://www.indeed.com/viewjob?jk=ad5d067156fc62f1</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Software Engineering Intern – Data Engineering (Cloud &amp; Streaming)</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>NextPower</t>
+          <t>Hard Rock International</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Hollywood, FL, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, Snowflake, PostgreSQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,14 +5676,14 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e588be3c533008</t>
+          <t>https://www.indeed.com/viewjob?jk=169d4a00d377fdae</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior LLM Engineer</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -5697,11 +5697,11 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Power BI, Tableau, MLOps, MLflow</t>
+          <t>AWS, Azure, Vertex AI, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5711,14 +5711,14 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaf9596bf4159924</t>
+          <t>https://www.indeed.com/viewjob?jk=109c9c4a6595ba95</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior LLM Engineer</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -5732,11 +5732,11 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Power BI, Tableau, MLOps, MLflow</t>
+          <t>AWS, Azure, Vertex AI, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5746,24 +5746,24 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab90611f6b141379</t>
+          <t>https://www.indeed.com/viewjob?jk=8723fa94634ae387</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Python)</t>
+          <t>Software Engineering Intern – Data Engineering (Cloud &amp; Streaming)</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>NextPower</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,34 +5771,34 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f65ac6c3f1cf1646</t>
+          <t>https://www.indeed.com/viewjob?jk=28e588be3c533008</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Senior Cloud Systems Engineer (Databricks Administrator)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Providge Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Scala, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Power BI, Tableau, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5816,24 +5816,24 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e094ab218ebab2ed</t>
+          <t>https://www.indeed.com/viewjob?jk=aaf9596bf4159924</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Sr. ETL/SQL Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Capgemini Government Solutions</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Power BI, Tableau, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -5851,24 +5851,24 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724ffe7f1d3da135</t>
+          <t>https://www.indeed.com/viewjob?jk=ab90611f6b141379</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Senior Software Engineer, Back End (Python)</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Space Telescope Science Institute</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,34 +5876,34 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Hive, Scala, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6055970eb603df79</t>
+          <t>https://www.indeed.com/viewjob?jk=f65ac6c3f1cf1646</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>AI Engineer III</t>
+          <t>Senior Cloud Systems Engineer (Databricks Administrator)</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>CareSource</t>
+          <t>Providge Consulting</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5921,24 +5921,24 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=640c68fe3716b1e6</t>
+          <t>https://www.indeed.com/viewjob?jk=e094ab218ebab2ed</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Sr. ETL/SQL Engineer</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Capgemini Government Solutions</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5956,24 +5956,24 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f85f1e8c0778adba</t>
+          <t>https://www.indeed.com/viewjob?jk=724ffe7f1d3da135</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Space Telescope Science Institute</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, ECS, IAM, Hive, Scala, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5991,24 +5991,24 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e2da1f14c27a331</t>
+          <t>https://www.indeed.com/viewjob?jk=6055970eb603df79</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>AI Engineer III</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>CareSource</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>API Gateway, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6026,24 +6026,24 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=140d02e1f58501f6</t>
+          <t>https://www.indeed.com/viewjob?jk=640c68fe3716b1e6</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Senior Software Engineer (Python + Distributed systems)</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6061,24 +6061,24 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eff547fec829449a</t>
+          <t>https://www.indeed.com/viewjob?jk=c4af4ef5dfeb0026</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Senior Software Engineer (Python + Distributed systems)</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6086,17 +6086,17 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29d22d712d7958f0</t>
+          <t>https://www.indeed.com/viewjob?jk=c116b8acf805f138</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4af4ef5dfeb0026</t>
+          <t>https://www.indeed.com/viewjob?jk=f996f9a35281bba7</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c116b8acf805f138</t>
+          <t>https://www.indeed.com/viewjob?jk=ca3982c4f2be4e49</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f996f9a35281bba7</t>
+          <t>https://www.indeed.com/viewjob?jk=9f2a3e577d5623a4</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca3982c4f2be4e49</t>
+          <t>https://www.indeed.com/viewjob?jk=629b89e40e1e1bb5</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f2a3e577d5623a4</t>
+          <t>https://www.indeed.com/viewjob?jk=db6cf98112c1bc9f</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=629b89e40e1e1bb5</t>
+          <t>https://www.indeed.com/viewjob?jk=80b26c4d48449b15</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db6cf98112c1bc9f</t>
+          <t>https://www.indeed.com/viewjob?jk=83ba9763cad5f2f8</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80b26c4d48449b15</t>
+          <t>https://www.indeed.com/viewjob?jk=05460d1c364a2974</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83ba9763cad5f2f8</t>
+          <t>https://www.indeed.com/viewjob?jk=b01dc956f073aaf8</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05460d1c364a2974</t>
+          <t>https://www.indeed.com/viewjob?jk=807aad5f4045241d</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b01dc956f073aaf8</t>
+          <t>https://www.indeed.com/viewjob?jk=655ea21e25dbce1e</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=807aad5f4045241d</t>
+          <t>https://www.indeed.com/viewjob?jk=c46ceb995e304d69</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=655ea21e25dbce1e</t>
+          <t>https://www.indeed.com/viewjob?jk=7f29df76fe446a26</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c46ceb995e304d69</t>
+          <t>https://www.indeed.com/viewjob?jk=d6574f30d9366e40</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f29df76fe446a26</t>
+          <t>https://www.indeed.com/viewjob?jk=8536b186707d6516</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6574f30d9366e40</t>
+          <t>https://www.indeed.com/viewjob?jk=6a4c9600c5ead18d</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6691,24 +6691,24 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8536b186707d6516</t>
+          <t>https://www.indeed.com/viewjob?jk=78388f22c8e1c7cc</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python + Distributed systems)</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>H2O.ai</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -6726,24 +6726,24 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a4c9600c5ead18d</t>
+          <t>https://www.indeed.com/viewjob?jk=fe52f92aedddcda4</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python + Distributed systems)</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>H2O.ai</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -6761,24 +6761,24 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78388f22c8e1c7cc</t>
+          <t>https://www.indeed.com/viewjob?jk=0d2b8979a3b5f81b</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>H2O.ai</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -6796,24 +6796,24 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe52f92aedddcda4</t>
+          <t>https://www.indeed.com/viewjob?jk=d44e3274520e56d6</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Data Engineer - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>H2O.ai</t>
+          <t>WesBanco Bank, Inc.</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bowie, MD, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -6831,24 +6831,24 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d2b8979a3b5f81b</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a02cdb2b181be3</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Data Engineer - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>WesBanco Bank, Inc.</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Wheeling, WV, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -6866,24 +6866,24 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d44e3274520e56d6</t>
+          <t>https://www.indeed.com/viewjob?jk=fb6ee55d393e301c</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Software Developer - Database Engineer</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Centene</t>
+          <t>RAMSOFT</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6891,34 +6891,34 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, HBase, Scala, Snowflake, MySQL, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11d92da9c37770a7</t>
+          <t>https://www.indeed.com/viewjob?jk=4ce0ac7d0a937f32</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data &amp; Analytics</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>WesBanco Bank, Inc.</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Bowie, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -6936,24 +6936,24 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a02cdb2b181be3</t>
+          <t>https://www.indeed.com/viewjob?jk=e2b622ee37d8f63f</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data &amp; Analytics</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>WesBanco Bank, Inc.</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Wheeling, WV, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -6971,24 +6971,24 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb6ee55d393e301c</t>
+          <t>https://www.indeed.com/viewjob?jk=7ba10ede755adc88</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Software Developer - Database Engineer</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>RAMSOFT</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, HBase, Scala, Snowflake, MySQL, NoSQL, Data Modeling, Power BI</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ce0ac7d0a937f32</t>
+          <t>https://www.indeed.com/viewjob?jk=035e833a0affea06</t>
         </is>
       </c>
     </row>
@@ -7023,7 +7023,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2b622ee37d8f63f</t>
+          <t>https://www.indeed.com/viewjob?jk=34ea65634bf231fc</t>
         </is>
       </c>
     </row>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ba10ede755adc88</t>
+          <t>https://www.indeed.com/viewjob?jk=db2fffa7ab4fc3c6</t>
         </is>
       </c>
     </row>
@@ -7093,7 +7093,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=035e833a0affea06</t>
+          <t>https://www.indeed.com/viewjob?jk=726fca60377106fb</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -7146,7 +7146,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ea65634bf231fc</t>
+          <t>https://www.indeed.com/viewjob?jk=ae1bbd4c5bfc6dc1</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db2fffa7ab4fc3c6</t>
+          <t>https://www.indeed.com/viewjob?jk=7d44fb63e0c3570e</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=726fca60377106fb</t>
+          <t>https://www.indeed.com/viewjob?jk=ac1d3f6a217585b1</t>
         </is>
       </c>
     </row>
@@ -7233,7 +7233,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae1bbd4c5bfc6dc1</t>
+          <t>https://www.indeed.com/viewjob?jk=594c2209c74b60f3</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d44fb63e0c3570e</t>
+          <t>https://www.indeed.com/viewjob?jk=300951fa8a03d9ab</t>
         </is>
       </c>
     </row>
@@ -7303,7 +7303,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac1d3f6a217585b1</t>
+          <t>https://www.indeed.com/viewjob?jk=224f85378fe66226</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=594c2209c74b60f3</t>
+          <t>https://www.indeed.com/viewjob?jk=609ed15647075bf2</t>
         </is>
       </c>
     </row>
@@ -7373,7 +7373,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=300951fa8a03d9ab</t>
+          <t>https://www.indeed.com/viewjob?jk=f7da2bae9861dfa9</t>
         </is>
       </c>
     </row>
@@ -7408,7 +7408,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224f85378fe66226</t>
+          <t>https://www.indeed.com/viewjob?jk=9f44f95326fb5d8b</t>
         </is>
       </c>
     </row>
@@ -7443,7 +7443,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=609ed15647075bf2</t>
+          <t>https://www.indeed.com/viewjob?jk=f7f6777f3346c150</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7da2bae9861dfa9</t>
+          <t>https://www.indeed.com/viewjob?jk=99001099f8e56675</t>
         </is>
       </c>
     </row>
@@ -7513,7 +7513,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f44f95326fb5d8b</t>
+          <t>https://www.indeed.com/viewjob?jk=1d562fde2d3ab4ec</t>
         </is>
       </c>
     </row>
@@ -7548,7 +7548,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -7566,24 +7566,24 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7f6777f3346c150</t>
+          <t>https://www.indeed.com/viewjob?jk=49363af061447f75</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Centene</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -7591,42 +7591,42 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99001099f8e56675</t>
+          <t>https://www.indeed.com/viewjob?jk=11d92da9c37770a7</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -7636,32 +7636,32 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d562fde2d3ab4ec</t>
+          <t>https://www.indeed.com/viewjob?jk=ed1b9b0328def6aa</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>SAP NS2 Senior HANA Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -7671,24 +7671,24 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49363af061447f75</t>
+          <t>https://www.indeed.com/viewjob?jk=8999a6d9da6831ef</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D208" t="n">
@@ -7696,7 +7696,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -7706,24 +7706,24 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed1b9b0328def6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=2e60ff8bc1e60898</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>SAP NS2 Senior HANA Cloud DevOps Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Callaway Golf</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D209" t="n">
@@ -7731,34 +7731,34 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8999a6d9da6831ef</t>
+          <t>https://www.indeed.com/viewjob?jk=9ae59fccd3421dc5</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D210" t="n">
@@ -7766,34 +7766,34 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e60ff8bc1e60898</t>
+          <t>https://www.indeed.com/viewjob?jk=50c61f5469ce333f</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Callaway Golf</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D211" t="n">
@@ -7801,17 +7801,17 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ae59fccd3421dc5</t>
+          <t>https://www.indeed.com/viewjob?jk=4303ceb5e8c627c4</t>
         </is>
       </c>
     </row>
@@ -7828,7 +7828,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D212" t="n">
@@ -7846,24 +7846,24 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c61f5469ce333f</t>
+          <t>https://www.indeed.com/viewjob?jk=0c4db6d385ae6ea3</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Snowflake Administrator</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D213" t="n">
@@ -7871,34 +7871,34 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4303ceb5e8c627c4</t>
+          <t>https://www.indeed.com/viewjob?jk=085de5867e567658</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>LLM Application Engineer</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D214" t="n">
@@ -7906,34 +7906,34 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c4db6d385ae6ea3</t>
+          <t>https://www.indeed.com/viewjob?jk=5633278896c16c3b</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Snowflake Administrator</t>
+          <t>LLM Application Engineer</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D215" t="n">
@@ -7941,7 +7941,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
+          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -7951,24 +7951,24 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=085de5867e567658</t>
+          <t>https://www.indeed.com/viewjob?jk=4e56614bfb72e3b3</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>LLM Application Engineer</t>
+          <t>Product Architect Big Data Google Cloud Platform</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Reston Hospital Center - Reston</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D216" t="n">
@@ -7976,7 +7976,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
+          <t>Lambda, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Docker</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -7986,24 +7986,24 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5633278896c16c3b</t>
+          <t>https://www.indeed.com/viewjob?jk=cc86aeda9d2a8bcb</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>LLM Application Engineer</t>
+          <t>Product Architect Big Data Google Cloud Platform</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>St. David's HealthCare</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D217" t="n">
@@ -8011,7 +8011,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
+          <t>Lambda, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Docker</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e56614bfb72e3b3</t>
+          <t>https://www.indeed.com/viewjob?jk=613cb57ccf3485d6</t>
         </is>
       </c>
     </row>
@@ -8033,12 +8033,12 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Reston Hospital Center - Reston</t>
+          <t>HCA Florida West Tampa Hospital</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D218" t="n">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc86aeda9d2a8bcb</t>
+          <t>https://www.indeed.com/viewjob?jk=1ee6462dda08d180</t>
         </is>
       </c>
     </row>
@@ -8068,12 +8068,12 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>St. David's HealthCare</t>
+          <t>Medical City Healthcare</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D219" t="n">
@@ -8091,24 +8091,24 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613cb57ccf3485d6</t>
+          <t>https://www.indeed.com/viewjob?jk=ae11beaa0be9d78e</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Product Architect Big Data Google Cloud Platform</t>
+          <t>Senior Java Integration Consultant</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>HCA Florida West Tampa Hospital</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D220" t="n">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Docker</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -8126,24 +8126,24 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ee6462dda08d180</t>
+          <t>https://www.indeed.com/viewjob?jk=7439985744d87583</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Product Architect Big Data Google Cloud Platform</t>
+          <t>Senior Backend Engineer - Startup</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Medical City Healthcare</t>
+          <t>TALENThire</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D221" t="n">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Docker</t>
+          <t>AWS, Kinesis, GCP, Scala, Kafka, PostgreSQL, ELT, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -8161,7 +8161,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae11beaa0be9d78e</t>
+          <t>https://www.indeed.com/viewjob?jk=5f9f397d4f8fa7f1</t>
         </is>
       </c>
     </row>
@@ -8203,17 +8203,17 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Senior BI Developer - Investment Services</t>
+          <t>Sr. Full Stack Software Engineer (Onsite - San Diego)</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Carlsmed</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D223" t="n">
@@ -8221,7 +8221,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, Scala, PostgreSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6861136ad5c92fec</t>
+          <t>https://www.indeed.com/viewjob?jk=47ffb86f604e14df</t>
         </is>
       </c>
     </row>
@@ -8248,7 +8248,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D224" t="n">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0459e004fd012bc</t>
+          <t>https://www.indeed.com/viewjob?jk=6861136ad5c92fec</t>
         </is>
       </c>
     </row>
@@ -8283,7 +8283,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D225" t="n">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00bd0c85ee5af1cc</t>
+          <t>https://www.indeed.com/viewjob?jk=d0459e004fd012bc</t>
         </is>
       </c>
     </row>
@@ -8318,7 +8318,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D226" t="n">
@@ -8336,7 +8336,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a227aff44c18bd</t>
+          <t>https://www.indeed.com/viewjob?jk=00bd0c85ee5af1cc</t>
         </is>
       </c>
     </row>
@@ -8353,7 +8353,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D227" t="n">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f36e77b3ab4b1808</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a227aff44c18bd</t>
         </is>
       </c>
     </row>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D228" t="n">
@@ -8406,24 +8406,24 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b03b046a7e4b4373</t>
+          <t>https://www.indeed.com/viewjob?jk=f36e77b3ab4b1808</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Software Engineer (Onsite - San Diego)</t>
+          <t>Senior BI Developer - Investment Services</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Carlsmed</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D229" t="n">
@@ -8431,7 +8431,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, Scala, PostgreSQL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47ffb86f604e14df</t>
+          <t>https://www.indeed.com/viewjob?jk=b03b046a7e4b4373</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-06.xlsx
+++ b/results/job_matches_2026-03-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G235"/>
+  <dimension ref="A1:G219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>AV Safety Engineering Analytics AI/ML Engineer (GPSSC)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, MongoDB, NoSQL</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Dataflow, Spark, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60711b668acbd0b3</t>
+          <t>https://www.indeed.com/viewjob?jk=1b0a8c3e1d955c79</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Data Engineer – DE20260503002</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>eGrove Systems Corporation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, Spark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db8a35e2b334dacc</t>
+          <t>https://www.indeed.com/viewjob?jk=6093ead5fe385f5d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer – DE20260503002</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>eGrove Systems Corporation</t>
+          <t>Spire Energy</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, Spark, Scala, Oracle</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6093ead5fe385f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=df7314eb6a45de22</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Data Engineer - INDIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Spire Energy</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Prosper, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df7314eb6a45de22</t>
+          <t>https://www.indeed.com/viewjob?jk=f8eebff65cda31d0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Senior Analyst, Risk Data Engineering</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Lincoln Financial Group</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd9f71c3bc119fac</t>
+          <t>https://www.indeed.com/viewjob?jk=4c054d24fbe757c5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bc520629d7c84b2</t>
+          <t>https://www.indeed.com/viewjob?jk=fc1fd3766a845e85</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - INDIA</t>
+          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Prosper, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,67 +811,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8eebff65cda31d0</t>
+          <t>https://www.indeed.com/viewjob?jk=3c46cd564ba01b6c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Analyst, Risk Data Engineering</t>
+          <t>Senior Data Engineer (Python, Spark, AWS)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lincoln Financial Group</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c054d24fbe757c5</t>
+          <t>https://www.indeed.com/viewjob?jk=6d52dce08f82e688</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc1fd3766a845e85</t>
+          <t>https://www.indeed.com/viewjob?jk=175b82022b025c3d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c46cd564ba01b6c</t>
+          <t>https://www.indeed.com/viewjob?jk=32d044bc27a4af8a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python, Spark, AWS)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -946,12 +946,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d52dce08f82e688</t>
+          <t>https://www.indeed.com/viewjob?jk=aed60e56cae31294</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -981,12 +981,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=175b82022b025c3d</t>
+          <t>https://www.indeed.com/viewjob?jk=44f958ba0cbc0f43</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>JBS Dev</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32d044bc27a4af8a</t>
+          <t>https://www.indeed.com/viewjob?jk=49f6c2df00dd6e11</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (Costa Rica)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>JBS Dev</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aed60e56cae31294</t>
+          <t>https://www.indeed.com/viewjob?jk=05c819aa2a88511d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>System Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Systems Engineering Solutions Corporation</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,42 +1081,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44f958ba0cbc0f43</t>
+          <t>https://www.indeed.com/viewjob?jk=634fcd15ef04d7bf</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>JBS Dev</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49f6c2df00dd6e11</t>
+          <t>https://www.indeed.com/viewjob?jk=c7869ee373ec84ed</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Costa Rica)</t>
+          <t>CLOUD ENGINEER (AWS) (REMOTE/USA) - GDM (GRAY MEDIA GROUP)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>JBS Dev</t>
+          <t>GRAY MEDIA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05c819aa2a88511d</t>
+          <t>https://www.indeed.com/viewjob?jk=0beb94e2f1648144</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Systems Administrator, Cloud (GTA)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, AWS CodePipeline</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=094fcc384185954f</t>
+          <t>https://www.indeed.com/viewjob?jk=e83bd0fd320bb829</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>System Architect</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Systems Engineering Solutions Corporation</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=634fcd15ef04d7bf</t>
+          <t>https://www.indeed.com/viewjob?jk=105f562c4b87c831</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7869ee373ec84ed</t>
+          <t>https://www.indeed.com/viewjob?jk=56a2fccd9b09c654</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CLOUD ENGINEER (AWS) (REMOTE/USA) - GDM (GRAY MEDIA GROUP)</t>
+          <t>Senior Software Engineer - Clinical Systems (Lab Ops)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GRAY MEDIA</t>
+          <t>Caris Life Sciences</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, DynamoDB</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, GCP, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0beb94e2f1648144</t>
+          <t>https://www.indeed.com/viewjob?jk=fb8de235a110895a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Clinical Systems (Lab Ops)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Caris Life Sciences</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, GCP, Scala, PostgreSQL</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb8de235a110895a</t>
+          <t>https://www.indeed.com/viewjob?jk=afa51ac883fa48a6</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior BI Analyst</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e83bd0fd320bb829</t>
+          <t>https://www.indeed.com/viewjob?jk=ad414f3a9ab0a2bc</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Scala, Snowflake</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=105f562c4b87c831</t>
+          <t>https://www.indeed.com/viewjob?jk=459162c660bc8082</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Upstart</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Scala, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56a2fccd9b09c654</t>
+          <t>https://www.indeed.com/viewjob?jk=3dab96c17b78fc32</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Azure CI/CD Developer (FTE / Hybrid)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Oaks, PA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afa51ac883fa48a6</t>
+          <t>https://www.indeed.com/viewjob?jk=ffe5d7e4f5833213</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior BI Analyst</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad414f3a9ab0a2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=022d9e279d3ddb80</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=459162c660bc8082</t>
+          <t>https://www.indeed.com/viewjob?jk=f059a12d002721db</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Software Engineer III- Python/PySpark</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Upstart</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dab96c17b78fc32</t>
+          <t>https://www.indeed.com/viewjob?jk=82b1dd2ce5d3671a</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>REFRAME Platform Architect</t>
+          <t>Sr Software Development Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>North Carolina State University</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Vertex AI, Scala, NoSQL, MLOps, MLflow</t>
+          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22e67d3b77565a62</t>
+          <t>https://www.indeed.com/viewjob?jk=6efe960a7ab141ac</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Cloud Data Platform Administartor</t>
+          <t>SENIOR DATA ENGINEER</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>The Evolvers Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3909667b0ea7e00b</t>
+          <t>https://www.indeed.com/viewjob?jk=bee5a340a7f65e61</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Azure CI/CD Developer (FTE / Hybrid)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>BOULDER SCIENTIFIC CO</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Oaks, PA, US USA</t>
+          <t>Longmont, CO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,19 +1686,19 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffe5d7e4f5833213</t>
+          <t>https://www.indeed.com/viewjob?jk=9486135c47b58364</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1707,11 +1707,11 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, Splunk</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=022d9e279d3ddb80</t>
+          <t>https://www.indeed.com/viewjob?jk=ba5a22f3941b5b26</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Support Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f059a12d002721db</t>
+          <t>https://www.indeed.com/viewjob?jk=625bf5ef0b332ad3</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python/PySpark</t>
+          <t>AI Support Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b1dd2ce5d3671a</t>
+          <t>https://www.indeed.com/viewjob?jk=dd39a203b7587e31</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>Yusen Logistics</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6efe960a7ab141ac</t>
+          <t>https://www.indeed.com/viewjob?jk=7f92de33105c0bad</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SENIOR DATA ENGINEER</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Yusen Logistics</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, SQL Server, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bee5a340a7f65e61</t>
+          <t>https://www.indeed.com/viewjob?jk=772460af87c5b60c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BOULDER SCIENTIFIC CO</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Longmont, CO, US USA</t>
+          <t>Royal Oak, MI, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9486135c47b58364</t>
+          <t>https://www.indeed.com/viewjob?jk=6bb3681c5da818f2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba5a22f3941b5b26</t>
+          <t>https://www.indeed.com/viewjob?jk=343b07159d1b6928</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AI Support Engineer</t>
+          <t>Cloud Platform Engineer - Virtual</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=625bf5ef0b332ad3</t>
+          <t>https://www.indeed.com/viewjob?jk=a286c7ca862c4e1a</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AI Support Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>TWG Global AI</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,19 +2001,19 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd39a203b7587e31</t>
+          <t>https://www.indeed.com/viewjob?jk=edb6a72ac37333e2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Yusen Logistics</t>
+          <t>AllCloud</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2022,11 +2022,11 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kimball, ELT, dbt</t>
+          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f92de33105c0bad</t>
+          <t>https://www.indeed.com/viewjob?jk=49fcd1d4ac195cdf</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>IT BI Solutions Engineer, ES</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Yusen Logistics</t>
+          <t>Terex Corporation</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chattanooga, TN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kimball, ELT, dbt</t>
+          <t>AWS, Redshift, RDS, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=772460af87c5b60c</t>
+          <t>https://www.indeed.com/viewjob?jk=e8376f8e501b07a8</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Royal Oak, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, Step Functions, Medallion Architecture, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bb3681c5da818f2</t>
+          <t>https://www.indeed.com/viewjob?jk=83c604950fd47a32</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Platform Engineer-3</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=343b07159d1b6928</t>
+          <t>https://www.indeed.com/viewjob?jk=f753e538739bd670</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer - Virtual</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Alight Solutions</t>
+          <t>Advance Auto Parts</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,67 +2176,67 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a286c7ca862c4e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=3e2d8bc5a4c9174d</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Advisor Application Designer</t>
+          <t>Junior AI/MLOps Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>HJ Staffing</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, NoSQL, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a988f0c0aeaa0fa5</t>
+          <t>https://www.indeed.com/viewjob?jk=fe34817d3b1a40dc</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>TWG Global AI</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edb6a72ac37333e2</t>
+          <t>https://www.indeed.com/viewjob?jk=90d33ae33b62c3a0</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>AllCloud</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49fcd1d4ac195cdf</t>
+          <t>https://www.indeed.com/viewjob?jk=ec56a8fbf5328856</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>IT BI Solutions Engineer, ES</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Terex Corporation</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chattanooga, TN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8376f8e501b07a8</t>
+          <t>https://www.indeed.com/viewjob?jk=3d4834b7dd63e5a3</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Medallion Architecture, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions, AWS CodePipeline</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83c604950fd47a32</t>
+          <t>https://www.indeed.com/viewjob?jk=314cd9d2f824e302</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-3</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f753e538739bd670</t>
+          <t>https://www.indeed.com/viewjob?jk=ec0d14ba7f6cc782</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Advance Auto Parts</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e2d8bc5a4c9174d</t>
+          <t>https://www.indeed.com/viewjob?jk=cd9783225b203a0f</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, Power BI</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76cb3bc7e109c2ac</t>
+          <t>https://www.indeed.com/viewjob?jk=5fcdb3a443f803a9</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Kafka, Power BI</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8547c2271ca5aef</t>
+          <t>https://www.indeed.com/viewjob?jk=154ab74a68ca6406</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90d33ae33b62c3a0</t>
+          <t>https://www.indeed.com/viewjob?jk=31f45e1ed037bd50</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec56a8fbf5328856</t>
+          <t>https://www.indeed.com/viewjob?jk=f5d14ef4e88a3e5a</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,14 +2596,14 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d4834b7dd63e5a3</t>
+          <t>https://www.indeed.com/viewjob?jk=5f6ccf05e64c984b</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2631,14 +2631,14 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=314cd9d2f824e302</t>
+          <t>https://www.indeed.com/viewjob?jk=7b4b4f98c48563cd</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,14 +2666,14 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec0d14ba7f6cc782</t>
+          <t>https://www.indeed.com/viewjob?jk=c6c2c604bb89e64b</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,14 +2701,14 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd9783225b203a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=6e02fe4d607063c1</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,14 +2736,14 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fcdb3a443f803a9</t>
+          <t>https://www.indeed.com/viewjob?jk=9fbafb89e71fb39e</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,14 +2771,14 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=154ab74a68ca6406</t>
+          <t>https://www.indeed.com/viewjob?jk=e8ac438ef838975b</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,14 +2806,14 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31f45e1ed037bd50</t>
+          <t>https://www.indeed.com/viewjob?jk=74bd0f0f93d9a1a5</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5d14ef4e88a3e5a</t>
+          <t>https://www.indeed.com/viewjob?jk=4c53e85e359970d4</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f6ccf05e64c984b</t>
+          <t>https://www.indeed.com/viewjob?jk=0c433c70839583dc</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,14 +2911,14 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b4b4f98c48563cd</t>
+          <t>https://www.indeed.com/viewjob?jk=35e828bfc556b676</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6c2c604bb89e64b</t>
+          <t>https://www.indeed.com/viewjob?jk=3058b24332d31ded</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,14 +2981,14 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e02fe4d607063c1</t>
+          <t>https://www.indeed.com/viewjob?jk=10e23f958e9e8b09</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fbafb89e71fb39e</t>
+          <t>https://www.indeed.com/viewjob?jk=357547d890623cb5</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,14 +3051,14 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8ac438ef838975b</t>
+          <t>https://www.indeed.com/viewjob?jk=3884844e18945dee</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,14 +3086,14 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74bd0f0f93d9a1a5</t>
+          <t>https://www.indeed.com/viewjob?jk=17b7c64ee8dc67e0</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c53e85e359970d4</t>
+          <t>https://www.indeed.com/viewjob?jk=a75982d2aedba052</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,14 +3156,14 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c433c70839583dc</t>
+          <t>https://www.indeed.com/viewjob?jk=4b3d8d96e19fcbe6</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,14 +3191,14 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35e828bfc556b676</t>
+          <t>https://www.indeed.com/viewjob?jk=a60a56d62d329dea</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3058b24332d31ded</t>
+          <t>https://www.indeed.com/viewjob?jk=93902824d8ac4d0c</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10e23f958e9e8b09</t>
+          <t>https://www.indeed.com/viewjob?jk=088398b8f22d3683</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=357547d890623cb5</t>
+          <t>https://www.indeed.com/viewjob?jk=60f8a4d4b303056b</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3884844e18945dee</t>
+          <t>https://www.indeed.com/viewjob?jk=459cc0fec55fdc6f</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,14 +3366,14 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17b7c64ee8dc67e0</t>
+          <t>https://www.indeed.com/viewjob?jk=a58d376929282400</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a75982d2aedba052</t>
+          <t>https://www.indeed.com/viewjob?jk=521ae718282fb788</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b3d8d96e19fcbe6</t>
+          <t>https://www.indeed.com/viewjob?jk=559d1352317c1f33</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a60a56d62d329dea</t>
+          <t>https://www.indeed.com/viewjob?jk=361e87b55f4161f4</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93902824d8ac4d0c</t>
+          <t>https://www.indeed.com/viewjob?jk=32e0b2833cebefe3</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=088398b8f22d3683</t>
+          <t>https://www.indeed.com/viewjob?jk=9f5df27af3031e62</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Genentech</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Step Functions, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f8a4d4b303056b</t>
+          <t>https://www.indeed.com/viewjob?jk=d20f4b9e6a3cbb70</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Genentech</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Step Functions, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=459cc0fec55fdc6f</t>
+          <t>https://www.indeed.com/viewjob?jk=c89d6a7d2041de38</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Site Reliability Developer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,14 +3646,14 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a58d376929282400</t>
+          <t>https://www.indeed.com/viewjob?jk=3fedd79bbbee99bb</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Software Engineer II (Backend + Data pipelines)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3663,15 +3663,15 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,14 +3681,14 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=521ae718282fb788</t>
+          <t>https://www.indeed.com/viewjob?jk=7d4fca4ad337ae6c</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Software Engineer II (Backend + Data pipelines)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3698,15 +3698,15 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,14 +3716,14 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=559d1352317c1f33</t>
+          <t>https://www.indeed.com/viewjob?jk=1ae76b185563f91b</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Software Engineer II (Backend + Data pipelines)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3733,15 +3733,15 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,14 +3751,14 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=361e87b55f4161f4</t>
+          <t>https://www.indeed.com/viewjob?jk=ef2a73b324528506</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Software Engineer II (Backend + Data pipelines)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3768,15 +3768,15 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,14 +3786,14 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32e0b2833cebefe3</t>
+          <t>https://www.indeed.com/viewjob?jk=92aaafaf1efb9ec4</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Software Engineer II (Backend + Data pipelines)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3803,15 +3803,15 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f5df27af3031e62</t>
+          <t>https://www.indeed.com/viewjob?jk=c9981aefe519f0cd</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Junior AI/MLOps Engineer</t>
+          <t>Software Engineer II (Backend + Data pipelines)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, NoSQL, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe34817d3b1a40dc</t>
+          <t>https://www.indeed.com/viewjob?jk=fce2095df8206466</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Software Engineer II (Backend + Data pipelines)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Kubernetes, Airflow</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d20f4b9e6a3cbb70</t>
+          <t>https://www.indeed.com/viewjob?jk=ee34633b7838a9b3</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Software Engineer II (Backend + Data pipelines)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Kubernetes, Airflow</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c89d6a7d2041de38</t>
+          <t>https://www.indeed.com/viewjob?jk=cc57f588c654f1cd</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II (Backend + Data pipelines)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,19 +3961,19 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38b673fd36dffa19</t>
+          <t>https://www.indeed.com/viewjob?jk=5aaeb4c54cdfa77e</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Developer</t>
+          <t>Software Engineer II (Backend + Data pipelines)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fedd79bbbee99bb</t>
+          <t>https://www.indeed.com/viewjob?jk=eb06d74f6367bb04</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4fca4ad337ae6c</t>
+          <t>https://www.indeed.com/viewjob?jk=49799e02e3e0a925</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ae76b185563f91b</t>
+          <t>https://www.indeed.com/viewjob?jk=52ff9083bc8990ce</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef2a73b324528506</t>
+          <t>https://www.indeed.com/viewjob?jk=66f89817131cfa0d</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92aaafaf1efb9ec4</t>
+          <t>https://www.indeed.com/viewjob?jk=cdb757efdefad0ca</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9981aefe519f0cd</t>
+          <t>https://www.indeed.com/viewjob?jk=57fc4e97a319b123</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fce2095df8206466</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fcc67143e3ff8a</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee34633b7838a9b3</t>
+          <t>https://www.indeed.com/viewjob?jk=5dad4bf1e950e1c9</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc57f588c654f1cd</t>
+          <t>https://www.indeed.com/viewjob?jk=0f9ed5d278a8086d</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5aaeb4c54cdfa77e</t>
+          <t>https://www.indeed.com/viewjob?jk=8809421834292084</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend + Data pipelines)</t>
+          <t>Senior Digital Engineer – Full Stack &amp; Systems Architecture</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Berkeley, MO, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb06d74f6367bb04</t>
+          <t>https://www.indeed.com/viewjob?jk=5360d83db3589d68</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend + Data pipelines)</t>
+          <t>Senior Digital Engineer – Full Stack &amp; Systems Architecture</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49799e02e3e0a925</t>
+          <t>https://www.indeed.com/viewjob?jk=12a4a8cde3354706</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend + Data pipelines)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>LERETA, LLC</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Pomona, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52ff9083bc8990ce</t>
+          <t>https://www.indeed.com/viewjob?jk=ad5d067156fc62f1</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend + Data pipelines)</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Hard Rock International</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Hollywood, FL, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, Snowflake, PostgreSQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f89817131cfa0d</t>
+          <t>https://www.indeed.com/viewjob?jk=169d4a00d377fdae</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend + Data pipelines)</t>
+          <t>Senior Application Platform Architect - 6163848</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Hadoop, Scala, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdb757efdefad0ca</t>
+          <t>https://www.indeed.com/viewjob?jk=7ea7fc0fae83610a</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend + Data pipelines)</t>
+          <t>Senior LLM Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, Azure, Vertex AI, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57fc4e97a319b123</t>
+          <t>https://www.indeed.com/viewjob?jk=109c9c4a6595ba95</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend + Data pipelines)</t>
+          <t>Senior LLM Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, Azure, Vertex AI, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,14 +4556,14 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fcc67143e3ff8a</t>
+          <t>https://www.indeed.com/viewjob?jk=8723fa94634ae387</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend + Data pipelines)</t>
+          <t>Senior Machine Learning Engineer (Search)</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,14 +4591,14 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dad4bf1e950e1c9</t>
+          <t>https://www.indeed.com/viewjob?jk=cff2f5a9dcacb28f</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend + Data pipelines)</t>
+          <t>Senior Machine Learning Engineer (Search)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,14 +4626,14 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f9ed5d278a8086d</t>
+          <t>https://www.indeed.com/viewjob?jk=3216b4c3b2c151f8</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend + Data pipelines)</t>
+          <t>Senior Machine Learning Engineer (Search)</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8809421834292084</t>
+          <t>https://www.indeed.com/viewjob?jk=a0fc0424a2f74ea8</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Sr. Business Development Consultant</t>
+          <t>Senior Machine Learning Engineer (Search)</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1da3fc8da87b47c9</t>
+          <t>https://www.indeed.com/viewjob?jk=c0ff98f788ff107b</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Senior Machine Learning Engineer (Search)</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22b3d9d74319cb4d</t>
+          <t>https://www.indeed.com/viewjob?jk=0442372baf83ee82</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Senior Machine Learning Engineer (Search)</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c6fa42304d7e851</t>
+          <t>https://www.indeed.com/viewjob?jk=fe6ea91421159ece</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Senior Machine Learning Engineer (Search)</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf51adf8a1f9c98</t>
+          <t>https://www.indeed.com/viewjob?jk=aecbf4d450f1441b</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ML Infrastructure Architect</t>
+          <t>Senior Machine Learning Engineer (Search)</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfd0ac225b61c5b4</t>
+          <t>https://www.indeed.com/viewjob?jk=31056dc236b5ce67</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Selenium Automation tester</t>
+          <t>Senior Machine Learning Engineer (Search)</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Maven</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc0fe4c47cda2838</t>
+          <t>https://www.indeed.com/viewjob?jk=eca84bb19e700f2b</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Applied Machine Learning Engineer (All Levels)</t>
+          <t>Senior Machine Learning Engineer (Search)</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, ELT, MLflow, CI/CD, Terraform, Docker, Git</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1910fa4b9572adb</t>
+          <t>https://www.indeed.com/viewjob?jk=7401294591da0c90</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cff2f5a9dcacb28f</t>
+          <t>https://www.indeed.com/viewjob?jk=5eed535b1fcfea26</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3216b4c3b2c151f8</t>
+          <t>https://www.indeed.com/viewjob?jk=b29243583190aa6a</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0fc0424a2f74ea8</t>
+          <t>https://www.indeed.com/viewjob?jk=1c0d7ebd3a2ee36f</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0ff98f788ff107b</t>
+          <t>https://www.indeed.com/viewjob?jk=28e3397c0e70024e</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0442372baf83ee82</t>
+          <t>https://www.indeed.com/viewjob?jk=35f50cc085f1bbd9</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe6ea91421159ece</t>
+          <t>https://www.indeed.com/viewjob?jk=72be3b8aba169a59</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aecbf4d450f1441b</t>
+          <t>https://www.indeed.com/viewjob?jk=b61af8e418fcf231</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31056dc236b5ce67</t>
+          <t>https://www.indeed.com/viewjob?jk=552a8172dcf24a7a</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,32 +5221,32 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eca84bb19e700f2b</t>
+          <t>https://www.indeed.com/viewjob?jk=4fa51ea3c52768d7</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Search)</t>
+          <t>Software Engineering Intern – Data Engineering (Cloud &amp; Streaming)</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>NextPower</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,32 +5256,32 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7401294591da0c90</t>
+          <t>https://www.indeed.com/viewjob?jk=28e588be3c533008</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Search)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Power BI, Tableau, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,32 +5291,32 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eed535b1fcfea26</t>
+          <t>https://www.indeed.com/viewjob?jk=aaf9596bf4159924</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Search)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Power BI, Tableau, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,67 +5326,67 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29243583190aa6a</t>
+          <t>https://www.indeed.com/viewjob?jk=ab90611f6b141379</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Search)</t>
+          <t>Senior Software Engineer, Back End (Python)</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c0d7ebd3a2ee36f</t>
+          <t>https://www.indeed.com/viewjob?jk=f65ac6c3f1cf1646</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Search)</t>
+          <t>Senior Cloud Systems Engineer (Databricks Administrator)</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Providge Consulting</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,32 +5396,32 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e3397c0e70024e</t>
+          <t>https://www.indeed.com/viewjob?jk=e094ab218ebab2ed</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Search)</t>
+          <t>Sr. ETL/SQL Engineer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Capgemini Government Solutions</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,32 +5431,32 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35f50cc085f1bbd9</t>
+          <t>https://www.indeed.com/viewjob?jk=724ffe7f1d3da135</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Search)</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Space Telescope Science Institute</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, S3, ECS, IAM, Hive, Scala, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,32 +5466,32 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72be3b8aba169a59</t>
+          <t>https://www.indeed.com/viewjob?jk=6055970eb603df79</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Search)</t>
+          <t>AI Engineer III</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>CareSource</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>API Gateway, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,32 +5501,32 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b61af8e418fcf231</t>
+          <t>https://www.indeed.com/viewjob?jk=640c68fe3716b1e6</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Search)</t>
+          <t>Sr Software Engineer (Site Reliability Engineering) (2026-10114)</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, MySQL, Splunk</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,32 +5536,32 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=552a8172dcf24a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=b5ab755eddd54b18</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Search)</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>H2O.ai</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,32 +5571,32 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fa51ea3c52768d7</t>
+          <t>https://www.indeed.com/viewjob?jk=fe52f92aedddcda4</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Senior Application Platform Architect - 6163848</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>H2O.ai</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Hadoop, Scala, PostgreSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,32 +5606,32 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ea7fc0fae83610a</t>
+          <t>https://www.indeed.com/viewjob?jk=0d2b8979a3b5f81b</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>LERETA, LLC</t>
+          <t>WesBanco Bank, Inc.</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Pomona, CA, US USA</t>
+          <t>Bowie, MD, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,32 +5641,32 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad5d067156fc62f1</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a02cdb2b181be3</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Senior Data Engineer - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Hard Rock International</t>
+          <t>WesBanco Bank, Inc.</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Hollywood, FL, US USA</t>
+          <t>Wheeling, WV, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, Snowflake, PostgreSQL, Cassandra, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,32 +5676,32 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=169d4a00d377fdae</t>
+          <t>https://www.indeed.com/viewjob?jk=fb6ee55d393e301c</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Senior LLM Engineer</t>
+          <t>Software Developer - Database Engineer</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RAMSOFT</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, MLOps</t>
+          <t>AWS, RDS, Azure, HBase, Scala, Snowflake, MySQL, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5711,32 +5711,32 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109c9c4a6595ba95</t>
+          <t>https://www.indeed.com/viewjob?jk=4ce0ac7d0a937f32</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Senior LLM Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5746,24 +5746,24 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8723fa94634ae387</t>
+          <t>https://www.indeed.com/viewjob?jk=d44e3274520e56d6</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Software Engineering Intern – Data Engineering (Cloud &amp; Streaming)</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>NextPower</t>
+          <t>Centene</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,34 +5771,34 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e588be3c533008</t>
+          <t>https://www.indeed.com/viewjob?jk=11d92da9c37770a7</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Power BI, Tableau, MLOps, MLflow</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5816,24 +5816,24 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaf9596bf4159924</t>
+          <t>https://www.indeed.com/viewjob?jk=e2b622ee37d8f63f</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Power BI, Tableau, MLOps, MLflow</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -5851,24 +5851,24 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab90611f6b141379</t>
+          <t>https://www.indeed.com/viewjob?jk=7ba10ede755adc88</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Python)</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,34 +5876,34 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f65ac6c3f1cf1646</t>
+          <t>https://www.indeed.com/viewjob?jk=035e833a0affea06</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Senior Cloud Systems Engineer (Databricks Administrator)</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Providge Consulting</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Scala, ELT, CI/CD</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5921,24 +5921,24 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e094ab218ebab2ed</t>
+          <t>https://www.indeed.com/viewjob?jk=34ea65634bf231fc</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Sr. ETL/SQL Engineer</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Capgemini Government Solutions</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5956,24 +5956,24 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724ffe7f1d3da135</t>
+          <t>https://www.indeed.com/viewjob?jk=db2fffa7ab4fc3c6</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Space Telescope Science Institute</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Hive, Scala, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5991,24 +5991,24 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6055970eb603df79</t>
+          <t>https://www.indeed.com/viewjob?jk=726fca60377106fb</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>AI Engineer III</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>CareSource</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6026,14 +6026,14 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=640c68fe3716b1e6</t>
+          <t>https://www.indeed.com/viewjob?jk=ae1bbd4c5bfc6dc1</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python + Distributed systems)</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,14 +6061,14 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4af4ef5dfeb0026</t>
+          <t>https://www.indeed.com/viewjob?jk=7d44fb63e0c3570e</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python + Distributed systems)</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6096,14 +6096,14 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c116b8acf805f138</t>
+          <t>https://www.indeed.com/viewjob?jk=ac1d3f6a217585b1</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python + Distributed systems)</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -6113,7 +6113,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6131,14 +6131,14 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f996f9a35281bba7</t>
+          <t>https://www.indeed.com/viewjob?jk=594c2209c74b60f3</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python + Distributed systems)</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6166,14 +6166,14 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca3982c4f2be4e49</t>
+          <t>https://www.indeed.com/viewjob?jk=300951fa8a03d9ab</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python + Distributed systems)</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6201,14 +6201,14 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f2a3e577d5623a4</t>
+          <t>https://www.indeed.com/viewjob?jk=224f85378fe66226</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python + Distributed systems)</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6236,14 +6236,14 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=629b89e40e1e1bb5</t>
+          <t>https://www.indeed.com/viewjob?jk=609ed15647075bf2</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python + Distributed systems)</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6271,14 +6271,14 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db6cf98112c1bc9f</t>
+          <t>https://www.indeed.com/viewjob?jk=f7da2bae9861dfa9</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python + Distributed systems)</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6306,14 +6306,14 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80b26c4d48449b15</t>
+          <t>https://www.indeed.com/viewjob?jk=9f44f95326fb5d8b</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python + Distributed systems)</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6341,14 +6341,14 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83ba9763cad5f2f8</t>
+          <t>https://www.indeed.com/viewjob?jk=f7f6777f3346c150</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python + Distributed systems)</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -6358,7 +6358,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6376,14 +6376,14 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05460d1c364a2974</t>
+          <t>https://www.indeed.com/viewjob?jk=99001099f8e56675</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python + Distributed systems)</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6411,14 +6411,14 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b01dc956f073aaf8</t>
+          <t>https://www.indeed.com/viewjob?jk=1d562fde2d3ab4ec</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python + Distributed systems)</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -6428,7 +6428,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=807aad5f4045241d</t>
+          <t>https://www.indeed.com/viewjob?jk=49363af061447f75</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=655ea21e25dbce1e</t>
+          <t>https://www.indeed.com/viewjob?jk=c4af4ef5dfeb0026</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c46ceb995e304d69</t>
+          <t>https://www.indeed.com/viewjob?jk=c116b8acf805f138</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f29df76fe446a26</t>
+          <t>https://www.indeed.com/viewjob?jk=f996f9a35281bba7</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6574f30d9366e40</t>
+          <t>https://www.indeed.com/viewjob?jk=ca3982c4f2be4e49</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8536b186707d6516</t>
+          <t>https://www.indeed.com/viewjob?jk=9f2a3e577d5623a4</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a4c9600c5ead18d</t>
+          <t>https://www.indeed.com/viewjob?jk=629b89e40e1e1bb5</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6691,24 +6691,24 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78388f22c8e1c7cc</t>
+          <t>https://www.indeed.com/viewjob?jk=db6cf98112c1bc9f</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Software Engineer (Python + Distributed systems)</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>H2O.ai</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -6726,24 +6726,24 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe52f92aedddcda4</t>
+          <t>https://www.indeed.com/viewjob?jk=80b26c4d48449b15</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Software Engineer (Python + Distributed systems)</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>H2O.ai</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -6761,24 +6761,24 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d2b8979a3b5f81b</t>
+          <t>https://www.indeed.com/viewjob?jk=83ba9763cad5f2f8</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Software Engineer (Python + Distributed systems)</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -6796,24 +6796,24 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d44e3274520e56d6</t>
+          <t>https://www.indeed.com/viewjob?jk=05460d1c364a2974</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data &amp; Analytics</t>
+          <t>Senior Software Engineer (Python + Distributed systems)</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>WesBanco Bank, Inc.</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Bowie, MD, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -6831,24 +6831,24 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a02cdb2b181be3</t>
+          <t>https://www.indeed.com/viewjob?jk=b01dc956f073aaf8</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data &amp; Analytics</t>
+          <t>Senior Software Engineer (Python + Distributed systems)</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>WesBanco Bank, Inc.</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Wheeling, WV, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -6866,24 +6866,24 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb6ee55d393e301c</t>
+          <t>https://www.indeed.com/viewjob?jk=807aad5f4045241d</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Software Developer - Database Engineer</t>
+          <t>Senior Software Engineer (Python + Distributed systems)</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>RAMSOFT</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, HBase, Scala, Snowflake, MySQL, NoSQL, Data Modeling, Power BI</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -6901,14 +6901,14 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ce0ac7d0a937f32</t>
+          <t>https://www.indeed.com/viewjob?jk=655ea21e25dbce1e</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>Senior Software Engineer (Python + Distributed systems)</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6936,14 +6936,14 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2b622ee37d8f63f</t>
+          <t>https://www.indeed.com/viewjob?jk=c46ceb995e304d69</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>Senior Software Engineer (Python + Distributed systems)</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -6953,7 +6953,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6971,14 +6971,14 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ba10ede755adc88</t>
+          <t>https://www.indeed.com/viewjob?jk=7f29df76fe446a26</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>Senior Software Engineer (Python + Distributed systems)</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -6988,7 +6988,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -7006,14 +7006,14 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=035e833a0affea06</t>
+          <t>https://www.indeed.com/viewjob?jk=d6574f30d9366e40</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>Senior Software Engineer (Python + Distributed systems)</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -7023,7 +7023,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -7041,14 +7041,14 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ea65634bf231fc</t>
+          <t>https://www.indeed.com/viewjob?jk=8536b186707d6516</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>Senior Software Engineer (Python + Distributed systems)</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -7058,7 +7058,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -7076,14 +7076,14 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db2fffa7ab4fc3c6</t>
+          <t>https://www.indeed.com/viewjob?jk=6a4c9600c5ead18d</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>Senior Software Engineer (Python + Distributed systems)</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -7093,7 +7093,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -7111,32 +7111,32 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=726fca60377106fb</t>
+          <t>https://www.indeed.com/viewjob?jk=78388f22c8e1c7cc</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>AV Safety Engineering Analytics Simulation Engineer (GPSSC)</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -7146,67 +7146,67 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae1bbd4c5bfc6dc1</t>
+          <t>https://www.indeed.com/viewjob?jk=4b9eec46bbab109b</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>Data Engineer-Remote</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Mutual of Omaha</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, Glue, RDS, Scala, Snowflake, SQL Server, MongoDB, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d44fb63e0c3570e</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc1efbee94e32a9</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -7216,32 +7216,32 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac1d3f6a217585b1</t>
+          <t>https://www.indeed.com/viewjob?jk=ed1b9b0328def6aa</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>SAP NS2 Senior HANA Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -7251,32 +7251,32 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=594c2209c74b60f3</t>
+          <t>https://www.indeed.com/viewjob?jk=8999a6d9da6831ef</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -7286,67 +7286,67 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=300951fa8a03d9ab</t>
+          <t>https://www.indeed.com/viewjob?jk=2e60ff8bc1e60898</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Callaway Golf</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224f85378fe66226</t>
+          <t>https://www.indeed.com/viewjob?jk=9ae59fccd3421dc5</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>Senior AI/ML Scientist</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -7356,32 +7356,32 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=609ed15647075bf2</t>
+          <t>https://www.indeed.com/viewjob?jk=300d4ca14be662c3</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>AV Safety Engineering Analytics Engineer (GPSSC)</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -7391,32 +7391,32 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7da2bae9861dfa9</t>
+          <t>https://www.indeed.com/viewjob?jk=60da6f50aaadfe48</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>Visualization Engineer</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>RDS, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -7426,102 +7426,102 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f44f95326fb5d8b</t>
+          <t>https://www.indeed.com/viewjob?jk=b28a6ad6f45c5471</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>Product Engineer</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>ALTIMATE</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, ECS, RDS, Spark, Scala, PostgreSQL, dbt, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7f6777f3346c150</t>
+          <t>https://www.indeed.com/viewjob?jk=95f4b6534ba4c3cd</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>SENIOR DATA ENGINEER (REMOTE)</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Morrison Healthcare</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Snowflake, ETL, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99001099f8e56675</t>
+          <t>https://www.indeed.com/viewjob?jk=d530073f998c3698</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>Snowflake Administrator</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -7531,32 +7531,32 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d562fde2d3ab4ec</t>
+          <t>https://www.indeed.com/viewjob?jk=085de5867e567658</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>LLM Application Engineer</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -7566,59 +7566,59 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49363af061447f75</t>
+          <t>https://www.indeed.com/viewjob?jk=5633278896c16c3b</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>LLM Application Engineer</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Centene</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11d92da9c37770a7</t>
+          <t>https://www.indeed.com/viewjob?jk=4e56614bfb72e3b3</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Teradata Developer</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -7626,34 +7626,34 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed1b9b0328def6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=7fddb4ec439f1237</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>SAP NS2 Senior HANA Cloud DevOps Engineer</t>
+          <t>Senior BI Developer - Investment Services</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D207" t="n">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -7671,24 +7671,24 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8999a6d9da6831ef</t>
+          <t>https://www.indeed.com/viewjob?jk=6861136ad5c92fec</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior BI Developer - Investment Services</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D208" t="n">
@@ -7696,7 +7696,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -7706,24 +7706,24 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e60ff8bc1e60898</t>
+          <t>https://www.indeed.com/viewjob?jk=d0459e004fd012bc</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior BI Developer - Investment Services</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Callaway Golf</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D209" t="n">
@@ -7731,34 +7731,34 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ae59fccd3421dc5</t>
+          <t>https://www.indeed.com/viewjob?jk=00bd0c85ee5af1cc</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior BI Developer - Investment Services</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D210" t="n">
@@ -7766,34 +7766,34 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c61f5469ce333f</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a227aff44c18bd</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior BI Developer - Investment Services</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D211" t="n">
@@ -7801,34 +7801,34 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4303ceb5e8c627c4</t>
+          <t>https://www.indeed.com/viewjob?jk=f36e77b3ab4b1808</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior BI Developer - Investment Services</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D212" t="n">
@@ -7836,34 +7836,34 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c4db6d385ae6ea3</t>
+          <t>https://www.indeed.com/viewjob?jk=b03b046a7e4b4373</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Snowflake Administrator</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D213" t="n">
@@ -7871,34 +7871,34 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=085de5867e567658</t>
+          <t>https://www.indeed.com/viewjob?jk=50c61f5469ce333f</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>LLM Application Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D214" t="n">
@@ -7906,34 +7906,34 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5633278896c16c3b</t>
+          <t>https://www.indeed.com/viewjob?jk=4303ceb5e8c627c4</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>LLM Application Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D215" t="n">
@@ -7941,34 +7941,34 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e56614bfb72e3b3</t>
+          <t>https://www.indeed.com/viewjob?jk=0c4db6d385ae6ea3</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Product Architect Big Data Google Cloud Platform</t>
+          <t>Sr. Full Stack Software Engineer (Onsite - San Diego)</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Reston Hospital Center - Reston</t>
+          <t>Carlsmed</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D216" t="n">
@@ -7976,7 +7976,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, Scala, PostgreSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -7986,24 +7986,24 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc86aeda9d2a8bcb</t>
+          <t>https://www.indeed.com/viewjob?jk=47ffb86f604e14df</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Product Architect Big Data Google Cloud Platform</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>St. David's HealthCare</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D217" t="n">
@@ -8011,7 +8011,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -8021,24 +8021,24 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=613cb57ccf3485d6</t>
+          <t>https://www.indeed.com/viewjob?jk=c70cf8723aeaf7eb</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Product Architect Big Data Google Cloud Platform</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>HCA Florida West Tampa Hospital</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D218" t="n">
@@ -8046,7 +8046,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -8056,24 +8056,24 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ee6462dda08d180</t>
+          <t>https://www.indeed.com/viewjob?jk=6f106012aaf32c49</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Product Architect Big Data Google Cloud Platform</t>
+          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Medical City Healthcare</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D219" t="n">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Lambda, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -8091,567 +8091,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae11beaa0be9d78e</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>Senior Java Integration Consultant</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>Fiserv</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>Springfield, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D220" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7439985744d87583</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer - Startup</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>TALENThire</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D221" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, GCP, Scala, Kafka, PostgreSQL, ELT, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5f9f397d4f8fa7f1</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>SENIOR DATA ENGINEER (REMOTE)</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>Morrison Healthcare</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>IL, US USA</t>
-        </is>
-      </c>
-      <c r="D222" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Snowflake, ETL, dbt, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F222" t="inlineStr">
-        <is>
-          <t>2026-01-05</t>
-        </is>
-      </c>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d530073f998c3698</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>Sr. Full Stack Software Engineer (Onsite - San Diego)</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>Carlsmed</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>Carlsbad, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D223" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, Scala, PostgreSQL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F223" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=47ffb86f604e14df</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>Senior BI Developer - Investment Services</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>U.S. Bank</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D224" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F224" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6861136ad5c92fec</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>Senior BI Developer - Investment Services</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>U.S. Bank</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D225" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F225" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G225" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d0459e004fd012bc</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>Senior BI Developer - Investment Services</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>U.S. Bank</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D226" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=00bd0c85ee5af1cc</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>Senior BI Developer - Investment Services</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>U.S. Bank</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>Saint Paul, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D227" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F227" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a227aff44c18bd</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>Senior BI Developer - Investment Services</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>U.S. Bank</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>Milwaukee, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D228" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F228" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G228" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f36e77b3ab4b1808</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>Senior BI Developer - Investment Services</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>U.S. Bank</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>Hopkins, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D229" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E229" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F229" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G229" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b03b046a7e4b4373</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>Engineer II- Java</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D230" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F230" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G230" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c70cf8723aeaf7eb</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>Engineer II- Java</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D231" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F231" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G231" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6f106012aaf32c49</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>Teradata Developer</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D232" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E232" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F232" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G232" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7fddb4ec439f1237</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>CrowdStrike</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>Sunnyvale, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D233" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E233" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F233" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G233" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=a1593d7242ad3914</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B234" t="inlineStr">
-        <is>
-          <t>Walkme</t>
-        </is>
-      </c>
-      <c r="C234" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D234" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E234" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F234" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G234" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=00aac4a1caed5c4b</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B235" t="inlineStr">
-        <is>
-          <t>Walkme</t>
-        </is>
-      </c>
-      <c r="C235" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D235" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, MySQL, MongoDB, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F235" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G235" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=36669407e627b585</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-06.xlsx
+++ b/results/job_matches_2026-03-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G219"/>
+  <dimension ref="A1:G221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer - Sr. Consultant level - DevOps</t>
+          <t>Cloud ETL Software Engineer III</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Databricks, Hadoop, Hive, HBase, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28ca6064f69a534e</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ae806cfdce5e5c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (React + Node.js)-5</t>
+          <t>Software Engineer - Sr. Consultant level - DevOps</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,42 +556,42 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01d5f2b9fa96100b</t>
+          <t>https://www.indeed.com/viewjob?jk=28ca6064f69a534e</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AV Safety Engineering Analytics AI/ML Engineer (GPSSC)</t>
+          <t>Full Stack Engineer (React + Node.js)-5</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>20.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Dataflow, Spark, PySpark</t>
+          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b0a8c3e1d955c79</t>
+          <t>https://www.indeed.com/viewjob?jk=01d5f2b9fa96100b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer – DE20260503002</t>
+          <t>AV Safety Engineering Analytics AI/ML Engineer (GPSSC)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>eGrove Systems Corporation</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, Spark, Scala, Oracle</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Dataflow, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6093ead5fe385f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=1b0a8c3e1d955c79</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Engineer – DE20260503002</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Spire Energy</t>
+          <t>eGrove Systems Corporation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, Spark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df7314eb6a45de22</t>
+          <t>https://www.indeed.com/viewjob?jk=6093ead5fe385f5d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - INDIA</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Spire Energy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Prosper, TX, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8eebff65cda31d0</t>
+          <t>https://www.indeed.com/viewjob?jk=df7314eb6a45de22</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Analyst, Risk Data Engineering</t>
+          <t>Senior Data Engineer - INDIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lincoln Financial Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Prosper, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c054d24fbe757c5</t>
+          <t>https://www.indeed.com/viewjob?jk=f8eebff65cda31d0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Analyst, Risk Data Engineering</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Lincoln Financial Group</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,42 +766,42 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc1fd3766a845e85</t>
+          <t>https://www.indeed.com/viewjob?jk=4c054d24fbe757c5</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c46cd564ba01b6c</t>
+          <t>https://www.indeed.com/viewjob?jk=fc1fd3766a845e85</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python, Spark, AWS)</t>
+          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -846,14 +846,14 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d52dce08f82e688</t>
+          <t>https://www.indeed.com/viewjob?jk=3c46cd564ba01b6c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (Python, Spark, AWS)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=175b82022b025c3d</t>
+          <t>https://www.indeed.com/viewjob?jk=6d52dce08f82e688</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32d044bc27a4af8a</t>
+          <t>https://www.indeed.com/viewjob?jk=175b82022b025c3d</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>JBS Dev</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aed60e56cae31294</t>
+          <t>https://www.indeed.com/viewjob?jk=49f6c2df00dd6e11</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (Costa Rica)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>JBS Dev</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,17 +976,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44f958ba0cbc0f43</t>
+          <t>https://www.indeed.com/viewjob?jk=05c819aa2a88511d</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JBS Dev</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49f6c2df00dd6e11</t>
+          <t>https://www.indeed.com/viewjob?jk=32d044bc27a4af8a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Costa Rica)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JBS Dev</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05c819aa2a88511d</t>
+          <t>https://www.indeed.com/viewjob?jk=aed60e56cae31294</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>System Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Systems Engineering Solutions Corporation</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,42 +1081,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=634fcd15ef04d7bf</t>
+          <t>https://www.indeed.com/viewjob?jk=44f958ba0cbc0f43</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>System Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Systems Engineering Solutions Corporation</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7869ee373ec84ed</t>
+          <t>https://www.indeed.com/viewjob?jk=634fcd15ef04d7bf</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CLOUD ENGINEER (AWS) (REMOTE/USA) - GDM (GRAY MEDIA GROUP)</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GRAY MEDIA</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, DynamoDB</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0beb94e2f1648144</t>
+          <t>https://www.indeed.com/viewjob?jk=c7869ee373ec84ed</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>CLOUD ENGINEER (AWS) (REMOTE/USA) - GDM (GRAY MEDIA GROUP)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>GRAY MEDIA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e83bd0fd320bb829</t>
+          <t>https://www.indeed.com/viewjob?jk=0beb94e2f1648144</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Engineer - Clinical Systems (Lab Ops)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Caris Life Sciences</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, GCP, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=105f562c4b87c831</t>
+          <t>https://www.indeed.com/viewjob?jk=fb8de235a110895a</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56a2fccd9b09c654</t>
+          <t>https://www.indeed.com/viewjob?jk=e83bd0fd320bb829</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Clinical Systems (Lab Ops)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Caris Life Sciences</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, GCP, Scala, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb8de235a110895a</t>
+          <t>https://www.indeed.com/viewjob?jk=105f562c4b87c831</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afa51ac883fa48a6</t>
+          <t>https://www.indeed.com/viewjob?jk=56a2fccd9b09c654</t>
         </is>
       </c>
     </row>
@@ -1413,17 +1413,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Upstart</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dab96c17b78fc32</t>
+          <t>https://www.indeed.com/viewjob?jk=afa51ac883fa48a6</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Azure CI/CD Developer (FTE / Hybrid)</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Upstart</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Oaks, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffe5d7e4f5833213</t>
+          <t>https://www.indeed.com/viewjob?jk=3dab96c17b78fc32</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Software Engineer III - AI/ML</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,42 +1501,42 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, Splunk</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=022d9e279d3ddb80</t>
+          <t>https://www.indeed.com/viewjob?jk=fcd181016bc08a7a</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure CI/CD Developer (FTE / Hybrid)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oaks, PA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f059a12d002721db</t>
+          <t>https://www.indeed.com/viewjob?jk=ffe5d7e4f5833213</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python/PySpark</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b1dd2ce5d3671a</t>
+          <t>https://www.indeed.com/viewjob?jk=022d9e279d3ddb80</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>BOULDER SCIENTIFIC CO</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Longmont, CO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6efe960a7ab141ac</t>
+          <t>https://www.indeed.com/viewjob?jk=9486135c47b58364</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SENIOR DATA ENGINEER</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bee5a340a7f65e61</t>
+          <t>https://www.indeed.com/viewjob?jk=ba5a22f3941b5b26</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BOULDER SCIENTIFIC CO</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Longmont, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9486135c47b58364</t>
+          <t>https://www.indeed.com/viewjob?jk=f059a12d002721db</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer III- Python/PySpark</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba5a22f3941b5b26</t>
+          <t>https://www.indeed.com/viewjob?jk=82b1dd2ce5d3671a</t>
         </is>
       </c>
     </row>
@@ -1973,17 +1973,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>SENIOR DATA ENGINEER</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>TWG Global AI</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edb6a72ac37333e2</t>
+          <t>https://www.indeed.com/viewjob?jk=bee5a340a7f65e61</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Sr Software Development Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>AllCloud</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
+          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49fcd1d4ac195cdf</t>
+          <t>https://www.indeed.com/viewjob?jk=6efe960a7ab141ac</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>IT BI Solutions Engineer, ES</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Terex Corporation</t>
+          <t>TWG Global AI</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chattanooga, TN, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8376f8e501b07a8</t>
+          <t>https://www.indeed.com/viewjob?jk=edb6a72ac37333e2</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>IT BI Solutions Engineer, ES</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Terex Corporation</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chattanooga, TN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Medallion Architecture, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions, AWS CodePipeline</t>
+          <t>AWS, Redshift, RDS, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83c604950fd47a32</t>
+          <t>https://www.indeed.com/viewjob?jk=e8376f8e501b07a8</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-3</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, Step Functions, Medallion Architecture, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f753e538739bd670</t>
+          <t>https://www.indeed.com/viewjob?jk=83c604950fd47a32</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Platform Engineer-3</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Advance Auto Parts</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Kafka, Snowflake, ETL</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e2d8bc5a4c9174d</t>
+          <t>https://www.indeed.com/viewjob?jk=f753e538739bd670</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Junior AI/MLOps Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>AllCloud</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, NoSQL, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe34817d3b1a40dc</t>
+          <t>https://www.indeed.com/viewjob?jk=49fcd1d4ac195cdf</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Junior AI/MLOps Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, NoSQL, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90d33ae33b62c3a0</t>
+          <t>https://www.indeed.com/viewjob?jk=fe34817d3b1a40dc</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec56a8fbf5328856</t>
+          <t>https://www.indeed.com/viewjob?jk=90d33ae33b62c3a0</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,14 +2316,14 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d4834b7dd63e5a3</t>
+          <t>https://www.indeed.com/viewjob?jk=ec56a8fbf5328856</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,14 +2351,14 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=314cd9d2f824e302</t>
+          <t>https://www.indeed.com/viewjob?jk=3d4834b7dd63e5a3</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec0d14ba7f6cc782</t>
+          <t>https://www.indeed.com/viewjob?jk=314cd9d2f824e302</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,14 +2421,14 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd9783225b203a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=ec0d14ba7f6cc782</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,14 +2456,14 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fcdb3a443f803a9</t>
+          <t>https://www.indeed.com/viewjob?jk=cd9783225b203a0f</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=154ab74a68ca6406</t>
+          <t>https://www.indeed.com/viewjob?jk=5fcdb3a443f803a9</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31f45e1ed037bd50</t>
+          <t>https://www.indeed.com/viewjob?jk=154ab74a68ca6406</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5d14ef4e88a3e5a</t>
+          <t>https://www.indeed.com/viewjob?jk=31f45e1ed037bd50</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f6ccf05e64c984b</t>
+          <t>https://www.indeed.com/viewjob?jk=f5d14ef4e88a3e5a</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,14 +2631,14 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b4b4f98c48563cd</t>
+          <t>https://www.indeed.com/viewjob?jk=5f6ccf05e64c984b</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6c2c604bb89e64b</t>
+          <t>https://www.indeed.com/viewjob?jk=7b4b4f98c48563cd</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,14 +2701,14 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e02fe4d607063c1</t>
+          <t>https://www.indeed.com/viewjob?jk=c6c2c604bb89e64b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,14 +2736,14 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fbafb89e71fb39e</t>
+          <t>https://www.indeed.com/viewjob?jk=6e02fe4d607063c1</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8ac438ef838975b</t>
+          <t>https://www.indeed.com/viewjob?jk=9fbafb89e71fb39e</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74bd0f0f93d9a1a5</t>
+          <t>https://www.indeed.com/viewjob?jk=e8ac438ef838975b</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,14 +2841,14 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c53e85e359970d4</t>
+          <t>https://www.indeed.com/viewjob?jk=74bd0f0f93d9a1a5</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c433c70839583dc</t>
+          <t>https://www.indeed.com/viewjob?jk=4c53e85e359970d4</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35e828bfc556b676</t>
+          <t>https://www.indeed.com/viewjob?jk=0c433c70839583dc</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,14 +2946,14 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3058b24332d31ded</t>
+          <t>https://www.indeed.com/viewjob?jk=35e828bfc556b676</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10e23f958e9e8b09</t>
+          <t>https://www.indeed.com/viewjob?jk=3058b24332d31ded</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=357547d890623cb5</t>
+          <t>https://www.indeed.com/viewjob?jk=10e23f958e9e8b09</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,14 +3051,14 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3884844e18945dee</t>
+          <t>https://www.indeed.com/viewjob?jk=357547d890623cb5</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17b7c64ee8dc67e0</t>
+          <t>https://www.indeed.com/viewjob?jk=3884844e18945dee</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a75982d2aedba052</t>
+          <t>https://www.indeed.com/viewjob?jk=17b7c64ee8dc67e0</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,14 +3156,14 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b3d8d96e19fcbe6</t>
+          <t>https://www.indeed.com/viewjob?jk=a75982d2aedba052</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a60a56d62d329dea</t>
+          <t>https://www.indeed.com/viewjob?jk=4b3d8d96e19fcbe6</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93902824d8ac4d0c</t>
+          <t>https://www.indeed.com/viewjob?jk=a60a56d62d329dea</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=088398b8f22d3683</t>
+          <t>https://www.indeed.com/viewjob?jk=93902824d8ac4d0c</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f8a4d4b303056b</t>
+          <t>https://www.indeed.com/viewjob?jk=088398b8f22d3683</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,14 +3331,14 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=459cc0fec55fdc6f</t>
+          <t>https://www.indeed.com/viewjob?jk=60f8a4d4b303056b</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,14 +3366,14 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a58d376929282400</t>
+          <t>https://www.indeed.com/viewjob?jk=459cc0fec55fdc6f</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,14 +3401,14 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=521ae718282fb788</t>
+          <t>https://www.indeed.com/viewjob?jk=a58d376929282400</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,14 +3436,14 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=559d1352317c1f33</t>
+          <t>https://www.indeed.com/viewjob?jk=521ae718282fb788</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=361e87b55f4161f4</t>
+          <t>https://www.indeed.com/viewjob?jk=559d1352317c1f33</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32e0b2833cebefe3</t>
+          <t>https://www.indeed.com/viewjob?jk=361e87b55f4161f4</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f5df27af3031e62</t>
+          <t>https://www.indeed.com/viewjob?jk=32e0b2833cebefe3</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Kubernetes, Airflow</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d20f4b9e6a3cbb70</t>
+          <t>https://www.indeed.com/viewjob?jk=9f5df27af3031e62</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Site Reliability Developer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Kubernetes, Airflow</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c89d6a7d2041de38</t>
+          <t>https://www.indeed.com/viewjob?jk=3fedd79bbbee99bb</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Developer</t>
+          <t>Software Engineer II (Backend + Data pipelines)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fedd79bbbee99bb</t>
+          <t>https://www.indeed.com/viewjob?jk=7d4fca4ad337ae6c</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4fca4ad337ae6c</t>
+          <t>https://www.indeed.com/viewjob?jk=1ae76b185563f91b</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ae76b185563f91b</t>
+          <t>https://www.indeed.com/viewjob?jk=ef2a73b324528506</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef2a73b324528506</t>
+          <t>https://www.indeed.com/viewjob?jk=92aaafaf1efb9ec4</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92aaafaf1efb9ec4</t>
+          <t>https://www.indeed.com/viewjob?jk=c9981aefe519f0cd</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9981aefe519f0cd</t>
+          <t>https://www.indeed.com/viewjob?jk=fce2095df8206466</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fce2095df8206466</t>
+          <t>https://www.indeed.com/viewjob?jk=ee34633b7838a9b3</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee34633b7838a9b3</t>
+          <t>https://www.indeed.com/viewjob?jk=cc57f588c654f1cd</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc57f588c654f1cd</t>
+          <t>https://www.indeed.com/viewjob?jk=5aaeb4c54cdfa77e</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5aaeb4c54cdfa77e</t>
+          <t>https://www.indeed.com/viewjob?jk=eb06d74f6367bb04</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb06d74f6367bb04</t>
+          <t>https://www.indeed.com/viewjob?jk=49799e02e3e0a925</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49799e02e3e0a925</t>
+          <t>https://www.indeed.com/viewjob?jk=52ff9083bc8990ce</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52ff9083bc8990ce</t>
+          <t>https://www.indeed.com/viewjob?jk=66f89817131cfa0d</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f89817131cfa0d</t>
+          <t>https://www.indeed.com/viewjob?jk=cdb757efdefad0ca</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdb757efdefad0ca</t>
+          <t>https://www.indeed.com/viewjob?jk=57fc4e97a319b123</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57fc4e97a319b123</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fcc67143e3ff8a</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fcc67143e3ff8a</t>
+          <t>https://www.indeed.com/viewjob?jk=5dad4bf1e950e1c9</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dad4bf1e950e1c9</t>
+          <t>https://www.indeed.com/viewjob?jk=0f9ed5d278a8086d</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f9ed5d278a8086d</t>
+          <t>https://www.indeed.com/viewjob?jk=8809421834292084</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend + Data pipelines)</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8809421834292084</t>
+          <t>https://www.indeed.com/viewjob?jk=eb77847b7cd88f45</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Digital Engineer – Full Stack &amp; Systems Architecture</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Genentech</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Berkeley, MO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Step Functions, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5360d83db3589d68</t>
+          <t>https://www.indeed.com/viewjob?jk=d20f4b9e6a3cbb70</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Digital Engineer – Full Stack &amp; Systems Architecture</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Genentech</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Step Functions, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12a4a8cde3354706</t>
+          <t>https://www.indeed.com/viewjob?jk=c89d6a7d2041de38</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Digital Engineer – Full Stack &amp; Systems Architecture</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>LERETA, LLC</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Pomona, CA, US USA</t>
+          <t>Berkeley, MO, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad5d067156fc62f1</t>
+          <t>https://www.indeed.com/viewjob?jk=5360d83db3589d68</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Senior Digital Engineer – Full Stack &amp; Systems Architecture</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Hard Rock International</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Hollywood, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, Snowflake, PostgreSQL, Cassandra, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=169d4a00d377fdae</t>
+          <t>https://www.indeed.com/viewjob?jk=12a4a8cde3354706</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Application Platform Architect - 6163848</t>
+          <t>Senior LLM Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Hadoop, Scala, PostgreSQL, CI/CD, Docker</t>
+          <t>AWS, Azure, Vertex AI, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ea7fc0fae83610a</t>
+          <t>https://www.indeed.com/viewjob?jk=109c9c4a6595ba95</t>
         </is>
       </c>
     </row>
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109c9c4a6595ba95</t>
+          <t>https://www.indeed.com/viewjob?jk=8723fa94634ae387</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior LLM Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>LERETA, LLC</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Pomona, CA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, MLOps</t>
+          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8723fa94634ae387</t>
+          <t>https://www.indeed.com/viewjob?jk=ad5d067156fc62f1</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Search)</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Hard Rock International</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Hollywood, FL, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, Snowflake, PostgreSQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cff2f5a9dcacb28f</t>
+          <t>https://www.indeed.com/viewjob?jk=169d4a00d377fdae</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Search)</t>
+          <t>Senior Application Platform Architect - 6163848</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Hadoop, Scala, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3216b4c3b2c151f8</t>
+          <t>https://www.indeed.com/viewjob?jk=7ea7fc0fae83610a</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0fc0424a2f74ea8</t>
+          <t>https://www.indeed.com/viewjob?jk=cff2f5a9dcacb28f</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0ff98f788ff107b</t>
+          <t>https://www.indeed.com/viewjob?jk=3216b4c3b2c151f8</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0442372baf83ee82</t>
+          <t>https://www.indeed.com/viewjob?jk=a0fc0424a2f74ea8</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe6ea91421159ece</t>
+          <t>https://www.indeed.com/viewjob?jk=c0ff98f788ff107b</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aecbf4d450f1441b</t>
+          <t>https://www.indeed.com/viewjob?jk=0442372baf83ee82</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31056dc236b5ce67</t>
+          <t>https://www.indeed.com/viewjob?jk=fe6ea91421159ece</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eca84bb19e700f2b</t>
+          <t>https://www.indeed.com/viewjob?jk=aecbf4d450f1441b</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7401294591da0c90</t>
+          <t>https://www.indeed.com/viewjob?jk=31056dc236b5ce67</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eed535b1fcfea26</t>
+          <t>https://www.indeed.com/viewjob?jk=eca84bb19e700f2b</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29243583190aa6a</t>
+          <t>https://www.indeed.com/viewjob?jk=7401294591da0c90</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c0d7ebd3a2ee36f</t>
+          <t>https://www.indeed.com/viewjob?jk=5eed535b1fcfea26</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e3397c0e70024e</t>
+          <t>https://www.indeed.com/viewjob?jk=b29243583190aa6a</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35f50cc085f1bbd9</t>
+          <t>https://www.indeed.com/viewjob?jk=1c0d7ebd3a2ee36f</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72be3b8aba169a59</t>
+          <t>https://www.indeed.com/viewjob?jk=28e3397c0e70024e</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b61af8e418fcf231</t>
+          <t>https://www.indeed.com/viewjob?jk=35f50cc085f1bbd9</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=552a8172dcf24a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=72be3b8aba169a59</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,32 +5221,32 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fa51ea3c52768d7</t>
+          <t>https://www.indeed.com/viewjob?jk=b61af8e418fcf231</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Software Engineering Intern – Data Engineering (Cloud &amp; Streaming)</t>
+          <t>Senior Machine Learning Engineer (Search)</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>NextPower</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,32 +5256,32 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e588be3c533008</t>
+          <t>https://www.indeed.com/viewjob?jk=552a8172dcf24a7a</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Machine Learning Engineer (Search)</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Power BI, Tableau, MLOps, MLflow</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaf9596bf4159924</t>
+          <t>https://www.indeed.com/viewjob?jk=4fa51ea3c52768d7</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Cloud Systems Engineer (Databricks Administrator)</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Providge Consulting</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Power BI, Tableau, MLOps, MLflow</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab90611f6b141379</t>
+          <t>https://www.indeed.com/viewjob?jk=e094ab218ebab2ed</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Python)</t>
+          <t>Software Engineering Intern – Data Engineering (Cloud &amp; Streaming)</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>NextPower</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,34 +5351,34 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f65ac6c3f1cf1646</t>
+          <t>https://www.indeed.com/viewjob?jk=28e588be3c533008</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Senior Cloud Systems Engineer (Databricks Administrator)</t>
+          <t>Sr. ETL/SQL Engineer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Providge Consulting</t>
+          <t>Capgemini Government Solutions</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Scala, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e094ab218ebab2ed</t>
+          <t>https://www.indeed.com/viewjob?jk=724ffe7f1d3da135</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Sr. ETL/SQL Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Capgemini Government Solutions</t>
+          <t>Space Telescope Science Institute</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, ECS, IAM, Hive, Scala, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724ffe7f1d3da135</t>
+          <t>https://www.indeed.com/viewjob?jk=6055970eb603df79</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>AI Engineer III</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Space Telescope Science Institute</t>
+          <t>CareSource</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Hive, Scala, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>API Gateway, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6055970eb603df79</t>
+          <t>https://www.indeed.com/viewjob?jk=640c68fe3716b1e6</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>AI Engineer III</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>CareSource</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Power BI, Tableau, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=640c68fe3716b1e6</t>
+          <t>https://www.indeed.com/viewjob?jk=aaf9596bf4159924</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Sr Software Engineer (Site Reliability Engineering) (2026-10114)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, MySQL, Splunk</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Power BI, Tableau, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,24 +5536,24 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5ab755eddd54b18</t>
+          <t>https://www.indeed.com/viewjob?jk=ab90611f6b141379</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Software Engineer, Back End (Python)</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>H2O.ai</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,34 +5561,34 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe52f92aedddcda4</t>
+          <t>https://www.indeed.com/viewjob?jk=f65ac6c3f1cf1646</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Sr Software Engineer (Site Reliability Engineering) (2026-10114)</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>H2O.ai</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, MySQL, Splunk</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,24 +5606,24 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d2b8979a3b5f81b</t>
+          <t>https://www.indeed.com/viewjob?jk=b5ab755eddd54b18</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data &amp; Analytics</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>WesBanco Bank, Inc.</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Bowie, MD, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,24 +5641,24 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a02cdb2b181be3</t>
+          <t>https://www.indeed.com/viewjob?jk=d44e3274520e56d6</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data &amp; Analytics</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>WesBanco Bank, Inc.</t>
+          <t>Centene</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Wheeling, WV, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,34 +5666,34 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb6ee55d393e301c</t>
+          <t>https://www.indeed.com/viewjob?jk=11d92da9c37770a7</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Software Developer - Database Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>RAMSOFT</t>
+          <t>H2O.ai</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, HBase, Scala, Snowflake, MySQL, NoSQL, Data Modeling, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5711,24 +5711,24 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ce0ac7d0a937f32</t>
+          <t>https://www.indeed.com/viewjob?jk=fe52f92aedddcda4</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>H2O.ai</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5746,24 +5746,24 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d44e3274520e56d6</t>
+          <t>https://www.indeed.com/viewjob?jk=0d2b8979a3b5f81b</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Data Engineer - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Centene</t>
+          <t>WesBanco Bank, Inc.</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Bowie, MD, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,34 +5771,34 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11d92da9c37770a7</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a02cdb2b181be3</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>Senior Data Engineer - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>WesBanco Bank, Inc.</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Wheeling, WV, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5816,24 +5816,24 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2b622ee37d8f63f</t>
+          <t>https://www.indeed.com/viewjob?jk=fb6ee55d393e301c</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>Software Developer - Database Engineer</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>RAMSOFT</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, HBase, Scala, Snowflake, MySQL, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ba10ede755adc88</t>
+          <t>https://www.indeed.com/viewjob?jk=4ce0ac7d0a937f32</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=035e833a0affea06</t>
+          <t>https://www.indeed.com/viewjob?jk=e2b622ee37d8f63f</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ea65634bf231fc</t>
+          <t>https://www.indeed.com/viewjob?jk=7ba10ede755adc88</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db2fffa7ab4fc3c6</t>
+          <t>https://www.indeed.com/viewjob?jk=035e833a0affea06</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=726fca60377106fb</t>
+          <t>https://www.indeed.com/viewjob?jk=34ea65634bf231fc</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae1bbd4c5bfc6dc1</t>
+          <t>https://www.indeed.com/viewjob?jk=db2fffa7ab4fc3c6</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d44fb63e0c3570e</t>
+          <t>https://www.indeed.com/viewjob?jk=726fca60377106fb</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac1d3f6a217585b1</t>
+          <t>https://www.indeed.com/viewjob?jk=ae1bbd4c5bfc6dc1</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=594c2209c74b60f3</t>
+          <t>https://www.indeed.com/viewjob?jk=7d44fb63e0c3570e</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=300951fa8a03d9ab</t>
+          <t>https://www.indeed.com/viewjob?jk=ac1d3f6a217585b1</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224f85378fe66226</t>
+          <t>https://www.indeed.com/viewjob?jk=594c2209c74b60f3</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=609ed15647075bf2</t>
+          <t>https://www.indeed.com/viewjob?jk=300951fa8a03d9ab</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7da2bae9861dfa9</t>
+          <t>https://www.indeed.com/viewjob?jk=224f85378fe66226</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f44f95326fb5d8b</t>
+          <t>https://www.indeed.com/viewjob?jk=609ed15647075bf2</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7f6777f3346c150</t>
+          <t>https://www.indeed.com/viewjob?jk=f7da2bae9861dfa9</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99001099f8e56675</t>
+          <t>https://www.indeed.com/viewjob?jk=9f44f95326fb5d8b</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d562fde2d3ab4ec</t>
+          <t>https://www.indeed.com/viewjob?jk=f7f6777f3346c150</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6446,14 +6446,14 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49363af061447f75</t>
+          <t>https://www.indeed.com/viewjob?jk=99001099f8e56675</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python + Distributed systems)</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6481,14 +6481,14 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4af4ef5dfeb0026</t>
+          <t>https://www.indeed.com/viewjob?jk=1d562fde2d3ab4ec</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python + Distributed systems)</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -6498,7 +6498,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c116b8acf805f138</t>
+          <t>https://www.indeed.com/viewjob?jk=49363af061447f75</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f996f9a35281bba7</t>
+          <t>https://www.indeed.com/viewjob?jk=c4af4ef5dfeb0026</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca3982c4f2be4e49</t>
+          <t>https://www.indeed.com/viewjob?jk=c116b8acf805f138</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f2a3e577d5623a4</t>
+          <t>https://www.indeed.com/viewjob?jk=f996f9a35281bba7</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=629b89e40e1e1bb5</t>
+          <t>https://www.indeed.com/viewjob?jk=ca3982c4f2be4e49</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db6cf98112c1bc9f</t>
+          <t>https://www.indeed.com/viewjob?jk=9f2a3e577d5623a4</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80b26c4d48449b15</t>
+          <t>https://www.indeed.com/viewjob?jk=629b89e40e1e1bb5</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83ba9763cad5f2f8</t>
+          <t>https://www.indeed.com/viewjob?jk=db6cf98112c1bc9f</t>
         </is>
       </c>
     </row>
@@ -6778,7 +6778,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05460d1c364a2974</t>
+          <t>https://www.indeed.com/viewjob?jk=80b26c4d48449b15</t>
         </is>
       </c>
     </row>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b01dc956f073aaf8</t>
+          <t>https://www.indeed.com/viewjob?jk=83ba9763cad5f2f8</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=807aad5f4045241d</t>
+          <t>https://www.indeed.com/viewjob?jk=05460d1c364a2974</t>
         </is>
       </c>
     </row>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=655ea21e25dbce1e</t>
+          <t>https://www.indeed.com/viewjob?jk=b01dc956f073aaf8</t>
         </is>
       </c>
     </row>
@@ -6918,7 +6918,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c46ceb995e304d69</t>
+          <t>https://www.indeed.com/viewjob?jk=807aad5f4045241d</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f29df76fe446a26</t>
+          <t>https://www.indeed.com/viewjob?jk=655ea21e25dbce1e</t>
         </is>
       </c>
     </row>
@@ -6988,7 +6988,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6574f30d9366e40</t>
+          <t>https://www.indeed.com/viewjob?jk=c46ceb995e304d69</t>
         </is>
       </c>
     </row>
@@ -7023,7 +7023,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8536b186707d6516</t>
+          <t>https://www.indeed.com/viewjob?jk=7f29df76fe446a26</t>
         </is>
       </c>
     </row>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a4c9600c5ead18d</t>
+          <t>https://www.indeed.com/viewjob?jk=d6574f30d9366e40</t>
         </is>
       </c>
     </row>
@@ -7093,7 +7093,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -7111,32 +7111,32 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78388f22c8e1c7cc</t>
+          <t>https://www.indeed.com/viewjob?jk=8536b186707d6516</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>AV Safety Engineering Analytics Simulation Engineer (GPSSC)</t>
+          <t>Senior Software Engineer (Python + Distributed systems)</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -7146,59 +7146,59 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b9eec46bbab109b</t>
+          <t>https://www.indeed.com/viewjob?jk=6a4c9600c5ead18d</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Data Engineer-Remote</t>
+          <t>Senior Software Engineer (Python + Distributed systems)</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Mutual of Omaha</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Scala, Snowflake, SQL Server, MongoDB, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc1efbee94e32a9</t>
+          <t>https://www.indeed.com/viewjob?jk=78388f22c8e1c7cc</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer-Remote</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Mutual of Omaha</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -7206,34 +7206,34 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, RDS, Scala, Snowflake, SQL Server, MongoDB, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed1b9b0328def6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc1efbee94e32a9</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>SAP NS2 Senior HANA Cloud DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -7251,24 +7251,24 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8999a6d9da6831ef</t>
+          <t>https://www.indeed.com/viewjob?jk=ed1b9b0328def6aa</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>SAP NS2 Senior HANA Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -7286,24 +7286,24 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e60ff8bc1e60898</t>
+          <t>https://www.indeed.com/viewjob?jk=8999a6d9da6831ef</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Callaway Golf</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -7311,34 +7311,34 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ae59fccd3421dc5</t>
+          <t>https://www.indeed.com/viewjob?jk=2e60ff8bc1e60898</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Senior AI/ML Scientist</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Callaway Golf</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Milford, MI, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -7346,24 +7346,24 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, MLflow, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=300d4ca14be662c3</t>
+          <t>https://www.indeed.com/viewjob?jk=9ae59fccd3421dc5</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>AV Safety Engineering Analytics Engineer (GPSSC)</t>
+          <t>AV Safety Engineering Analytics Simulation Engineer (GPSSC)</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -7391,24 +7391,24 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60da6f50aaadfe48</t>
+          <t>https://www.indeed.com/viewjob?jk=4b9eec46bbab109b</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Visualization Engineer</t>
+          <t>Senior AI/ML Scientist</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -7416,7 +7416,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>RDS, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -7426,24 +7426,24 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b28a6ad6f45c5471</t>
+          <t>https://www.indeed.com/viewjob?jk=300d4ca14be662c3</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Product Engineer</t>
+          <t>Visualization Engineer</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>ALTIMATE</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -7451,34 +7451,34 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Spark, Scala, PostgreSQL, dbt, Kubernetes, Airflow, Git</t>
+          <t>RDS, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95f4b6534ba4c3cd</t>
+          <t>https://www.indeed.com/viewjob?jk=b28a6ad6f45c5471</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>SENIOR DATA ENGINEER (REMOTE)</t>
+          <t>AV Safety Engineering Analytics Engineer (GPSSC)</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Morrison Healthcare</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -7486,34 +7486,34 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Snowflake, ETL, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d530073f998c3698</t>
+          <t>https://www.indeed.com/viewjob?jk=60da6f50aaadfe48</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Snowflake Administrator</t>
+          <t>SENIOR DATA ENGINEER (REMOTE)</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Morrison Healthcare</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -7521,34 +7521,34 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Snowflake, ETL, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=085de5867e567658</t>
+          <t>https://www.indeed.com/viewjob?jk=d530073f998c3698</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>LLM Application Engineer</t>
+          <t>Product Engineer</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ALTIMATE</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -7556,34 +7556,34 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
+          <t>AWS, ECS, RDS, Spark, Scala, PostgreSQL, dbt, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5633278896c16c3b</t>
+          <t>https://www.indeed.com/viewjob?jk=95f4b6534ba4c3cd</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>LLM Application Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -7591,34 +7591,34 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e56614bfb72e3b3</t>
+          <t>https://www.indeed.com/viewjob?jk=50c61f5469ce333f</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Teradata Developer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -7626,7 +7626,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -7636,24 +7636,24 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fddb4ec439f1237</t>
+          <t>https://www.indeed.com/viewjob?jk=4303ceb5e8c627c4</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Senior BI Developer - Investment Services</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D207" t="n">
@@ -7661,34 +7661,34 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6861136ad5c92fec</t>
+          <t>https://www.indeed.com/viewjob?jk=0c4db6d385ae6ea3</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Senior BI Developer - Investment Services</t>
+          <t>Sr. Full Stack Software Engineer (Onsite - San Diego)</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Carlsmed</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D208" t="n">
@@ -7696,7 +7696,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, Scala, PostgreSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -7706,24 +7706,24 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0459e004fd012bc</t>
+          <t>https://www.indeed.com/viewjob?jk=47ffb86f604e14df</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Senior BI Developer - Investment Services</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D209" t="n">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -7741,24 +7741,24 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00bd0c85ee5af1cc</t>
+          <t>https://www.indeed.com/viewjob?jk=c70cf8723aeaf7eb</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Senior BI Developer - Investment Services</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D210" t="n">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -7776,24 +7776,24 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a227aff44c18bd</t>
+          <t>https://www.indeed.com/viewjob?jk=6f106012aaf32c49</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Senior BI Developer - Investment Services</t>
+          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D211" t="n">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -7811,24 +7811,24 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f36e77b3ab4b1808</t>
+          <t>https://www.indeed.com/viewjob?jk=a1593d7242ad3914</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Senior BI Developer - Investment Services</t>
+          <t>Snowflake Administrator</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D212" t="n">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -7846,24 +7846,24 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b03b046a7e4b4373</t>
+          <t>https://www.indeed.com/viewjob?jk=085de5867e567658</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>LLM Application Engineer</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D213" t="n">
@@ -7871,34 +7871,34 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c61f5469ce333f</t>
+          <t>https://www.indeed.com/viewjob?jk=5633278896c16c3b</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>LLM Application Engineer</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D214" t="n">
@@ -7906,34 +7906,34 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4303ceb5e8c627c4</t>
+          <t>https://www.indeed.com/viewjob?jk=4e56614bfb72e3b3</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Teradata Developer</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D215" t="n">
@@ -7941,7 +7941,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -7951,24 +7951,24 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c4db6d385ae6ea3</t>
+          <t>https://www.indeed.com/viewjob?jk=7fddb4ec439f1237</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Software Engineer (Onsite - San Diego)</t>
+          <t>Senior BI Developer - Investment Services</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Carlsmed</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D216" t="n">
@@ -7976,7 +7976,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, Scala, PostgreSQL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -7986,24 +7986,24 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47ffb86f604e14df</t>
+          <t>https://www.indeed.com/viewjob?jk=6861136ad5c92fec</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Senior BI Developer - Investment Services</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D217" t="n">
@@ -8011,7 +8011,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -8021,24 +8021,24 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c70cf8723aeaf7eb</t>
+          <t>https://www.indeed.com/viewjob?jk=d0459e004fd012bc</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Senior BI Developer - Investment Services</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D218" t="n">
@@ -8046,7 +8046,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -8056,24 +8056,24 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f106012aaf32c49</t>
+          <t>https://www.indeed.com/viewjob?jk=00bd0c85ee5af1cc</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
+          <t>Senior BI Developer - Investment Services</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D219" t="n">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -8091,7 +8091,77 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1593d7242ad3914</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a227aff44c18bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Senior BI Developer - Investment Services</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Milwaukee, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f36e77b3ab4b1808</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Senior BI Developer - Investment Services</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Hopkins, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b03b046a7e4b4373</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-06.xlsx
+++ b/results/job_matches_2026-03-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G221"/>
+  <dimension ref="A1:G223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -928,12 +928,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>JBS Dev</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49f6c2df00dd6e11</t>
+          <t>https://www.indeed.com/viewjob?jk=32d044bc27a4af8a</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Costa Rica)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JBS Dev</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,17 +976,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05c819aa2a88511d</t>
+          <t>https://www.indeed.com/viewjob?jk=aed60e56cae31294</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1016,12 +1016,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32d044bc27a4af8a</t>
+          <t>https://www.indeed.com/viewjob?jk=44f958ba0cbc0f43</t>
         </is>
       </c>
     </row>
@@ -1033,12 +1033,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>JBS Dev</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aed60e56cae31294</t>
+          <t>https://www.indeed.com/viewjob?jk=49f6c2df00dd6e11</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (Costa Rica)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>JBS Dev</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,17 +1081,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44f958ba0cbc0f43</t>
+          <t>https://www.indeed.com/viewjob?jk=05c819aa2a88511d</t>
         </is>
       </c>
     </row>
@@ -1343,17 +1343,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior BI Analyst</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad414f3a9ab0a2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=afa51ac883fa48a6</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Senior BI Analyst</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=459162c660bc8082</t>
+          <t>https://www.indeed.com/viewjob?jk=ad414f3a9ab0a2bc</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afa51ac883fa48a6</t>
+          <t>https://www.indeed.com/viewjob?jk=459162c660bc8082</t>
         </is>
       </c>
     </row>
@@ -1588,17 +1588,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BOULDER SCIENTIFIC CO</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Longmont, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9486135c47b58364</t>
+          <t>https://www.indeed.com/viewjob?jk=f059a12d002721db</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer III- Python/PySpark</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba5a22f3941b5b26</t>
+          <t>https://www.indeed.com/viewjob?jk=82b1dd2ce5d3671a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Software Development Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
+          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f059a12d002721db</t>
+          <t>https://www.indeed.com/viewjob?jk=6efe960a7ab141ac</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python/PySpark</t>
+          <t>SENIOR DATA ENGINEER</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b1dd2ce5d3671a</t>
+          <t>https://www.indeed.com/viewjob?jk=bee5a340a7f65e61</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AI Support Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>PetSmart</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=625bf5ef0b332ad3</t>
+          <t>https://www.indeed.com/viewjob?jk=157ddcd0636f7c11</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AI Support Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>BOULDER SCIENTIFIC CO</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Longmont, CO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd39a203b7587e31</t>
+          <t>https://www.indeed.com/viewjob?jk=9486135c47b58364</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Yusen Logistics</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kimball, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f92de33105c0bad</t>
+          <t>https://www.indeed.com/viewjob?jk=ba5a22f3941b5b26</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Support Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Yusen Logistics</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kimball, ELT, dbt</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=772460af87c5b60c</t>
+          <t>https://www.indeed.com/viewjob?jk=625bf5ef0b332ad3</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Support Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Royal Oak, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bb3681c5da818f2</t>
+          <t>https://www.indeed.com/viewjob?jk=dd39a203b7587e31</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Yusen Logistics</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=343b07159d1b6928</t>
+          <t>https://www.indeed.com/viewjob?jk=7f92de33105c0bad</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer - Virtual</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Alight Solutions</t>
+          <t>Yusen Logistics</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a286c7ca862c4e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=772460af87c5b60c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SENIOR DATA ENGINEER</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Royal Oak, MI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bee5a340a7f65e61</t>
+          <t>https://www.indeed.com/viewjob?jk=6bb3681c5da818f2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6efe960a7ab141ac</t>
+          <t>https://www.indeed.com/viewjob?jk=343b07159d1b6928</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Cloud Platform Engineer - Virtual</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>TWG Global AI</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edb6a72ac37333e2</t>
+          <t>https://www.indeed.com/viewjob?jk=a286c7ca862c4e1a</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>IT BI Solutions Engineer, ES</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Terex Corporation</t>
+          <t>TWG Global AI</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chattanooga, TN, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8376f8e501b07a8</t>
+          <t>https://www.indeed.com/viewjob?jk=edb6a72ac37333e2</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>AllCloud</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Medallion Architecture, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions, AWS CodePipeline</t>
+          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83c604950fd47a32</t>
+          <t>https://www.indeed.com/viewjob?jk=49fcd1d4ac195cdf</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-3</t>
+          <t>IT BI Solutions Engineer, ES</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Terex Corporation</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Chattanooga, TN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f753e538739bd670</t>
+          <t>https://www.indeed.com/viewjob?jk=e8376f8e501b07a8</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>AllCloud</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
+          <t>AWS, Step Functions, Medallion Architecture, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49fcd1d4ac195cdf</t>
+          <t>https://www.indeed.com/viewjob?jk=83c604950fd47a32</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Junior AI/MLOps Engineer</t>
+          <t>Data Platform Engineer-3</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, NoSQL, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe34817d3b1a40dc</t>
+          <t>https://www.indeed.com/viewjob?jk=f753e538739bd670</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Junior AI/MLOps Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, NoSQL, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90d33ae33b62c3a0</t>
+          <t>https://www.indeed.com/viewjob?jk=fe34817d3b1a40dc</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec56a8fbf5328856</t>
+          <t>https://www.indeed.com/viewjob?jk=90d33ae33b62c3a0</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,14 +2351,14 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d4834b7dd63e5a3</t>
+          <t>https://www.indeed.com/viewjob?jk=ec56a8fbf5328856</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,14 +2386,14 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=314cd9d2f824e302</t>
+          <t>https://www.indeed.com/viewjob?jk=3d4834b7dd63e5a3</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec0d14ba7f6cc782</t>
+          <t>https://www.indeed.com/viewjob?jk=314cd9d2f824e302</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,14 +2456,14 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd9783225b203a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=ec0d14ba7f6cc782</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,14 +2491,14 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fcdb3a443f803a9</t>
+          <t>https://www.indeed.com/viewjob?jk=cd9783225b203a0f</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=154ab74a68ca6406</t>
+          <t>https://www.indeed.com/viewjob?jk=5fcdb3a443f803a9</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31f45e1ed037bd50</t>
+          <t>https://www.indeed.com/viewjob?jk=154ab74a68ca6406</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5d14ef4e88a3e5a</t>
+          <t>https://www.indeed.com/viewjob?jk=31f45e1ed037bd50</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f6ccf05e64c984b</t>
+          <t>https://www.indeed.com/viewjob?jk=f5d14ef4e88a3e5a</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,14 +2666,14 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b4b4f98c48563cd</t>
+          <t>https://www.indeed.com/viewjob?jk=5f6ccf05e64c984b</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6c2c604bb89e64b</t>
+          <t>https://www.indeed.com/viewjob?jk=7b4b4f98c48563cd</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,14 +2736,14 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e02fe4d607063c1</t>
+          <t>https://www.indeed.com/viewjob?jk=c6c2c604bb89e64b</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,14 +2771,14 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fbafb89e71fb39e</t>
+          <t>https://www.indeed.com/viewjob?jk=6e02fe4d607063c1</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8ac438ef838975b</t>
+          <t>https://www.indeed.com/viewjob?jk=9fbafb89e71fb39e</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74bd0f0f93d9a1a5</t>
+          <t>https://www.indeed.com/viewjob?jk=e8ac438ef838975b</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,14 +2876,14 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c53e85e359970d4</t>
+          <t>https://www.indeed.com/viewjob?jk=74bd0f0f93d9a1a5</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c433c70839583dc</t>
+          <t>https://www.indeed.com/viewjob?jk=4c53e85e359970d4</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35e828bfc556b676</t>
+          <t>https://www.indeed.com/viewjob?jk=0c433c70839583dc</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,14 +2981,14 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3058b24332d31ded</t>
+          <t>https://www.indeed.com/viewjob?jk=35e828bfc556b676</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10e23f958e9e8b09</t>
+          <t>https://www.indeed.com/viewjob?jk=3058b24332d31ded</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=357547d890623cb5</t>
+          <t>https://www.indeed.com/viewjob?jk=10e23f958e9e8b09</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,14 +3086,14 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3884844e18945dee</t>
+          <t>https://www.indeed.com/viewjob?jk=357547d890623cb5</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17b7c64ee8dc67e0</t>
+          <t>https://www.indeed.com/viewjob?jk=3884844e18945dee</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a75982d2aedba052</t>
+          <t>https://www.indeed.com/viewjob?jk=17b7c64ee8dc67e0</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,14 +3191,14 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b3d8d96e19fcbe6</t>
+          <t>https://www.indeed.com/viewjob?jk=a75982d2aedba052</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a60a56d62d329dea</t>
+          <t>https://www.indeed.com/viewjob?jk=4b3d8d96e19fcbe6</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93902824d8ac4d0c</t>
+          <t>https://www.indeed.com/viewjob?jk=a60a56d62d329dea</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=088398b8f22d3683</t>
+          <t>https://www.indeed.com/viewjob?jk=93902824d8ac4d0c</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f8a4d4b303056b</t>
+          <t>https://www.indeed.com/viewjob?jk=088398b8f22d3683</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,14 +3366,14 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=459cc0fec55fdc6f</t>
+          <t>https://www.indeed.com/viewjob?jk=60f8a4d4b303056b</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,14 +3401,14 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a58d376929282400</t>
+          <t>https://www.indeed.com/viewjob?jk=459cc0fec55fdc6f</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,14 +3436,14 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=521ae718282fb788</t>
+          <t>https://www.indeed.com/viewjob?jk=a58d376929282400</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,14 +3471,14 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=559d1352317c1f33</t>
+          <t>https://www.indeed.com/viewjob?jk=521ae718282fb788</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=361e87b55f4161f4</t>
+          <t>https://www.indeed.com/viewjob?jk=559d1352317c1f33</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32e0b2833cebefe3</t>
+          <t>https://www.indeed.com/viewjob?jk=361e87b55f4161f4</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f5df27af3031e62</t>
+          <t>https://www.indeed.com/viewjob?jk=32e0b2833cebefe3</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Developer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fedd79bbbee99bb</t>
+          <t>https://www.indeed.com/viewjob?jk=9f5df27af3031e62</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend + Data pipelines)</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4fca4ad337ae6c</t>
+          <t>https://www.indeed.com/viewjob?jk=eb77847b7cd88f45</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend + Data pipelines)</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Genentech</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, Step Functions, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ae76b185563f91b</t>
+          <t>https://www.indeed.com/viewjob?jk=d20f4b9e6a3cbb70</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend + Data pipelines)</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Genentech</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, Step Functions, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef2a73b324528506</t>
+          <t>https://www.indeed.com/viewjob?jk=c89d6a7d2041de38</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend + Data pipelines)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Teradata</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, API Gateway, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92aaafaf1efb9ec4</t>
+          <t>https://www.indeed.com/viewjob?jk=806bff32d1d719ff</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend + Data pipelines)</t>
+          <t>Senior Site Reliability Developer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9981aefe519f0cd</t>
+          <t>https://www.indeed.com/viewjob?jk=3fedd79bbbee99bb</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fce2095df8206466</t>
+          <t>https://www.indeed.com/viewjob?jk=7d4fca4ad337ae6c</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee34633b7838a9b3</t>
+          <t>https://www.indeed.com/viewjob?jk=1ae76b185563f91b</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc57f588c654f1cd</t>
+          <t>https://www.indeed.com/viewjob?jk=ef2a73b324528506</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5aaeb4c54cdfa77e</t>
+          <t>https://www.indeed.com/viewjob?jk=92aaafaf1efb9ec4</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb06d74f6367bb04</t>
+          <t>https://www.indeed.com/viewjob?jk=c9981aefe519f0cd</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49799e02e3e0a925</t>
+          <t>https://www.indeed.com/viewjob?jk=fce2095df8206466</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52ff9083bc8990ce</t>
+          <t>https://www.indeed.com/viewjob?jk=ee34633b7838a9b3</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f89817131cfa0d</t>
+          <t>https://www.indeed.com/viewjob?jk=cc57f588c654f1cd</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdb757efdefad0ca</t>
+          <t>https://www.indeed.com/viewjob?jk=5aaeb4c54cdfa77e</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57fc4e97a319b123</t>
+          <t>https://www.indeed.com/viewjob?jk=eb06d74f6367bb04</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fcc67143e3ff8a</t>
+          <t>https://www.indeed.com/viewjob?jk=49799e02e3e0a925</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dad4bf1e950e1c9</t>
+          <t>https://www.indeed.com/viewjob?jk=52ff9083bc8990ce</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f9ed5d278a8086d</t>
+          <t>https://www.indeed.com/viewjob?jk=66f89817131cfa0d</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8809421834292084</t>
+          <t>https://www.indeed.com/viewjob?jk=cdb757efdefad0ca</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Software Engineer II (Backend + Data pipelines)</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, MongoDB, Data Modeling</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb77847b7cd88f45</t>
+          <t>https://www.indeed.com/viewjob?jk=57fc4e97a319b123</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Software Engineer II (Backend + Data pipelines)</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Kubernetes, Airflow</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d20f4b9e6a3cbb70</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fcc67143e3ff8a</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Software Engineer II (Backend + Data pipelines)</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Kubernetes, Airflow</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c89d6a7d2041de38</t>
+          <t>https://www.indeed.com/viewjob?jk=5dad4bf1e950e1c9</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Digital Engineer – Full Stack &amp; Systems Architecture</t>
+          <t>Software Engineer II (Backend + Data pipelines)</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Berkeley, MO, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5360d83db3589d68</t>
+          <t>https://www.indeed.com/viewjob?jk=0f9ed5d278a8086d</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Digital Engineer – Full Stack &amp; Systems Architecture</t>
+          <t>Software Engineer II (Backend + Data pipelines)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12a4a8cde3354706</t>
+          <t>https://www.indeed.com/viewjob?jk=8809421834292084</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior LLM Engineer</t>
+          <t>Senior Digital Engineer – Full Stack &amp; Systems Architecture</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Berkeley, MO, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, MLOps</t>
+          <t>AWS, IAM, RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109c9c4a6595ba95</t>
+          <t>https://www.indeed.com/viewjob?jk=5360d83db3589d68</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior LLM Engineer</t>
+          <t>Senior Digital Engineer – Full Stack &amp; Systems Architecture</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, MLOps</t>
+          <t>AWS, IAM, RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8723fa94634ae387</t>
+          <t>https://www.indeed.com/viewjob?jk=12a4a8cde3354706</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Application Platform Architect - 6163848</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>LERETA, LLC</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Pomona, CA, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Hadoop, Scala, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad5d067156fc62f1</t>
+          <t>https://www.indeed.com/viewjob?jk=7ea7fc0fae83610a</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Senior LLM Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Hard Rock International</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Hollywood, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, Snowflake, PostgreSQL, Cassandra, CI/CD, Terraform</t>
+          <t>AWS, Azure, Vertex AI, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=169d4a00d377fdae</t>
+          <t>https://www.indeed.com/viewjob?jk=109c9c4a6595ba95</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Application Platform Architect - 6163848</t>
+          <t>Senior LLM Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Hadoop, Scala, PostgreSQL, CI/CD, Docker</t>
+          <t>AWS, Azure, Vertex AI, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ea7fc0fae83610a</t>
+          <t>https://www.indeed.com/viewjob?jk=8723fa94634ae387</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Search)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>LERETA, LLC</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Pomona, CA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cff2f5a9dcacb28f</t>
+          <t>https://www.indeed.com/viewjob?jk=ad5d067156fc62f1</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Search)</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Hard Rock International</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Hollywood, FL, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, Snowflake, PostgreSQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3216b4c3b2c151f8</t>
+          <t>https://www.indeed.com/viewjob?jk=169d4a00d377fdae</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0fc0424a2f74ea8</t>
+          <t>https://www.indeed.com/viewjob?jk=cff2f5a9dcacb28f</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0ff98f788ff107b</t>
+          <t>https://www.indeed.com/viewjob?jk=3216b4c3b2c151f8</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0442372baf83ee82</t>
+          <t>https://www.indeed.com/viewjob?jk=a0fc0424a2f74ea8</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe6ea91421159ece</t>
+          <t>https://www.indeed.com/viewjob?jk=c0ff98f788ff107b</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aecbf4d450f1441b</t>
+          <t>https://www.indeed.com/viewjob?jk=0442372baf83ee82</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31056dc236b5ce67</t>
+          <t>https://www.indeed.com/viewjob?jk=fe6ea91421159ece</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eca84bb19e700f2b</t>
+          <t>https://www.indeed.com/viewjob?jk=aecbf4d450f1441b</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7401294591da0c90</t>
+          <t>https://www.indeed.com/viewjob?jk=31056dc236b5ce67</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eed535b1fcfea26</t>
+          <t>https://www.indeed.com/viewjob?jk=eca84bb19e700f2b</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29243583190aa6a</t>
+          <t>https://www.indeed.com/viewjob?jk=7401294591da0c90</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c0d7ebd3a2ee36f</t>
+          <t>https://www.indeed.com/viewjob?jk=5eed535b1fcfea26</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e3397c0e70024e</t>
+          <t>https://www.indeed.com/viewjob?jk=b29243583190aa6a</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35f50cc085f1bbd9</t>
+          <t>https://www.indeed.com/viewjob?jk=1c0d7ebd3a2ee36f</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72be3b8aba169a59</t>
+          <t>https://www.indeed.com/viewjob?jk=28e3397c0e70024e</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b61af8e418fcf231</t>
+          <t>https://www.indeed.com/viewjob?jk=35f50cc085f1bbd9</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=552a8172dcf24a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=72be3b8aba169a59</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,32 +5291,32 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fa51ea3c52768d7</t>
+          <t>https://www.indeed.com/viewjob?jk=b61af8e418fcf231</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Senior Cloud Systems Engineer (Databricks Administrator)</t>
+          <t>Senior Machine Learning Engineer (Search)</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Providge Consulting</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Scala, ELT, CI/CD</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,32 +5326,32 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e094ab218ebab2ed</t>
+          <t>https://www.indeed.com/viewjob?jk=552a8172dcf24a7a</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Software Engineering Intern – Data Engineering (Cloud &amp; Streaming)</t>
+          <t>Senior Machine Learning Engineer (Search)</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>NextPower</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e588be3c533008</t>
+          <t>https://www.indeed.com/viewjob?jk=4fa51ea3c52768d7</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Sr. ETL/SQL Engineer</t>
+          <t>Software Engineering Intern – Data Engineering (Cloud &amp; Streaming)</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Capgemini Government Solutions</t>
+          <t>NextPower</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724ffe7f1d3da135</t>
+          <t>https://www.indeed.com/viewjob?jk=28e588be3c533008</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Space Telescope Science Institute</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Hive, Scala, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Power BI, Tableau, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6055970eb603df79</t>
+          <t>https://www.indeed.com/viewjob?jk=aaf9596bf4159924</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>AI Engineer III</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>CareSource</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Power BI, Tableau, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=640c68fe3716b1e6</t>
+          <t>https://www.indeed.com/viewjob?jk=ab90611f6b141379</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Software Engineer, Back End (Python)</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,34 +5491,34 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Power BI, Tableau, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaf9596bf4159924</t>
+          <t>https://www.indeed.com/viewjob?jk=f65ac6c3f1cf1646</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Cloud Systems Engineer (Databricks Administrator)</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Providge Consulting</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Power BI, Tableau, MLOps, MLflow</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,19 +5536,19 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab90611f6b141379</t>
+          <t>https://www.indeed.com/viewjob?jk=e094ab218ebab2ed</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Python)</t>
+          <t>Sr. ETL/SQL Engineer</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Capgemini Government Solutions</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5561,34 +5561,34 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f65ac6c3f1cf1646</t>
+          <t>https://www.indeed.com/viewjob?jk=724ffe7f1d3da135</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Sr Software Engineer (Site Reliability Engineering) (2026-10114)</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Space Telescope Science Institute</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, MySQL, Splunk</t>
+          <t>AWS, S3, ECS, IAM, Hive, Scala, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,24 +5606,24 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5ab755eddd54b18</t>
+          <t>https://www.indeed.com/viewjob?jk=6055970eb603df79</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>AI Engineer III</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>CareSource</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>API Gateway, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,24 +5641,24 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d44e3274520e56d6</t>
+          <t>https://www.indeed.com/viewjob?jk=640c68fe3716b1e6</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Sr Software Engineer (Site Reliability Engineering) (2026-10114)</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Centene</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,34 +5666,34 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, MySQL, Splunk</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11d92da9c37770a7</t>
+          <t>https://www.indeed.com/viewjob?jk=b5ab755eddd54b18</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>H2O.ai</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5711,24 +5711,24 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe52f92aedddcda4</t>
+          <t>https://www.indeed.com/viewjob?jk=d44e3274520e56d6</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>H2O.ai</t>
+          <t>Centene</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,34 +5736,34 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d2b8979a3b5f81b</t>
+          <t>https://www.indeed.com/viewjob?jk=11d92da9c37770a7</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data &amp; Analytics</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>WesBanco Bank, Inc.</t>
+          <t>H2O.ai</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Bowie, MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -5781,24 +5781,24 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a02cdb2b181be3</t>
+          <t>https://www.indeed.com/viewjob?jk=fe52f92aedddcda4</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data &amp; Analytics</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>WesBanco Bank, Inc.</t>
+          <t>H2O.ai</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Wheeling, WV, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5816,24 +5816,24 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb6ee55d393e301c</t>
+          <t>https://www.indeed.com/viewjob?jk=0d2b8979a3b5f81b</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Software Developer - Database Engineer</t>
+          <t>Senior Data Engineer - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>RAMSOFT</t>
+          <t>WesBanco Bank, Inc.</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Bowie, MD, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, HBase, Scala, Snowflake, MySQL, NoSQL, Data Modeling, Power BI</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -5851,24 +5851,24 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ce0ac7d0a937f32</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a02cdb2b181be3</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>Senior Data Engineer - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>WesBanco Bank, Inc.</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Wheeling, WV, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5886,24 +5886,24 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2b622ee37d8f63f</t>
+          <t>https://www.indeed.com/viewjob?jk=fb6ee55d393e301c</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>Software Developer - Database Engineer</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>RAMSOFT</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, HBase, Scala, Snowflake, MySQL, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ba10ede755adc88</t>
+          <t>https://www.indeed.com/viewjob?jk=4ce0ac7d0a937f32</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=035e833a0affea06</t>
+          <t>https://www.indeed.com/viewjob?jk=e2b622ee37d8f63f</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ea65634bf231fc</t>
+          <t>https://www.indeed.com/viewjob?jk=7ba10ede755adc88</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db2fffa7ab4fc3c6</t>
+          <t>https://www.indeed.com/viewjob?jk=035e833a0affea06</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=726fca60377106fb</t>
+          <t>https://www.indeed.com/viewjob?jk=34ea65634bf231fc</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae1bbd4c5bfc6dc1</t>
+          <t>https://www.indeed.com/viewjob?jk=db2fffa7ab4fc3c6</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d44fb63e0c3570e</t>
+          <t>https://www.indeed.com/viewjob?jk=726fca60377106fb</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac1d3f6a217585b1</t>
+          <t>https://www.indeed.com/viewjob?jk=ae1bbd4c5bfc6dc1</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=594c2209c74b60f3</t>
+          <t>https://www.indeed.com/viewjob?jk=7d44fb63e0c3570e</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=300951fa8a03d9ab</t>
+          <t>https://www.indeed.com/viewjob?jk=ac1d3f6a217585b1</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224f85378fe66226</t>
+          <t>https://www.indeed.com/viewjob?jk=594c2209c74b60f3</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=609ed15647075bf2</t>
+          <t>https://www.indeed.com/viewjob?jk=300951fa8a03d9ab</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7da2bae9861dfa9</t>
+          <t>https://www.indeed.com/viewjob?jk=224f85378fe66226</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f44f95326fb5d8b</t>
+          <t>https://www.indeed.com/viewjob?jk=609ed15647075bf2</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7f6777f3346c150</t>
+          <t>https://www.indeed.com/viewjob?jk=f7da2bae9861dfa9</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99001099f8e56675</t>
+          <t>https://www.indeed.com/viewjob?jk=9f44f95326fb5d8b</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d562fde2d3ab4ec</t>
+          <t>https://www.indeed.com/viewjob?jk=f7f6777f3346c150</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6516,14 +6516,14 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49363af061447f75</t>
+          <t>https://www.indeed.com/viewjob?jk=99001099f8e56675</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python + Distributed systems)</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -6533,7 +6533,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6551,14 +6551,14 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4af4ef5dfeb0026</t>
+          <t>https://www.indeed.com/viewjob?jk=1d562fde2d3ab4ec</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python + Distributed systems)</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -6568,7 +6568,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c116b8acf805f138</t>
+          <t>https://www.indeed.com/viewjob?jk=49363af061447f75</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f996f9a35281bba7</t>
+          <t>https://www.indeed.com/viewjob?jk=c4af4ef5dfeb0026</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca3982c4f2be4e49</t>
+          <t>https://www.indeed.com/viewjob?jk=c116b8acf805f138</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f2a3e577d5623a4</t>
+          <t>https://www.indeed.com/viewjob?jk=f996f9a35281bba7</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=629b89e40e1e1bb5</t>
+          <t>https://www.indeed.com/viewjob?jk=ca3982c4f2be4e49</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db6cf98112c1bc9f</t>
+          <t>https://www.indeed.com/viewjob?jk=9f2a3e577d5623a4</t>
         </is>
       </c>
     </row>
@@ -6778,7 +6778,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80b26c4d48449b15</t>
+          <t>https://www.indeed.com/viewjob?jk=629b89e40e1e1bb5</t>
         </is>
       </c>
     </row>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83ba9763cad5f2f8</t>
+          <t>https://www.indeed.com/viewjob?jk=db6cf98112c1bc9f</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05460d1c364a2974</t>
+          <t>https://www.indeed.com/viewjob?jk=80b26c4d48449b15</t>
         </is>
       </c>
     </row>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b01dc956f073aaf8</t>
+          <t>https://www.indeed.com/viewjob?jk=83ba9763cad5f2f8</t>
         </is>
       </c>
     </row>
@@ -6918,7 +6918,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=807aad5f4045241d</t>
+          <t>https://www.indeed.com/viewjob?jk=05460d1c364a2974</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=655ea21e25dbce1e</t>
+          <t>https://www.indeed.com/viewjob?jk=b01dc956f073aaf8</t>
         </is>
       </c>
     </row>
@@ -6988,7 +6988,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c46ceb995e304d69</t>
+          <t>https://www.indeed.com/viewjob?jk=807aad5f4045241d</t>
         </is>
       </c>
     </row>
@@ -7023,7 +7023,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f29df76fe446a26</t>
+          <t>https://www.indeed.com/viewjob?jk=655ea21e25dbce1e</t>
         </is>
       </c>
     </row>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6574f30d9366e40</t>
+          <t>https://www.indeed.com/viewjob?jk=c46ceb995e304d69</t>
         </is>
       </c>
     </row>
@@ -7093,7 +7093,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8536b186707d6516</t>
+          <t>https://www.indeed.com/viewjob?jk=7f29df76fe446a26</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -7146,7 +7146,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a4c9600c5ead18d</t>
+          <t>https://www.indeed.com/viewjob?jk=d6574f30d9366e40</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -7181,54 +7181,54 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78388f22c8e1c7cc</t>
+          <t>https://www.indeed.com/viewjob?jk=8536b186707d6516</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Data Engineer-Remote</t>
+          <t>Senior Software Engineer (Python + Distributed systems)</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Mutual of Omaha</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Scala, Snowflake, SQL Server, MongoDB, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc1efbee94e32a9</t>
+          <t>https://www.indeed.com/viewjob?jk=6a4c9600c5ead18d</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer (Python + Distributed systems)</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -7237,11 +7237,11 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -7251,24 +7251,24 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed1b9b0328def6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=78388f22c8e1c7cc</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>SAP NS2 Senior HANA Cloud DevOps Engineer</t>
+          <t>AV Safety Engineering Analytics Simulation Engineer (GPSSC)</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -7286,24 +7286,24 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8999a6d9da6831ef</t>
+          <t>https://www.indeed.com/viewjob?jk=4b9eec46bbab109b</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer-Remote</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>Mutual of Omaha</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -7311,34 +7311,34 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Glue, RDS, Scala, Snowflake, SQL Server, MongoDB, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e60ff8bc1e60898</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc1efbee94e32a9</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Callaway Golf</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -7346,34 +7346,34 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ae59fccd3421dc5</t>
+          <t>https://www.indeed.com/viewjob?jk=ed1b9b0328def6aa</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>AV Safety Engineering Analytics Simulation Engineer (GPSSC)</t>
+          <t>SAP NS2 Senior HANA Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -7391,24 +7391,24 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b9eec46bbab109b</t>
+          <t>https://www.indeed.com/viewjob?jk=8999a6d9da6831ef</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Senior AI/ML Scientist</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Milford, MI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -7416,7 +7416,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, MLflow, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -7426,24 +7426,24 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=300d4ca14be662c3</t>
+          <t>https://www.indeed.com/viewjob?jk=2e60ff8bc1e60898</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Visualization Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Callaway Golf</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -7451,24 +7451,24 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>RDS, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD, Git, Python</t>
+          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b28a6ad6f45c5471</t>
+          <t>https://www.indeed.com/viewjob?jk=9ae59fccd3421dc5</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>AV Safety Engineering Analytics Engineer (GPSSC)</t>
+          <t>Senior AI/ML Scientist</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -7496,24 +7496,24 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60da6f50aaadfe48</t>
+          <t>https://www.indeed.com/viewjob?jk=300d4ca14be662c3</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>SENIOR DATA ENGINEER (REMOTE)</t>
+          <t>Visualization Engineer</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Morrison Healthcare</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -7521,34 +7521,34 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Snowflake, ETL, dbt, CI/CD, Azure DevOps</t>
+          <t>RDS, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d530073f998c3698</t>
+          <t>https://www.indeed.com/viewjob?jk=b28a6ad6f45c5471</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Product Engineer</t>
+          <t>AV Safety Engineering Analytics Engineer (GPSSC)</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>ALTIMATE</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -7556,34 +7556,34 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Spark, Scala, PostgreSQL, dbt, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95f4b6534ba4c3cd</t>
+          <t>https://www.indeed.com/viewjob?jk=60da6f50aaadfe48</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>SENIOR DATA ENGINEER (REMOTE)</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Morrison Healthcare</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -7591,34 +7591,34 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Snowflake, ETL, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c61f5469ce333f</t>
+          <t>https://www.indeed.com/viewjob?jk=d530073f998c3698</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Product Engineer</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>ALTIMATE</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -7626,7 +7626,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Spark, Scala, PostgreSQL, dbt, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4303ceb5e8c627c4</t>
+          <t>https://www.indeed.com/viewjob?jk=95f4b6534ba4c3cd</t>
         </is>
       </c>
     </row>
@@ -7653,7 +7653,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D207" t="n">
@@ -7671,24 +7671,24 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c4db6d385ae6ea3</t>
+          <t>https://www.indeed.com/viewjob?jk=50c61f5469ce333f</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Software Engineer (Onsite - San Diego)</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Carlsmed</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D208" t="n">
@@ -7696,24 +7696,24 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, Scala, PostgreSQL, CI/CD, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47ffb86f604e14df</t>
+          <t>https://www.indeed.com/viewjob?jk=4303ceb5e8c627c4</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -7731,34 +7731,34 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c70cf8723aeaf7eb</t>
+          <t>https://www.indeed.com/viewjob?jk=0c4db6d385ae6ea3</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Sr. Full Stack Software Engineer (Onsite - San Diego)</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Carlsmed</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D210" t="n">
@@ -7766,7 +7766,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, Scala, PostgreSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -7776,24 +7776,24 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f106012aaf32c49</t>
+          <t>https://www.indeed.com/viewjob?jk=47ffb86f604e14df</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D211" t="n">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -7811,24 +7811,24 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1593d7242ad3914</t>
+          <t>https://www.indeed.com/viewjob?jk=c70cf8723aeaf7eb</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Snowflake Administrator</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D212" t="n">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -7846,24 +7846,24 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=085de5867e567658</t>
+          <t>https://www.indeed.com/viewjob?jk=6f106012aaf32c49</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>LLM Application Engineer</t>
+          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D213" t="n">
@@ -7871,7 +7871,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -7881,24 +7881,24 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5633278896c16c3b</t>
+          <t>https://www.indeed.com/viewjob?jk=a1593d7242ad3914</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>LLM Application Engineer</t>
+          <t>Teradata Developer</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D214" t="n">
@@ -7906,34 +7906,34 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e56614bfb72e3b3</t>
+          <t>https://www.indeed.com/viewjob?jk=7fddb4ec439f1237</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Teradata Developer</t>
+          <t>Senior BI Developer - Investment Services</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D215" t="n">
@@ -7941,17 +7941,17 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fddb4ec439f1237</t>
+          <t>https://www.indeed.com/viewjob?jk=6861136ad5c92fec</t>
         </is>
       </c>
     </row>
@@ -7968,7 +7968,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D216" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6861136ad5c92fec</t>
+          <t>https://www.indeed.com/viewjob?jk=d0459e004fd012bc</t>
         </is>
       </c>
     </row>
@@ -8003,7 +8003,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D217" t="n">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0459e004fd012bc</t>
+          <t>https://www.indeed.com/viewjob?jk=00bd0c85ee5af1cc</t>
         </is>
       </c>
     </row>
@@ -8038,7 +8038,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D218" t="n">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00bd0c85ee5af1cc</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a227aff44c18bd</t>
         </is>
       </c>
     </row>
@@ -8073,7 +8073,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D219" t="n">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a227aff44c18bd</t>
+          <t>https://www.indeed.com/viewjob?jk=f36e77b3ab4b1808</t>
         </is>
       </c>
     </row>
@@ -8108,7 +8108,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D220" t="n">
@@ -8126,24 +8126,24 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f36e77b3ab4b1808</t>
+          <t>https://www.indeed.com/viewjob?jk=b03b046a7e4b4373</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Senior BI Developer - Investment Services</t>
+          <t>Snowflake Administrator</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D221" t="n">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -8161,7 +8161,77 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b03b046a7e4b4373</t>
+          <t>https://www.indeed.com/viewjob?jk=085de5867e567658</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>LLM Application Engineer</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5633278896c16c3b</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>LLM Application Engineer</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e56614bfb72e3b3</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-06.xlsx
+++ b/results/job_matches_2026-03-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G223"/>
+  <dimension ref="A1:G225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4458,17 +4458,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Digital Engineer – Full Stack &amp; Systems Architecture</t>
+          <t>AWS Developer/Integration Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>rockITdata</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Berkeley, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,17 +4476,17 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, DynamoDB, Amazon QuickSight, CI/CD</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5360d83db3589d68</t>
+          <t>https://www.indeed.com/viewjob?jk=4a60d7d509fbceed</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Berkeley, MO, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12a4a8cde3354706</t>
+          <t>https://www.indeed.com/viewjob?jk=5360d83db3589d68</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Application Platform Architect - 6163848</t>
+          <t>Senior Digital Engineer – Full Stack &amp; Systems Architecture</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Hadoop, Scala, PostgreSQL, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ea7fc0fae83610a</t>
+          <t>https://www.indeed.com/viewjob?jk=12a4a8cde3354706</t>
         </is>
       </c>
     </row>
@@ -4668,17 +4668,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Senior Application Platform Architect - 6163848</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Hard Rock International</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Hollywood, FL, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, Snowflake, PostgreSQL, Cassandra, CI/CD, Terraform</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Hadoop, Scala, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=169d4a00d377fdae</t>
+          <t>https://www.indeed.com/viewjob?jk=7ea7fc0fae83610a</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Search)</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Hard Rock International</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Hollywood, FL, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, Snowflake, PostgreSQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cff2f5a9dcacb28f</t>
+          <t>https://www.indeed.com/viewjob?jk=169d4a00d377fdae</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3216b4c3b2c151f8</t>
+          <t>https://www.indeed.com/viewjob?jk=cff2f5a9dcacb28f</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0fc0424a2f74ea8</t>
+          <t>https://www.indeed.com/viewjob?jk=3216b4c3b2c151f8</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0ff98f788ff107b</t>
+          <t>https://www.indeed.com/viewjob?jk=a0fc0424a2f74ea8</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0442372baf83ee82</t>
+          <t>https://www.indeed.com/viewjob?jk=c0ff98f788ff107b</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe6ea91421159ece</t>
+          <t>https://www.indeed.com/viewjob?jk=0442372baf83ee82</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aecbf4d450f1441b</t>
+          <t>https://www.indeed.com/viewjob?jk=fe6ea91421159ece</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31056dc236b5ce67</t>
+          <t>https://www.indeed.com/viewjob?jk=aecbf4d450f1441b</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eca84bb19e700f2b</t>
+          <t>https://www.indeed.com/viewjob?jk=31056dc236b5ce67</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7401294591da0c90</t>
+          <t>https://www.indeed.com/viewjob?jk=eca84bb19e700f2b</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eed535b1fcfea26</t>
+          <t>https://www.indeed.com/viewjob?jk=7401294591da0c90</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29243583190aa6a</t>
+          <t>https://www.indeed.com/viewjob?jk=5eed535b1fcfea26</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c0d7ebd3a2ee36f</t>
+          <t>https://www.indeed.com/viewjob?jk=b29243583190aa6a</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e3397c0e70024e</t>
+          <t>https://www.indeed.com/viewjob?jk=1c0d7ebd3a2ee36f</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35f50cc085f1bbd9</t>
+          <t>https://www.indeed.com/viewjob?jk=28e3397c0e70024e</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72be3b8aba169a59</t>
+          <t>https://www.indeed.com/viewjob?jk=35f50cc085f1bbd9</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b61af8e418fcf231</t>
+          <t>https://www.indeed.com/viewjob?jk=72be3b8aba169a59</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=552a8172dcf24a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=b61af8e418fcf231</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,32 +5361,32 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fa51ea3c52768d7</t>
+          <t>https://www.indeed.com/viewjob?jk=552a8172dcf24a7a</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Software Engineering Intern – Data Engineering (Cloud &amp; Streaming)</t>
+          <t>Senior Machine Learning Engineer (Search)</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>NextPower</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e588be3c533008</t>
+          <t>https://www.indeed.com/viewjob?jk=4fa51ea3c52768d7</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineering Intern – Data Engineering (Cloud &amp; Streaming)</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NextPower</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Power BI, Tableau, MLOps, MLflow</t>
+          <t>AWS, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaf9596bf4159924</t>
+          <t>https://www.indeed.com/viewjob?jk=28e588be3c533008</t>
         </is>
       </c>
     </row>
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab90611f6b141379</t>
+          <t>https://www.indeed.com/viewjob?jk=aaf9596bf4159924</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Python)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,34 +5491,34 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Power BI, Tableau, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f65ac6c3f1cf1646</t>
+          <t>https://www.indeed.com/viewjob?jk=ab90611f6b141379</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Senior Cloud Systems Engineer (Databricks Administrator)</t>
+          <t>Senior Software Engineer, Back End (Python)</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Providge Consulting</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,34 +5526,34 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Scala, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e094ab218ebab2ed</t>
+          <t>https://www.indeed.com/viewjob?jk=f65ac6c3f1cf1646</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Sr. ETL/SQL Engineer</t>
+          <t>Senior Cloud Systems Engineer (Databricks Administrator)</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Capgemini Government Solutions</t>
+          <t>Providge Consulting</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,24 +5571,24 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724ffe7f1d3da135</t>
+          <t>https://www.indeed.com/viewjob?jk=e094ab218ebab2ed</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Sr. ETL/SQL Engineer</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Space Telescope Science Institute</t>
+          <t>Capgemini Government Solutions</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Hive, Scala, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,24 +5606,24 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6055970eb603df79</t>
+          <t>https://www.indeed.com/viewjob?jk=724ffe7f1d3da135</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>AI Engineer III</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>CareSource</t>
+          <t>Space Telescope Science Institute</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, S3, ECS, IAM, Hive, Scala, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,24 +5641,24 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=640c68fe3716b1e6</t>
+          <t>https://www.indeed.com/viewjob?jk=6055970eb603df79</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Sr Software Engineer (Site Reliability Engineering) (2026-10114)</t>
+          <t>AI Engineer III</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CareSource</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, MySQL, Splunk</t>
+          <t>API Gateway, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,24 +5676,24 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5ab755eddd54b18</t>
+          <t>https://www.indeed.com/viewjob?jk=640c68fe3716b1e6</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr Software Engineer (Site Reliability Engineering) (2026-10114)</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, MySQL, Splunk</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5711,24 +5711,24 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d44e3274520e56d6</t>
+          <t>https://www.indeed.com/viewjob?jk=b5ab755eddd54b18</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Centene</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,34 +5736,34 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11d92da9c37770a7</t>
+          <t>https://www.indeed.com/viewjob?jk=d44e3274520e56d6</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>H2O.ai</t>
+          <t>Centene</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,17 +5771,17 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe52f92aedddcda4</t>
+          <t>https://www.indeed.com/viewjob?jk=11d92da9c37770a7</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,24 +5816,24 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d2b8979a3b5f81b</t>
+          <t>https://www.indeed.com/viewjob?jk=fe52f92aedddcda4</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data &amp; Analytics</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>WesBanco Bank, Inc.</t>
+          <t>H2O.ai</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Bowie, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a02cdb2b181be3</t>
+          <t>https://www.indeed.com/viewjob?jk=0d2b8979a3b5f81b</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Wheeling, WV, US USA</t>
+          <t>Bowie, MD, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,24 +5886,24 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb6ee55d393e301c</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a02cdb2b181be3</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Software Developer - Database Engineer</t>
+          <t>Senior Data Engineer - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>RAMSOFT</t>
+          <t>WesBanco Bank, Inc.</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Wheeling, WV, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, HBase, Scala, Snowflake, MySQL, NoSQL, Data Modeling, Power BI</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5921,24 +5921,24 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ce0ac7d0a937f32</t>
+          <t>https://www.indeed.com/viewjob?jk=fb6ee55d393e301c</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>Software Developer - Database Engineer</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>RAMSOFT</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, HBase, Scala, Snowflake, MySQL, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2b622ee37d8f63f</t>
+          <t>https://www.indeed.com/viewjob?jk=4ce0ac7d0a937f32</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ba10ede755adc88</t>
+          <t>https://www.indeed.com/viewjob?jk=e2b622ee37d8f63f</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=035e833a0affea06</t>
+          <t>https://www.indeed.com/viewjob?jk=7ba10ede755adc88</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ea65634bf231fc</t>
+          <t>https://www.indeed.com/viewjob?jk=035e833a0affea06</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db2fffa7ab4fc3c6</t>
+          <t>https://www.indeed.com/viewjob?jk=34ea65634bf231fc</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=726fca60377106fb</t>
+          <t>https://www.indeed.com/viewjob?jk=db2fffa7ab4fc3c6</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae1bbd4c5bfc6dc1</t>
+          <t>https://www.indeed.com/viewjob?jk=726fca60377106fb</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d44fb63e0c3570e</t>
+          <t>https://www.indeed.com/viewjob?jk=ae1bbd4c5bfc6dc1</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac1d3f6a217585b1</t>
+          <t>https://www.indeed.com/viewjob?jk=7d44fb63e0c3570e</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=594c2209c74b60f3</t>
+          <t>https://www.indeed.com/viewjob?jk=ac1d3f6a217585b1</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=300951fa8a03d9ab</t>
+          <t>https://www.indeed.com/viewjob?jk=594c2209c74b60f3</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224f85378fe66226</t>
+          <t>https://www.indeed.com/viewjob?jk=300951fa8a03d9ab</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=609ed15647075bf2</t>
+          <t>https://www.indeed.com/viewjob?jk=224f85378fe66226</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7da2bae9861dfa9</t>
+          <t>https://www.indeed.com/viewjob?jk=609ed15647075bf2</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f44f95326fb5d8b</t>
+          <t>https://www.indeed.com/viewjob?jk=f7da2bae9861dfa9</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7f6777f3346c150</t>
+          <t>https://www.indeed.com/viewjob?jk=9f44f95326fb5d8b</t>
         </is>
       </c>
     </row>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99001099f8e56675</t>
+          <t>https://www.indeed.com/viewjob?jk=f7f6777f3346c150</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d562fde2d3ab4ec</t>
+          <t>https://www.indeed.com/viewjob?jk=99001099f8e56675</t>
         </is>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6586,14 +6586,14 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49363af061447f75</t>
+          <t>https://www.indeed.com/viewjob?jk=1d562fde2d3ab4ec</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python + Distributed systems)</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4af4ef5dfeb0026</t>
+          <t>https://www.indeed.com/viewjob?jk=49363af061447f75</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c116b8acf805f138</t>
+          <t>https://www.indeed.com/viewjob?jk=c4af4ef5dfeb0026</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f996f9a35281bba7</t>
+          <t>https://www.indeed.com/viewjob?jk=c116b8acf805f138</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca3982c4f2be4e49</t>
+          <t>https://www.indeed.com/viewjob?jk=f996f9a35281bba7</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f2a3e577d5623a4</t>
+          <t>https://www.indeed.com/viewjob?jk=ca3982c4f2be4e49</t>
         </is>
       </c>
     </row>
@@ -6778,7 +6778,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=629b89e40e1e1bb5</t>
+          <t>https://www.indeed.com/viewjob?jk=9f2a3e577d5623a4</t>
         </is>
       </c>
     </row>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db6cf98112c1bc9f</t>
+          <t>https://www.indeed.com/viewjob?jk=629b89e40e1e1bb5</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80b26c4d48449b15</t>
+          <t>https://www.indeed.com/viewjob?jk=db6cf98112c1bc9f</t>
         </is>
       </c>
     </row>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83ba9763cad5f2f8</t>
+          <t>https://www.indeed.com/viewjob?jk=80b26c4d48449b15</t>
         </is>
       </c>
     </row>
@@ -6918,7 +6918,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05460d1c364a2974</t>
+          <t>https://www.indeed.com/viewjob?jk=83ba9763cad5f2f8</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b01dc956f073aaf8</t>
+          <t>https://www.indeed.com/viewjob?jk=05460d1c364a2974</t>
         </is>
       </c>
     </row>
@@ -6988,7 +6988,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=807aad5f4045241d</t>
+          <t>https://www.indeed.com/viewjob?jk=b01dc956f073aaf8</t>
         </is>
       </c>
     </row>
@@ -7023,7 +7023,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=655ea21e25dbce1e</t>
+          <t>https://www.indeed.com/viewjob?jk=807aad5f4045241d</t>
         </is>
       </c>
     </row>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c46ceb995e304d69</t>
+          <t>https://www.indeed.com/viewjob?jk=655ea21e25dbce1e</t>
         </is>
       </c>
     </row>
@@ -7093,7 +7093,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f29df76fe446a26</t>
+          <t>https://www.indeed.com/viewjob?jk=c46ceb995e304d69</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -7146,7 +7146,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6574f30d9366e40</t>
+          <t>https://www.indeed.com/viewjob?jk=7f29df76fe446a26</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7163,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8536b186707d6516</t>
+          <t>https://www.indeed.com/viewjob?jk=d6574f30d9366e40</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a4c9600c5ead18d</t>
+          <t>https://www.indeed.com/viewjob?jk=8536b186707d6516</t>
         </is>
       </c>
     </row>
@@ -7233,7 +7233,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -7251,32 +7251,32 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78388f22c8e1c7cc</t>
+          <t>https://www.indeed.com/viewjob?jk=6a4c9600c5ead18d</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>AV Safety Engineering Analytics Simulation Engineer (GPSSC)</t>
+          <t>Senior Software Engineer (Python + Distributed systems)</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -7286,19 +7286,19 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b9eec46bbab109b</t>
+          <t>https://www.indeed.com/viewjob?jk=78388f22c8e1c7cc</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Data Engineer-Remote</t>
+          <t>AV Safety Engineering Analytics Simulation Engineer (GPSSC)</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Mutual of Omaha</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -7311,34 +7311,34 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Scala, Snowflake, SQL Server, MongoDB, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc1efbee94e32a9</t>
+          <t>https://www.indeed.com/viewjob?jk=4b9eec46bbab109b</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AWS Cloud Administrator</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>rockITdata</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -7346,34 +7346,34 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, Azure, DynamoDB, Terraform</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed1b9b0328def6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0a98e5951373b4</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>SAP NS2 Senior HANA Cloud DevOps Engineer</t>
+          <t>Data Engineer-Remote</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Mutual of Omaha</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -7381,34 +7381,34 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Glue, RDS, Scala, Snowflake, SQL Server, MongoDB, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8999a6d9da6831ef</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc1efbee94e32a9</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -7416,7 +7416,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -7426,24 +7426,24 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e60ff8bc1e60898</t>
+          <t>https://www.indeed.com/viewjob?jk=ed1b9b0328def6aa</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>SAP NS2 Senior HANA Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Callaway Golf</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -7451,34 +7451,34 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
+          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ae59fccd3421dc5</t>
+          <t>https://www.indeed.com/viewjob?jk=8999a6d9da6831ef</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Senior AI/ML Scientist</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Milford, MI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, MLflow, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -7496,24 +7496,24 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=300d4ca14be662c3</t>
+          <t>https://www.indeed.com/viewjob?jk=2e60ff8bc1e60898</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Visualization Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Callaway Golf</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -7521,34 +7521,34 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>RDS, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD, Git, Python</t>
+          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b28a6ad6f45c5471</t>
+          <t>https://www.indeed.com/viewjob?jk=9ae59fccd3421dc5</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>AV Safety Engineering Analytics Engineer (GPSSC)</t>
+          <t>Visualization Engineer</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>RDS, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -7566,24 +7566,24 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60da6f50aaadfe48</t>
+          <t>https://www.indeed.com/viewjob?jk=b28a6ad6f45c5471</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>SENIOR DATA ENGINEER (REMOTE)</t>
+          <t>AV Safety Engineering Analytics Engineer (GPSSC)</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Morrison Healthcare</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -7591,34 +7591,34 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Snowflake, ETL, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d530073f998c3698</t>
+          <t>https://www.indeed.com/viewjob?jk=60da6f50aaadfe48</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Product Engineer</t>
+          <t>Senior AI/ML Scientist</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>ALTIMATE</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -7626,34 +7626,34 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Spark, Scala, PostgreSQL, dbt, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95f4b6534ba4c3cd</t>
+          <t>https://www.indeed.com/viewjob?jk=300d4ca14be662c3</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>SENIOR DATA ENGINEER (REMOTE)</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Morrison Healthcare</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D207" t="n">
@@ -7661,34 +7661,34 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Snowflake, ETL, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c61f5469ce333f</t>
+          <t>https://www.indeed.com/viewjob?jk=d530073f998c3698</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Product Engineer</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>ALTIMATE</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D208" t="n">
@@ -7696,7 +7696,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Spark, Scala, PostgreSQL, dbt, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4303ceb5e8c627c4</t>
+          <t>https://www.indeed.com/viewjob?jk=95f4b6534ba4c3cd</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D209" t="n">
@@ -7741,24 +7741,24 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c4db6d385ae6ea3</t>
+          <t>https://www.indeed.com/viewjob?jk=50c61f5469ce333f</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Software Engineer (Onsite - San Diego)</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Carlsmed</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D210" t="n">
@@ -7766,24 +7766,24 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, Scala, PostgreSQL, CI/CD, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47ffb86f604e14df</t>
+          <t>https://www.indeed.com/viewjob?jk=4303ceb5e8c627c4</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -7801,34 +7801,34 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c70cf8723aeaf7eb</t>
+          <t>https://www.indeed.com/viewjob?jk=0c4db6d385ae6ea3</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Sr. Full Stack Software Engineer (Onsite - San Diego)</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Carlsmed</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D212" t="n">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, Scala, PostgreSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -7846,24 +7846,24 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f106012aaf32c49</t>
+          <t>https://www.indeed.com/viewjob?jk=47ffb86f604e14df</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D213" t="n">
@@ -7871,7 +7871,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -7881,24 +7881,24 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1593d7242ad3914</t>
+          <t>https://www.indeed.com/viewjob?jk=c70cf8723aeaf7eb</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Teradata Developer</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D214" t="n">
@@ -7906,34 +7906,34 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fddb4ec439f1237</t>
+          <t>https://www.indeed.com/viewjob?jk=6f106012aaf32c49</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Senior BI Developer - Investment Services</t>
+          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D215" t="n">
@@ -7941,7 +7941,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -7951,24 +7951,24 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6861136ad5c92fec</t>
+          <t>https://www.indeed.com/viewjob?jk=a1593d7242ad3914</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Senior BI Developer - Investment Services</t>
+          <t>Snowflake Administrator</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D216" t="n">
@@ -7976,7 +7976,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -7986,24 +7986,24 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0459e004fd012bc</t>
+          <t>https://www.indeed.com/viewjob?jk=085de5867e567658</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Senior BI Developer - Investment Services</t>
+          <t>LLM Application Engineer</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D217" t="n">
@@ -8011,7 +8011,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -8021,24 +8021,24 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00bd0c85ee5af1cc</t>
+          <t>https://www.indeed.com/viewjob?jk=5633278896c16c3b</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Senior BI Developer - Investment Services</t>
+          <t>LLM Application Engineer</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D218" t="n">
@@ -8046,7 +8046,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -8056,24 +8056,24 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a227aff44c18bd</t>
+          <t>https://www.indeed.com/viewjob?jk=4e56614bfb72e3b3</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Senior BI Developer - Investment Services</t>
+          <t>Teradata Developer</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D219" t="n">
@@ -8081,17 +8081,17 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f36e77b3ab4b1808</t>
+          <t>https://www.indeed.com/viewjob?jk=7fddb4ec439f1237</t>
         </is>
       </c>
     </row>
@@ -8108,7 +8108,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D220" t="n">
@@ -8126,24 +8126,24 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b03b046a7e4b4373</t>
+          <t>https://www.indeed.com/viewjob?jk=6861136ad5c92fec</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Snowflake Administrator</t>
+          <t>Senior BI Developer - Investment Services</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D221" t="n">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -8161,24 +8161,24 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=085de5867e567658</t>
+          <t>https://www.indeed.com/viewjob?jk=d0459e004fd012bc</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>LLM Application Engineer</t>
+          <t>Senior BI Developer - Investment Services</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D222" t="n">
@@ -8186,7 +8186,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -8196,24 +8196,24 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5633278896c16c3b</t>
+          <t>https://www.indeed.com/viewjob?jk=00bd0c85ee5af1cc</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>LLM Application Engineer</t>
+          <t>Senior BI Developer - Investment Services</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D223" t="n">
@@ -8221,7 +8221,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -8231,7 +8231,77 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e56614bfb72e3b3</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a227aff44c18bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Senior BI Developer - Investment Services</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Milwaukee, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f36e77b3ab4b1808</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Senior BI Developer - Investment Services</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Hopkins, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D225" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b03b046a7e4b4373</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-06.xlsx
+++ b/results/job_matches_2026-03-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G225"/>
+  <dimension ref="A1:G226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=157ddcd0636f7c11</t>
+          <t>https://www.indeed.com/viewjob?jk=0c8a098e9a2c0e1a</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BOULDER SCIENTIFIC CO</t>
+          <t>PetSmart</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Longmont, CO, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9486135c47b58364</t>
+          <t>https://www.indeed.com/viewjob?jk=157ddcd0636f7c11</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>BOULDER SCIENTIFIC CO</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Longmont, CO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba5a22f3941b5b26</t>
+          <t>https://www.indeed.com/viewjob?jk=9486135c47b58364</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AI Support Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=625bf5ef0b332ad3</t>
+          <t>https://www.indeed.com/viewjob?jk=ba5a22f3941b5b26</t>
         </is>
       </c>
     </row>
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd39a203b7587e31</t>
+          <t>https://www.indeed.com/viewjob?jk=625bf5ef0b332ad3</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Support Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Yusen Logistics</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kimball, ELT, dbt</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f92de33105c0bad</t>
+          <t>https://www.indeed.com/viewjob?jk=dd39a203b7587e31</t>
         </is>
       </c>
     </row>
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=772460af87c5b60c</t>
+          <t>https://www.indeed.com/viewjob?jk=7f92de33105c0bad</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Yusen Logistics</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Royal Oak, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bb3681c5da818f2</t>
+          <t>https://www.indeed.com/viewjob?jk=772460af87c5b60c</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Royal Oak, MI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=343b07159d1b6928</t>
+          <t>https://www.indeed.com/viewjob?jk=6bb3681c5da818f2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer - Virtual</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Alight Solutions</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a286c7ca862c4e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=343b07159d1b6928</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Cloud Platform Engineer - Virtual</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>TWG Global AI</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edb6a72ac37333e2</t>
+          <t>https://www.indeed.com/viewjob?jk=a286c7ca862c4e1a</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>AllCloud</t>
+          <t>TWG Global AI</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49fcd1d4ac195cdf</t>
+          <t>https://www.indeed.com/viewjob?jk=edb6a72ac37333e2</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>IT BI Solutions Engineer, ES</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Terex Corporation</t>
+          <t>AllCloud</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chattanooga, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8376f8e501b07a8</t>
+          <t>https://www.indeed.com/viewjob?jk=49fcd1d4ac195cdf</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>IT BI Solutions Engineer, ES</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Terex Corporation</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chattanooga, TN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Medallion Architecture, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions, AWS CodePipeline</t>
+          <t>AWS, Redshift, RDS, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83c604950fd47a32</t>
+          <t>https://www.indeed.com/viewjob?jk=e8376f8e501b07a8</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-3</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, Step Functions, Medallion Architecture, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions, AWS CodePipeline</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f753e538739bd670</t>
+          <t>https://www.indeed.com/viewjob?jk=83c604950fd47a32</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Junior AI/MLOps Engineer</t>
+          <t>Data Platform Engineer-3</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, NoSQL, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe34817d3b1a40dc</t>
+          <t>https://www.indeed.com/viewjob?jk=f753e538739bd670</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Junior AI/MLOps Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, NoSQL, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90d33ae33b62c3a0</t>
+          <t>https://www.indeed.com/viewjob?jk=fe34817d3b1a40dc</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec56a8fbf5328856</t>
+          <t>https://www.indeed.com/viewjob?jk=90d33ae33b62c3a0</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,14 +2386,14 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d4834b7dd63e5a3</t>
+          <t>https://www.indeed.com/viewjob?jk=ec56a8fbf5328856</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,14 +2421,14 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=314cd9d2f824e302</t>
+          <t>https://www.indeed.com/viewjob?jk=3d4834b7dd63e5a3</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec0d14ba7f6cc782</t>
+          <t>https://www.indeed.com/viewjob?jk=314cd9d2f824e302</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,14 +2491,14 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd9783225b203a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=ec0d14ba7f6cc782</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,14 +2526,14 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fcdb3a443f803a9</t>
+          <t>https://www.indeed.com/viewjob?jk=cd9783225b203a0f</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=154ab74a68ca6406</t>
+          <t>https://www.indeed.com/viewjob?jk=5fcdb3a443f803a9</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31f45e1ed037bd50</t>
+          <t>https://www.indeed.com/viewjob?jk=154ab74a68ca6406</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5d14ef4e88a3e5a</t>
+          <t>https://www.indeed.com/viewjob?jk=31f45e1ed037bd50</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f6ccf05e64c984b</t>
+          <t>https://www.indeed.com/viewjob?jk=f5d14ef4e88a3e5a</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,14 +2701,14 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b4b4f98c48563cd</t>
+          <t>https://www.indeed.com/viewjob?jk=5f6ccf05e64c984b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6c2c604bb89e64b</t>
+          <t>https://www.indeed.com/viewjob?jk=7b4b4f98c48563cd</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,14 +2771,14 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e02fe4d607063c1</t>
+          <t>https://www.indeed.com/viewjob?jk=c6c2c604bb89e64b</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,14 +2806,14 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fbafb89e71fb39e</t>
+          <t>https://www.indeed.com/viewjob?jk=6e02fe4d607063c1</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8ac438ef838975b</t>
+          <t>https://www.indeed.com/viewjob?jk=9fbafb89e71fb39e</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74bd0f0f93d9a1a5</t>
+          <t>https://www.indeed.com/viewjob?jk=e8ac438ef838975b</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,14 +2911,14 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c53e85e359970d4</t>
+          <t>https://www.indeed.com/viewjob?jk=74bd0f0f93d9a1a5</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c433c70839583dc</t>
+          <t>https://www.indeed.com/viewjob?jk=4c53e85e359970d4</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35e828bfc556b676</t>
+          <t>https://www.indeed.com/viewjob?jk=0c433c70839583dc</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,14 +3016,14 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3058b24332d31ded</t>
+          <t>https://www.indeed.com/viewjob?jk=35e828bfc556b676</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10e23f958e9e8b09</t>
+          <t>https://www.indeed.com/viewjob?jk=3058b24332d31ded</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=357547d890623cb5</t>
+          <t>https://www.indeed.com/viewjob?jk=10e23f958e9e8b09</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,14 +3121,14 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3884844e18945dee</t>
+          <t>https://www.indeed.com/viewjob?jk=357547d890623cb5</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17b7c64ee8dc67e0</t>
+          <t>https://www.indeed.com/viewjob?jk=3884844e18945dee</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a75982d2aedba052</t>
+          <t>https://www.indeed.com/viewjob?jk=17b7c64ee8dc67e0</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,14 +3226,14 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b3d8d96e19fcbe6</t>
+          <t>https://www.indeed.com/viewjob?jk=a75982d2aedba052</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a60a56d62d329dea</t>
+          <t>https://www.indeed.com/viewjob?jk=4b3d8d96e19fcbe6</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93902824d8ac4d0c</t>
+          <t>https://www.indeed.com/viewjob?jk=a60a56d62d329dea</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=088398b8f22d3683</t>
+          <t>https://www.indeed.com/viewjob?jk=93902824d8ac4d0c</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f8a4d4b303056b</t>
+          <t>https://www.indeed.com/viewjob?jk=088398b8f22d3683</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,14 +3401,14 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=459cc0fec55fdc6f</t>
+          <t>https://www.indeed.com/viewjob?jk=60f8a4d4b303056b</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,14 +3436,14 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a58d376929282400</t>
+          <t>https://www.indeed.com/viewjob?jk=459cc0fec55fdc6f</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,14 +3471,14 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=521ae718282fb788</t>
+          <t>https://www.indeed.com/viewjob?jk=a58d376929282400</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,14 +3506,14 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=559d1352317c1f33</t>
+          <t>https://www.indeed.com/viewjob?jk=521ae718282fb788</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=361e87b55f4161f4</t>
+          <t>https://www.indeed.com/viewjob?jk=559d1352317c1f33</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32e0b2833cebefe3</t>
+          <t>https://www.indeed.com/viewjob?jk=361e87b55f4161f4</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,59 +3611,59 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f5df27af3031e62</t>
+          <t>https://www.indeed.com/viewjob?jk=32e0b2833cebefe3</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, MongoDB, Data Modeling</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb77847b7cd88f45</t>
+          <t>https://www.indeed.com/viewjob?jk=9f5df27af3031e62</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,17 +3671,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d20f4b9e6a3cbb70</t>
+          <t>https://www.indeed.com/viewjob?jk=eb77847b7cd88f45</t>
         </is>
       </c>
     </row>
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c89d6a7d2041de38</t>
+          <t>https://www.indeed.com/viewjob?jk=d20f4b9e6a3cbb70</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Teradata</t>
+          <t>Genentech</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Step Functions, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=806bff32d1d719ff</t>
+          <t>https://www.indeed.com/viewjob?jk=c89d6a7d2041de38</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Teradata</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fedd79bbbee99bb</t>
+          <t>https://www.indeed.com/viewjob?jk=806bff32d1d719ff</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend + Data pipelines)</t>
+          <t>Senior Site Reliability Developer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4fca4ad337ae6c</t>
+          <t>https://www.indeed.com/viewjob?jk=3fedd79bbbee99bb</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ae76b185563f91b</t>
+          <t>https://www.indeed.com/viewjob?jk=7d4fca4ad337ae6c</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef2a73b324528506</t>
+          <t>https://www.indeed.com/viewjob?jk=1ae76b185563f91b</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92aaafaf1efb9ec4</t>
+          <t>https://www.indeed.com/viewjob?jk=ef2a73b324528506</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9981aefe519f0cd</t>
+          <t>https://www.indeed.com/viewjob?jk=92aaafaf1efb9ec4</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fce2095df8206466</t>
+          <t>https://www.indeed.com/viewjob?jk=c9981aefe519f0cd</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee34633b7838a9b3</t>
+          <t>https://www.indeed.com/viewjob?jk=fce2095df8206466</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc57f588c654f1cd</t>
+          <t>https://www.indeed.com/viewjob?jk=ee34633b7838a9b3</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5aaeb4c54cdfa77e</t>
+          <t>https://www.indeed.com/viewjob?jk=cc57f588c654f1cd</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb06d74f6367bb04</t>
+          <t>https://www.indeed.com/viewjob?jk=5aaeb4c54cdfa77e</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49799e02e3e0a925</t>
+          <t>https://www.indeed.com/viewjob?jk=eb06d74f6367bb04</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52ff9083bc8990ce</t>
+          <t>https://www.indeed.com/viewjob?jk=49799e02e3e0a925</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f89817131cfa0d</t>
+          <t>https://www.indeed.com/viewjob?jk=52ff9083bc8990ce</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdb757efdefad0ca</t>
+          <t>https://www.indeed.com/viewjob?jk=66f89817131cfa0d</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57fc4e97a319b123</t>
+          <t>https://www.indeed.com/viewjob?jk=cdb757efdefad0ca</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fcc67143e3ff8a</t>
+          <t>https://www.indeed.com/viewjob?jk=57fc4e97a319b123</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dad4bf1e950e1c9</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fcc67143e3ff8a</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f9ed5d278a8086d</t>
+          <t>https://www.indeed.com/viewjob?jk=5dad4bf1e950e1c9</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8809421834292084</t>
+          <t>https://www.indeed.com/viewjob?jk=0f9ed5d278a8086d</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>AWS Developer/Integration Engineer</t>
+          <t>Software Engineer II (Backend + Data pipelines)</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>rockITdata</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, DynamoDB, Amazon QuickSight, CI/CD</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a60d7d509fbceed</t>
+          <t>https://www.indeed.com/viewjob?jk=8809421834292084</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Digital Engineer – Full Stack &amp; Systems Architecture</t>
+          <t>AWS Developer/Integration Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>rockITdata</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Berkeley, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,17 +4511,17 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, DynamoDB, Amazon QuickSight, CI/CD</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5360d83db3589d68</t>
+          <t>https://www.indeed.com/viewjob?jk=4a60d7d509fbceed</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Berkeley, MO, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12a4a8cde3354706</t>
+          <t>https://www.indeed.com/viewjob?jk=5360d83db3589d68</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior LLM Engineer</t>
+          <t>Senior Digital Engineer – Full Stack &amp; Systems Architecture</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, MLOps</t>
+          <t>AWS, IAM, RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109c9c4a6595ba95</t>
+          <t>https://www.indeed.com/viewjob?jk=12a4a8cde3354706</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior LLM Engineer</t>
+          <t>Senior Application Platform Architect - 6163848</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, MLOps</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Hadoop, Scala, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8723fa94634ae387</t>
+          <t>https://www.indeed.com/viewjob?jk=7ea7fc0fae83610a</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior LLM Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>LERETA, LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Pomona, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
+          <t>AWS, Azure, Vertex AI, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad5d067156fc62f1</t>
+          <t>https://www.indeed.com/viewjob?jk=109c9c4a6595ba95</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Application Platform Architect - 6163848</t>
+          <t>Senior LLM Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Hadoop, Scala, PostgreSQL, CI/CD, Docker</t>
+          <t>AWS, Azure, Vertex AI, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ea7fc0fae83610a</t>
+          <t>https://www.indeed.com/viewjob?jk=8723fa94634ae387</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Hard Rock International</t>
+          <t>LERETA, LLC</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Hollywood, FL, US USA</t>
+          <t>Pomona, CA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, Snowflake, PostgreSQL, Cassandra, CI/CD, Terraform</t>
+          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=169d4a00d377fdae</t>
+          <t>https://www.indeed.com/viewjob?jk=ad5d067156fc62f1</t>
         </is>
       </c>
     </row>
@@ -7538,17 +7538,17 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Visualization Engineer</t>
+          <t>Software Engineer Intern</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -7556,34 +7556,34 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>RDS, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b28a6ad6f45c5471</t>
+          <t>https://www.indeed.com/viewjob?jk=c65c6376729ba486</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>AV Safety Engineering Analytics Engineer (GPSSC)</t>
+          <t>Visualization Engineer</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -7591,7 +7591,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>RDS, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60da6f50aaadfe48</t>
+          <t>https://www.indeed.com/viewjob?jk=b28a6ad6f45c5471</t>
         </is>
       </c>
     </row>
@@ -7643,17 +7643,17 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>SENIOR DATA ENGINEER (REMOTE)</t>
+          <t>AV Safety Engineering Analytics Engineer (GPSSC)</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Morrison Healthcare</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D207" t="n">
@@ -7661,34 +7661,34 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Snowflake, ETL, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d530073f998c3698</t>
+          <t>https://www.indeed.com/viewjob?jk=60da6f50aaadfe48</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Product Engineer</t>
+          <t>SENIOR DATA ENGINEER (REMOTE)</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>ALTIMATE</t>
+          <t>Morrison Healthcare</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D208" t="n">
@@ -7696,34 +7696,34 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Spark, Scala, PostgreSQL, dbt, Kubernetes, Airflow, Git</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Snowflake, ETL, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95f4b6534ba4c3cd</t>
+          <t>https://www.indeed.com/viewjob?jk=d530073f998c3698</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Product Engineer</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>ALTIMATE</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D209" t="n">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Spark, Scala, PostgreSQL, dbt, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -7741,7 +7741,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c61f5469ce333f</t>
+          <t>https://www.indeed.com/viewjob?jk=95f4b6534ba4c3cd</t>
         </is>
       </c>
     </row>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D210" t="n">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4303ceb5e8c627c4</t>
+          <t>https://www.indeed.com/viewjob?jk=50c61f5469ce333f</t>
         </is>
       </c>
     </row>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D211" t="n">
@@ -7811,24 +7811,24 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c4db6d385ae6ea3</t>
+          <t>https://www.indeed.com/viewjob?jk=4303ceb5e8c627c4</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Software Engineer (Onsite - San Diego)</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Carlsmed</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D212" t="n">
@@ -7836,34 +7836,34 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, Scala, PostgreSQL, CI/CD, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47ffb86f604e14df</t>
+          <t>https://www.indeed.com/viewjob?jk=0c4db6d385ae6ea3</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Sr. Full Stack Software Engineer (Onsite - San Diego)</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Carlsmed</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D213" t="n">
@@ -7871,7 +7871,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, Scala, PostgreSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c70cf8723aeaf7eb</t>
+          <t>https://www.indeed.com/viewjob?jk=47ffb86f604e14df</t>
         </is>
       </c>
     </row>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D214" t="n">
@@ -7916,24 +7916,24 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f106012aaf32c49</t>
+          <t>https://www.indeed.com/viewjob?jk=c70cf8723aeaf7eb</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D215" t="n">
@@ -7941,7 +7941,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -7951,24 +7951,24 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1593d7242ad3914</t>
+          <t>https://www.indeed.com/viewjob?jk=6f106012aaf32c49</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Snowflake Administrator</t>
+          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D216" t="n">
@@ -7976,7 +7976,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -7986,24 +7986,24 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=085de5867e567658</t>
+          <t>https://www.indeed.com/viewjob?jk=a1593d7242ad3914</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>LLM Application Engineer</t>
+          <t>Snowflake Administrator</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D217" t="n">
@@ -8011,7 +8011,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -8021,7 +8021,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5633278896c16c3b</t>
+          <t>https://www.indeed.com/viewjob?jk=085de5867e567658</t>
         </is>
       </c>
     </row>
@@ -8056,24 +8056,24 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e56614bfb72e3b3</t>
+          <t>https://www.indeed.com/viewjob?jk=5633278896c16c3b</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Teradata Developer</t>
+          <t>LLM Application Engineer</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D219" t="n">
@@ -8081,34 +8081,34 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fddb4ec439f1237</t>
+          <t>https://www.indeed.com/viewjob?jk=4e56614bfb72e3b3</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Senior BI Developer - Investment Services</t>
+          <t>Teradata Developer</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D220" t="n">
@@ -8116,17 +8116,17 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6861136ad5c92fec</t>
+          <t>https://www.indeed.com/viewjob?jk=7fddb4ec439f1237</t>
         </is>
       </c>
     </row>
@@ -8143,7 +8143,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D221" t="n">
@@ -8161,7 +8161,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0459e004fd012bc</t>
+          <t>https://www.indeed.com/viewjob?jk=6861136ad5c92fec</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D222" t="n">
@@ -8196,7 +8196,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00bd0c85ee5af1cc</t>
+          <t>https://www.indeed.com/viewjob?jk=d0459e004fd012bc</t>
         </is>
       </c>
     </row>
@@ -8213,7 +8213,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D223" t="n">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a227aff44c18bd</t>
+          <t>https://www.indeed.com/viewjob?jk=00bd0c85ee5af1cc</t>
         </is>
       </c>
     </row>
@@ -8248,7 +8248,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D224" t="n">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f36e77b3ab4b1808</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a227aff44c18bd</t>
         </is>
       </c>
     </row>
@@ -8283,7 +8283,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D225" t="n">
@@ -8300,6 +8300,41 @@
         </is>
       </c>
       <c r="G225" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f36e77b3ab4b1808</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Senior BI Developer - Investment Services</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>U.S. Bank</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Hopkins, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D226" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b03b046a7e4b4373</t>
         </is>

--- a/results/job_matches_2026-03-06.xlsx
+++ b/results/job_matches_2026-03-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G226"/>
+  <dimension ref="A1:G206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -928,12 +928,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>JBS Dev</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32d044bc27a4af8a</t>
+          <t>https://www.indeed.com/viewjob?jk=49f6c2df00dd6e11</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (Costa Rica)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>JBS Dev</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aed60e56cae31294</t>
+          <t>https://www.indeed.com/viewjob?jk=05c819aa2a88511d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>System Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Systems Engineering Solutions Corporation</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,42 +1011,42 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44f958ba0cbc0f43</t>
+          <t>https://www.indeed.com/viewjob?jk=634fcd15ef04d7bf</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JBS Dev</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49f6c2df00dd6e11</t>
+          <t>https://www.indeed.com/viewjob?jk=c7869ee373ec84ed</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Costa Rica)</t>
+          <t>CLOUD ENGINEER (AWS) (REMOTE/USA) - GDM (GRAY MEDIA GROUP)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>JBS Dev</t>
+          <t>GRAY MEDIA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05c819aa2a88511d</t>
+          <t>https://www.indeed.com/viewjob?jk=0beb94e2f1648144</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>System Architect</t>
+          <t>Senior Software Engineer - Clinical Systems (Lab Ops)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Systems Engineering Solutions Corporation</t>
+          <t>Caris Life Sciences</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, GCP, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=634fcd15ef04d7bf</t>
+          <t>https://www.indeed.com/viewjob?jk=fb8de235a110895a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7869ee373ec84ed</t>
+          <t>https://www.indeed.com/viewjob?jk=afa51ac883fa48a6</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CLOUD ENGINEER (AWS) (REMOTE/USA) - GDM (GRAY MEDIA GROUP)</t>
+          <t>Senior BI Analyst</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GRAY MEDIA</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0beb94e2f1648144</t>
+          <t>https://www.indeed.com/viewjob?jk=ad414f3a9ab0a2bc</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Clinical Systems (Lab Ops)</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Caris Life Sciences</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, GCP, Scala, PostgreSQL</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb8de235a110895a</t>
+          <t>https://www.indeed.com/viewjob?jk=459162c660bc8082</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>Upstart</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Scala, Snowflake</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,67 +1266,67 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e83bd0fd320bb829</t>
+          <t>https://www.indeed.com/viewjob?jk=3dab96c17b78fc32</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer III - AI/ML</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tulsa, OK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, Kafka, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=105f562c4b87c831</t>
+          <t>https://www.indeed.com/viewjob?jk=fcd181016bc08a7a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Azure CI/CD Developer (FTE / Hybrid)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Koch</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>Oaks, PA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56a2fccd9b09c654</t>
+          <t>https://www.indeed.com/viewjob?jk=ffe5d7e4f5833213</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
+          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afa51ac883fa48a6</t>
+          <t>https://www.indeed.com/viewjob?jk=f059a12d002721db</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior BI Analyst</t>
+          <t>Software Engineer III- Python/PySpark</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad414f3a9ab0a2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=82b1dd2ce5d3671a</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Sr Software Development Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=459162c660bc8082</t>
+          <t>https://www.indeed.com/viewjob?jk=6efe960a7ab141ac</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>SENIOR DATA ENGINEER</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Upstart</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,67 +1476,67 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dab96c17b78fc32</t>
+          <t>https://www.indeed.com/viewjob?jk=bee5a340a7f65e61</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>PetSmart</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcd181016bc08a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=0c8a098e9a2c0e1a</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Azure CI/CD Developer (FTE / Hybrid)</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>PetSmart</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Oaks, PA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffe5d7e4f5833213</t>
+          <t>https://www.indeed.com/viewjob?jk=157ddcd0636f7c11</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>BOULDER SCIENTIFIC CO</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Longmont, CO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, Splunk</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=022d9e279d3ddb80</t>
+          <t>https://www.indeed.com/viewjob?jk=9486135c47b58364</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f059a12d002721db</t>
+          <t>https://www.indeed.com/viewjob?jk=ba5a22f3941b5b26</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python/PySpark</t>
+          <t>AI Support Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b1dd2ce5d3671a</t>
+          <t>https://www.indeed.com/viewjob?jk=625bf5ef0b332ad3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer</t>
+          <t>AI Support Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6efe960a7ab141ac</t>
+          <t>https://www.indeed.com/viewjob?jk=dd39a203b7587e31</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SENIOR DATA ENGINEER</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Yusen Logistics</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, SQL Server, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bee5a340a7f65e61</t>
+          <t>https://www.indeed.com/viewjob?jk=7f92de33105c0bad</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PetSmart</t>
+          <t>Yusen Logistics</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c8a098e9a2c0e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=772460af87c5b60c</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PetSmart</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Royal Oak, MI, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=157ddcd0636f7c11</t>
+          <t>https://www.indeed.com/viewjob?jk=6bb3681c5da818f2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BOULDER SCIENTIFIC CO</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Longmont, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9486135c47b58364</t>
+          <t>https://www.indeed.com/viewjob?jk=343b07159d1b6928</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Platform Engineer - Virtual</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba5a22f3941b5b26</t>
+          <t>https://www.indeed.com/viewjob?jk=a286c7ca862c4e1a</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AI Support Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>TWG Global AI</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=625bf5ef0b332ad3</t>
+          <t>https://www.indeed.com/viewjob?jk=edb6a72ac37333e2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AI Support Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AllCloud</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake</t>
+          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd39a203b7587e31</t>
+          <t>https://www.indeed.com/viewjob?jk=49fcd1d4ac195cdf</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>IT BI Solutions Engineer, ES</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Yusen Logistics</t>
+          <t>Terex Corporation</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chattanooga, TN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kimball, ELT, dbt</t>
+          <t>AWS, Redshift, RDS, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f92de33105c0bad</t>
+          <t>https://www.indeed.com/viewjob?jk=e8376f8e501b07a8</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform Engineer-3</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Yusen Logistics</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kimball, ELT, dbt</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=772460af87c5b60c</t>
+          <t>https://www.indeed.com/viewjob?jk=f753e538739bd670</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Junior AI/MLOps Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Royal Oak, MI, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, NoSQL, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bb3681c5da818f2</t>
+          <t>https://www.indeed.com/viewjob?jk=fe34817d3b1a40dc</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=343b07159d1b6928</t>
+          <t>https://www.indeed.com/viewjob?jk=90d33ae33b62c3a0</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer - Virtual</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Alight Solutions</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a286c7ca862c4e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=ec56a8fbf5328856</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>TWG Global AI</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edb6a72ac37333e2</t>
+          <t>https://www.indeed.com/viewjob?jk=3d4834b7dd63e5a3</t>
         </is>
       </c>
     </row>
@@ -2153,12 +2153,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>AllCloud</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49fcd1d4ac195cdf</t>
+          <t>https://www.indeed.com/viewjob?jk=314cd9d2f824e302</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>IT BI Solutions Engineer, ES</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Terex Corporation</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chattanooga, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8376f8e501b07a8</t>
+          <t>https://www.indeed.com/viewjob?jk=ec0d14ba7f6cc782</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Medallion Architecture, Spark, Scala, ETL, ELT, CI/CD, GitHub Actions, AWS CodePipeline</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83c604950fd47a32</t>
+          <t>https://www.indeed.com/viewjob?jk=cd9783225b203a0f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-3</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f753e538739bd670</t>
+          <t>https://www.indeed.com/viewjob?jk=5fcdb3a443f803a9</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Junior AI/MLOps Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, NoSQL, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe34817d3b1a40dc</t>
+          <t>https://www.indeed.com/viewjob?jk=154ab74a68ca6406</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90d33ae33b62c3a0</t>
+          <t>https://www.indeed.com/viewjob?jk=31f45e1ed037bd50</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec56a8fbf5328856</t>
+          <t>https://www.indeed.com/viewjob?jk=f5d14ef4e88a3e5a</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,14 +2421,14 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d4834b7dd63e5a3</t>
+          <t>https://www.indeed.com/viewjob?jk=5f6ccf05e64c984b</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2456,14 +2456,14 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=314cd9d2f824e302</t>
+          <t>https://www.indeed.com/viewjob?jk=7b4b4f98c48563cd</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,14 +2491,14 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec0d14ba7f6cc782</t>
+          <t>https://www.indeed.com/viewjob?jk=c6c2c604bb89e64b</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,14 +2526,14 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd9783225b203a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=6e02fe4d607063c1</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,14 +2561,14 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fcdb3a443f803a9</t>
+          <t>https://www.indeed.com/viewjob?jk=9fbafb89e71fb39e</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,14 +2596,14 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=154ab74a68ca6406</t>
+          <t>https://www.indeed.com/viewjob?jk=e8ac438ef838975b</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,14 +2631,14 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31f45e1ed037bd50</t>
+          <t>https://www.indeed.com/viewjob?jk=74bd0f0f93d9a1a5</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5d14ef4e88a3e5a</t>
+          <t>https://www.indeed.com/viewjob?jk=4c53e85e359970d4</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f6ccf05e64c984b</t>
+          <t>https://www.indeed.com/viewjob?jk=0c433c70839583dc</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,14 +2736,14 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b4b4f98c48563cd</t>
+          <t>https://www.indeed.com/viewjob?jk=35e828bfc556b676</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6c2c604bb89e64b</t>
+          <t>https://www.indeed.com/viewjob?jk=3058b24332d31ded</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,14 +2806,14 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e02fe4d607063c1</t>
+          <t>https://www.indeed.com/viewjob?jk=10e23f958e9e8b09</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fbafb89e71fb39e</t>
+          <t>https://www.indeed.com/viewjob?jk=357547d890623cb5</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,14 +2876,14 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8ac438ef838975b</t>
+          <t>https://www.indeed.com/viewjob?jk=3884844e18945dee</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,14 +2911,14 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74bd0f0f93d9a1a5</t>
+          <t>https://www.indeed.com/viewjob?jk=17b7c64ee8dc67e0</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c53e85e359970d4</t>
+          <t>https://www.indeed.com/viewjob?jk=a75982d2aedba052</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,14 +2981,14 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c433c70839583dc</t>
+          <t>https://www.indeed.com/viewjob?jk=4b3d8d96e19fcbe6</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,14 +3016,14 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35e828bfc556b676</t>
+          <t>https://www.indeed.com/viewjob?jk=a60a56d62d329dea</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3058b24332d31ded</t>
+          <t>https://www.indeed.com/viewjob?jk=93902824d8ac4d0c</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10e23f958e9e8b09</t>
+          <t>https://www.indeed.com/viewjob?jk=088398b8f22d3683</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=357547d890623cb5</t>
+          <t>https://www.indeed.com/viewjob?jk=60f8a4d4b303056b</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,42 +3156,42 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3884844e18945dee</t>
+          <t>https://www.indeed.com/viewjob?jk=459cc0fec55fdc6f</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17b7c64ee8dc67e0</t>
+          <t>https://www.indeed.com/viewjob?jk=eb77847b7cd88f45</t>
         </is>
       </c>
     </row>
@@ -3203,20 +3203,20 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Genentech</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Step Functions, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a75982d2aedba052</t>
+          <t>https://www.indeed.com/viewjob?jk=d20f4b9e6a3cbb70</t>
         </is>
       </c>
     </row>
@@ -3238,20 +3238,20 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Genentech</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Step Functions, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b3d8d96e19fcbe6</t>
+          <t>https://www.indeed.com/viewjob?jk=c89d6a7d2041de38</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Teradata</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, API Gateway, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a60a56d62d329dea</t>
+          <t>https://www.indeed.com/viewjob?jk=806bff32d1d719ff</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Site Reliability Developer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,14 +3331,14 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93902824d8ac4d0c</t>
+          <t>https://www.indeed.com/viewjob?jk=3fedd79bbbee99bb</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Software Engineer II (Backend + Data pipelines)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3348,15 +3348,15 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,14 +3366,14 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=088398b8f22d3683</t>
+          <t>https://www.indeed.com/viewjob?jk=7d4fca4ad337ae6c</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Software Engineer II (Backend + Data pipelines)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3383,15 +3383,15 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,14 +3401,14 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f8a4d4b303056b</t>
+          <t>https://www.indeed.com/viewjob?jk=1ae76b185563f91b</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Software Engineer II (Backend + Data pipelines)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3418,15 +3418,15 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,14 +3436,14 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=459cc0fec55fdc6f</t>
+          <t>https://www.indeed.com/viewjob?jk=ef2a73b324528506</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Software Engineer II (Backend + Data pipelines)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3453,15 +3453,15 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,14 +3471,14 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a58d376929282400</t>
+          <t>https://www.indeed.com/viewjob?jk=92aaafaf1efb9ec4</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Software Engineer II (Backend + Data pipelines)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3488,15 +3488,15 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,14 +3506,14 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=521ae718282fb788</t>
+          <t>https://www.indeed.com/viewjob?jk=c9981aefe519f0cd</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Software Engineer II (Backend + Data pipelines)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3523,15 +3523,15 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,14 +3541,14 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=559d1352317c1f33</t>
+          <t>https://www.indeed.com/viewjob?jk=fce2095df8206466</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Software Engineer II (Backend + Data pipelines)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3562,11 +3562,11 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,14 +3576,14 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=361e87b55f4161f4</t>
+          <t>https://www.indeed.com/viewjob?jk=ee34633b7838a9b3</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Software Engineer II (Backend + Data pipelines)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3597,11 +3597,11 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,14 +3611,14 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32e0b2833cebefe3</t>
+          <t>https://www.indeed.com/viewjob?jk=cc57f588c654f1cd</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Software Engineer II (Backend + Data pipelines)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3628,15 +3628,15 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f5df27af3031e62</t>
+          <t>https://www.indeed.com/viewjob?jk=5aaeb4c54cdfa77e</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Software Engineer II (Backend + Data pipelines)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, MongoDB, Data Modeling</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb77847b7cd88f45</t>
+          <t>https://www.indeed.com/viewjob?jk=eb06d74f6367bb04</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Software Engineer II (Backend + Data pipelines)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Kubernetes, Airflow</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d20f4b9e6a3cbb70</t>
+          <t>https://www.indeed.com/viewjob?jk=49799e02e3e0a925</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Software Engineer II (Backend + Data pipelines)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Kubernetes, Airflow</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c89d6a7d2041de38</t>
+          <t>https://www.indeed.com/viewjob?jk=52ff9083bc8990ce</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer II (Backend + Data pipelines)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Teradata</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=806bff32d1d719ff</t>
+          <t>https://www.indeed.com/viewjob?jk=66f89817131cfa0d</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Developer</t>
+          <t>Software Engineer II (Backend + Data pipelines)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fedd79bbbee99bb</t>
+          <t>https://www.indeed.com/viewjob?jk=cdb757efdefad0ca</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4fca4ad337ae6c</t>
+          <t>https://www.indeed.com/viewjob?jk=57fc4e97a319b123</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ae76b185563f91b</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fcc67143e3ff8a</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef2a73b324528506</t>
+          <t>https://www.indeed.com/viewjob?jk=5dad4bf1e950e1c9</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92aaafaf1efb9ec4</t>
+          <t>https://www.indeed.com/viewjob?jk=0f9ed5d278a8086d</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9981aefe519f0cd</t>
+          <t>https://www.indeed.com/viewjob?jk=8809421834292084</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend + Data pipelines)</t>
+          <t>AWS Developer/Integration Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>rockITdata</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, DynamoDB, Amazon QuickSight, CI/CD</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fce2095df8206466</t>
+          <t>https://www.indeed.com/viewjob?jk=4a60d7d509fbceed</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend + Data pipelines)</t>
+          <t>Senior Digital Engineer – Full Stack &amp; Systems Architecture</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Berkeley, MO, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee34633b7838a9b3</t>
+          <t>https://www.indeed.com/viewjob?jk=5360d83db3589d68</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend + Data pipelines)</t>
+          <t>Senior Digital Engineer – Full Stack &amp; Systems Architecture</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc57f588c654f1cd</t>
+          <t>https://www.indeed.com/viewjob?jk=12a4a8cde3354706</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend + Data pipelines)</t>
+          <t>Senior Application Platform Architect - 6163848</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Hadoop, Scala, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5aaeb4c54cdfa77e</t>
+          <t>https://www.indeed.com/viewjob?jk=7ea7fc0fae83610a</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend + Data pipelines)</t>
+          <t>Senior LLM Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, Azure, Vertex AI, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb06d74f6367bb04</t>
+          <t>https://www.indeed.com/viewjob?jk=109c9c4a6595ba95</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend + Data pipelines)</t>
+          <t>Senior LLM Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, Azure, Vertex AI, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49799e02e3e0a925</t>
+          <t>https://www.indeed.com/viewjob?jk=8723fa94634ae387</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend + Data pipelines)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>LERETA, LLC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Pomona, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,14 +4241,14 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52ff9083bc8990ce</t>
+          <t>https://www.indeed.com/viewjob?jk=ad5d067156fc62f1</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend + Data pipelines)</t>
+          <t>Senior Machine Learning Engineer (Search)</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,14 +4276,14 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f89817131cfa0d</t>
+          <t>https://www.indeed.com/viewjob?jk=cff2f5a9dcacb28f</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend + Data pipelines)</t>
+          <t>Senior Machine Learning Engineer (Search)</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,14 +4311,14 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdb757efdefad0ca</t>
+          <t>https://www.indeed.com/viewjob?jk=3216b4c3b2c151f8</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend + Data pipelines)</t>
+          <t>Senior Machine Learning Engineer (Search)</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,14 +4346,14 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57fc4e97a319b123</t>
+          <t>https://www.indeed.com/viewjob?jk=a0fc0424a2f74ea8</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend + Data pipelines)</t>
+          <t>Senior Machine Learning Engineer (Search)</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,14 +4381,14 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fcc67143e3ff8a</t>
+          <t>https://www.indeed.com/viewjob?jk=c0ff98f788ff107b</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend + Data pipelines)</t>
+          <t>Senior Machine Learning Engineer (Search)</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,14 +4416,14 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dad4bf1e950e1c9</t>
+          <t>https://www.indeed.com/viewjob?jk=0442372baf83ee82</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend + Data pipelines)</t>
+          <t>Senior Machine Learning Engineer (Search)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,14 +4451,14 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f9ed5d278a8086d</t>
+          <t>https://www.indeed.com/viewjob?jk=fe6ea91421159ece</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend + Data pipelines)</t>
+          <t>Senior Machine Learning Engineer (Search)</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8809421834292084</t>
+          <t>https://www.indeed.com/viewjob?jk=aecbf4d450f1441b</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>AWS Developer/Integration Engineer</t>
+          <t>Senior Machine Learning Engineer (Search)</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>rockITdata</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, DynamoDB, Amazon QuickSight, CI/CD</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a60d7d509fbceed</t>
+          <t>https://www.indeed.com/viewjob?jk=31056dc236b5ce67</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Digital Engineer – Full Stack &amp; Systems Architecture</t>
+          <t>Senior Machine Learning Engineer (Search)</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Berkeley, MO, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5360d83db3589d68</t>
+          <t>https://www.indeed.com/viewjob?jk=eca84bb19e700f2b</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Digital Engineer – Full Stack &amp; Systems Architecture</t>
+          <t>Senior Machine Learning Engineer (Search)</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12a4a8cde3354706</t>
+          <t>https://www.indeed.com/viewjob?jk=7401294591da0c90</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Application Platform Architect - 6163848</t>
+          <t>Senior Machine Learning Engineer (Search)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Hadoop, Scala, PostgreSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ea7fc0fae83610a</t>
+          <t>https://www.indeed.com/viewjob?jk=5eed535b1fcfea26</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior LLM Engineer</t>
+          <t>Senior Machine Learning Engineer (Search)</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, MLOps</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109c9c4a6595ba95</t>
+          <t>https://www.indeed.com/viewjob?jk=b29243583190aa6a</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior LLM Engineer</t>
+          <t>Senior Machine Learning Engineer (Search)</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, MLOps</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8723fa94634ae387</t>
+          <t>https://www.indeed.com/viewjob?jk=1c0d7ebd3a2ee36f</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Machine Learning Engineer (Search)</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>LERETA, LLC</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Pomona, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad5d067156fc62f1</t>
+          <t>https://www.indeed.com/viewjob?jk=28e3397c0e70024e</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cff2f5a9dcacb28f</t>
+          <t>https://www.indeed.com/viewjob?jk=35f50cc085f1bbd9</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3216b4c3b2c151f8</t>
+          <t>https://www.indeed.com/viewjob?jk=72be3b8aba169a59</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0fc0424a2f74ea8</t>
+          <t>https://www.indeed.com/viewjob?jk=b61af8e418fcf231</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0ff98f788ff107b</t>
+          <t>https://www.indeed.com/viewjob?jk=552a8172dcf24a7a</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,32 +4906,32 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0442372baf83ee82</t>
+          <t>https://www.indeed.com/viewjob?jk=4fa51ea3c52768d7</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Search)</t>
+          <t>Software Engineering Intern – Data Engineering (Cloud &amp; Streaming)</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>NextPower</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,32 +4941,32 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe6ea91421159ece</t>
+          <t>https://www.indeed.com/viewjob?jk=28e588be3c533008</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Search)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Power BI, Tableau, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,32 +4976,32 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aecbf4d450f1441b</t>
+          <t>https://www.indeed.com/viewjob?jk=aaf9596bf4159924</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Search)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Power BI, Tableau, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,32 +5011,32 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31056dc236b5ce67</t>
+          <t>https://www.indeed.com/viewjob?jk=ab90611f6b141379</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Search)</t>
+          <t>Senior Cloud Systems Engineer (Databricks Administrator)</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Providge Consulting</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,32 +5046,32 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eca84bb19e700f2b</t>
+          <t>https://www.indeed.com/viewjob?jk=e094ab218ebab2ed</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Search)</t>
+          <t>Sr. ETL/SQL Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Capgemini Government Solutions</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,32 +5081,32 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7401294591da0c90</t>
+          <t>https://www.indeed.com/viewjob?jk=724ffe7f1d3da135</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Search)</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Space Telescope Science Institute</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, S3, ECS, IAM, Hive, Scala, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,32 +5116,32 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eed535b1fcfea26</t>
+          <t>https://www.indeed.com/viewjob?jk=6055970eb603df79</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Search)</t>
+          <t>AI Engineer III</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>CareSource</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>API Gateway, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,32 +5151,32 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29243583190aa6a</t>
+          <t>https://www.indeed.com/viewjob?jk=640c68fe3716b1e6</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Search)</t>
+          <t>Sr Software Engineer (Site Reliability Engineering) (2026-10114)</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, MySQL, Splunk</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,32 +5186,32 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c0d7ebd3a2ee36f</t>
+          <t>https://www.indeed.com/viewjob?jk=b5ab755eddd54b18</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Search)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,49 +5221,49 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e3397c0e70024e</t>
+          <t>https://www.indeed.com/viewjob?jk=d44e3274520e56d6</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Search)</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Centene</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35f50cc085f1bbd9</t>
+          <t>https://www.indeed.com/viewjob?jk=11d92da9c37770a7</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Search)</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5273,15 +5273,15 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,14 +5291,14 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72be3b8aba169a59</t>
+          <t>https://www.indeed.com/viewjob?jk=e2b622ee37d8f63f</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Search)</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5308,15 +5308,15 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,14 +5326,14 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b61af8e418fcf231</t>
+          <t>https://www.indeed.com/viewjob?jk=7ba10ede755adc88</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Search)</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5343,15 +5343,15 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,14 +5361,14 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=552a8172dcf24a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=035e833a0affea06</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Search)</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5378,15 +5378,15 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fa51ea3c52768d7</t>
+          <t>https://www.indeed.com/viewjob?jk=34ea65634bf231fc</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Software Engineering Intern – Data Engineering (Cloud &amp; Streaming)</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>NextPower</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e588be3c533008</t>
+          <t>https://www.indeed.com/viewjob?jk=db2fffa7ab4fc3c6</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Power BI, Tableau, MLOps, MLflow</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaf9596bf4159924</t>
+          <t>https://www.indeed.com/viewjob?jk=726fca60377106fb</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Power BI, Tableau, MLOps, MLflow</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab90611f6b141379</t>
+          <t>https://www.indeed.com/viewjob?jk=ae1bbd4c5bfc6dc1</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Python)</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,34 +5526,34 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f65ac6c3f1cf1646</t>
+          <t>https://www.indeed.com/viewjob?jk=7d44fb63e0c3570e</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Senior Cloud Systems Engineer (Databricks Administrator)</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Providge Consulting</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Scala, ELT, CI/CD</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,24 +5571,24 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e094ab218ebab2ed</t>
+          <t>https://www.indeed.com/viewjob?jk=ac1d3f6a217585b1</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Sr. ETL/SQL Engineer</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Capgemini Government Solutions</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,24 +5606,24 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724ffe7f1d3da135</t>
+          <t>https://www.indeed.com/viewjob?jk=594c2209c74b60f3</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Space Telescope Science Institute</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Hive, Scala, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,24 +5641,24 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6055970eb603df79</t>
+          <t>https://www.indeed.com/viewjob?jk=300951fa8a03d9ab</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>AI Engineer III</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>CareSource</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,24 +5676,24 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=640c68fe3716b1e6</t>
+          <t>https://www.indeed.com/viewjob?jk=224f85378fe66226</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Sr Software Engineer (Site Reliability Engineering) (2026-10114)</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, MySQL, Splunk</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5711,24 +5711,24 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5ab755eddd54b18</t>
+          <t>https://www.indeed.com/viewjob?jk=609ed15647075bf2</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5746,24 +5746,24 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d44e3274520e56d6</t>
+          <t>https://www.indeed.com/viewjob?jk=f7da2bae9861dfa9</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Centene</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,34 +5771,34 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11d92da9c37770a7</t>
+          <t>https://www.indeed.com/viewjob?jk=9f44f95326fb5d8b</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>H2O.ai</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5816,24 +5816,24 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe52f92aedddcda4</t>
+          <t>https://www.indeed.com/viewjob?jk=f7f6777f3346c150</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>H2O.ai</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -5851,24 +5851,24 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d2b8979a3b5f81b</t>
+          <t>https://www.indeed.com/viewjob?jk=99001099f8e56675</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data &amp; Analytics</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>WesBanco Bank, Inc.</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Bowie, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5886,24 +5886,24 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a02cdb2b181be3</t>
+          <t>https://www.indeed.com/viewjob?jk=1d562fde2d3ab4ec</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data &amp; Analytics</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>WesBanco Bank, Inc.</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Wheeling, WV, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5921,24 +5921,24 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb6ee55d393e301c</t>
+          <t>https://www.indeed.com/viewjob?jk=49363af061447f75</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Software Developer - Database Engineer</t>
+          <t>Senior Software Engineer (Python + Distributed systems)</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>RAMSOFT</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, HBase, Scala, Snowflake, MySQL, NoSQL, Data Modeling, Power BI</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5956,14 +5956,14 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ce0ac7d0a937f32</t>
+          <t>https://www.indeed.com/viewjob?jk=c4af4ef5dfeb0026</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>Senior Software Engineer (Python + Distributed systems)</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,14 +5991,14 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2b622ee37d8f63f</t>
+          <t>https://www.indeed.com/viewjob?jk=c116b8acf805f138</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>Senior Software Engineer (Python + Distributed systems)</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,14 +6026,14 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ba10ede755adc88</t>
+          <t>https://www.indeed.com/viewjob?jk=f996f9a35281bba7</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>Senior Software Engineer (Python + Distributed systems)</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,14 +6061,14 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=035e833a0affea06</t>
+          <t>https://www.indeed.com/viewjob?jk=ca3982c4f2be4e49</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>Senior Software Engineer (Python + Distributed systems)</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6096,14 +6096,14 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ea65634bf231fc</t>
+          <t>https://www.indeed.com/viewjob?jk=9f2a3e577d5623a4</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>Senior Software Engineer (Python + Distributed systems)</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -6113,7 +6113,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6131,14 +6131,14 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db2fffa7ab4fc3c6</t>
+          <t>https://www.indeed.com/viewjob?jk=629b89e40e1e1bb5</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>Senior Software Engineer (Python + Distributed systems)</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6166,14 +6166,14 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=726fca60377106fb</t>
+          <t>https://www.indeed.com/viewjob?jk=db6cf98112c1bc9f</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>Senior Software Engineer (Python + Distributed systems)</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6201,14 +6201,14 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae1bbd4c5bfc6dc1</t>
+          <t>https://www.indeed.com/viewjob?jk=80b26c4d48449b15</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>Senior Software Engineer (Python + Distributed systems)</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6236,14 +6236,14 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d44fb63e0c3570e</t>
+          <t>https://www.indeed.com/viewjob?jk=83ba9763cad5f2f8</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>Senior Software Engineer (Python + Distributed systems)</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6271,14 +6271,14 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac1d3f6a217585b1</t>
+          <t>https://www.indeed.com/viewjob?jk=05460d1c364a2974</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>Senior Software Engineer (Python + Distributed systems)</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6306,14 +6306,14 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=594c2209c74b60f3</t>
+          <t>https://www.indeed.com/viewjob?jk=b01dc956f073aaf8</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>Senior Software Engineer (Python + Distributed systems)</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6341,14 +6341,14 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=300951fa8a03d9ab</t>
+          <t>https://www.indeed.com/viewjob?jk=807aad5f4045241d</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>Senior Software Engineer (Python + Distributed systems)</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -6358,7 +6358,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6376,14 +6376,14 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224f85378fe66226</t>
+          <t>https://www.indeed.com/viewjob?jk=655ea21e25dbce1e</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>Senior Software Engineer (Python + Distributed systems)</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6411,24 +6411,24 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=609ed15647075bf2</t>
+          <t>https://www.indeed.com/viewjob?jk=c46ceb995e304d69</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>H2O.ai</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -6446,24 +6446,24 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7da2bae9861dfa9</t>
+          <t>https://www.indeed.com/viewjob?jk=fe52f92aedddcda4</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>H2O.ai</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -6481,24 +6481,24 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f44f95326fb5d8b</t>
+          <t>https://www.indeed.com/viewjob?jk=0d2b8979a3b5f81b</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>Senior Data Engineer - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>WesBanco Bank, Inc.</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Bowie, MD, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -6516,24 +6516,24 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7f6777f3346c150</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a02cdb2b181be3</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>Senior Data Engineer - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>WesBanco Bank, Inc.</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Wheeling, WV, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -6551,24 +6551,24 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99001099f8e56675</t>
+          <t>https://www.indeed.com/viewjob?jk=fb6ee55d393e301c</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>Software Developer - Database Engineer</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>RAMSOFT</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, HBase, Scala, Snowflake, MySQL, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -6586,32 +6586,32 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d562fde2d3ab4ec</t>
+          <t>https://www.indeed.com/viewjob?jk=4ce0ac7d0a937f32</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>AV Safety Engineering Analytics Simulation Engineer (GPSSC)</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -6621,102 +6621,102 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49363af061447f75</t>
+          <t>https://www.indeed.com/viewjob?jk=4b9eec46bbab109b</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python + Distributed systems)</t>
+          <t>AWS Cloud Administrator</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>rockITdata</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, Azure, DynamoDB, Terraform</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4af4ef5dfeb0026</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0a98e5951373b4</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python + Distributed systems)</t>
+          <t>Data Engineer-Remote</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Mutual of Omaha</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, Glue, RDS, Scala, Snowflake, SQL Server, MongoDB, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c116b8acf805f138</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc1efbee94e32a9</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python + Distributed systems)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -6726,32 +6726,32 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f996f9a35281bba7</t>
+          <t>https://www.indeed.com/viewjob?jk=ed1b9b0328def6aa</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python + Distributed systems)</t>
+          <t>SAP NS2 Senior HANA Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -6761,32 +6761,32 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca3982c4f2be4e49</t>
+          <t>https://www.indeed.com/viewjob?jk=8999a6d9da6831ef</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python + Distributed systems)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -6796,102 +6796,102 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f2a3e577d5623a4</t>
+          <t>https://www.indeed.com/viewjob?jk=2e60ff8bc1e60898</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python + Distributed systems)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Callaway Golf</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=629b89e40e1e1bb5</t>
+          <t>https://www.indeed.com/viewjob?jk=9ae59fccd3421dc5</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python + Distributed systems)</t>
+          <t>Software Engineer Intern</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db6cf98112c1bc9f</t>
+          <t>https://www.indeed.com/viewjob?jk=c65c6376729ba486</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python + Distributed systems)</t>
+          <t>Visualization Engineer</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>RDS, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -6901,32 +6901,32 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80b26c4d48449b15</t>
+          <t>https://www.indeed.com/viewjob?jk=b28a6ad6f45c5471</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python + Distributed systems)</t>
+          <t>Senior AI/ML Scientist</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -6936,32 +6936,32 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83ba9763cad5f2f8</t>
+          <t>https://www.indeed.com/viewjob?jk=300d4ca14be662c3</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python + Distributed systems)</t>
+          <t>AV Safety Engineering Analytics Engineer (GPSSC)</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -6971,137 +6971,137 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05460d1c364a2974</t>
+          <t>https://www.indeed.com/viewjob?jk=60da6f50aaadfe48</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python + Distributed systems)</t>
+          <t>SENIOR DATA ENGINEER (REMOTE)</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Morrison Healthcare</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Snowflake, ETL, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b01dc956f073aaf8</t>
+          <t>https://www.indeed.com/viewjob?jk=d530073f998c3698</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python + Distributed systems)</t>
+          <t>Product Engineer</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>ALTIMATE</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, ECS, RDS, Spark, Scala, PostgreSQL, dbt, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=807aad5f4045241d</t>
+          <t>https://www.indeed.com/viewjob?jk=95f4b6534ba4c3cd</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python + Distributed systems)</t>
+          <t>Teradata Developer</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=655ea21e25dbce1e</t>
+          <t>https://www.indeed.com/viewjob?jk=7fddb4ec439f1237</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python + Distributed systems)</t>
+          <t>Senior BI Developer - Investment Services</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D191" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -7111,32 +7111,32 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c46ceb995e304d69</t>
+          <t>https://www.indeed.com/viewjob?jk=6861136ad5c92fec</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python + Distributed systems)</t>
+          <t>Senior BI Developer - Investment Services</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -7146,32 +7146,32 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f29df76fe446a26</t>
+          <t>https://www.indeed.com/viewjob?jk=d0459e004fd012bc</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python + Distributed systems)</t>
+          <t>Senior BI Developer - Investment Services</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -7181,32 +7181,32 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6574f30d9366e40</t>
+          <t>https://www.indeed.com/viewjob?jk=00bd0c85ee5af1cc</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python + Distributed systems)</t>
+          <t>Senior BI Developer - Investment Services</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -7216,32 +7216,32 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8536b186707d6516</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a227aff44c18bd</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python + Distributed systems)</t>
+          <t>Senior BI Developer - Investment Services</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -7251,32 +7251,32 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a4c9600c5ead18d</t>
+          <t>https://www.indeed.com/viewjob?jk=f36e77b3ab4b1808</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python + Distributed systems)</t>
+          <t>Senior BI Developer - Investment Services</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -7286,24 +7286,24 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78388f22c8e1c7cc</t>
+          <t>https://www.indeed.com/viewjob?jk=b03b046a7e4b4373</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>AV Safety Engineering Analytics Simulation Engineer (GPSSC)</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -7311,34 +7311,34 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b9eec46bbab109b</t>
+          <t>https://www.indeed.com/viewjob?jk=50c61f5469ce333f</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>AWS Cloud Administrator</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>rockITdata</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, Azure, DynamoDB, Terraform</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -7356,24 +7356,24 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0a98e5951373b4</t>
+          <t>https://www.indeed.com/viewjob?jk=4303ceb5e8c627c4</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Data Engineer-Remote</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Mutual of Omaha</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Scala, Snowflake, SQL Server, MongoDB, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -7391,24 +7391,24 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc1efbee94e32a9</t>
+          <t>https://www.indeed.com/viewjob?jk=0c4db6d385ae6ea3</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Full Stack Software Engineer (Onsite - San Diego)</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Carlsmed</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -7416,7 +7416,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, Scala, PostgreSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -7426,24 +7426,24 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed1b9b0328def6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=47ffb86f604e14df</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>SAP NS2 Senior HANA Cloud DevOps Engineer</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -7461,24 +7461,24 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8999a6d9da6831ef</t>
+          <t>https://www.indeed.com/viewjob?jk=c70cf8723aeaf7eb</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -7496,24 +7496,24 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e60ff8bc1e60898</t>
+          <t>https://www.indeed.com/viewjob?jk=6f106012aaf32c49</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Callaway Golf</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -7521,34 +7521,34 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ae59fccd3421dc5</t>
+          <t>https://www.indeed.com/viewjob?jk=a1593d7242ad3914</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Software Engineer Intern</t>
+          <t>Snowflake Administrator</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -7556,34 +7556,34 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c65c6376729ba486</t>
+          <t>https://www.indeed.com/viewjob?jk=085de5867e567658</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Visualization Engineer</t>
+          <t>LLM Application Engineer</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -7591,7 +7591,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>RDS, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD, Git, Python</t>
+          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -7601,24 +7601,24 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b28a6ad6f45c5471</t>
+          <t>https://www.indeed.com/viewjob?jk=5633278896c16c3b</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Senior AI/ML Scientist</t>
+          <t>LLM Application Engineer</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Milford, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -7626,7 +7626,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, MLflow, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -7636,707 +7636,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=300d4ca14be662c3</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>AV Safety Engineering Analytics Engineer (GPSSC)</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D207" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=60da6f50aaadfe48</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>SENIOR DATA ENGINEER (REMOTE)</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>Morrison Healthcare</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>IL, US USA</t>
-        </is>
-      </c>
-      <c r="D208" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Snowflake, ETL, dbt, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>2026-01-05</t>
-        </is>
-      </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d530073f998c3698</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>Product Engineer</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>ALTIMATE</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>Sunnyvale, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D209" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Spark, Scala, PostgreSQL, dbt, Kubernetes, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=95f4b6534ba4c3cd</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D210" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=50c61f5469ce333f</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D211" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4303ceb5e8c627c4</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D212" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0c4db6d385ae6ea3</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>Sr. Full Stack Software Engineer (Onsite - San Diego)</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>Carlsmed</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>Carlsbad, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D213" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, Scala, PostgreSQL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=47ffb86f604e14df</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>Engineer II- Java</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D214" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c70cf8723aeaf7eb</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>Engineer II- Java</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D215" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6f106012aaf32c49</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>CrowdStrike</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>Sunnyvale, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D216" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a1593d7242ad3914</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>Snowflake Administrator</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D217" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=085de5867e567658</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>LLM Application Engineer</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D218" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
-        </is>
-      </c>
-      <c r="F218" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G218" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5633278896c16c3b</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>LLM Application Engineer</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D219" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
-        </is>
-      </c>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G219" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=4e56614bfb72e3b3</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>Teradata Developer</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D220" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7fddb4ec439f1237</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>Senior BI Developer - Investment Services</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>U.S. Bank</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D221" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6861136ad5c92fec</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>Senior BI Developer - Investment Services</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>U.S. Bank</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D222" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F222" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d0459e004fd012bc</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>Senior BI Developer - Investment Services</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>U.S. Bank</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D223" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F223" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=00bd0c85ee5af1cc</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>Senior BI Developer - Investment Services</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>U.S. Bank</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>Saint Paul, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D224" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F224" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a227aff44c18bd</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>Senior BI Developer - Investment Services</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>U.S. Bank</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>Milwaukee, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D225" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F225" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G225" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f36e77b3ab4b1808</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>Senior BI Developer - Investment Services</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>U.S. Bank</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>Hopkins, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D226" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b03b046a7e4b4373</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-06.xlsx
+++ b/results/job_matches_2026-03-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G206"/>
+  <dimension ref="A1:G200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Data Engineer (Python, PySpark, Lambda)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Spire Energy</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL</t>
+          <t>AWS, EMR, Lambda, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df7314eb6a45de22</t>
+          <t>https://www.indeed.com/viewjob?jk=59f97860142550fe</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - INDIA</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Spire Energy</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Prosper, TX, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8eebff65cda31d0</t>
+          <t>https://www.indeed.com/viewjob?jk=df7314eb6a45de22</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Analyst, Risk Data Engineering</t>
+          <t>Senior Data Engineer - INDIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lincoln Financial Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Radnor, PA, US USA</t>
+          <t>Prosper, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c054d24fbe757c5</t>
+          <t>https://www.indeed.com/viewjob?jk=f8eebff65cda31d0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Analyst, Risk Data Engineering</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Lincoln Financial Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Radnor, PA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,42 +801,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc1fd3766a845e85</t>
+          <t>https://www.indeed.com/viewjob?jk=4c054d24fbe757c5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Dataflow, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c46cd564ba01b6c</t>
+          <t>https://www.indeed.com/viewjob?jk=fc1fd3766a845e85</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d52dce08f82e688</t>
+          <t>https://www.indeed.com/viewjob?jk=bac9e3177a7c184b</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=175b82022b025c3d</t>
+          <t>https://www.indeed.com/viewjob?jk=72f18d450d1d99d9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>JBS Dev</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49f6c2df00dd6e11</t>
+          <t>https://www.indeed.com/viewjob?jk=b45360d720d413c7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Costa Rica)</t>
+          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JBS Dev</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05c819aa2a88511d</t>
+          <t>https://www.indeed.com/viewjob?jk=3c46cd564ba01b6c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>System Architect</t>
+          <t>Senior Data Engineer (Python, Spark, AWS)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Systems Engineering Solutions Corporation</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=634fcd15ef04d7bf</t>
+          <t>https://www.indeed.com/viewjob?jk=6d52dce08f82e688</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7869ee373ec84ed</t>
+          <t>https://www.indeed.com/viewjob?jk=175b82022b025c3d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CLOUD ENGINEER (AWS) (REMOTE/USA) - GDM (GRAY MEDIA GROUP)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GRAY MEDIA</t>
+          <t>JBS Dev</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, DynamoDB</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0beb94e2f1648144</t>
+          <t>https://www.indeed.com/viewjob?jk=49f6c2df00dd6e11</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Clinical Systems (Lab Ops)</t>
+          <t>Senior Data Engineer (Costa Rica)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Caris Life Sciences</t>
+          <t>JBS Dev</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, RDS, Azure, GCP, Scala, PostgreSQL</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb8de235a110895a</t>
+          <t>https://www.indeed.com/viewjob?jk=05c819aa2a88511d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>System Architect</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Systems Engineering Solutions Corporation</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afa51ac883fa48a6</t>
+          <t>https://www.indeed.com/viewjob?jk=634fcd15ef04d7bf</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior BI Analyst</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad414f3a9ab0a2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=c7869ee373ec84ed</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>CLOUD ENGINEER (AWS) (REMOTE/USA) - GDM (GRAY MEDIA GROUP)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>GRAY MEDIA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=459162c660bc8082</t>
+          <t>https://www.indeed.com/viewjob?jk=0beb94e2f1648144</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Upstart</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dab96c17b78fc32</t>
+          <t>https://www.indeed.com/viewjob?jk=afa51ac883fa48a6</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML</t>
+          <t>Senior BI Analyst</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Spark, Scala, Kafka, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcd181016bc08a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=ad414f3a9ab0a2bc</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Azure CI/CD Developer (FTE / Hybrid)</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Oaks, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,19 +1336,19 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffe5d7e4f5833213</t>
+          <t>https://www.indeed.com/viewjob?jk=459162c660bc8082</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Upstart</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1357,11 +1357,11 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f059a12d002721db</t>
+          <t>https://www.indeed.com/viewjob?jk=3dab96c17b78fc32</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python/PySpark</t>
+          <t>Azure CI/CD Developer (FTE / Hybrid)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Oaks, PA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b1dd2ce5d3671a</t>
+          <t>https://www.indeed.com/viewjob?jk=ffe5d7e4f5833213</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
+          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6efe960a7ab141ac</t>
+          <t>https://www.indeed.com/viewjob?jk=f059a12d002721db</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SENIOR DATA ENGINEER</t>
+          <t>Software Engineer III- Python/PySpark</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bee5a340a7f65e61</t>
+          <t>https://www.indeed.com/viewjob?jk=82b1dd2ce5d3671a</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Sr Software Development Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PetSmart</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
+          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c8a098e9a2c0e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=6efe960a7ab141ac</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>SENIOR DATA ENGINEER</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PetSmart</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=157ddcd0636f7c11</t>
+          <t>https://www.indeed.com/viewjob?jk=bee5a340a7f65e61</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BOULDER SCIENTIFIC CO</t>
+          <t>PetSmart</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Longmont, CO, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9486135c47b58364</t>
+          <t>https://www.indeed.com/viewjob?jk=0c8a098e9a2c0e1a</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>PetSmart</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba5a22f3941b5b26</t>
+          <t>https://www.indeed.com/viewjob?jk=157ddcd0636f7c11</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AI Support Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>BOULDER SCIENTIFIC CO</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Longmont, CO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=625bf5ef0b332ad3</t>
+          <t>https://www.indeed.com/viewjob?jk=9486135c47b58364</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AI Support Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd39a203b7587e31</t>
+          <t>https://www.indeed.com/viewjob?jk=ba5a22f3941b5b26</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Support Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Yusen Logistics</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kimball, ELT, dbt</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f92de33105c0bad</t>
+          <t>https://www.indeed.com/viewjob?jk=625bf5ef0b332ad3</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Support Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Yusen Logistics</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kimball, ELT, dbt</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=772460af87c5b60c</t>
+          <t>https://www.indeed.com/viewjob?jk=dd39a203b7587e31</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Yusen Logistics</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Royal Oak, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bb3681c5da818f2</t>
+          <t>https://www.indeed.com/viewjob?jk=7f92de33105c0bad</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Yusen Logistics</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=343b07159d1b6928</t>
+          <t>https://www.indeed.com/viewjob?jk=772460af87c5b60c</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer - Virtual</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Alight Solutions</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Royal Oak, MI, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a286c7ca862c4e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=6bb3681c5da818f2</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>TWG Global AI</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edb6a72ac37333e2</t>
+          <t>https://www.indeed.com/viewjob?jk=343b07159d1b6928</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Cloud Platform Engineer - Virtual</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>AllCloud</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49fcd1d4ac195cdf</t>
+          <t>https://www.indeed.com/viewjob?jk=a286c7ca862c4e1a</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>IT BI Solutions Engineer, ES</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Terex Corporation</t>
+          <t>TWG Global AI</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chattanooga, TN, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8376f8e501b07a8</t>
+          <t>https://www.indeed.com/viewjob?jk=edb6a72ac37333e2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-3</t>
+          <t>Senior Software Engineer (Python, PySpark, Lambda)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f753e538739bd670</t>
+          <t>https://www.indeed.com/viewjob?jk=c588b2aa81b85891</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Junior AI/MLOps Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>AllCloud</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, NoSQL, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe34817d3b1a40dc</t>
+          <t>https://www.indeed.com/viewjob?jk=49fcd1d4ac195cdf</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>IT BI Solutions Engineer, ES</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Terex Corporation</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Chattanooga, TN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90d33ae33b62c3a0</t>
+          <t>https://www.indeed.com/viewjob?jk=e8376f8e501b07a8</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Data Platform Engineer-3</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec56a8fbf5328856</t>
+          <t>https://www.indeed.com/viewjob?jk=f753e538739bd670</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Junior AI/MLOps Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, NoSQL, MLOps, MLflow, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,14 +2141,14 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d4834b7dd63e5a3</t>
+          <t>https://www.indeed.com/viewjob?jk=fe34817d3b1a40dc</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=314cd9d2f824e302</t>
+          <t>https://www.indeed.com/viewjob?jk=90d33ae33b62c3a0</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec0d14ba7f6cc782</t>
+          <t>https://www.indeed.com/viewjob?jk=ec56a8fbf5328856</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd9783225b203a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=3d4834b7dd63e5a3</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fcdb3a443f803a9</t>
+          <t>https://www.indeed.com/viewjob?jk=314cd9d2f824e302</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=154ab74a68ca6406</t>
+          <t>https://www.indeed.com/viewjob?jk=ec0d14ba7f6cc782</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,14 +2351,14 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31f45e1ed037bd50</t>
+          <t>https://www.indeed.com/viewjob?jk=cd9783225b203a0f</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5d14ef4e88a3e5a</t>
+          <t>https://www.indeed.com/viewjob?jk=5fcdb3a443f803a9</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f6ccf05e64c984b</t>
+          <t>https://www.indeed.com/viewjob?jk=154ab74a68ca6406</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,14 +2456,14 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b4b4f98c48563cd</t>
+          <t>https://www.indeed.com/viewjob?jk=31f45e1ed037bd50</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,14 +2491,14 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6c2c604bb89e64b</t>
+          <t>https://www.indeed.com/viewjob?jk=f5d14ef4e88a3e5a</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e02fe4d607063c1</t>
+          <t>https://www.indeed.com/viewjob?jk=5f6ccf05e64c984b</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fbafb89e71fb39e</t>
+          <t>https://www.indeed.com/viewjob?jk=7b4b4f98c48563cd</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8ac438ef838975b</t>
+          <t>https://www.indeed.com/viewjob?jk=c6c2c604bb89e64b</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,14 +2631,14 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74bd0f0f93d9a1a5</t>
+          <t>https://www.indeed.com/viewjob?jk=6e02fe4d607063c1</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,14 +2666,14 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c53e85e359970d4</t>
+          <t>https://www.indeed.com/viewjob?jk=9fbafb89e71fb39e</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,14 +2701,14 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c433c70839583dc</t>
+          <t>https://www.indeed.com/viewjob?jk=e8ac438ef838975b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,14 +2736,14 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35e828bfc556b676</t>
+          <t>https://www.indeed.com/viewjob?jk=74bd0f0f93d9a1a5</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,14 +2771,14 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3058b24332d31ded</t>
+          <t>https://www.indeed.com/viewjob?jk=4c53e85e359970d4</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,14 +2806,14 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10e23f958e9e8b09</t>
+          <t>https://www.indeed.com/viewjob?jk=0c433c70839583dc</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,14 +2841,14 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=357547d890623cb5</t>
+          <t>https://www.indeed.com/viewjob?jk=35e828bfc556b676</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,14 +2876,14 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3884844e18945dee</t>
+          <t>https://www.indeed.com/viewjob?jk=3058b24332d31ded</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,14 +2911,14 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17b7c64ee8dc67e0</t>
+          <t>https://www.indeed.com/viewjob?jk=10e23f958e9e8b09</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,14 +2946,14 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a75982d2aedba052</t>
+          <t>https://www.indeed.com/viewjob?jk=357547d890623cb5</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,14 +2981,14 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b3d8d96e19fcbe6</t>
+          <t>https://www.indeed.com/viewjob?jk=3884844e18945dee</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,14 +3016,14 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a60a56d62d329dea</t>
+          <t>https://www.indeed.com/viewjob?jk=17b7c64ee8dc67e0</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,14 +3051,14 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93902824d8ac4d0c</t>
+          <t>https://www.indeed.com/viewjob?jk=a75982d2aedba052</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=088398b8f22d3683</t>
+          <t>https://www.indeed.com/viewjob?jk=4b3d8d96e19fcbe6</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f8a4d4b303056b</t>
+          <t>https://www.indeed.com/viewjob?jk=a60a56d62d329dea</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,67 +3156,67 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=459cc0fec55fdc6f</t>
+          <t>https://www.indeed.com/viewjob?jk=93902824d8ac4d0c</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, MongoDB, Data Modeling</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb77847b7cd88f45</t>
+          <t>https://www.indeed.com/viewjob?jk=088398b8f22d3683</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Kubernetes, Airflow</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d20f4b9e6a3cbb70</t>
+          <t>https://www.indeed.com/viewjob?jk=60f8a4d4b303056b</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c89d6a7d2041de38</t>
+          <t>https://www.indeed.com/viewjob?jk=eb77847b7cd88f45</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Teradata</t>
+          <t>Genentech</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Step Functions, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=806bff32d1d719ff</t>
+          <t>https://www.indeed.com/viewjob?jk=d20f4b9e6a3cbb70</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Developer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Genentech</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Step Functions, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fedd79bbbee99bb</t>
+          <t>https://www.indeed.com/viewjob?jk=c89d6a7d2041de38</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend + Data pipelines)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Teradata</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, API Gateway, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4fca4ad337ae6c</t>
+          <t>https://www.indeed.com/viewjob?jk=806bff32d1d719ff</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend + Data pipelines)</t>
+          <t>Senior Site Reliability Developer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ae76b185563f91b</t>
+          <t>https://www.indeed.com/viewjob?jk=3fedd79bbbee99bb</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef2a73b324528506</t>
+          <t>https://www.indeed.com/viewjob?jk=7d4fca4ad337ae6c</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92aaafaf1efb9ec4</t>
+          <t>https://www.indeed.com/viewjob?jk=1ae76b185563f91b</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9981aefe519f0cd</t>
+          <t>https://www.indeed.com/viewjob?jk=ef2a73b324528506</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fce2095df8206466</t>
+          <t>https://www.indeed.com/viewjob?jk=92aaafaf1efb9ec4</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee34633b7838a9b3</t>
+          <t>https://www.indeed.com/viewjob?jk=c9981aefe519f0cd</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc57f588c654f1cd</t>
+          <t>https://www.indeed.com/viewjob?jk=fce2095df8206466</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5aaeb4c54cdfa77e</t>
+          <t>https://www.indeed.com/viewjob?jk=ee34633b7838a9b3</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb06d74f6367bb04</t>
+          <t>https://www.indeed.com/viewjob?jk=cc57f588c654f1cd</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49799e02e3e0a925</t>
+          <t>https://www.indeed.com/viewjob?jk=5aaeb4c54cdfa77e</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52ff9083bc8990ce</t>
+          <t>https://www.indeed.com/viewjob?jk=eb06d74f6367bb04</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f89817131cfa0d</t>
+          <t>https://www.indeed.com/viewjob?jk=49799e02e3e0a925</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdb757efdefad0ca</t>
+          <t>https://www.indeed.com/viewjob?jk=52ff9083bc8990ce</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57fc4e97a319b123</t>
+          <t>https://www.indeed.com/viewjob?jk=66f89817131cfa0d</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fcc67143e3ff8a</t>
+          <t>https://www.indeed.com/viewjob?jk=cdb757efdefad0ca</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dad4bf1e950e1c9</t>
+          <t>https://www.indeed.com/viewjob?jk=57fc4e97a319b123</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f9ed5d278a8086d</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fcc67143e3ff8a</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8809421834292084</t>
+          <t>https://www.indeed.com/viewjob?jk=5dad4bf1e950e1c9</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>AWS Developer/Integration Engineer</t>
+          <t>Software Engineer II (Backend + Data pipelines)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>rockITdata</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, DynamoDB, Amazon QuickSight, CI/CD</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a60d7d509fbceed</t>
+          <t>https://www.indeed.com/viewjob?jk=0f9ed5d278a8086d</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Digital Engineer – Full Stack &amp; Systems Architecture</t>
+          <t>Software Engineer II (Backend + Data pipelines)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Berkeley, MO, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5360d83db3589d68</t>
+          <t>https://www.indeed.com/viewjob?jk=8809421834292084</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Digital Engineer – Full Stack &amp; Systems Architecture</t>
+          <t>Senior Application Platform Architect - 6163848</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Hadoop, Scala, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12a4a8cde3354706</t>
+          <t>https://www.indeed.com/viewjob?jk=7ea7fc0fae83610a</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Application Platform Architect - 6163848</t>
+          <t>Senior LLM Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Hadoop, Scala, PostgreSQL, CI/CD, Docker</t>
+          <t>AWS, Azure, Vertex AI, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ea7fc0fae83610a</t>
+          <t>https://www.indeed.com/viewjob?jk=109c9c4a6595ba95</t>
         </is>
       </c>
     </row>
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109c9c4a6595ba95</t>
+          <t>https://www.indeed.com/viewjob?jk=8723fa94634ae387</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior LLM Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>LERETA, LLC</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Pomona, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, MLOps</t>
+          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8723fa94634ae387</t>
+          <t>https://www.indeed.com/viewjob?jk=ad5d067156fc62f1</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Machine Learning Engineer (Search)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>LERETA, LLC</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Pomona, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad5d067156fc62f1</t>
+          <t>https://www.indeed.com/viewjob?jk=cff2f5a9dcacb28f</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cff2f5a9dcacb28f</t>
+          <t>https://www.indeed.com/viewjob?jk=3216b4c3b2c151f8</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3216b4c3b2c151f8</t>
+          <t>https://www.indeed.com/viewjob?jk=a0fc0424a2f74ea8</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0fc0424a2f74ea8</t>
+          <t>https://www.indeed.com/viewjob?jk=c0ff98f788ff107b</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0ff98f788ff107b</t>
+          <t>https://www.indeed.com/viewjob?jk=0442372baf83ee82</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0442372baf83ee82</t>
+          <t>https://www.indeed.com/viewjob?jk=fe6ea91421159ece</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe6ea91421159ece</t>
+          <t>https://www.indeed.com/viewjob?jk=aecbf4d450f1441b</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aecbf4d450f1441b</t>
+          <t>https://www.indeed.com/viewjob?jk=31056dc236b5ce67</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31056dc236b5ce67</t>
+          <t>https://www.indeed.com/viewjob?jk=eca84bb19e700f2b</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eca84bb19e700f2b</t>
+          <t>https://www.indeed.com/viewjob?jk=7401294591da0c90</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7401294591da0c90</t>
+          <t>https://www.indeed.com/viewjob?jk=5eed535b1fcfea26</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eed535b1fcfea26</t>
+          <t>https://www.indeed.com/viewjob?jk=b29243583190aa6a</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29243583190aa6a</t>
+          <t>https://www.indeed.com/viewjob?jk=1c0d7ebd3a2ee36f</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c0d7ebd3a2ee36f</t>
+          <t>https://www.indeed.com/viewjob?jk=28e3397c0e70024e</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e3397c0e70024e</t>
+          <t>https://www.indeed.com/viewjob?jk=35f50cc085f1bbd9</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35f50cc085f1bbd9</t>
+          <t>https://www.indeed.com/viewjob?jk=72be3b8aba169a59</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72be3b8aba169a59</t>
+          <t>https://www.indeed.com/viewjob?jk=b61af8e418fcf231</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b61af8e418fcf231</t>
+          <t>https://www.indeed.com/viewjob?jk=552a8172dcf24a7a</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,32 +4871,32 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=552a8172dcf24a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=4fa51ea3c52768d7</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Search)</t>
+          <t>Software Engineering Intern – Data Engineering (Cloud &amp; Streaming)</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>NextPower</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fa51ea3c52768d7</t>
+          <t>https://www.indeed.com/viewjob?jk=28e588be3c533008</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Software Engineering Intern – Data Engineering (Cloud &amp; Streaming)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>NextPower</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Power BI, Tableau, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e588be3c533008</t>
+          <t>https://www.indeed.com/viewjob?jk=aaf9596bf4159924</t>
         </is>
       </c>
     </row>
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaf9596bf4159924</t>
+          <t>https://www.indeed.com/viewjob?jk=ab90611f6b141379</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Cloud Systems Engineer (Databricks Administrator)</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Providge Consulting</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Power BI, Tableau, MLOps, MLflow</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab90611f6b141379</t>
+          <t>https://www.indeed.com/viewjob?jk=e094ab218ebab2ed</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Cloud Systems Engineer (Databricks Administrator)</t>
+          <t>Sr. ETL/SQL Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Providge Consulting</t>
+          <t>Capgemini Government Solutions</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Scala, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e094ab218ebab2ed</t>
+          <t>https://www.indeed.com/viewjob?jk=724ffe7f1d3da135</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Sr. ETL/SQL Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Capgemini Government Solutions</t>
+          <t>Space Telescope Science Institute</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, ECS, IAM, Hive, Scala, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724ffe7f1d3da135</t>
+          <t>https://www.indeed.com/viewjob?jk=6055970eb603df79</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>AI Engineer III</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Space Telescope Science Institute</t>
+          <t>CareSource</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Hive, Scala, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>API Gateway, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6055970eb603df79</t>
+          <t>https://www.indeed.com/viewjob?jk=640c68fe3716b1e6</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>AI Engineer III</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>CareSource</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=640c68fe3716b1e6</t>
+          <t>https://www.indeed.com/viewjob?jk=d44e3274520e56d6</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Sr Software Engineer (Site Reliability Engineering) (2026-10114)</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, MySQL, Splunk</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5ab755eddd54b18</t>
+          <t>https://www.indeed.com/viewjob?jk=e2b622ee37d8f63f</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d44e3274520e56d6</t>
+          <t>https://www.indeed.com/viewjob?jk=7ba10ede755adc88</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Centene</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,17 +5246,17 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11d92da9c37770a7</t>
+          <t>https://www.indeed.com/viewjob?jk=035e833a0affea06</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2b622ee37d8f63f</t>
+          <t>https://www.indeed.com/viewjob?jk=34ea65634bf231fc</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ba10ede755adc88</t>
+          <t>https://www.indeed.com/viewjob?jk=db2fffa7ab4fc3c6</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=035e833a0affea06</t>
+          <t>https://www.indeed.com/viewjob?jk=726fca60377106fb</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ea65634bf231fc</t>
+          <t>https://www.indeed.com/viewjob?jk=ae1bbd4c5bfc6dc1</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db2fffa7ab4fc3c6</t>
+          <t>https://www.indeed.com/viewjob?jk=7d44fb63e0c3570e</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=726fca60377106fb</t>
+          <t>https://www.indeed.com/viewjob?jk=ac1d3f6a217585b1</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae1bbd4c5bfc6dc1</t>
+          <t>https://www.indeed.com/viewjob?jk=594c2209c74b60f3</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d44fb63e0c3570e</t>
+          <t>https://www.indeed.com/viewjob?jk=300951fa8a03d9ab</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac1d3f6a217585b1</t>
+          <t>https://www.indeed.com/viewjob?jk=224f85378fe66226</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=594c2209c74b60f3</t>
+          <t>https://www.indeed.com/viewjob?jk=609ed15647075bf2</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=300951fa8a03d9ab</t>
+          <t>https://www.indeed.com/viewjob?jk=f7da2bae9861dfa9</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224f85378fe66226</t>
+          <t>https://www.indeed.com/viewjob?jk=9f44f95326fb5d8b</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=609ed15647075bf2</t>
+          <t>https://www.indeed.com/viewjob?jk=f7f6777f3346c150</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7da2bae9861dfa9</t>
+          <t>https://www.indeed.com/viewjob?jk=99001099f8e56675</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f44f95326fb5d8b</t>
+          <t>https://www.indeed.com/viewjob?jk=1d562fde2d3ab4ec</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,14 +5816,14 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7f6777f3346c150</t>
+          <t>https://www.indeed.com/viewjob?jk=49363af061447f75</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>Senior Software Engineer (Python + Distributed systems)</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,14 +5851,14 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99001099f8e56675</t>
+          <t>https://www.indeed.com/viewjob?jk=c4af4ef5dfeb0026</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>Senior Software Engineer (Python + Distributed systems)</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,14 +5886,14 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d562fde2d3ab4ec</t>
+          <t>https://www.indeed.com/viewjob?jk=c116b8acf805f138</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>Senior Software Engineer (Python + Distributed systems)</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49363af061447f75</t>
+          <t>https://www.indeed.com/viewjob?jk=f996f9a35281bba7</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4af4ef5dfeb0026</t>
+          <t>https://www.indeed.com/viewjob?jk=ca3982c4f2be4e49</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c116b8acf805f138</t>
+          <t>https://www.indeed.com/viewjob?jk=9f2a3e577d5623a4</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f996f9a35281bba7</t>
+          <t>https://www.indeed.com/viewjob?jk=629b89e40e1e1bb5</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca3982c4f2be4e49</t>
+          <t>https://www.indeed.com/viewjob?jk=db6cf98112c1bc9f</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f2a3e577d5623a4</t>
+          <t>https://www.indeed.com/viewjob?jk=80b26c4d48449b15</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=629b89e40e1e1bb5</t>
+          <t>https://www.indeed.com/viewjob?jk=83ba9763cad5f2f8</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db6cf98112c1bc9f</t>
+          <t>https://www.indeed.com/viewjob?jk=05460d1c364a2974</t>
         </is>
       </c>
     </row>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80b26c4d48449b15</t>
+          <t>https://www.indeed.com/viewjob?jk=b01dc956f073aaf8</t>
         </is>
       </c>
     </row>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83ba9763cad5f2f8</t>
+          <t>https://www.indeed.com/viewjob?jk=807aad5f4045241d</t>
         </is>
       </c>
     </row>
@@ -6253,7 +6253,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05460d1c364a2974</t>
+          <t>https://www.indeed.com/viewjob?jk=655ea21e25dbce1e</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6306,24 +6306,24 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b01dc956f073aaf8</t>
+          <t>https://www.indeed.com/viewjob?jk=c46ceb995e304d69</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python + Distributed systems)</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>H2O.ai</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6341,24 +6341,24 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=807aad5f4045241d</t>
+          <t>https://www.indeed.com/viewjob?jk=fe52f92aedddcda4</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python + Distributed systems)</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>H2O.ai</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -6376,24 +6376,24 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=655ea21e25dbce1e</t>
+          <t>https://www.indeed.com/viewjob?jk=0d2b8979a3b5f81b</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python + Distributed systems)</t>
+          <t>Senior Data Engineer - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>WesBanco Bank, Inc.</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Bowie, MD, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -6411,24 +6411,24 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c46ceb995e304d69</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a02cdb2b181be3</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Data Engineer - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>H2O.ai</t>
+          <t>WesBanco Bank, Inc.</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Wheeling, WV, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -6446,32 +6446,32 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe52f92aedddcda4</t>
+          <t>https://www.indeed.com/viewjob?jk=fb6ee55d393e301c</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>AV Safety Engineering Analytics Simulation Engineer (GPSSC)</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>H2O.ai</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -6481,102 +6481,102 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d2b8979a3b5f81b</t>
+          <t>https://www.indeed.com/viewjob?jk=4b9eec46bbab109b</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data &amp; Analytics</t>
+          <t>AWS Cloud Administrator</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>WesBanco Bank, Inc.</t>
+          <t>rockITdata</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Bowie, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, Azure, DynamoDB, Terraform</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a02cdb2b181be3</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0a98e5951373b4</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data &amp; Analytics</t>
+          <t>Data Engineer-Remote</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>WesBanco Bank, Inc.</t>
+          <t>Mutual of Omaha</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Wheeling, WV, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, Glue, RDS, Scala, Snowflake, SQL Server, MongoDB, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb6ee55d393e301c</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc1efbee94e32a9</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Software Developer - Database Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>RAMSOFT</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, HBase, Scala, Snowflake, MySQL, NoSQL, Data Modeling, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -6586,24 +6586,24 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ce0ac7d0a937f32</t>
+          <t>https://www.indeed.com/viewjob?jk=ed1b9b0328def6aa</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>AV Safety Engineering Analytics Simulation Engineer (GPSSC)</t>
+          <t>SAP NS2 Senior HANA Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -6621,24 +6621,24 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b9eec46bbab109b</t>
+          <t>https://www.indeed.com/viewjob?jk=8999a6d9da6831ef</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>AWS Cloud Administrator</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>rockITdata</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6646,34 +6646,34 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, Azure, DynamoDB, Terraform</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0a98e5951373b4</t>
+          <t>https://www.indeed.com/viewjob?jk=2e60ff8bc1e60898</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Data Engineer-Remote</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Mutual of Omaha</t>
+          <t>Callaway Golf</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6681,34 +6681,34 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Scala, Snowflake, SQL Server, MongoDB, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc1efbee94e32a9</t>
+          <t>https://www.indeed.com/viewjob?jk=9ae59fccd3421dc5</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>SENIOR DATA ENGINEER (REMOTE)</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Morrison Healthcare</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6716,34 +6716,34 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Snowflake, ETL, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed1b9b0328def6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=d530073f998c3698</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>SAP NS2 Senior HANA Cloud DevOps Engineer</t>
+          <t>Teradata Developer</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6751,34 +6751,34 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8999a6d9da6831ef</t>
+          <t>https://www.indeed.com/viewjob?jk=7fddb4ec439f1237</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior BI Developer - Investment Services</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -6796,24 +6796,24 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e60ff8bc1e60898</t>
+          <t>https://www.indeed.com/viewjob?jk=6861136ad5c92fec</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior BI Developer - Investment Services</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Callaway Golf</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6821,34 +6821,34 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ae59fccd3421dc5</t>
+          <t>https://www.indeed.com/viewjob?jk=d0459e004fd012bc</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Software Engineer Intern</t>
+          <t>Senior BI Developer - Investment Services</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6856,34 +6856,34 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c65c6376729ba486</t>
+          <t>https://www.indeed.com/viewjob?jk=00bd0c85ee5af1cc</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Visualization Engineer</t>
+          <t>Senior BI Developer - Investment Services</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>RDS, Scala, Data Modeling, Star Schema, ETL, ELT, Power BI, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -6901,24 +6901,24 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b28a6ad6f45c5471</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a227aff44c18bd</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Senior AI/ML Scientist</t>
+          <t>Senior BI Developer - Investment Services</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Milford, MI, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, MLflow, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -6936,24 +6936,24 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=300d4ca14be662c3</t>
+          <t>https://www.indeed.com/viewjob?jk=f36e77b3ab4b1808</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>AV Safety Engineering Analytics Engineer (GPSSC)</t>
+          <t>Senior BI Developer - Investment Services</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -6971,24 +6971,24 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60da6f50aaadfe48</t>
+          <t>https://www.indeed.com/viewjob?jk=b03b046a7e4b4373</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>SENIOR DATA ENGINEER (REMOTE)</t>
+          <t>Data Modeler</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Morrison Healthcare</t>
+          <t>Union Bank &amp; Trust Co.</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -6996,34 +6996,34 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Snowflake, ETL, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d530073f998c3698</t>
+          <t>https://www.indeed.com/viewjob?jk=c3cbc74799dc9ea0</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Product Engineer</t>
+          <t>Software Engineer Intern</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>ALTIMATE</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -7031,7 +7031,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Spark, Scala, PostgreSQL, dbt, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -7041,24 +7041,24 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95f4b6534ba4c3cd</t>
+          <t>https://www.indeed.com/viewjob?jk=c65c6376729ba486</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Teradata Developer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -7066,7 +7066,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -7076,24 +7076,24 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fddb4ec439f1237</t>
+          <t>https://www.indeed.com/viewjob?jk=50c61f5469ce333f</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Senior BI Developer - Investment Services</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -7101,34 +7101,34 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6861136ad5c92fec</t>
+          <t>https://www.indeed.com/viewjob?jk=4303ceb5e8c627c4</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Senior BI Developer - Investment Services</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -7136,34 +7136,34 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0459e004fd012bc</t>
+          <t>https://www.indeed.com/viewjob?jk=0c4db6d385ae6ea3</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Senior BI Developer - Investment Services</t>
+          <t>Sr. Full Stack Software Engineer (Onsite - San Diego)</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Carlsmed</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -7171,7 +7171,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, Scala, PostgreSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -7181,24 +7181,24 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00bd0c85ee5af1cc</t>
+          <t>https://www.indeed.com/viewjob?jk=47ffb86f604e14df</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Senior BI Developer - Investment Services</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -7216,24 +7216,24 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a227aff44c18bd</t>
+          <t>https://www.indeed.com/viewjob?jk=c70cf8723aeaf7eb</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Senior BI Developer - Investment Services</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -7251,24 +7251,24 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f36e77b3ab4b1808</t>
+          <t>https://www.indeed.com/viewjob?jk=6f106012aaf32c49</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Senior BI Developer - Investment Services</t>
+          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -7286,24 +7286,24 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b03b046a7e4b4373</t>
+          <t>https://www.indeed.com/viewjob?jk=a1593d7242ad3914</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior AI/ML Scientist</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -7311,34 +7311,34 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c61f5469ce333f</t>
+          <t>https://www.indeed.com/viewjob?jk=300d4ca14be662c3</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Snowflake Administrator</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -7346,34 +7346,34 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4303ceb5e8c627c4</t>
+          <t>https://www.indeed.com/viewjob?jk=085de5867e567658</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>LLM Application Engineer</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -7381,34 +7381,34 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c4db6d385ae6ea3</t>
+          <t>https://www.indeed.com/viewjob?jk=5633278896c16c3b</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Software Engineer (Onsite - San Diego)</t>
+          <t>LLM Application Engineer</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Carlsmed</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -7416,7 +7416,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, Scala, PostgreSQL, CI/CD, Git</t>
+          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -7425,216 +7425,6 @@
         </is>
       </c>
       <c r="G200" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=47ffb86f604e14df</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>Engineer II- Java</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D201" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c70cf8723aeaf7eb</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>Engineer II- Java</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D202" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6f106012aaf32c49</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>CrowdStrike</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>Sunnyvale, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D203" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F203" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a1593d7242ad3914</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>Snowflake Administrator</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D204" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F204" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=085de5867e567658</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>LLM Application Engineer</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D205" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
-        </is>
-      </c>
-      <c r="F205" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5633278896c16c3b</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>LLM Application Engineer</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D206" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
-        </is>
-      </c>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G206" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=4e56614bfb72e3b3</t>
         </is>

--- a/results/job_matches_2026-03-06.xlsx
+++ b/results/job_matches_2026-03-06.xlsx
@@ -1063,17 +1063,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>TxDMV - Systems Analyst - Data Engineer (Remote in TX)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>JBS Dev</t>
+          <t>Texas Department of Motor Vehicles</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Cloud Storage, Scala, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49f6c2df00dd6e11</t>
+          <t>https://www.indeed.com/viewjob?jk=934456836d756b7d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Costa Rica)</t>
+          <t>TxDMV - Data Analyst - Senior BI Developer (Remote in Texas)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>JBS Dev</t>
+          <t>Texas Department of Motor Vehicles</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05c819aa2a88511d</t>
+          <t>https://www.indeed.com/viewjob?jk=4fb5c05e83aa7c0e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>System Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Systems Engineering Solutions Corporation</t>
+          <t>JBS Dev</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=634fcd15ef04d7bf</t>
+          <t>https://www.indeed.com/viewjob?jk=49f6c2df00dd6e11</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Senior Data Engineer (Costa Rica)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>JBS Dev</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7869ee373ec84ed</t>
+          <t>https://www.indeed.com/viewjob?jk=05c819aa2a88511d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CLOUD ENGINEER (AWS) (REMOTE/USA) - GDM (GRAY MEDIA GROUP)</t>
+          <t>System Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GRAY MEDIA</t>
+          <t>Systems Engineering Solutions Corporation</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, DynamoDB</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0beb94e2f1648144</t>
+          <t>https://www.indeed.com/viewjob?jk=634fcd15ef04d7bf</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afa51ac883fa48a6</t>
+          <t>https://www.indeed.com/viewjob?jk=c7869ee373ec84ed</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior BI Analyst</t>
+          <t>CLOUD ENGINEER (AWS) (REMOTE/USA) - GDM (GRAY MEDIA GROUP)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>GRAY MEDIA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad414f3a9ab0a2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=0beb94e2f1648144</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=459162c660bc8082</t>
+          <t>https://www.indeed.com/viewjob?jk=afa51ac883fa48a6</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior BI Analyst</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Upstart</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, BigQuery, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3dab96c17b78fc32</t>
+          <t>https://www.indeed.com/viewjob?jk=ad414f3a9ab0a2bc</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Azure CI/CD Developer (FTE / Hybrid)</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Oaks, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,67 +1406,67 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffe5d7e4f5833213</t>
+          <t>https://www.indeed.com/viewjob?jk=459162c660bc8082</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Data Platform Administrator – Remote</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Creative Information Technology India</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f059a12d002721db</t>
+          <t>https://www.indeed.com/viewjob?jk=9dc4962750543485</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python/PySpark</t>
+          <t>Azure CI/CD Developer (FTE / Hybrid)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Oaks, PA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b1dd2ce5d3671a</t>
+          <t>https://www.indeed.com/viewjob?jk=ffe5d7e4f5833213</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
+          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6efe960a7ab141ac</t>
+          <t>https://www.indeed.com/viewjob?jk=f059a12d002721db</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SENIOR DATA ENGINEER</t>
+          <t>Software Engineer III- Python/PySpark</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bee5a340a7f65e61</t>
+          <t>https://www.indeed.com/viewjob?jk=82b1dd2ce5d3671a</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Sr Software Development Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PetSmart</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
+          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c8a098e9a2c0e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=6efe960a7ab141ac</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>SENIOR DATA ENGINEER</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PetSmart</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=157ddcd0636f7c11</t>
+          <t>https://www.indeed.com/viewjob?jk=bee5a340a7f65e61</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BOULDER SCIENTIFIC CO</t>
+          <t>PetSmart</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Longmont, CO, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9486135c47b58364</t>
+          <t>https://www.indeed.com/viewjob?jk=0c8a098e9a2c0e1a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>PetSmart</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba5a22f3941b5b26</t>
+          <t>https://www.indeed.com/viewjob?jk=157ddcd0636f7c11</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AI Support Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>BOULDER SCIENTIFIC CO</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Longmont, CO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=625bf5ef0b332ad3</t>
+          <t>https://www.indeed.com/viewjob?jk=9486135c47b58364</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AI Support Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd39a203b7587e31</t>
+          <t>https://www.indeed.com/viewjob?jk=ba5a22f3941b5b26</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Support Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Yusen Logistics</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kimball, ELT, dbt</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f92de33105c0bad</t>
+          <t>https://www.indeed.com/viewjob?jk=625bf5ef0b332ad3</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Support Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Yusen Logistics</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kimball, ELT, dbt</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=772460af87c5b60c</t>
+          <t>https://www.indeed.com/viewjob?jk=dd39a203b7587e31</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Yusen Logistics</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Royal Oak, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bb3681c5da818f2</t>
+          <t>https://www.indeed.com/viewjob?jk=7f92de33105c0bad</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Yusen Logistics</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=343b07159d1b6928</t>
+          <t>https://www.indeed.com/viewjob?jk=772460af87c5b60c</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer - Virtual</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Alight Solutions</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Royal Oak, MI, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a286c7ca862c4e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=6bb3681c5da818f2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>TWG Global AI</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edb6a72ac37333e2</t>
+          <t>https://www.indeed.com/viewjob?jk=343b07159d1b6928</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python, PySpark, Lambda)</t>
+          <t>Cloud Platform Engineer - Virtual</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c588b2aa81b85891</t>
+          <t>https://www.indeed.com/viewjob?jk=a286c7ca862c4e1a</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>AllCloud</t>
+          <t>TWG Global AI</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49fcd1d4ac195cdf</t>
+          <t>https://www.indeed.com/viewjob?jk=edb6a72ac37333e2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>IT BI Solutions Engineer, ES</t>
+          <t>Senior Software Engineer (Python, PySpark, Lambda)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Terex Corporation</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chattanooga, TN, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8376f8e501b07a8</t>
+          <t>https://www.indeed.com/viewjob?jk=c588b2aa81b85891</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-3</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>AllCloud</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f753e538739bd670</t>
+          <t>https://www.indeed.com/viewjob?jk=49fcd1d4ac195cdf</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Junior AI/MLOps Engineer</t>
+          <t>IT BI Solutions Engineer, ES</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Terex Corporation</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Chattanooga, TN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, NoSQL, MLOps, MLflow, CI/CD, Terraform</t>
+          <t>AWS, Redshift, RDS, Scala, Snowflake, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe34817d3b1a40dc</t>
+          <t>https://www.indeed.com/viewjob?jk=e8376f8e501b07a8</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Data Platform Engineer-3</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Parsippany-Troy Hills, NJ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90d33ae33b62c3a0</t>
+          <t>https://www.indeed.com/viewjob?jk=f753e538739bd670</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec56a8fbf5328856</t>
+          <t>https://www.indeed.com/viewjob?jk=90d33ae33b62c3a0</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,14 +2246,14 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d4834b7dd63e5a3</t>
+          <t>https://www.indeed.com/viewjob?jk=ec56a8fbf5328856</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,14 +2281,14 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=314cd9d2f824e302</t>
+          <t>https://www.indeed.com/viewjob?jk=3d4834b7dd63e5a3</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec0d14ba7f6cc782</t>
+          <t>https://www.indeed.com/viewjob?jk=314cd9d2f824e302</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,14 +2351,14 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd9783225b203a0f</t>
+          <t>https://www.indeed.com/viewjob?jk=ec0d14ba7f6cc782</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,14 +2386,14 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fcdb3a443f803a9</t>
+          <t>https://www.indeed.com/viewjob?jk=cd9783225b203a0f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=154ab74a68ca6406</t>
+          <t>https://www.indeed.com/viewjob?jk=5fcdb3a443f803a9</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31f45e1ed037bd50</t>
+          <t>https://www.indeed.com/viewjob?jk=154ab74a68ca6406</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5d14ef4e88a3e5a</t>
+          <t>https://www.indeed.com/viewjob?jk=31f45e1ed037bd50</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f6ccf05e64c984b</t>
+          <t>https://www.indeed.com/viewjob?jk=f5d14ef4e88a3e5a</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,14 +2561,14 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b4b4f98c48563cd</t>
+          <t>https://www.indeed.com/viewjob?jk=5f6ccf05e64c984b</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6c2c604bb89e64b</t>
+          <t>https://www.indeed.com/viewjob?jk=7b4b4f98c48563cd</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,14 +2631,14 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e02fe4d607063c1</t>
+          <t>https://www.indeed.com/viewjob?jk=c6c2c604bb89e64b</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,14 +2666,14 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fbafb89e71fb39e</t>
+          <t>https://www.indeed.com/viewjob?jk=6e02fe4d607063c1</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8ac438ef838975b</t>
+          <t>https://www.indeed.com/viewjob?jk=9fbafb89e71fb39e</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74bd0f0f93d9a1a5</t>
+          <t>https://www.indeed.com/viewjob?jk=e8ac438ef838975b</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,14 +2771,14 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c53e85e359970d4</t>
+          <t>https://www.indeed.com/viewjob?jk=74bd0f0f93d9a1a5</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c433c70839583dc</t>
+          <t>https://www.indeed.com/viewjob?jk=4c53e85e359970d4</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35e828bfc556b676</t>
+          <t>https://www.indeed.com/viewjob?jk=0c433c70839583dc</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,14 +2876,14 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3058b24332d31ded</t>
+          <t>https://www.indeed.com/viewjob?jk=35e828bfc556b676</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10e23f958e9e8b09</t>
+          <t>https://www.indeed.com/viewjob?jk=3058b24332d31ded</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=357547d890623cb5</t>
+          <t>https://www.indeed.com/viewjob?jk=10e23f958e9e8b09</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,14 +2981,14 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3884844e18945dee</t>
+          <t>https://www.indeed.com/viewjob?jk=357547d890623cb5</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17b7c64ee8dc67e0</t>
+          <t>https://www.indeed.com/viewjob?jk=3884844e18945dee</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a75982d2aedba052</t>
+          <t>https://www.indeed.com/viewjob?jk=17b7c64ee8dc67e0</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,14 +3086,14 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b3d8d96e19fcbe6</t>
+          <t>https://www.indeed.com/viewjob?jk=a75982d2aedba052</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a60a56d62d329dea</t>
+          <t>https://www.indeed.com/viewjob?jk=4b3d8d96e19fcbe6</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93902824d8ac4d0c</t>
+          <t>https://www.indeed.com/viewjob?jk=a60a56d62d329dea</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,59 +3191,59 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=088398b8f22d3683</t>
+          <t>https://www.indeed.com/viewjob?jk=93902824d8ac4d0c</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60f8a4d4b303056b</t>
+          <t>https://www.indeed.com/viewjob?jk=eb77847b7cd88f45</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Genentech</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,17 +3251,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, MongoDB, Data Modeling</t>
+          <t>AWS, Step Functions, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb77847b7cd88f45</t>
+          <t>https://www.indeed.com/viewjob?jk=d20f4b9e6a3cbb70</t>
         </is>
       </c>
     </row>
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d20f4b9e6a3cbb70</t>
+          <t>https://www.indeed.com/viewjob?jk=c89d6a7d2041de38</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>Teradata</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Kubernetes, Airflow</t>
+          <t>AWS, API Gateway, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c89d6a7d2041de38</t>
+          <t>https://www.indeed.com/viewjob?jk=806bff32d1d719ff</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Site Reliability Developer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Teradata</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=806bff32d1d719ff</t>
+          <t>https://www.indeed.com/viewjob?jk=3fedd79bbbee99bb</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Developer</t>
+          <t>Software Engineer II (Backend + Data pipelines)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fedd79bbbee99bb</t>
+          <t>https://www.indeed.com/viewjob?jk=7d4fca4ad337ae6c</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4fca4ad337ae6c</t>
+          <t>https://www.indeed.com/viewjob?jk=1ae76b185563f91b</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ae76b185563f91b</t>
+          <t>https://www.indeed.com/viewjob?jk=ef2a73b324528506</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef2a73b324528506</t>
+          <t>https://www.indeed.com/viewjob?jk=92aaafaf1efb9ec4</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92aaafaf1efb9ec4</t>
+          <t>https://www.indeed.com/viewjob?jk=c9981aefe519f0cd</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9981aefe519f0cd</t>
+          <t>https://www.indeed.com/viewjob?jk=fce2095df8206466</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fce2095df8206466</t>
+          <t>https://www.indeed.com/viewjob?jk=ee34633b7838a9b3</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee34633b7838a9b3</t>
+          <t>https://www.indeed.com/viewjob?jk=cc57f588c654f1cd</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc57f588c654f1cd</t>
+          <t>https://www.indeed.com/viewjob?jk=5aaeb4c54cdfa77e</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5aaeb4c54cdfa77e</t>
+          <t>https://www.indeed.com/viewjob?jk=eb06d74f6367bb04</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb06d74f6367bb04</t>
+          <t>https://www.indeed.com/viewjob?jk=49799e02e3e0a925</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49799e02e3e0a925</t>
+          <t>https://www.indeed.com/viewjob?jk=52ff9083bc8990ce</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52ff9083bc8990ce</t>
+          <t>https://www.indeed.com/viewjob?jk=66f89817131cfa0d</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f89817131cfa0d</t>
+          <t>https://www.indeed.com/viewjob?jk=cdb757efdefad0ca</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdb757efdefad0ca</t>
+          <t>https://www.indeed.com/viewjob?jk=57fc4e97a319b123</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57fc4e97a319b123</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fcc67143e3ff8a</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fcc67143e3ff8a</t>
+          <t>https://www.indeed.com/viewjob?jk=5dad4bf1e950e1c9</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dad4bf1e950e1c9</t>
+          <t>https://www.indeed.com/viewjob?jk=0f9ed5d278a8086d</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f9ed5d278a8086d</t>
+          <t>https://www.indeed.com/viewjob?jk=8809421834292084</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend + Data pipelines)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,17 +4056,17 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, Scala, Oracle, ETL, ELT, dbt, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8809421834292084</t>
+          <t>https://www.indeed.com/viewjob?jk=cdf704f3d9c632a6</t>
         </is>
       </c>
     </row>
@@ -5088,17 +5088,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>AI Engineer III</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>CareSource</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, Scala, MLOps, MLflow, CI/CD, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=640c68fe3716b1e6</t>
+          <t>https://www.indeed.com/viewjob?jk=d44e3274520e56d6</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>TransCore</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,17 +5141,17 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d44e3274520e56d6</t>
+          <t>https://www.indeed.com/viewjob?jk=931daa2509e88e14</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-06.xlsx
+++ b/results/job_matches_2026-03-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G200"/>
+  <dimension ref="A1:G195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,95 +573,95 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Full Stack Engineer (React + Node.js)-5</t>
+          <t>Data Engineer I (Base Camp)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Quorum Business Solutions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01d5f2b9fa96100b</t>
+          <t>https://www.indeed.com/viewjob?jk=59a4bbdbdd64fe68</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AV Safety Engineering Analytics AI/ML Engineer (GPSSC)</t>
+          <t>Data Engineer I (Base Camp)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Quorum Business Solutions</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Dataflow, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b0a8c3e1d955c79</t>
+          <t>https://www.indeed.com/viewjob?jk=ba37e62a9a87f91a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer – DE20260503002</t>
+          <t>AV Safety Engineering Analytics AI/ML Engineer (GPSSC)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>eGrove Systems Corporation</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, Spark, Scala, Oracle</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Dataflow, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6093ead5fe385f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=1b0a8c3e1d955c79</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python, PySpark, Lambda)</t>
+          <t>Data Engineer – DE20260503002</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>eGrove Systems Corporation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, HDFS, Hive, Spark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59f97860142550fe</t>
+          <t>https://www.indeed.com/viewjob?jk=6093ead5fe385f5d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Data Engineer (Python, PySpark, Lambda)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Spire Energy</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL</t>
+          <t>AWS, EMR, Lambda, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df7314eb6a45de22</t>
+          <t>https://www.indeed.com/viewjob?jk=59f97860142550fe</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - INDIA</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Spire Energy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Prosper, TX, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Oracle, Azure Cosmos DB, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8eebff65cda31d0</t>
+          <t>https://www.indeed.com/viewjob?jk=df7314eb6a45de22</t>
         </is>
       </c>
     </row>
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python, Spark, AWS)</t>
+          <t>TxDMV - Data Analyst - Senior BI Developer (Remote in Texas)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Texas Comptroller of Public Accounts</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bac9e3177a7c184b</t>
+          <t>https://www.indeed.com/viewjob?jk=5b98eb455b4295de</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>TxDMV - Systems Analyst - Data Engineer (Remote in TX)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Texas Comptroller of Public Accounts</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Cloud Storage, Scala, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72f18d450d1d99d9</t>
+          <t>https://www.indeed.com/viewjob?jk=73e61a163308157a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
+          <t>TxDMV - Systems Analyst - Data Engineer (Remote in TX)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Texas Department of Motor Vehicles</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Cloud Storage, Scala, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b45360d720d413c7</t>
+          <t>https://www.indeed.com/viewjob?jk=934456836d756b7d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
+          <t>TxDMV - Data Analyst - Senior BI Developer (Remote in Texas)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Texas Department of Motor Vehicles</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,17 +976,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c46cd564ba01b6c</t>
+          <t>https://www.indeed.com/viewjob?jk=4fb5c05e83aa7c0e</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d52dce08f82e688</t>
+          <t>https://www.indeed.com/viewjob?jk=bac9e3177a7c184b</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=175b82022b025c3d</t>
+          <t>https://www.indeed.com/viewjob?jk=72f18d450d1d99d9</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TxDMV - Systems Analyst - Data Engineer (Remote in TX)</t>
+          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Texas Department of Motor Vehicles</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Cloud Storage, Scala, Informatica PowerCenter</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=934456836d756b7d</t>
+          <t>https://www.indeed.com/viewjob?jk=b45360d720d413c7</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TxDMV - Data Analyst - Senior BI Developer (Remote in Texas)</t>
+          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Texas Department of Motor Vehicles</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fb5c05e83aa7c0e</t>
+          <t>https://www.indeed.com/viewjob?jk=3c46cd564ba01b6c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (Python, Spark, AWS)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>JBS Dev</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,14 +1161,14 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49f6c2df00dd6e11</t>
+          <t>https://www.indeed.com/viewjob?jk=6d52dce08f82e688</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Costa Rica)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05c819aa2a88511d</t>
+          <t>https://www.indeed.com/viewjob?jk=49f6c2df00dd6e11</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>System Architect</t>
+          <t>Senior Data Engineer (Costa Rica)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Systems Engineering Solutions Corporation</t>
+          <t>JBS Dev</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=634fcd15ef04d7bf</t>
+          <t>https://www.indeed.com/viewjob?jk=05c819aa2a88511d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>System Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Systems Engineering Solutions Corporation</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, IAM, RDS, Spark, PySpark</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7869ee373ec84ed</t>
+          <t>https://www.indeed.com/viewjob?jk=634fcd15ef04d7bf</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CLOUD ENGINEER (AWS) (REMOTE/USA) - GDM (GRAY MEDIA GROUP)</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GRAY MEDIA</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Google Cloud Platform, GCP, Scala, DynamoDB</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0beb94e2f1648144</t>
+          <t>https://www.indeed.com/viewjob?jk=c7869ee373ec84ed</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior BI Analyst</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afa51ac883fa48a6</t>
+          <t>https://www.indeed.com/viewjob?jk=ad414f3a9ab0a2bc</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior BI Analyst</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad414f3a9ab0a2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=459162c660bc8082</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=459162c660bc8082</t>
+          <t>https://www.indeed.com/viewjob?jk=afa51ac883fa48a6</t>
         </is>
       </c>
     </row>
@@ -1483,17 +1483,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>PetSmart</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f059a12d002721db</t>
+          <t>https://www.indeed.com/viewjob?jk=0c8a098e9a2c0e1a</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python/PySpark</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>PetSmart</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b1dd2ce5d3671a</t>
+          <t>https://www.indeed.com/viewjob?jk=157ddcd0636f7c11</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>BOULDER SCIENTIFIC CO</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Longmont, CO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6efe960a7ab141ac</t>
+          <t>https://www.indeed.com/viewjob?jk=9486135c47b58364</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SENIOR DATA ENGINEER</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bee5a340a7f65e61</t>
+          <t>https://www.indeed.com/viewjob?jk=ba5a22f3941b5b26</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>PetSmart</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c8a098e9a2c0e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=f059a12d002721db</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Software Engineer III- Python/PySpark</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>PetSmart</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=157ddcd0636f7c11</t>
+          <t>https://www.indeed.com/viewjob?jk=82b1dd2ce5d3671a</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Support Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BOULDER SCIENTIFIC CO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Longmont, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9486135c47b58364</t>
+          <t>https://www.indeed.com/viewjob?jk=625bf5ef0b332ad3</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Support Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba5a22f3941b5b26</t>
+          <t>https://www.indeed.com/viewjob?jk=dd39a203b7587e31</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AI Support Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Yusen Logistics</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=625bf5ef0b332ad3</t>
+          <t>https://www.indeed.com/viewjob?jk=7f92de33105c0bad</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AI Support Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Yusen Logistics</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd39a203b7587e31</t>
+          <t>https://www.indeed.com/viewjob?jk=772460af87c5b60c</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Yusen Logistics</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Royal Oak, MI, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kimball, ELT, dbt</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f92de33105c0bad</t>
+          <t>https://www.indeed.com/viewjob?jk=6bb3681c5da818f2</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Yusen Logistics</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kimball, ELT, dbt</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=772460af87c5b60c</t>
+          <t>https://www.indeed.com/viewjob?jk=343b07159d1b6928</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Platform Engineer - Virtual</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Alight Solutions</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Royal Oak, MI, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bb3681c5da818f2</t>
+          <t>https://www.indeed.com/viewjob?jk=a286c7ca862c4e1a</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Software Development Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=343b07159d1b6928</t>
+          <t>https://www.indeed.com/viewjob?jk=6efe960a7ab141ac</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer - Virtual</t>
+          <t>AI Agent Developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Alight Solutions</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a286c7ca862c4e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=5a2ad11ba93593c4</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>AI Agent Developer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>TWG Global AI</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,42 +2026,42 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, Oracle, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=edb6a72ac37333e2</t>
+          <t>https://www.indeed.com/viewjob?jk=351ba96e7e08391a</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python, PySpark, Lambda)</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>TWG Global AI</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c588b2aa81b85891</t>
+          <t>https://www.indeed.com/viewjob?jk=edb6a72ac37333e2</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>AllCloud</t>
+          <t>Innovaccer</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,17 +2096,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, EMR, Kinesis, Redshift, RDS, Hadoop, Spark, Scala, Kafka, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49fcd1d4ac195cdf</t>
+          <t>https://www.indeed.com/viewjob?jk=20b59922ac0a0969</t>
         </is>
       </c>
     </row>
@@ -2148,17 +2148,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Platform Engineer-3</t>
+          <t>Senior Software Engineer (Python, PySpark, Lambda)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Parsippany-Troy Hills, NJ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, IAM, RDS, HBase, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f753e538739bd670</t>
+          <t>https://www.indeed.com/viewjob?jk=c588b2aa81b85891</t>
         </is>
       </c>
     </row>
@@ -2883,60 +2883,60 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Big Data Software Engineer Remote</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Azure, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3058b24332d31ded</t>
+          <t>https://www.indeed.com/viewjob?jk=a41f510e2e081307</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Teradata</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, API Gateway, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10e23f958e9e8b09</t>
+          <t>https://www.indeed.com/viewjob?jk=806bff32d1d719ff</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Site Reliability Developer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,14 +2981,14 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=357547d890623cb5</t>
+          <t>https://www.indeed.com/viewjob?jk=3fedd79bbbee99bb</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Software Engineer II (Backend + Data pipelines)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2998,15 +2998,15 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,14 +3016,14 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3884844e18945dee</t>
+          <t>https://www.indeed.com/viewjob?jk=7d4fca4ad337ae6c</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Software Engineer II (Backend + Data pipelines)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3033,15 +3033,15 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,14 +3051,14 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17b7c64ee8dc67e0</t>
+          <t>https://www.indeed.com/viewjob?jk=1ae76b185563f91b</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Software Engineer II (Backend + Data pipelines)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3068,15 +3068,15 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,14 +3086,14 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a75982d2aedba052</t>
+          <t>https://www.indeed.com/viewjob?jk=ef2a73b324528506</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Software Engineer II (Backend + Data pipelines)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3103,15 +3103,15 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,14 +3121,14 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b3d8d96e19fcbe6</t>
+          <t>https://www.indeed.com/viewjob?jk=92aaafaf1efb9ec4</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Software Engineer II (Backend + Data pipelines)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3138,15 +3138,15 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,14 +3156,14 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a60a56d62d329dea</t>
+          <t>https://www.indeed.com/viewjob?jk=c9981aefe519f0cd</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Software Engineer II (Backend + Data pipelines)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3173,15 +3173,15 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93902824d8ac4d0c</t>
+          <t>https://www.indeed.com/viewjob?jk=fce2095df8206466</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr. Data Scientist</t>
+          <t>Software Engineer II (Backend + Data pipelines)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, MongoDB, Data Modeling</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb77847b7cd88f45</t>
+          <t>https://www.indeed.com/viewjob?jk=ee34633b7838a9b3</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Software Engineer II (Backend + Data pipelines)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Kubernetes, Airflow</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d20f4b9e6a3cbb70</t>
+          <t>https://www.indeed.com/viewjob?jk=cc57f588c654f1cd</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Software Engineer II (Backend + Data pipelines)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Genentech</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Kubernetes, Airflow</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c89d6a7d2041de38</t>
+          <t>https://www.indeed.com/viewjob?jk=5aaeb4c54cdfa77e</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer II (Backend + Data pipelines)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Teradata</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=806bff32d1d719ff</t>
+          <t>https://www.indeed.com/viewjob?jk=eb06d74f6367bb04</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Developer</t>
+          <t>Software Engineer II (Backend + Data pipelines)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fedd79bbbee99bb</t>
+          <t>https://www.indeed.com/viewjob?jk=49799e02e3e0a925</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d4fca4ad337ae6c</t>
+          <t>https://www.indeed.com/viewjob?jk=52ff9083bc8990ce</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ae76b185563f91b</t>
+          <t>https://www.indeed.com/viewjob?jk=66f89817131cfa0d</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef2a73b324528506</t>
+          <t>https://www.indeed.com/viewjob?jk=cdb757efdefad0ca</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92aaafaf1efb9ec4</t>
+          <t>https://www.indeed.com/viewjob?jk=57fc4e97a319b123</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9981aefe519f0cd</t>
+          <t>https://www.indeed.com/viewjob?jk=f6fcc67143e3ff8a</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fce2095df8206466</t>
+          <t>https://www.indeed.com/viewjob?jk=5dad4bf1e950e1c9</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee34633b7838a9b3</t>
+          <t>https://www.indeed.com/viewjob?jk=0f9ed5d278a8086d</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc57f588c654f1cd</t>
+          <t>https://www.indeed.com/viewjob?jk=8809421834292084</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend + Data pipelines)</t>
+          <t>Sr. Data Scientist</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Hadoop, Spark, Scala, Snowflake, MongoDB, Data Modeling</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5aaeb4c54cdfa77e</t>
+          <t>https://www.indeed.com/viewjob?jk=eb77847b7cd88f45</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend + Data pipelines)</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Genentech</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, Step Functions, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb06d74f6367bb04</t>
+          <t>https://www.indeed.com/viewjob?jk=d20f4b9e6a3cbb70</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend + Data pipelines)</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Genentech</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, Step Functions, Hadoop, Spark, Scala, MLOps, MLflow, CI/CD, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49799e02e3e0a925</t>
+          <t>https://www.indeed.com/viewjob?jk=c89d6a7d2041de38</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend + Data pipelines)</t>
+          <t>Regulatory Compliance Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52ff9083bc8990ce</t>
+          <t>https://www.indeed.com/viewjob?jk=c43803189a7eb93f</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend + Data pipelines)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, Scala, Oracle, ETL, ELT, dbt, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f89817131cfa0d</t>
+          <t>https://www.indeed.com/viewjob?jk=cdf704f3d9c632a6</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend + Data pipelines)</t>
+          <t>Senior Application Platform Architect - 6163848</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Hadoop, Scala, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdb757efdefad0ca</t>
+          <t>https://www.indeed.com/viewjob?jk=7ea7fc0fae83610a</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend + Data pipelines)</t>
+          <t>Senior LLM Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, Azure, Vertex AI, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57fc4e97a319b123</t>
+          <t>https://www.indeed.com/viewjob?jk=109c9c4a6595ba95</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend + Data pipelines)</t>
+          <t>Senior LLM Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, Azure, Vertex AI, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, MLOps</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6fcc67143e3ff8a</t>
+          <t>https://www.indeed.com/viewjob?jk=8723fa94634ae387</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend + Data pipelines)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>LERETA, LLC</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Pomona, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,14 +3961,14 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dad4bf1e950e1c9</t>
+          <t>https://www.indeed.com/viewjob?jk=ad5d067156fc62f1</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend + Data pipelines)</t>
+          <t>Senior Machine Learning Engineer (Search)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,14 +3996,14 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f9ed5d278a8086d</t>
+          <t>https://www.indeed.com/viewjob?jk=cff2f5a9dcacb28f</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend + Data pipelines)</t>
+          <t>Senior Machine Learning Engineer (Search)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8809421834292084</t>
+          <t>https://www.indeed.com/viewjob?jk=3216b4c3b2c151f8</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Machine Learning Engineer (Search)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Scala, Oracle, ETL, ELT, dbt, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf704f3d9c632a6</t>
+          <t>https://www.indeed.com/viewjob?jk=a0fc0424a2f74ea8</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Application Platform Architect - 6163848</t>
+          <t>Senior Machine Learning Engineer (Search)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Hadoop, Scala, PostgreSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ea7fc0fae83610a</t>
+          <t>https://www.indeed.com/viewjob?jk=c0ff98f788ff107b</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior LLM Engineer</t>
+          <t>Senior Machine Learning Engineer (Search)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, MLOps</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109c9c4a6595ba95</t>
+          <t>https://www.indeed.com/viewjob?jk=0442372baf83ee82</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior LLM Engineer</t>
+          <t>Senior Machine Learning Engineer (Search)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, MLOps</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8723fa94634ae387</t>
+          <t>https://www.indeed.com/viewjob?jk=fe6ea91421159ece</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Machine Learning Engineer (Search)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>LERETA, LLC</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Pomona, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Data Lake Storage, Scala, Snowflake, SQL Server, Data Modeling, Fact Tables, ELT, Power BI</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad5d067156fc62f1</t>
+          <t>https://www.indeed.com/viewjob?jk=aecbf4d450f1441b</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cff2f5a9dcacb28f</t>
+          <t>https://www.indeed.com/viewjob?jk=31056dc236b5ce67</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3216b4c3b2c151f8</t>
+          <t>https://www.indeed.com/viewjob?jk=eca84bb19e700f2b</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0fc0424a2f74ea8</t>
+          <t>https://www.indeed.com/viewjob?jk=7401294591da0c90</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0ff98f788ff107b</t>
+          <t>https://www.indeed.com/viewjob?jk=5eed535b1fcfea26</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0442372baf83ee82</t>
+          <t>https://www.indeed.com/viewjob?jk=b29243583190aa6a</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe6ea91421159ece</t>
+          <t>https://www.indeed.com/viewjob?jk=1c0d7ebd3a2ee36f</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aecbf4d450f1441b</t>
+          <t>https://www.indeed.com/viewjob?jk=28e3397c0e70024e</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31056dc236b5ce67</t>
+          <t>https://www.indeed.com/viewjob?jk=35f50cc085f1bbd9</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eca84bb19e700f2b</t>
+          <t>https://www.indeed.com/viewjob?jk=72be3b8aba169a59</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7401294591da0c90</t>
+          <t>https://www.indeed.com/viewjob?jk=b61af8e418fcf231</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5eed535b1fcfea26</t>
+          <t>https://www.indeed.com/viewjob?jk=552a8172dcf24a7a</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,67 +4626,67 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b29243583190aa6a</t>
+          <t>https://www.indeed.com/viewjob?jk=4fa51ea3c52768d7</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Search)</t>
+          <t>Azure Security Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c0d7ebd3a2ee36f</t>
+          <t>https://www.indeed.com/viewjob?jk=f579d8b45d3c5251</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Search)</t>
+          <t>Senior Cloud Systems Engineer (Databricks Administrator)</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Providge Consulting</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Scala, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,32 +4696,32 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e3397c0e70024e</t>
+          <t>https://www.indeed.com/viewjob?jk=e094ab218ebab2ed</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Search)</t>
+          <t>Software Engineering Intern – Data Engineering (Cloud &amp; Streaming)</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>NextPower</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka, Databricks Lakehouse, Data Modeling</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,32 +4731,32 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35f50cc085f1bbd9</t>
+          <t>https://www.indeed.com/viewjob?jk=28e588be3c533008</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Search)</t>
+          <t>Sr. ETL/SQL Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Capgemini Government Solutions</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,32 +4766,32 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72be3b8aba169a59</t>
+          <t>https://www.indeed.com/viewjob?jk=724ffe7f1d3da135</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Search)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Power BI, Tableau, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,32 +4801,32 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b61af8e418fcf231</t>
+          <t>https://www.indeed.com/viewjob?jk=aaf9596bf4159924</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Search)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Power BI, Tableau, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,59 +4836,59 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=552a8172dcf24a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=ab90611f6b141379</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Search)</t>
+          <t>DevOps Engineer II (CI/CD)</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>jamf</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Scala, MySQL, DynamoDB, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fa51ea3c52768d7</t>
+          <t>https://www.indeed.com/viewjob?jk=79e35d1cd7a86f17</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Software Engineering Intern – Data Engineering (Cloud &amp; Streaming)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>NextPower</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, Event Hubs, GCP, Spark, Kafka, Databricks Lakehouse, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e588be3c533008</t>
+          <t>https://www.indeed.com/viewjob?jk=d44e3274520e56d6</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>TransCore</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Round Rock, TX, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,34 +4931,34 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Power BI, Tableau, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaf9596bf4159924</t>
+          <t>https://www.indeed.com/viewjob?jk=931daa2509e88e14</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>H2O.ai</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Power BI, Tableau, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab90611f6b141379</t>
+          <t>https://www.indeed.com/viewjob?jk=fe52f92aedddcda4</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Cloud Systems Engineer (Databricks Administrator)</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Providge Consulting</t>
+          <t>H2O.ai</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables, Scala, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e094ab218ebab2ed</t>
+          <t>https://www.indeed.com/viewjob?jk=0d2b8979a3b5f81b</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Sr. ETL/SQL Engineer</t>
+          <t>Senior Data Engineer - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Capgemini Government Solutions</t>
+          <t>WesBanco Bank, Inc.</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Bowie, MD, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724ffe7f1d3da135</t>
+          <t>https://www.indeed.com/viewjob?jk=a3a02cdb2b181be3</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Senior Data Engineer - Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Space Telescope Science Institute</t>
+          <t>WesBanco Bank, Inc.</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Wheeling, WV, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Hive, Scala, PostgreSQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6055970eb603df79</t>
+          <t>https://www.indeed.com/viewjob?jk=fb6ee55d393e301c</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d44e3274520e56d6</t>
+          <t>https://www.indeed.com/viewjob?jk=e2b622ee37d8f63f</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Software Engineer - Backend (Python)</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>TransCore</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,17 +5141,17 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=931daa2509e88e14</t>
+          <t>https://www.indeed.com/viewjob?jk=7ba10ede755adc88</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2b622ee37d8f63f</t>
+          <t>https://www.indeed.com/viewjob?jk=035e833a0affea06</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ba10ede755adc88</t>
+          <t>https://www.indeed.com/viewjob?jk=34ea65634bf231fc</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=035e833a0affea06</t>
+          <t>https://www.indeed.com/viewjob?jk=db2fffa7ab4fc3c6</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ea65634bf231fc</t>
+          <t>https://www.indeed.com/viewjob?jk=726fca60377106fb</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db2fffa7ab4fc3c6</t>
+          <t>https://www.indeed.com/viewjob?jk=ae1bbd4c5bfc6dc1</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=726fca60377106fb</t>
+          <t>https://www.indeed.com/viewjob?jk=7d44fb63e0c3570e</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae1bbd4c5bfc6dc1</t>
+          <t>https://www.indeed.com/viewjob?jk=ac1d3f6a217585b1</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d44fb63e0c3570e</t>
+          <t>https://www.indeed.com/viewjob?jk=594c2209c74b60f3</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac1d3f6a217585b1</t>
+          <t>https://www.indeed.com/viewjob?jk=300951fa8a03d9ab</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=594c2209c74b60f3</t>
+          <t>https://www.indeed.com/viewjob?jk=224f85378fe66226</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=300951fa8a03d9ab</t>
+          <t>https://www.indeed.com/viewjob?jk=609ed15647075bf2</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224f85378fe66226</t>
+          <t>https://www.indeed.com/viewjob?jk=f7da2bae9861dfa9</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=609ed15647075bf2</t>
+          <t>https://www.indeed.com/viewjob?jk=9f44f95326fb5d8b</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7da2bae9861dfa9</t>
+          <t>https://www.indeed.com/viewjob?jk=f7f6777f3346c150</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f44f95326fb5d8b</t>
+          <t>https://www.indeed.com/viewjob?jk=99001099f8e56675</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7f6777f3346c150</t>
+          <t>https://www.indeed.com/viewjob?jk=1d562fde2d3ab4ec</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,14 +5746,14 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99001099f8e56675</t>
+          <t>https://www.indeed.com/viewjob?jk=49363af061447f75</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>Senior Software Engineer (Python + Distributed systems)</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,14 +5781,14 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d562fde2d3ab4ec</t>
+          <t>https://www.indeed.com/viewjob?jk=c4af4ef5dfeb0026</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Software Engineer - Backend (Python)</t>
+          <t>Senior Software Engineer (Python + Distributed systems)</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49363af061447f75</t>
+          <t>https://www.indeed.com/viewjob?jk=c116b8acf805f138</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4af4ef5dfeb0026</t>
+          <t>https://www.indeed.com/viewjob?jk=f996f9a35281bba7</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c116b8acf805f138</t>
+          <t>https://www.indeed.com/viewjob?jk=ca3982c4f2be4e49</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f996f9a35281bba7</t>
+          <t>https://www.indeed.com/viewjob?jk=9f2a3e577d5623a4</t>
         </is>
       </c>
     </row>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca3982c4f2be4e49</t>
+          <t>https://www.indeed.com/viewjob?jk=629b89e40e1e1bb5</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f2a3e577d5623a4</t>
+          <t>https://www.indeed.com/viewjob?jk=db6cf98112c1bc9f</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=629b89e40e1e1bb5</t>
+          <t>https://www.indeed.com/viewjob?jk=80b26c4d48449b15</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db6cf98112c1bc9f</t>
+          <t>https://www.indeed.com/viewjob?jk=83ba9763cad5f2f8</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80b26c4d48449b15</t>
+          <t>https://www.indeed.com/viewjob?jk=05460d1c364a2974</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83ba9763cad5f2f8</t>
+          <t>https://www.indeed.com/viewjob?jk=b01dc956f073aaf8</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6166,137 +6166,137 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05460d1c364a2974</t>
+          <t>https://www.indeed.com/viewjob?jk=807aad5f4045241d</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python + Distributed systems)</t>
+          <t>Kubernetes Security Engineer</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Google Cloud Platform, Scala, CI/CD, Terraform, AWS CloudFormation, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b01dc956f073aaf8</t>
+          <t>https://www.indeed.com/viewjob?jk=41718eb34508c965</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python + Distributed systems)</t>
+          <t>AWS Cloud Administrator</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>rockITdata</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, Azure, DynamoDB, Terraform</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=807aad5f4045241d</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0a98e5951373b4</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python + Distributed systems)</t>
+          <t>Data Engineer-Remote</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Mutual of Omaha</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, Glue, RDS, Scala, Snowflake, SQL Server, MongoDB, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=655ea21e25dbce1e</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc1efbee94e32a9</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Python + Distributed systems)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, Databricks, Spark, Scala, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -6306,32 +6306,32 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c46ceb995e304d69</t>
+          <t>https://www.indeed.com/viewjob?jk=ed1b9b0328def6aa</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>SAP NS2 Senior HANA Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>H2O.ai</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Newtown Square, PA, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6341,32 +6341,32 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe52f92aedddcda4</t>
+          <t>https://www.indeed.com/viewjob?jk=8999a6d9da6831ef</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>H2O.ai</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Spark, Kafka, Snowflake, NoSQL</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -6376,67 +6376,67 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d2b8979a3b5f81b</t>
+          <t>https://www.indeed.com/viewjob?jk=2e60ff8bc1e60898</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data &amp; Analytics</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>WesBanco Bank, Inc.</t>
+          <t>Callaway Golf</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Bowie, MD, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3a02cdb2b181be3</t>
+          <t>https://www.indeed.com/viewjob?jk=9ae59fccd3421dc5</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data &amp; Analytics</t>
+          <t>AV Safety Engineering Analytics Simulation Engineer (GPSSC)</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>WesBanco Bank, Inc.</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Wheeling, WV, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -6446,24 +6446,24 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb6ee55d393e301c</t>
+          <t>https://www.indeed.com/viewjob?jk=4b9eec46bbab109b</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>AV Safety Engineering Analytics Simulation Engineer (GPSSC)</t>
+          <t>Expert Cloud Security Architect</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6471,34 +6471,34 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, EMR, Kinesis, Redshift, IAM, RDS, Azure, Google Cloud Platform, Vertex AI, CI/CD</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b9eec46bbab109b</t>
+          <t>https://www.indeed.com/viewjob?jk=1b8b47326f23edff</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>AWS Cloud Administrator</t>
+          <t>SENIOR DATA ENGINEER (REMOTE)</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>rockITdata</t>
+          <t>Morrison Healthcare</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6506,34 +6506,34 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, IAM, RDS, Azure, DynamoDB, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Snowflake, ETL, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0a98e5951373b4</t>
+          <t>https://www.indeed.com/viewjob?jk=d530073f998c3698</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Data Engineer-Remote</t>
+          <t>Senior Applications Programmer/Analyst (Hybrid)</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Mutual of Omaha</t>
+          <t>The University of Michigan</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Scala, Snowflake, SQL Server, MongoDB, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, S3, SQL Server, PostgreSQL, ETL, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -6551,24 +6551,24 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc1efbee94e32a9</t>
+          <t>https://www.indeed.com/viewjob?jk=5c8b685dab351e4a</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Teradata Developer</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6576,34 +6576,34 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, NoSQL, MLflow, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed1b9b0328def6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=7fddb4ec439f1237</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>SAP NS2 Senior HANA Cloud DevOps Engineer</t>
+          <t>Senior BI Developer - Investment Services</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -6621,24 +6621,24 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8999a6d9da6831ef</t>
+          <t>https://www.indeed.com/viewjob?jk=6861136ad5c92fec</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior BI Developer - Investment Services</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -6656,24 +6656,24 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e60ff8bc1e60898</t>
+          <t>https://www.indeed.com/viewjob?jk=d0459e004fd012bc</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior BI Developer - Investment Services</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Callaway Golf</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6681,34 +6681,34 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Spark, Snowflake, ETL, ELT, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ae59fccd3421dc5</t>
+          <t>https://www.indeed.com/viewjob?jk=00bd0c85ee5af1cc</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>SENIOR DATA ENGINEER (REMOTE)</t>
+          <t>Senior BI Developer - Investment Services</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Morrison Healthcare</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6716,34 +6716,34 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Snowflake, ETL, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d530073f998c3698</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a227aff44c18bd</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Teradata Developer</t>
+          <t>Senior BI Developer - Investment Services</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6751,17 +6751,17 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fddb4ec439f1237</t>
+          <t>https://www.indeed.com/viewjob?jk=f36e77b3ab4b1808</t>
         </is>
       </c>
     </row>
@@ -6778,7 +6778,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6796,24 +6796,24 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6861136ad5c92fec</t>
+          <t>https://www.indeed.com/viewjob?jk=b03b046a7e4b4373</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Senior BI Developer - Investment Services</t>
+          <t>Data Modeler</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Union Bank &amp; Trust Co.</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6821,34 +6821,34 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0459e004fd012bc</t>
+          <t>https://www.indeed.com/viewjob?jk=c3cbc74799dc9ea0</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Senior BI Developer - Investment Services</t>
+          <t>Software Engineer Intern</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>NetApp</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6856,34 +6856,34 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00bd0c85ee5af1cc</t>
+          <t>https://www.indeed.com/viewjob?jk=c65c6376729ba486</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Senior BI Developer - Investment Services</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6891,34 +6891,34 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a227aff44c18bd</t>
+          <t>https://www.indeed.com/viewjob?jk=50c61f5469ce333f</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Senior BI Developer - Investment Services</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6926,34 +6926,34 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f36e77b3ab4b1808</t>
+          <t>https://www.indeed.com/viewjob?jk=4303ceb5e8c627c4</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Senior BI Developer - Investment Services</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6961,34 +6961,34 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b03b046a7e4b4373</t>
+          <t>https://www.indeed.com/viewjob?jk=0c4db6d385ae6ea3</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Data Modeler</t>
+          <t>Sr. Full Stack Software Engineer (Onsite - San Diego)</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Union Bank &amp; Trust Co.</t>
+          <t>Carlsmed</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Carlsbad, CA, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -6996,34 +6996,34 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Dimensional Modeling, Snowflake Schema</t>
+          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, Scala, PostgreSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3cbc74799dc9ea0</t>
+          <t>https://www.indeed.com/viewjob?jk=47ffb86f604e14df</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Software Engineer Intern</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>NetApp</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -7031,24 +7031,24 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c65c6376729ba486</t>
+          <t>https://www.indeed.com/viewjob?jk=c70cf8723aeaf7eb</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -7066,34 +7066,34 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c61f5469ce333f</t>
+          <t>https://www.indeed.com/viewjob?jk=6f106012aaf32c49</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -7101,34 +7101,34 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4303ceb5e8c627c4</t>
+          <t>https://www.indeed.com/viewjob?jk=a1593d7242ad3914</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Snowflake Administrator</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -7136,34 +7136,34 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c4db6d385ae6ea3</t>
+          <t>https://www.indeed.com/viewjob?jk=085de5867e567658</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Software Engineer (Onsite - San Diego)</t>
+          <t>LLM Application Engineer</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Carlsmed</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Carlsbad, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -7171,7 +7171,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, RDS, Azure, Scala, PostgreSQL, CI/CD, Git</t>
+          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -7181,24 +7181,24 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47ffb86f604e14df</t>
+          <t>https://www.indeed.com/viewjob?jk=5633278896c16c3b</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>LLM Application Engineer</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -7216,24 +7216,24 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c70cf8723aeaf7eb</t>
+          <t>https://www.indeed.com/viewjob?jk=4e56614bfb72e3b3</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Senior AI/ML Scientist</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -7251,182 +7251,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f106012aaf32c49</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer - Risk Platform (Hybrid)</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>CrowdStrike</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>Sunnyvale, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D196" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Cassandra, ETL, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a1593d7242ad3914</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>Senior AI/ML Scientist</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>Milford, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D197" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Hive, Spark, Scala, MLflow, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G197" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=300d4ca14be662c3</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>Snowflake Administrator</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D198" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, Time Travel, ELT, Tableau, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=085de5867e567658</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>LLM Application Engineer</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D199" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
-        </is>
-      </c>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5633278896c16c3b</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>LLM Application Engineer</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D200" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Databricks, Google Cloud Platform, BigQuery, Vertex AI, Scala, Snowflake, MLOps</t>
-        </is>
-      </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4e56614bfb72e3b3</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-06.xlsx
+++ b/results/job_matches_2026-03-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G195"/>
+  <dimension ref="A1:G188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TxDMV - Data Analyst - Senior BI Developer (Remote in Texas)</t>
+          <t>Senior Data Engineer (Python, Spark, AWS)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Texas Comptroller of Public Accounts</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b98eb455b4295de</t>
+          <t>https://www.indeed.com/viewjob?jk=bac9e3177a7c184b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TxDMV - Systems Analyst - Data Engineer (Remote in TX)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Texas Comptroller of Public Accounts</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Cloud Storage, Scala, Informatica PowerCenter</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73e61a163308157a</t>
+          <t>https://www.indeed.com/viewjob?jk=72f18d450d1d99d9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TxDMV - Systems Analyst - Data Engineer (Remote in TX)</t>
+          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Texas Department of Motor Vehicles</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Cloud Storage, Scala, Informatica PowerCenter</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=934456836d756b7d</t>
+          <t>https://www.indeed.com/viewjob?jk=b45360d720d413c7</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TxDMV - Data Analyst - Senior BI Developer (Remote in Texas)</t>
+          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Texas Department of Motor Vehicles</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,17 +976,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fb5c05e83aa7c0e</t>
+          <t>https://www.indeed.com/viewjob?jk=3c46cd564ba01b6c</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bac9e3177a7c184b</t>
+          <t>https://www.indeed.com/viewjob?jk=6d52dce08f82e688</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>TxDMV - Data Analyst - Senior BI Developer (Remote in Texas)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Texas Comptroller of Public Accounts</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72f18d450d1d99d9</t>
+          <t>https://www.indeed.com/viewjob?jk=5b98eb455b4295de</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
+          <t>TxDMV - Systems Analyst - Data Engineer (Remote in TX)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Texas Comptroller of Public Accounts</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Cloud Storage, Scala, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b45360d720d413c7</t>
+          <t>https://www.indeed.com/viewjob?jk=73e61a163308157a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS, Spark, Python, SQL)</t>
+          <t>TxDMV - Systems Analyst - Data Engineer (Remote in TX)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Texas Department of Motor Vehicles</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, GCP, Dataflow, Cloud Storage, Scala, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c46cd564ba01b6c</t>
+          <t>https://www.indeed.com/viewjob?jk=934456836d756b7d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Python, Spark, AWS)</t>
+          <t>TxDMV - Data Analyst - Senior BI Developer (Remote in Texas)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Texas Department of Motor Vehicles</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d52dce08f82e688</t>
+          <t>https://www.indeed.com/viewjob?jk=4fb5c05e83aa7c0e</t>
         </is>
       </c>
     </row>
@@ -1238,25 +1238,25 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>System Architect</t>
+          <t>Senior Software Engineer, Data</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Systems Engineering Solutions Corporation</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, IAM, RDS, Spark, PySpark</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=634fcd15ef04d7bf</t>
+          <t>https://www.indeed.com/viewjob?jk=c7869ee373ec84ed</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data</t>
+          <t>Sr. Integration Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>SiriusPoint</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Polars, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, SQS, RDS, Azure, Databricks</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7869ee373ec84ed</t>
+          <t>https://www.indeed.com/viewjob?jk=a476b32ebbd3f63e</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior BI Analyst</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad414f3a9ab0a2bc</t>
+          <t>https://www.indeed.com/viewjob?jk=afa51ac883fa48a6</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer, Data</t>
+          <t>Senior BI Analyst</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=459162c660bc8082</t>
+          <t>https://www.indeed.com/viewjob?jk=ad414f3a9ab0a2bc</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Software Engineer, Data</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Dataflow, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afa51ac883fa48a6</t>
+          <t>https://www.indeed.com/viewjob?jk=459162c660bc8082</t>
         </is>
       </c>
     </row>
@@ -1483,17 +1483,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>PetSmart</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c8a098e9a2c0e1a</t>
+          <t>https://www.indeed.com/viewjob?jk=f059a12d002721db</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Software Engineer III- Python/PySpark</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PetSmart</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=157ddcd0636f7c11</t>
+          <t>https://www.indeed.com/viewjob?jk=82b1dd2ce5d3671a</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Software Development Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BOULDER SCIENTIFIC CO</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Longmont, CO, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9486135c47b58364</t>
+          <t>https://www.indeed.com/viewjob?jk=6efe960a7ab141ac</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>PetSmart</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba5a22f3941b5b26</t>
+          <t>https://www.indeed.com/viewjob?jk=0c8a098e9a2c0e1a</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>PetSmart</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f059a12d002721db</t>
+          <t>https://www.indeed.com/viewjob?jk=157ddcd0636f7c11</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python/PySpark</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>BOULDER SCIENTIFIC CO</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Longmont, CO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, SQL Server, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82b1dd2ce5d3671a</t>
+          <t>https://www.indeed.com/viewjob?jk=9486135c47b58364</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AI Support Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=625bf5ef0b332ad3</t>
+          <t>https://www.indeed.com/viewjob?jk=ba5a22f3941b5b26</t>
         </is>
       </c>
     </row>
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd39a203b7587e31</t>
+          <t>https://www.indeed.com/viewjob?jk=625bf5ef0b332ad3</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Support Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Yusen Logistics</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kimball, ELT, dbt</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f92de33105c0bad</t>
+          <t>https://www.indeed.com/viewjob?jk=dd39a203b7587e31</t>
         </is>
       </c>
     </row>
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=772460af87c5b60c</t>
+          <t>https://www.indeed.com/viewjob?jk=7f92de33105c0bad</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Yusen Logistics</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Royal Oak, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kimball, ELT, dbt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bb3681c5da818f2</t>
+          <t>https://www.indeed.com/viewjob?jk=772460af87c5b60c</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Royal Oak, MI, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=343b07159d1b6928</t>
+          <t>https://www.indeed.com/viewjob?jk=6bb3681c5da818f2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer - Virtual</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Alight Solutions</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, IAM, RDS, Scala